--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -23,17 +23,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$137</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$200</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1665,12 +1665,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
     <col width="52" customWidth="1" min="6" max="6"/>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -8064,8 +8064,736 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SRC-0123</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Jobbnorge - portal publico de contratacion de Noruega</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>https://www.jobbnorge.no/en/available-jobs</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Todas las vacantes publicas noruegas, incluidas las de UiO (Centre for Precision Psychiatry/NORMENT, LCBC, PROMENTA), NTNU, UiB y UiT: es el canal unico por el que Noruega anuncia postdocs de genetica psiquiatrica, post-GWAS y modelizacion estadistica de datos genomicos. No es un agregador academico generico sino el portal estatal de empleo publico.</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Las rutas de listado y busqueda devuelven HTTP 404 al fetch automatico; usar busqueda web restringida a jobbnorge.no con 'postdoctoral fellow genetics GWAS', 'statistical modeling genomic data' o 'Centre for Precision Psychiatry'. Los anuncios individuales si son legibles en /en/available-jobs/job/&lt;id&gt;/&lt;slug&gt; y en /en/available-jobs/joblisting/pdf/&lt;id&gt;</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Fuente NUEVA 2026-09-14. Cinco anuncios relevantes localizados (UiO Precision Psychiatry multi-omics 301627, MetaBrain, LCBC post-GWAS, NTNU modelizacion estadistica de datos genomicos 301707), todos ya cerrados: sirve para mapear los grupos que contratan de forma recurrente en su area dentro del EEE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SRC-0124</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>EURAXESS - anuncios individuales via buscador externo (rodeo al buscador roto)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs/</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Fichas completas de ofertas concretas de EURAXESS (titulo, institucion, pais, perfil R1-R4, plazo, estado abierto/expirado) sin pasar por el buscador de la propia web, que sigue roto.</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Busqueda web con allowed_domains=euraxess.ec.europa.eu y palabras clave del tema ('postdoc GWAS psychiatric genetics polygenic', 'genetic epidemiology complex traits biobank'), despues fetch directo de https://euraxess.ec.europa.eu/jobs/&lt;id&gt;</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Fuente NUEVA 2026-09-14. Hallazgo de esta pasada: algunas fichas individuales ya renderizan de verdad (p. ej. /jobs/127222 devolvio un anuncio unico con perfil R2, plazo y estado EXPIRED), pero otras (/jobs/630410, /jobs/519384) siguen devolviendo el listado generico de ~6.900 ofertas. Acierto aproximado 1 de 3: usar solo con IDs obtenidos por buscador externo y aceptar fallos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SRC-0125</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>THEunijobs (Times Higher Education) - postdocs en Australia</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Tablon academico</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://www.timeshighereducation.com/unijobs/listings/australia/postdocs/</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Vacantes postdoctorales de universidades australianas y neozelandesas con salario, ciudad y dias restantes; es el agregador que si responde al fetch, a diferencia de Seek (403) y de careers.uq.edu.au (404).</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Listado 'australia/postdocs'; alternar con el buscador por palabra clave 'genetics', 'genomics', 'epidemiology', 'mental health'.</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Probado el 2026-09-14: devolvio 17 postdocs australianos con salarios y plazos, ninguno de genetica en esa pasada. Cubre el hueco de Australia que Seek dejaba abierto por bloqueo. El listado por disciplina es corto, asi que conviene revisarlo entero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SRC-0126</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>scholarshipdb.net - agregador de vacantes academicas</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Agregador Tier 2</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://scholarshipdb.net/</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Reproduce anuncios de universidades de Australia, Canada y Europa que no se alcanzan por sus portales propios; util solo como PISTA, las fechas hay que verificarlas en origen.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Busqueda 'statistical genetics', 'genetic epidemiology', 'psychiatric genetics' filtrando por pais.</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Destapo las dos plazas de la University of Queensland de esta pasada, que ningun tablon en ambito daba. Riesgo alto de anuncios caducados y sin fecha de cierre: nunca marcar VERIFIED desde aqui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SRC-0127</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>University of Queensland - API publica del portal Workday de empleo</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://uq.wd3.myworkdayjobs.com/wday/cxs/uq/uqcareers/jobs</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>TODAS las vacantes de UQ con departamento, fecha de publicacion y fecha de cierre, incluidas las del IMB (Program in Complex Trait Genomics) y las del Child Health Research Centre. Rompe el bloqueo de dos pasadas: careers.uq.edu.au da 404 y la interfaz Workday llega vacia, pero la API responde JSON completo.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>POST con cuerpo {"appliedFacets":{},"limit":20,"offset":0,"searchText":"genetic"}; repetir con searchText 'mental health', 'genomics' y 'statistical'. La ficha completa se lee con GET a https://uq.wd3.myworkdayjobs.com/wday/cxs/uq/uqcareers/job/&lt;externalPath&gt;</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Asi se encontro el postdoc de Statistical Genomics de Loic Yengo (R-68861). Sustituye a cualquier intento por careers.uq.edu.au o por la web de Workday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SRC-0128</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Program in Complex Trait Genomics (PCTG, UQ) - pagina de reclutamiento</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://cnsgenomics.com/content/recruitment</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Las plazas de postdoc y de doctorado del PCTG (Visscher, Wray, Yang, Yengo, Zeng) enlazadas a UQ jobs, mas el aviso explicito de que aceptan contacto directo con los jefes de grupo cuando no hay plaza anunciada</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Abrir la pagina entera; seguir los enlaces a jobs.uq.edu.au (el dominio no resuelve desde aqui: usar la API Workday con el numero de requisicion)</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Es la via por paginas de grupo que pedia el encargo; el portal de empleo de UQ por si solo no dice a que laboratorio pertenece cada plaza</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SRC-0129</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>University of Edinburgh - API publica de vacantes (Oracle Recruiting CX_1001)</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://elxw.fa.em3.oraclecloud.com/hcmRestApi/resources/latest/recruitingCEJobRequisitions</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Vacantes de Edimburgo con titulo, campus, fecha de publicacion y resumen; la interfaz web del portal es JavaScript puro y llega vacia</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>GET con onlyData=true, expand=requisitionList y finder=findReqs;siteNumber=CX_1001,keyword=&lt;genetics|psychiatric|genomics&gt;,limit=25,sortBy=POSTING_DATES_DESC</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>El 14-09-2026 las 5 coincidencias de 'genetics' eran de Easter Bush (mejora genetica vegetal y animal), ninguna de genetica psiquiatrica</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SRC-0130</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>King's College London - busqueda por termino del portal de empleo</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/search?term=genetics</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Vacantes de KCL filtradas por palabra clave con enlace directo a la ficha completa (salario, duracion, cierre, PI): rompe el bloqueo de la vista de lista, que no exponia los puestos del IoPPN</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>term=genetics, term=psychiatric+genetics, term=genomics, term=sleep; las fichas estan en https://www.kcl.ac.uk/jobs/&lt;id&gt;-&lt;slug&gt; (el id solo, sin slug, redirige a 404)</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Complementa a SRC-0039, que apunta a la vista de lista sin parametro de busqueda</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SRC-0131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Broad Institute - paginacion del portal Avature</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://broadinstitute.avature.net/careers/SearchJobs/?jobOffset=6</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Las vacantes 7 a 36 del Broad, que la primera pantalla del portal nunca muestra (solo 6 de 36); los titulos si nombran laboratorio (p. ej. 'Karczewski Lab', 'Deverman Lab')</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Recorrer jobOffset=6, 12, 18, 24, 30 (6 resultados por pagina); buscar 'Stanley Center', 'Postdoctoral Associate' y nombres de laboratorio de genetica psiquiatrica</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Resuelve parcialmente el bloqueo conocido '6 de 35 sin decir laboratorio': la paginacion funciona por WebFetch aunque no por curl</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SRC-0132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Sacyl - Bolsa de Empleo Abierta y Permanente (BAPE, Castilla y Leon)</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://www.saludcastillayleon.es/profesionales/es/bolsa</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Bolsa autonomica permanentemente abierta de Castilla y Leon: alta telematica con autobaremo, convocatorias abiertas por categoria (Licenciados Especialistas incluye Analisis Clinicos y Bioquimica Clinica) y resoluciones de corte anuales.</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Convocatorias abiertas &gt; categoria Licenciados Especialistas (excepto Medicina Familiar y Comunitaria); vigilar tambien el procedimiento de inscripcion para quienes terminan el MIR</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Tercera CCAA con via permanente en la base, tras Andalucia y Galicia. Contiene un PDF de procedimiento de inscripcion FIN MIR con un plazo aparente de dos dias habiles que hay que abrir y confirmar antes de 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SRC-0133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>GSK Careers - busqueda de vacantes</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://jobs.gsk.com/us/en/search-results</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Familia recurrente de plazas de genetica humana de GSK: Statistical Geneticist Investigator, Investigator Novel Human Genetics, Genomic Data Scientist, Principal Scientist Genomics Analytics Engineer.</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>keywords 'statistical genetics', 'human genetics', 'genomic data scientist'</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Es el sustituto natural de Regeneron como fuente de vigilancia del carril farma, porque publica varias plazas simultaneas de su tecnica exacta. Aviso: las fichas individuales devuelven solo el armazon del portal al fetch automatico; se localizan por busqueda acotada al dominio pero hay que abrirlas a mano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>SRC-0134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Oxford PharmaGenesis - portal de vacantes (motor eploy)</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://careers.pharmagenesis.com/vacancies/vacancy-search-results.aspx</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Vacantes reales y legibles de una agencia MedComms: medical writer, senior medical writer, senior medical editor, communications consultant, con ubicacion y tipo de contrato.</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Listado completo; mirar medical writer, associate medical writer y medical editor, y si aparece ubicacion remota o europea</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Primera fuente Tier 1 que rinde en el carril de comunicacion cientifica tras dos pasadas en blanco. La pagina /careers/ del dominio principal no lista nada: hay que ir directamente a este portal. El motor eploy es el mismo que el de Cardiff (SRC-0038), asi que se puede leer sin navegador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SRC-0135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Genomics England - open positions</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://www.genomicsengland.co.uk/careers/open-positions</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Listado de vacantes del programa genomico publico britanico por departamento, incluidos Bioinformatics Engineering y Bioinformatics Research Services, mas suscripcion a avisos por correo.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Listado completo; filtrar por bioinformatics, data science y research</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Comprobado hoy: solo dos vacantes vivas (Chair of Access Review Committee y Monitoring &amp; Evaluation Analyst, contrato temporal de 18 meses) y ninguna de genetica estadistica, por eso no genera fila. El listado es legible sin navegador, asi que sirve como fuente estable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SRC-0136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>ASHG Career Center</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://careers.ashg.org/jobs/</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Bolsa de empleo de la American Society of Human Genetics: postdocs y puestos de personal en genetica humana y estadistica, sobre todo en EE. UU. (visado para ella, se anota). Complementa a ISPG y jobRxiv porque recoge tambien departamentos de genetica clinica y de laboratorio.</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>keywords=postdoctoral statistical genetics / polygenic / psychiatric genetics</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>BLOQUEO COMPROBADO 2026-09-14: careers.ashg.org devuelve pantalla de CAPTCHA y aviso de cookies a las herramientas automaticas; no se pudo leer ni un solo anuncio. Tratar como fuente de revision manual o buscar el feed RSS antes de volver a gastar llamadas en ella. ASHG solo figuraba hasta ahora en sources como fuente de congresos (SRC-0110), no de empleo.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J123"/>
+  <autoFilter ref="A1:J137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8196,7 +8924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15281,8 +16009,1184 @@
         </is>
       </c>
     </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>P-0023</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Fellowship in Multi-Omics at Centre for Precision Psychiatry</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>El Centre for Precision Psychiatry (NORMENT) es el grupo europeo que mejor solapa con sus lineas 1 y 2: metodos estadisticos sobre datos geneticos humanos a gran escala (GWAS, scores poligenicos, arquitectura poligenica compartida) aplicados a trastornos psiquiatricos graves, y ademas trabaja con ne</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://www.jobbnorge.no/en/available-jobs/job/301627/postdoctoral-research-fellowship-in-multi-omics-at-centre-for-precision-psychiatry</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>P-0024</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Postdoc in Computational Genomics</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Tecnicamente es su caja de herramientas exacta (GWAS, PRS, imputacion, R/Python sobre biobancos), pero el fenotipo es cardiometabolico, no psiquiatrico ni de sueno, asi que seria un giro de tema respecto a sus lineas 1-3; ademas exige doctorado defendido y arranque en nov-2026, imposible con la resi</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://employment.ku.dk/faculty/?show=162794</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>P-0025</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Fellow in Statistical Genetics / Genetic Epidemiology</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Es la descripcion mas parecida a su linea 1 y 2 que ha aparecido en tres pasadas: GWAS a gran escala en UK Biobank y randomizacion mendeliana es exactamente lo que hace con PLINK y R en su tesis de genetica estadistica, y el EGG Consortium (rasgos de crecimiento y desarrollo infantil) conecta de for</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://scholarshipdb.net/jobs-in-Australia/Postdoctoral-Research-Fellow-In-Statistical-Genetics-Genetic-Epidemiology-The-University-Of-Queensland=YeqPUAjM7BGUYQAlkGUTnw.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>P-0026</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Fellow in Genomics and Youth Mental Health</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Cruza sus tres activos a la vez: la linea 2 (GWAS/PRS de trastornos psiquiatricos) es el nucleo del puesto, el angulo de farmacogenetica es justo lo que su residencia de Medicina de Laboratorio le da y casi ningun candidato de genetica estadistica tiene, y el foco en poblacion infantil y juvenil enl</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://www.uq.edu.au/childhealthresearchcentre/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>P-0027</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Research Fellow (Genetic Analysis)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Metodologicamente encaja (analisis caso-control y fenotipos cuantitativos en R/Python) pero no es elegible: el contrato arranca el 01-09-2026 y termina el 31-08-2027, mientras ella sigue de residente en Malaga hasta el 22-05-2027; interesa solo como contacto de laboratorio, el grupo de Altmann combi</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSW126/research-fellow-genetic-analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>P-0028</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Bioinformatician</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Es un puesto de plantilla bioinformatica, no de investigacion propia, y con plazo el 23-09-2026, muy anterior a su disponibilidad (22-05-2027): se registra solo para no redescubrirlo y porque confirma que Medical &amp; Molecular Genetics de KCL contrata con regularidad.</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSU830/bioinformatician</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>P-0029</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Fellow/Research Fellow in Statistical Genomics (R-68861)</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Es su linea 1 literal (genetica estadistica de rasgos complejos) en el grupo de referencia mundial del area, el PCTG que ella ya conoce de oidas por su estancia en QIMR Berghofer (mismo ecosistema de Brisbane), y el perfil MD le daria valor en la interpretacion clinica de fenotipos; pero NO es elegi</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://uq.wd3.myworkdayjobs.com/uqcareers/job/St-Lucia-Campus/Postdoctoral-Research-Fellow-Research-Fellow-in-Statistical-Genomics_R-68861-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>P-0030</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Research Assistant - estudio CONNECT</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Puesto de asistente pre-doctoral sin componente de genetica estadistica y ademas incompatible con su residencia hasta mayo de 2027; se registra solo para no redescubrirlo y como senal de que el MRC Centre de Cardiff sigue contratando.</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://cardiffuniweb.eploy.net/vacancies/447/research-assistant.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>P-0031</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Associate (proyecto Youth Endowment Fund, CRIS)</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Es epidemiologia de registros clinicos (CRIS/SLaM) sobre TDAH y violencia juvenil, no genetica estadistica ni GWAS/PRS, y cierra el 21-09-2026 cuando ella no esta disponible; se registra para no redescubrirlo y porque confirma que el IoPPN publica postdocs de forma continua.</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/157565-postdoctoral-research-associate</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>P-0032</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Research Associate at the Human Functional Genomics Initiative</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Puesto de poyata (organoides cerebrales, cultivo de iPSC) sin componente de genetica estadistica: fuera de su perfil.</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/155527-research-associate-at-the-human-functional-genomics-initiative</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>P-0033</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Postdoctoral researcher in genome stability and neurotoxicity</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Biologia molecular de estabilidad genomica, no epidemiologia genetica ni genetica del sueno: fuera de su perfil; se registra para no redescubrirlo.</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://www.werkenbijerasmusmc.nl/vacature/1307326/postdoctoral-researcher-genome-stability-and-neurotoxicity-3-years-3416</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>P-0034</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Computational Scientist II - Karczewski Lab (ref 44894)</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Genomica poblacional computacional de alto nivel (entorno gnomAD): tematicamente vecino a su linea 1 pero es un puesto de staff con exigencia fuerte de ingenieria de datos y programacion que hoy no tiene, ademas de requerir visado H-1B/J-1.</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://broadinstitute.avature.net/en_US/careers/JobDetail/Computational-Scientist-II-Karczewski-Lab/22501</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>P-0035</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Postdoctoral Associate - Computational Biology (ref 44829)</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Postdoc de biologia computacional en el Broad sin laboratorio identificado en el listado: puede o no ser del Stanley Center, hace falta abrir la ficha antes de valorarlo de verdad.</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://broadinstitute.avature.net/en_US/careers/JobDetail/Postdoctoral-Associate-Computational-Biology/22430</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>P-0006</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Scientist in host genetics and data integration for liver cancer risk prediction</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Deadline, Last_Verified, Next_Action, Status</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSR614/postdoctoral-research-scientist-in-host-genetics-and-data-integration-for-liver-cancer-risk-predication-and-early-detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>P-0018</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Clinical Research Fellow (Psychological Medicine)</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Deadline, Last_Verified, Next_Action, Salary_EUR_Year, Status</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DST268/clinical-research-fellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>P-0014</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Research Assistant (Moondance Dementia Laboratory)</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://cardiffuniweb.eploy.net/vacancies/vacancy-search-results.aspx?culture=en-GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>P-0003</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow in Psychiatric Genomics</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/postdoctoral-fellow-in-psychiatric-genomics-icahn-school-of-medicine-at-mount-sinai-ismms-mshs-754125</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>P-0011</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Postdoctoral positions in human population genetics, complex disease and cancer</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/postdoctoral-positions-in-human-population-genetics-complex-disease-and-cancer-in-new-york-city-usa-albert-einstein-college-of-medicine-einstein-757285</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>P-0020</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow - Statistical Genetics and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://jobrxiv.org/job/postdoctoral-fellow-statistical-genetics-and-artificial-intelligence/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>P-0022</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Clinical Research Associate (farmacogenomica clinica)</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://iaejup.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/UOA-Careers/job/3142/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>P-0002</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Scientist in Statistical Genomics / Genetic Epidemiology</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Deadline, Last_Updated, Last_Verified, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://recruitingapp-5569.de.umantis.com/Vacancies/496/Description/2?lang=eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>J-0010</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Bolsa de Empleo Abierta y Permanente (BAPE) de Sacyl - categoria Licenciados Especialistas (incluye Analisis Clinicos y Bioquimica Clinica)</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Es una via PERMANENTE, del tipo que sobrevive a su calendario: ella no puede presentarse a nada que se cierre antes del 22-05-2027, y esta bolsa admite altas en cualquier momento con cortes anuales de baremacion, asi que basta con inscribirse el mismo dia que acabe la residencia. La categoria existe</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://www.saludcastillayleon.es/profesionales/es/bolsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>J-0011</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Borsa de treball de l'Institut Catala de la Salut - facultatiu/iva especialista</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Segunda via permanente del carril publico y la primera de Cataluna en la base. Encaja con su calendario por la misma razon que Andalucia o Castilla y Leon: no hay plazo que perder, el alta es telematica y continua, y el orden depende del curriculum baremado, no de acertar una convocatoria. La condic</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://ics.gencat.cat/ca/lics/treballeu-a-lics/treball-temporal/borsa-de-treball/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>J-0012</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Statistical Geneticist Investigator (Human Genetics / Genomic Sciences)</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Es el puesto arquetipico de su carril 1 y de su tecnica declarada: genetica estadistica en I+D de farma, que es exactamente GWAS/PRS con PLINK y R sobre cohortes grandes, y GSK es ademas el equipo de human genetics mas activo del sector europeo en contratacion continua. Encaja con ELLA en linea de t</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://jobs.gsk.com/en-gb/jobs/223316?lang=en-us</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>J-0013</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Medical Writer (Oxford o remoto en Reino Unido) y familia de plazas de redaccion y edicion medica</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Es la primera prueba de que el carril 3 existe de forma verificable, despues de dos pasadas en blanco: son plazas Tier 1 leidas en el portal del propio empleador, no anuncios de agregador. Encaja con ella de forma plausible pero no automatica: MD con ingles C2 y dos manuscritos propios en revision e</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://careers.pharmagenesis.com/vacancies/vacancy-search-results.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>J-0014</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Candidatura espontanea permanente en Health in Code (genetica clinica y genomica)</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Es el unico puente verificado esta semana entre su titulo de laboratorio y el sector privado espanol de genetica clinica, y tiene la ventaja de no depender de un plazo: el canal esta abierto siempre, asi que se puede usar exactamente cuando ella este disponible. Encaja con ELLA porque una empresa de</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://healthincode.com/trabaja-con-nosotros/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>J-0001</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Associate Manager, Statistical Genetics - Regeneron Genetics Center</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Fit_Rationale, Last_Verified, Next_Action, Status</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://careers.regeneron.com/en/jobs/r48469/associate-manager-statistical-genetics-regeneron-genetics-center/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>J-0003</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Via transitoria al titulo de especialista en Genetica Medica y en Genetica de Laboratorio (dos reales decretos separados, aun sin publicar)</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Fit_Rationale, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://www.sanidad.gob.es/normativa/audiencia/home.htm</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H172"/>
+  <autoFilter ref="A1:H200"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15688,7 +17592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AD36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15696,7 +17600,7 @@
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="52" customWidth="1" min="9" max="9"/>
@@ -15716,7 +17620,7 @@
     <col width="15" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="52" customWidth="1" min="26" max="26"/>
     <col width="52" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="52" customWidth="1" min="29" max="29"/>
@@ -16110,7 +18014,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -16120,17 +18024,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>DEADLINE_INFO: la plaza sigue publicada y aparece la ventana de revision de candidaturas, que la fila no tenia</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>En Q4 2027, con la defensa a la vista, escribir a Beate St Pourcain (beate.stpourcain@mpi.nl) preguntando por la siguiente vacante del grupo y ofreciendo su perfil MD+PhD con GWAS/PRS; la edicion actual empieza en diciembre de 2026 y le es inaplicable.</t>
+          <t>Revision continua de candidaturas a partir del 2026-10-08; sin fecha de cierre dura (plaza ROLLING). Preparar CV y carta antes del 2026-10-08 y escribir a la Language and Genetics group del MPI explicando que defiende en feb-2028 y no esta disponible hasta el 22-05-2027; confirmar si el contrato de 3 anos admite inicio diferido</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -16145,7 +18049,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Rama 5 (buzon y novedad) reverifico la fila en el tablon de la ISPG (SRC-0030) el 2026-09-07: sigue publicada, ahora con salario (EUR 73.999,91-91.055,27), inicio 01-12-2026 negociable, contrato de 3 anos, revision desde el 08-10-2026 hasta cubrir, encuadre EAGLE sobre correlatos geneticos de la conducta social desde la infancia, y contactos beate.stpourcain@mpi.nl y secretariat.genetics@mpi.nl. No se abrio el portal umantis de solicitud, de ahi LIKELY.</t>
+          <t>Tablon de la ISPG (ispg.net/resources/job-postings) anuncia revision continua desde el 2026-10-08; la pagina oficial de vacantes del MPI (mpi.nl/career-education/vacancies) confirma el 2026-09-14 que la plaza de 3 anos en Statistical Genomics/Genetic Epidemiology del grupo Language and Genetics sigue publicada, pero no reproduce la fecha</t>
         </is>
       </c>
     </row>
@@ -16237,27 +18141,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>La duena debe abrir la URL de Nature Careers en un navegador (bloquea el fetch automatico) para leer plazo y requisito de doctorado. Accion estrategica, no ahora: Niamh Mullins es un contacto nominal que merece un acercamiento real a mediados de 2027; la via ISGC/PGC conecta ademas con el WCPG (SRC-0026), el sitio mas barato para conocerla en persona antes de solicitar. Vigilar si el laboratorio reanuncia anualmente.</t>
+          <t>Sigue sin verificar. El buscador de Nature Careers ignora el parametro q= (devuelve el listado generico de anuncios recientes, sin ningun resultado de genetica estadistica), asi que no se puede comprobar si el anuncio continua activo. Probar la pagina de carreras de Mount Sinai directamente (mejor via rama 3) o la landing por disciplina de Nature Careers.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -16471,7 +18375,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-446</v>
+        <v>-452</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -16603,7 +18507,7 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -16617,7 +18521,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -16656,27 +18560,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>No aplicar: no puede incorporarse antes de mediados de 2027. En su lugar, crear una alerta guardada en jobs.ac.uk con University of Oxford + statistical genetics / genetic epidemiology y revisar NDM Experimental Medicine en Q4 2027. Si quiere un gancho ya, escribir a Azim Ansari en otono de 2027 (no antes) con el articulo de Nature Mental Health una vez aceptado, preguntando si estos puestos se repiten.</t>
+          <t>Ninguna: plazo vencido el 11-09-2026. La ficha sigue servida en jobs.ac.uk pero la fecha de cierre ya paso; archivar.</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -16759,7 +18663,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-129</v>
+        <v>-135</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -17024,7 +18928,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-200</v>
+        <v>-206</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -17309,27 +19213,27 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>La duena debe abrir la URL de Nature Careers manualmente e identificar al PI; si trabaja en fenotipos psiquiatricos o conductuales, ascender a elemento de seguimiento, y si no, descartar. En cualquier caso no es accionable antes de mediados de 2027.</t>
+          <t>Sigue sin verificar por la misma razon que P-0003: la busqueda por palabra clave de Nature Careers no filtra. Intentar la pagina de empleo de Albert Einstein College of Medicine (rama 3).</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -17416,7 +19320,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -17554,7 +19458,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -17688,7 +19592,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -17727,19 +19631,19 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z15" t="inlineStr">
         <is>
           <t>UPDATED</t>
@@ -17747,7 +19651,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Sin accion. Lo util es la URL de vacantes de Cardiff que si funciona: revisarla desde mediados de 2027 buscando plazas de Research Associate en genetica estadistica del MRC CNGG.</t>
+          <t>CONFLICTO PARCIALMENTE RESUELTO: NO son la misma plaza. La ref 459 de Cardiff es 'Research Assistant/Associate (Statistics)' del Centre for Trials Research (confirmada, cierre 17-09-2026), mientras que el puesto Moondance descrito en fuentes externas es de banco humedo (microglia en Alzheimer, procesado y tincion de cortes de tejido, edificio Hadyn Ellis), perfil incompatible con un puesto de estadistica. Ademas el texto Moondance coincide con un anuncio de Bright Network fechado en 2024, asi que esta fila puede venir de un anuncio caduco. El portal eploy ignora el parametro ?keywords= (devuelve los mismos 12 resultados de la pagina 1 para 'research assistant' y para 'dementia') y sigue sin servir las paginas 2 y 3, asi que no se puede confirmar ni descartar desde el portal. Proxima pasada: intentar la ficha de vacante por ID directo o el listado de la School of Medicine; si no aparece, cerrar la fila como caducada. Nota: el puesto Moondance es de laboratorio humedo y por tanto de bajo interes para ella aunque estuviera vivo.</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -17818,7 +19722,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-11</v>
+        <v>-17</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -17948,7 +19852,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>-6</v>
+        <v>-12</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -18189,7 +20093,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>53000</t>
+          <t>52800</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -18205,7 +20109,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -18239,32 +20143,32 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>En marzo de 2027 revisar jobs.ac.uk con el filtro de empleador KCL y comprobar si esta convocatoria se ha repetido con plazo compatible con mayo-2027</t>
+          <t>No solicitar: exige titulo medico britanico o equivalente CON registro completo en el GMC y licencia en vigor, mas practica clinica activa (ECG e induccion de puncion lumbar), y arranca antes del fin de su residencia (22-05-2027). PI Prof Dag Aarsland, Centre for Healthy Brain Ageing; contrato de 12 meses, 45.943 GBP sin London Weighting. Guardar a Aarsland como contacto si le interesa el eje envejecimiento cerebral.</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -18510,27 +20414,27 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>En Q3 2027, con la tesis depositada, mirar el portal careers.amgen.com (busqueda Postdoctoral) para la edicion siguiente y escribir al grupo de genetica estadistica de deCODE presentando su combo MD+PhD y sus pipelines GWAS/PRS.</t>
+          <t>Conflicto sin resolver: decode.com/careers no lista NINGUNA vacante concreta y solo remite al portal 50skills, que es JavaScript puro y llega vacio tanto por WebFetch como por curl. Confirmar la plaza de Reikiavik escribiendo directamente a deCODE (careers) en vez de seguir raspando el portal.</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -18804,47 +20708,1775 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Z23" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Intento unico al portal Oracle de la Universidad de Alberta: la pagina carga solo la cabecera 'University of Alberta Careers' sin contenido (renderizado por JavaScript), asi que no es verificable con fetch. Anotar como bloqueo permanente de ese portal y, si interesa la plaza, confirmarla por el tablon de la ISPG o por correo al departamento.</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>Ninguna accion antes de 2027; si en Q3 2027 interesa el carril farmacogenomico canadiense, revisar el portal de empleo de la Universidad de Alberta.</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>https://iaejup.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/UOA-Careers/job/3142/</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Rama 5 (buzon y novedad), tablon de empleo de la ISPG (SRC-0030) el 2026-09-07. Los datos proceden del anuncio reproducido en el tablon de la ISPG; no se abrio el portal Oracle de la universidad, por eso UNVERIFIED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>P-0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Fellowship in Multi-Omics at Centre for Precision Psychiatry</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>University of Oslo</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Centre for Precision Psychiatry / NORMENT, Institute of Clinical Medicine</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>UNKNOWN (centro dirigido por Ole A. Andreassen)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Postdoctoral research fellowship (stipendiat/postdoktor, contrato publico noruego)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>UNKNOWN (los postdocs de UiO suelen ser de 3 anos)</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>UNKNOWN (escala estatal noruega; no leida en Tier 1)</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>-104</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Doctorado en estadistica, genetica, informatica, medicina o psicologia; analisis multi-omico y genetico a gran escala; programacion</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>El Centre for Precision Psychiatry (NORMENT) es el grupo europeo que mejor solapa con sus lineas 1 y 2: metodos estadisticos sobre datos geneticos humanos a gran escala (GWAS, scores poligenicos, arquitectura poligenica compartida) aplicados a trastornos psiquiatricos graves, y ademas trabaja con neuroimagen, la tecnica que ella ha usado de forma supervisada en QIMR Berghofer; el combo MD + PhD en genetica estadistica es exactamente lo que estos centros clinico-genomicos valoran para hacer de puente entre fenotipado clinico y analisis. Esta convocatoria concreta YA ESTA CERRADA (plazo 2026-06-01) y, aunque siguiera abierta, ella NO seria elegible: exige doctorado y no defiende hasta feb-2028, y ademas esta atada a la residencia en Malaga hasta el 22-05-2027. Se registra por dos motivos operativos: (a) Noruega es UE/EEE, sin visado, movilidad libre; (b) el centro saca convocatorias de postdoc de forma recurrente (al menos cuatro anuncios distintos localizados en jobbnorge en 2025-2026), asi que la accion util es vigilar jobbnorge para la ronda de 2028 y, hacia 2027, escribir al responsable del area de genetica estadistica del centro con el gancho de MD + genetica estadistica de rasgos complejos y los dos manuscritos en revision. Esfuerzo real de una solicitud UiO: carta, CV, lista de publicaciones, research statement y 2-3 referencias.</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Centro de referencia internacional en genetica psiquiatrica con financiacion ERC/Novo Nordisk; convocatorias abiertas en ingles a todo el EEE</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>https://iaejup.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/UOA-Careers/job/3142/</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>Rama 5 (buzon y novedad), tablon de empleo de la ISPG (SRC-0030) el 2026-09-07. Los datos proceden del anuncio reproducido en el tablon de la ISPG; no se abrio el portal Oracle de la universidad, por eso UNVERIFIED.</t>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Vigilar jobbnorge (busqueda site:jobbnorge.no 'Centre for Precision Psychiatry') cada pasada; en 2027 escribir al centro presentando perfil MD + genetica estadistica</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>https://www.jobbnorge.no/en/available-jobs/job/301627/postdoctoral-research-fellowship-in-multi-omics-at-centre-for-precision-psychiatry</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Localizado con busqueda restringida a jobbnorge.no; la pagina de anuncio no se pudo abrir con fetch automatico (jobbnorge devuelve 404 a las rutas de listado), datos tomados de dos resultados de busqueda coincidentes: LIKELY, no VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P-0024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Postdoc in Computational Genomics</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>University of Copenhagen</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Novo Nordisk Foundation Center for Basic Metabolic Research (CBMR), Kilpelainen Group</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tuomas O. Kilpelainen</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Copenhagen</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>UNKNOWN (escala AC danesa, no leida en Tier 1)</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>No publicado en la fuente accesible; el agregador marca el anuncio como expirado</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Doctorado; GWAS, scores poligenicos, metodos de imputacion y epidemiologia genetica; Python o R sobre datos a gran escala</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Tecnicamente es su caja de herramientas exacta (GWAS, PRS, imputacion, R/Python sobre biobancos), pero el fenotipo es cardiometabolico, no psiquiatrico ni de sueno, asi que seria un giro de tema respecto a sus lineas 1-3; ademas exige doctorado defendido y arranque en nov-2026, imposible con la residencia hasta 22-05-2027 y la tesis hasta feb-2028. Se registra porque el grupo Kilpelainen en CBMR es un destino realista para 2028 en genetica estadistica de rasgos complejos y porque CBMR publica convocatorias recurrentes.</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Centro Novo Nordisk con salarios altos y visibilidad internacional en genomica de rasgos complejos</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Revisar employment.ku.dk periodicamente a partir de 2027 buscando CBMR; guardar a Kilpelainen como contacto para carta espontanea en 2027-2028</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>https://employment.ku.dk/faculty/?show=162794</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>La ficha de employment.ku.dk no renderiza el anuncio concreto al fetch automatico (devuelve la pagina generica); detalles tomados del espejo en jobrxiv.org, que marca el anuncio como expirado. Tier 2, LIKELY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>P-0025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Fellow in Statistical Genetics / Genetic Epidemiology</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>The University of Queensland</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>No confirmado (grupo de genetica estadistica / epidemiologia genetica)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>No publicado en la fuente consultada</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>no publicado en la fuente consultada</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Doctorado (o proximo a defensa) en genetica estadistica, epidemiologia genetica o bioestadistica; GWAS a gran escala en UK Biobank y en el Early Growth Genetics (EGG) Consortium; randomizacion mendeliana; programacion en R/Python y herramientas tipo PLINK</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Es la descripcion mas parecida a su linea 1 y 2 que ha aparecido en tres pasadas: GWAS a gran escala en UK Biobank y randomizacion mendeliana es exactamente lo que hace con PLINK y R en su tesis de genetica estadistica, y el EGG Consortium (rasgos de crecimiento y desarrollo infantil) conecta de forma natural con su tercera linea, la genetica del sueno en lactantes. UQ es ademas su unico vinculo vivo con Australia por la estancia de tres meses en QIMR Berghofer, a 15 minutos del campus de Herston, asi que puede pedir carta de referencia alli. NO ES ELEGIBLE AHORA: sigue de residente de Medicina de Laboratorio en Malaga hasta el 22-05-2027 y no defiende hasta feb-2028, y un postdoc de este tipo exige doctorado ya concedido; la via realista es contacto ahora para el ciclo 2028. Requeriria patrocinio de visado australiano (subclase 482 o Global Talent), que UQ tramita de forma rutinaria para postdocs. El esfuerzo real de la solicitud es alto: seleccion contra criterios australianos con respuesta punto por punto, y su punto debil es la ausencia de publicaciones (dos manuscritos en revision como primera autora, ninguno aceptado). Salario y plazo no publicados en la fuente consultada; la ficha oficial en careers.uq.edu.au no se pudo abrir (bloqueo conocido).</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Grupos de genetica estadistica de UQ e IMB son referencia mundial y atraen candidaturas internacionales; ademas la plaza puede llevar tiempo abierta.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Tratarla como objetivo de contacto, no como solicitud: escribir al grupo en 2027 preguntando por vacantes con inicio en 2028. Confirmar si la plaza sigue viva: careers.uq.edu.au esta bloqueado al fetch, asi que escribir al grupo o buscar la ficha por el numero de referencia; si esta cerrada, guardar el grupo como objetivo de contacto para 2027-2028.</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>https://scholarshipdb.net/jobs-in-Australia/Postdoctoral-Research-Fellow-In-Statistical-Genetics-Genetic-Epidemiology-The-University-Of-Queensland=YeqPUAjM7BGUYQAlkGUTnw.html</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Rama 2, 2026-09-14. Pista de nivel Tier 2 (scholarshipdb, agregador) recogida en busqueda web; no se pudo abrir la ficha oficial de UQ (careers.uq.edu.au tiene bloqueo conocido y redirige a 404). Sin fecha de publicacion ni de cierre: puede estar caducada. Registrada como UNVERIFIED y PENDING a proposito. VERIFICADO POR LA ORQUESTADORA 2026-09-14: la API publica del portal Workday de UQ (searchText=genetics) devuelve UNA sola plaza, R-68861 (PCTG, Yengo), asi que este anuncio no esta hoy en el portal oficial: o caduco o nunca fue una vacante publicada. Se conserva la fila como pista de grupo y via de contacto, no como plaza viva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>P-0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Fellow in Genomics and Youth Mental Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>The University of Queensland</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Child Health Research Centre</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>No publicado en la fuente consultada</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>no publicado en la fuente consultada</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Doctorado en genomica, genetica psiquiatrica, farmacogenetica o epidemiologia; analisis de datos geneticos a gran escala; interes en salud mental de jovenes</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Cruza sus tres activos a la vez: la linea 2 (GWAS/PRS de trastornos psiquiatricos) es el nucleo del puesto, el angulo de farmacogenetica es justo lo que su residencia de Medicina de Laboratorio le da y casi ningun candidato de genetica estadistica tiene, y el foco en poblacion infantil y juvenil enlaza con su trabajo de sueno en lactantes. El combo MD+PhD es aqui una ventaja real y no decorativa: un centro de salud infantil valora que sepa leer fenotipo clinico y datos de laboratorio, no solo correr PLINK. NO ES ELEGIBLE AHORA: residencia en Malaga hasta el 22-05-2027 y tesis sin defender hasta feb-2028; el puesto pide doctorado concedido. Necesitaria patrocinio de visado australiano. El trabajo de solicitud es medio-alto (criterios de seleccion australianos punto por punto) y su talon de Aquiles sigue siendo la falta de publicaciones aceptadas. Sin PI nombrado ni salario en la fuente consultada, asi que el gancho de contacto hay que construirlo tras identificar al responsable del grupo en el Child Health Research Centre; el gancho natural es su estancia previa en QIMR Berghofer mas los dos manuscritos en revision (Journal of Sleep Research y Nature Mental Health).</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Sin datos: no se pudo abrir la ficha oficial ni conocer el numero de candidaturas o la antiguedad del anuncio.</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>Tratarla como objetivo de contacto, no como solicitud: escribir al grupo en 2027 preguntando por vacantes con inicio en 2028. Identificar al PI del Child Health Research Centre que lleva genomica y salud mental juvenil y confirmar si la plaza sigue abierta; si esta cerrada, mantener el grupo en la lista de contacto directo para 2027-2028.</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>https://www.uq.edu.au/childhealthresearchcentre/</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Rama 2, 2026-09-14. Pista Tier 2 aparecida en busqueda web junto con la otra plaza de UQ; no se pudo abrir ninguna ficha oficial (careers.uq.edu.au bloqueado). La URL registrada es la del centro, no la del anuncio, para no inventar un enlace de vacante. UNVERIFIED. VERIFICADO POR LA ORQUESTADORA 2026-09-14: la API publica del portal Workday de UQ (searchText=genetics) devuelve UNA sola plaza, R-68861 (PCTG, Yengo), asi que este anuncio no esta hoy en el portal oficial: o caduco o nunca fue una vacante publicada. Se conserva la fila como pista de grupo y via de contacto, no como plaza viva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>P-0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Research Fellow (Genetic Analysis)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>University College London</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Department of Neurodegenerative Disease</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Andre Altmann y David Cash</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12 meses (01-09-2026 a 31-08-2027)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>53200</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>21</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Doctorado concedido (o previsto antes de incorporarse; si no, contrato como Research Assistant grado 6B); analisis genetico y bioinformatico con programacion avanzada en Python, R y Bash; analisis caso-control y de fenotipos cuantitativos; deseable neurodegeneracion y estadistica</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Metodologicamente encaja (analisis caso-control y fenotipos cuantitativos en R/Python) pero no es elegible: el contrato arranca el 01-09-2026 y termina el 31-08-2027, mientras ella sigue de residente en Malaga hasta el 22-05-2027; interesa solo como contacto de laboratorio, el grupo de Altmann combina genetica y neuroimagen, que es su estancia en QIMR.</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Sin datos publicados sobre numero de candidaturas.</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>No solicitar. Guardar a Andre Altmann (UCL) como contacto para 2027: su grupo une genetica estadistica y neuroimagen, combinacion que ella busca.</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSW126/research-fellow-genetic-analysis</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Rama 2, jobs.ac.uk (SRC-0002), busqueda 'statistical genetics' el 2026-09-14. Ficha individual abierta y leida: fechas, salario, PIs y criterios tomados del anuncio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>P-0028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bioinformatician</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Medical &amp; Molecular Genetics</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Londres</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Staff cientifico</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>No leido</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>53100</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>10</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Perfil de bioinformatica en genetica medica y molecular; no se abrio la ficha individual, criterios sin leer</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Es un puesto de plantilla bioinformatica, no de investigacion propia, y con plazo el 23-09-2026, muy anterior a su disponibilidad (22-05-2027): se registra solo para no redescubrirlo y porque confirma que Medical &amp; Molecular Genetics de KCL contrata con regularidad.</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Sin datos.</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>No solicitar. Vigilar el departamento Medical &amp; Molecular Genetics de KCL en pasadas futuras.</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSU830/bioinformatician</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Rama 2, jobs.ac.uk (SRC-0002), busqueda 'polygenic risk score' el 2026-09-14. Datos leidos en la pagina de resultados; no se abrio la ficha individual, de ahi LIKELY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>P-0029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Fellow/Research Fellow in Statistical Genomics (R-68861)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>University of Queensland</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Institute for Molecular Bioscience - Program in Complex Trait Genomics (PCTG)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Loic Yengo</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Brisbane (St Lucia Campus)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Postdoc (Academic Level A) o Research Fellow (Level B), fixed-term</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Hasta 2.5 anos</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>~60000-80000 (AUD 106294-113660 Level A / AUD 119463-141545 Level B, + 17% superannuation)</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="O30" t="n">
+        <v>30</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>PhD en genetica estadistica/cuantitativa, biologia computacional, estadistica o data science; estadistica bayesiana; modelizacion matematica; programacion en C/C++, Python o R; datasets genomicos a gran escala y single-cell omics valorados; productividad investigadora acorde a la etapa</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Es su linea 1 literal (genetica estadistica de rasgos complejos) en el grupo de referencia mundial del area, el PCTG que ella ya conoce de oidas por su estancia en QIMR Berghofer (mismo ecosistema de Brisbane), y el perfil MD le daria valor en la interpretacion clinica de fenotipos; pero NO es elegible por calendario: el plazo cierra el 13-10-2026, ella sigue de residente en Malaga hasta el 22-05-2027 y no defiende tesis hasta feb-2028, y el anuncio exige doctorado concedido. Ademas el puesto es de DESARROLLO de metodos (bayesiano, C/C++, track record de publicaciones y de solicitudes de financiacion) y ella es usuaria aplicada de PLINK/R sin publicaciones destacadas: hoy no competiria. Valor real de la fila: es el arquetipo exacto de plaza a la que debe poder optar en 2028 y el anuncio dice que el grupo capta 'recent PhD graduates'; ademas fija dos datos utiles, el rango salarial y que Yengo esta construyendo equipo. Australia exige patrocinio de visado (no es UE). Accion: escribir a Loic Yengo (IMB/PCTG) en 2027 presentandose como MD-PhD en genetica estadistica con contactos previos en QIMR Berghofer y preguntando por vacantes o por un esquema NHMRC/fellowship con fecha de inicio 2028.</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>PCTG/IMB es uno de los tres o cuatro grupos lideres mundiales en genetica estadistica; plaza anunciada globalmente y abierta tambien a nivel B</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>No aplicable ahora por calendario: guardar el anuncio como plantilla y contactar a Loic Yengo a finales de 2027 para vacantes con inicio 2028</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>https://uq.wd3.myworkdayjobs.com/uqcareers/job/St-Lucia-Campus/Postdoctoral-Research-Fellow-Research-Fellow-in-Statistical-Genomics_R-68861-2</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Portal Workday oficial de UQ consultado por su API publica (POST a /wday/cxs/uq/uqcareers/jobs y GET de la ficha): titulo, fechas 2026-09-11/2026-10-13, salario y criterios leidos integros. La pagina de reclutamiento del PCTG (cnsgenomics.com/content/recruitment) enlaza a UQ jobs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>P-0030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Research Assistant - estudio CONNECT</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Cardiff University</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Division of Psychological Medicine and Clinical Neurosciences, School of Medicine</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Cardiff</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Research Assistant (Grade 5)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>~39000-42000 (GBP 33951-36636)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>12</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Puesto de apoyo a la investigacion del estudio CONNECT en la sede de Cardiff; nivel pre-doctoral</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Puesto de asistente pre-doctoral sin componente de genetica estadistica y ademas incompatible con su residencia hasta mayo de 2027; se registra solo para no redescubrirlo y como senal de que el MRC Centre de Cardiff sigue contratando.</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>Ninguna; descartada por nivel y por calendario</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>https://cardiffuniweb.eploy.net/vacancies/447/research-assistant.html</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Portal oficial eploy de Cardiff (30 vacantes en total, unica coincidencia con psiquiatria/genetica); fecha de cierre leida en el listado oficial</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>P-0031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Associate (proyecto Youth Endowment Fund, CRIS)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>IoPPN - Department of Child &amp; Adolescent Psychiatry</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Mark Kennedy</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Postdoc (Research Associate), fixed-term</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>18 meses</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>~52000-56000 (GBP 45031-48607 incl. London Weighting)</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>8</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Doctorado concedido o tesis depositada en psicologia, psiquiatria, epidemiologia, estadistica, salud publica o criminologia; experiencia con historias clinicas electronicas a gran escala o cohortes longitudinales; plataforma CRIS del SLaM; regresion multivariable y analisis de supervivencia; R o Stata; publicaciones</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Es epidemiologia de registros clinicos (CRIS/SLaM) sobre TDAH y violencia juvenil, no genetica estadistica ni GWAS/PRS, y cierra el 21-09-2026 cuando ella no esta disponible; se registra para no redescubrirlo y porque confirma que el IoPPN publica postdocs de forma continua.</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>Ninguna; fuera de linea y fuera de plazo para ella</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/157565-postdoctoral-research-associate</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Ficha oficial de KCL leida entera (salario, duracion y cierre); localizada con la busqueda por termino del portal, que si expone los puestos del IoPPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>P-0032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Research Associate at the Human Functional Genomics Initiative</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>IoPPN - Centre for Developmental Neurobiology</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Jeronimo Jurado</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Postdoc (Research Associate), fixed-term</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Hasta el 13-05-2028</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>~52000-61000 (GBP 45031-52514 incl. London Weighting)</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Doctorado en ciencias de la vida; cultivo de celulas madre humanas (hiPSC/hESC); biologia molecular y microscopia confocal; organoides neurales y scRNA-seq valorables</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Puesto de poyata (organoides cerebrales, cultivo de iPSC) sin componente de genetica estadistica: fuera de su perfil.</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/155527-research-associate-at-the-human-functional-genomics-initiative</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Ficha oficial de KCL leida entera</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>P-0033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Postdoctoral researcher in genome stability and neurotoxicity</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Erasmus MC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Wetenschap en Onderzoek</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Postdoc, 36 h/semana</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3 anos</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Doctorado; estabilidad del genoma y neurotoxicidad (perfil de laboratorio molecular)</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Biologia molecular de estabilidad genomica, no epidemiologia genetica ni genetica del sueno: fuera de su perfil; se registra para no redescubrirlo.</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>https://www.werkenbijerasmusmc.nl/vacature/1307326/postdoctoral-researcher-genome-stability-and-neurotoxicity-3-years-3416</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Listado oficial werkenbijerasmusmc (131 vacantes; unica coincidencia con genetica); ficha individual no abierta por presupuesto, sin fecha de cierre publicada en el listado</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>P-0034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Computational Scientist II - Karczewski Lab (ref 44894)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Broad Institute</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Karczewski Lab (genomica poblacional, gnomAD)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Konrad Karczewski</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Computational Scientist (staff)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>No leidos (ficha individual no abierta); perfil de cientifico computacional en genomica poblacional</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Genomica poblacional computacional de alto nivel (entorno gnomAD): tematicamente vecino a su linea 1 pero es un puesto de staff con exigencia fuerte de ingenieria de datos y programacion que hoy no tiene, ademas de requerir visado H-1B/J-1.</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Broad Institute, laboratorio de referencia mundial en genomica poblacional</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>Abrir la ficha la proxima pasada para leer requisitos y confirmar si hay linea de genetica psiquiatrica asociada</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>https://broadinstitute.avature.net/en_US/careers/JobDetail/Computational-Scientist-II-Karczewski-Lab/22501</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Listado en el portal oficial Avature del Broad con fecha de publicacion 10-09-2026; ficha individual no abierta por presupuesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>P-0035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Postdoctoral Associate - Computational Biology (ref 44829)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Broad Institute</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>No indicado en el listado</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Cambridge, MA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>No leidos (ficha individual no abierta); postdoc de biologia computacional, presencial</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Postdoc de biologia computacional en el Broad sin laboratorio identificado en el listado: puede o no ser del Stanley Center, hace falta abrir la ficha antes de valorarlo de verdad.</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Broad Institute, convocatorias con competencia internacional</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>Abrir la ficha la proxima pasada para identificar laboratorio y requisitos; si es del Stanley Center, subir el Fit</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>https://broadinstitute.avature.net/en_US/careers/JobDetail/Postdoctoral-Associate-Computational-Biology/22430</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Listado en el portal oficial Avature del Broad con fecha de publicacion 04-09-2026; ficha individual no abierta por presupuesto</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD23"/>
+  <autoFilter ref="A1:AD36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18855,7 +22487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB10"/>
+  <dimension ref="A1:AB15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18863,7 +22495,7 @@
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
     <col width="52" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="52" customWidth="1" min="9" max="9"/>
@@ -19078,7 +22710,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -19095,7 +22727,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Closest match to research line 1 (statistical genetics of complex traits) found this run: the required toolkit - PLINK, R, GWAS, PRS, meta-analysis - is exactly the level she commands independently, and the 0-2 years post-PhD band is written for someone at her stage. Two real conditions. (a) TIMING: the advert requires a defended PhD (hers is an ETA of Feb 2028), so this requisition will be long closed; the row is a target-company record, not an apply-now item, and RGC posts statistical-genetics and computational-genomics requisitions continuously, so the action is to track the careers page and apply from late 2027. (b) VISA: USA, so H-1B or O-1 sponsorship is needed; Regeneron does sponsor but it is a filter, and four days onsite in Tarrytown rules out the remote working she prefers. An application needs a CV led with the MD+PhD combination - rare in an RGC analyst pool and directly useful for phenotype curation from EHR data - plus the Nature Mental Health first-author paper once accepted and evidence of pipeline work at scale. REGENIE is the concrete gap: she has PLINK, the advert names REGENIE explicitly, and a few months of self-directed work on UK Biobank-style data would close it. Salary is far above any Spanish public option and she has set no floor. Hook: RGC's psychiatric and behavioural phenotype work against her GWAS/PRS line; the natural meeting place is WCPG (SRC-0026) rather than a cold Workday application.</t>
+          <t>La ficha r48469 devuelve hoy HTTP 404 en el propio dominio de Regeneron: la vacante ya no admite solicitudes, cosa esperada para un anuncio de hace semanas y sin consecuencia para ella, que no podia optar sin el doctorado defendido. Se confirma ademas que la pagina de genetica y genomica de careers.regeneron.com no enumera puestos, solo invita a la talent community, asi que como fuente de vigilancia rinde poco. Lo que se conserva de esta fila es el perfil de referencia (genetica estadistica de biobanco, REGENIE y pipelines de cohortes grandes) y la laguna tecnica a cerrar durante 2027.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -19120,27 +22752,27 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>No aplicar ahora (doctorado sin defender). Anadir el filtro de genetica y genomica de careers.regeneron.com a la vigilancia; cerrar durante 2027 la laguna de REGENIE y pipelines de cohortes grandes; reabrir esta fila en otono de 2027.</t>
+          <t>Dar por cerrada la vacante concreta y conservar la fila como referencia de perfil y banda salarial. Sustituir la vigilancia por la familia de plazas equivalente de GSK (fila nueva) y reintentar el portal de Regeneron en 2027 con la ruta /en/genetics-and-genomics-jobs/, que hoy sigue viva pero solo como pagina de captacion.</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -19345,7 +22977,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sigue siendo la fila de mayor consecuencia del carril clinico: si la via transitoria se abre, una MD con residencia de Medicina de Laboratorio y doctorado en genetica estadistica obtiene el titulo de especialista en genetica sin repetir cuatro anos de residencia. ESTADO A 07-09-2026, VERIFICADO HOY Y NEGATIVO: el listado de audiencia e informacion publica del Ministerio de Sanidad tiene un unico proyecto abierto, el real decreto de personas en situacion de electrodependencia (24-07-2026 a 11-09-2026); no hay ningun proyecto de Genetica en tramite de audiencia. Tampoco aparece en el BOE ningun real decreto que establezca los titulos de especialista en Genetica Medica o en Genetica de Laboratorio: la unica norma reciente del ambito sigue siendo el RD 101/2025, de 18 de febrero (BOE-A-2025-3189), que crea Laboratorio Clinico. La tramitacion lleva veinte meses de anuncios sin acto administrativo: diciembre de 2024 aval de la Comision de RRHH del Consejo Interterritorial, junio de 2025 resolucion favorable de la Direccion General de Ordenacion Profesional, 01-07-2025 consulta publica previa (PDF 01.07.25_CPP_PRD_Especialidad_en_Genetica_laboratorio.pdf en sanidad.gob.es/normativa/docs), diciembre de 2025 la directora general dice que saldran a audiencia en breve, febrero-marzo de 2026 el Ministerio lo da por a punto y la AEGH anuncia que veran la luz en julio. Estamos en septiembre de 2026 y no han salido, con lo que la primera convocatoria MIR de estas especialidades en 2027 se da por muy comprometida. Consecuencia practica para ella: aunque el RD se publicara manana, el plazo de solicitud de la via transitoria caeria previsiblemente en 2027-2028 y le exigiria acreditar anos de servicio en genetica que no tendra; el encaje de perfil es total pero la elegibilidad real es dudosa y hay que leer la disposicion transitoria palabra por palabra en cuanto se publique el borrador.</t>
+          <t>Sin movimiento esta semana y con el expediente ahora mucho mejor fechado. El listado de audiencia e informacion publica de Sanidad, abierto hoy, tiene dos proyectos vivos (formulas infantiles y cereales, DG/73/26, plazo 8 a 29-09-2026; dependencia electromedica, DG/72/26, hasta 11-09-2026) y ninguno de Genetica: los dos reales decretos siguen sin llegar a audiencia publica. Dos hallazgos Tier 1 nuevos ordenan la cronologia y CIERRAN el conflicto con la AEGH que quedo abierto la pasada anterior. Primero, la nota de prensa 6697 del Ministerio, de 13-06-2025, dice que lo aprobado es la CREACION de las dos especialidades en respuesta al acuerdo de la Comision de Recursos Humanos del SNS de diciembre de 2024: eso es un acuerdo ministerial, no un real decreto publicado en el BOE, y es lo que la AEGH llama aprobacion. Segundo, existe el documento de consulta publica previa del proyecto de real decreto del titulo de especialista en Genetica de Laboratorio, fechado el 01-07-2025 y tramitado al amparo del articulo 133 de la Ley 39/2015: confirma que a julio de 2025 el expediente estaba todavia en el escalon anterior a la audiencia publica. La nota de prensa confirma tambien lo que esta fila ya sostenia: seran dos reales decretos independientes, ambas especialidades duraran cuatro anos, Genetica Medica quedara reservada a Medicina y Genetica de Laboratorio se abrira a Medicina, Farmacia, Biologia, Quimica y Veterinaria. Lo que sigue sin existir en ningun texto oficial es la disposicion transitoria: ni la nota de prensa ni el documento de consulta previa la mencionan, asi que la hipotesis de que exigira anos de ejercicio al modo de Pediatria y Urgencias sigue siendo hipotesis, y el riesgo para ella es el mismo: al acabar la residencia en mayo de 2027 no tendra anos de ejercicio en genetica que acreditar. Balance temporal: 15 meses desde la consulta publica previa y 21 desde el acuerdo de la Comision de RRHH sin borrador en audiencia publica.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -19370,19 +23002,19 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>UPDATED</t>
@@ -19390,7 +23022,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Revisar cada semana sanidad.gob.es/normativa/audiencia/home.htm hasta que aparezcan los dos proyectos de real decreto de Genetica; el dia que aparezca el borrador, leer su disposicion transitoria y comprobar si exige anos de ejercicio en genetica y si admite la residencia de Laboratorio Clinico como merito; en paralelo, buscar en el BOE por titulo cada mes</t>
+          <t>Seguir revisando cada semana el listado de audiencia publica de Sanidad; a partir de ahora vigilar tambien el paso previo, la consulta publica previa, y el buzon proyectosnormativos-dgorden@sanidad.gob.es como via de alegaciones cuando aparezca el borrador; en el BOE buscar por titulo cada mes. Si en 2027 sigue sin haber borrador, escribir a la AEGH preguntando si la disposicion transitoria acreditara anos de ejercicio y si computara la residencia de Laboratorio Clinico.</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -20108,7 +23740,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-42</v>
+        <v>-48</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -20186,8 +23818,613 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>J-0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bolsa de Empleo Abierta y Permanente (BAPE) de Sacyl - categoria Licenciados Especialistas (incluye Analisis Clinicos y Bioquimica Clinica)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gerencia Regional de Salud de Castilla y Leon (Sacyl)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sistema publico de salud (CCAA Castilla y Leon)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Valladolid (gestion regional; plazas en toda la comunidad)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Espana</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Nombramiento estatutario temporal (bolsa de contratacion)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Titulo de especialista de la categoria (Analisis Clinicos / Bioquimica Clinica, previsiblemente Laboratorio Clinico tras el RD 101/2025); nacionalidad UE; inscripcion telematica en la aplicacion BAPE con autobaremo, sin aportar documentacion en el momento del alta; los meritos se acreditan despues, cuando lo requiera la resolucion; los cortes de baremacion son anuales (ultima resolucion de corte publicada el 14-01-2026)</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Es una via PERMANENTE, del tipo que sobrevive a su calendario: ella no puede presentarse a nada que se cierre antes del 22-05-2027, y esta bolsa admite altas en cualquier momento con cortes anuales de baremacion, asi que basta con inscribirse el mismo dia que acabe la residencia. La categoria existe y esta viva: la pagina de convocatorias abiertas de Sacyl nombra literalmente Licenciado Especialista en Analisis Clinicos y en Bioquimica Clinica, que son los titulos que el RD 101/2025 sustituye por Laboratorio Clinico, el que ella obtendra. La solicitud es ligera (alta telematica y autobaremo; la documentacion se aporta despues), de ahi el esfuerzo XS-S, pero conviene tener el expediente de meritos ordenado antes de mayo de 2027 porque el autobaremo decide el orden en la lista. No hay sueldo publicado en la pagina: seria el de FEA estatutario temporal de Castilla y Leon. Sin visado ni homologacion (ciudadana UE con titulo espanol). Una regla vista en un PDF de Sacyl y NO confirmada por mi: quien termina el MIR tendria dos dias habiles desde el fin de la formacion para inscribirse en la bolsa; si se confirma, es critico, porque significa inscribirse el 25-05-2027 y no cuando le venga bien. Hay que abrir ese PDF antes de 2027. A quien escribir: al Servicio de Seleccion de Personal de la Gerencia Regional de Salud, preguntando a que categoria de bolsa se mapea el nuevo titulo de Laboratorio Clinico.</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Bolsa autonomica de una comunidad mediana con dificultad conocida para cubrir plazas de laboratorio; no hay numero de inscritos publicado en la pagina, de ahi que no se afirme mas.</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Antes de que acabe 2026 abrir el PDF de procedimiento de inscripcion FIN MIR de Sacyl y confirmar si el plazo es realmente de dos dias habiles tras finalizar la residencia; en abril de 2027 preparar el autobaremo y la documentacion de meritos; inscribirse en BAPE el 25-05-2027 como muy tarde.</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>https://www.saludcastillayleon.es/profesionales/es/bolsa</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Rama 4, carril 2 (sistema publico). Abierta y leida hoy la ficha Tier 1 de convocatorias abiertas de la categoria Licenciados Especialistas de Sacyl, donde figuran Analisis Clinicos y Bioquimica Clinica y el corte con resolucion de 14-01-2026. El plazo de dos dias habiles para quien termina el MIR procede del titulo de un PDF de Sacyl visto en resultados de busqueda y NO abierto: queda como no confirmado dentro de la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>J-0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Borsa de treball de l'Institut Catala de la Salut - facultatiu/iva especialista</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Institut Catala de la Salut (ICS), Generalitat de Catalunya</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sistema publico de salud (CCAA Cataluna)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Barcelona (gestion central; places a tot Catalunya)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Espana</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Nombramiento estatutario temporal (borsa de treball)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Inscripcion telematica permanente con usuario propio y carga del curriculum en el Gestor de Curriculums; hay que tener registrada la titulacion habilitante ANTES de poder elegir la categoria; nacionalidad espanola o de un Estado miembro de la UE; titulos extranjeros homologados; la baremacion del desempeno se activa al acumular periodos trabajados superiores a tres meses; la inscripcion puede desactivarse y reactivarse, con un minimo de dos meses de desactivacion</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Segunda via permanente del carril publico y la primera de Cataluna en la base. Encaja con su calendario por la misma razon que Andalucia o Castilla y Leon: no hay plazo que perder, el alta es telematica y continua, y el orden depende del curriculum baremado, no de acertar una convocatoria. La condicion tecnica que importa es que el ICS no deja seleccionar la categoria de facultativo especialista hasta que el titulo esta cargado en el Gestor de Curriculums, asi que no hay nada que hacer hasta tener el titulo de Laboratorio Clinico en mayo de 2027; lo que si se puede adelantar es el alta de usuario y el volcado del resto del curriculum (licenciatura, docencia, comunicaciones, los dos manuscritos cuando salgan). Esfuerzo bajo pero con trabajo real de curriculum. Ciudadana UE: sin visado ni homologacion. No hay salario en la pagina; seria el de facultativo especialista temporal del ICS. Cataluna suma ademas el idioma: el ICS exige acreditar nivel de catalan en los procesos, punto que esta fila NO verifica y que hay que comprobar en el pacte de seleccio temporal antes de contar con esta via.</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Cataluna concentra la mayor densidad de laboratorios clinicos y de genetica de Espana y la borsa es la puerta unica de entrada temporal al ICS; sin cifras publicadas de inscritos, la estimacion es cualitativa.</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>En Q1 2027 abrir el quadre de categories del ICS y el calendari de baremacions para fijar (a) a que categoria mapea Laboratorio Clinico y (b) que corte de baremacion pilla tras el 22-05-2027; comprobar en el pacte de seleccio temporal el requisito de catalan.</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>https://ics.gencat.cat/ca/lics/treballeu-a-lics/treball-temporal/borsa-de-treball/</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Rama 4, carril 2. Abierta la pagina Tier 1 de funcionament de la borsa del ICS: confirma inscripcion telematica, exigencia de titulacion habilitante cargada, homologacion de titulos extranjeros y las reglas de baremacion del desempeno, pero NO publica calendario de plazos, de ahi LIKELY y no VERIFIED. El requisito de nacionalidad UE procede de la pagina de tramits de la Generalitat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>J-0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Statistical Geneticist Investigator (Human Genetics / Genomic Sciences)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GSK (GlaxoSmithKline)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>I+D farmaceutica</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Multiple locations (no verificado)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>UNKNOWN (probablemente Reino Unido y Estados Unidos)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>No verificados: la ficha del puesto no se pudo leer (la pagina de GSK devuelve solo el armazon del portal al fetch automatico). Por el titulo, genetica estadistica de descubrimiento de dianas; en GSK este tipo de plaza suele pedir doctorado y experiencia en analisis de biobancos</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Es el puesto arquetipico de su carril 1 y de su tecnica declarada: genetica estadistica en I+D de farma, que es exactamente GWAS/PRS con PLINK y R sobre cohortes grandes, y GSK es ademas el equipo de human genetics mas activo del sector europeo en contratacion continua. Encaja con ELLA en linea de trabajo pero no en calendario ni en credencial: una plaza abierta hoy no seguira viva en mayo de 2027, y casi con seguridad pide doctorado defendido, que no tendra hasta feb-2028. Su valor real no es la vacante concreta sino la evidencia de que GSK mantiene abierta una familia entera de plazas (Statistical Geneticist Investigator, Investigator Novel Human Genetics, Genomic Data Scientist, Principal Scientist Genomics Analytics Engineer), es decir, una linea de contratacion recurrente a la que presentarse en 2028 con el doctorado en la mano. Lo que exige la solicitud es un CV con pipelines propios demostrables y publicaciones; ella tiene los pipelines y dos manuscritos en revision, y la laguna a cerrar durante 2027 es la misma que ya se identifico para Regeneron: REGENIE y analisis a escala de biobanco. Visado: si la plaza es de Reino Unido o Estados Unidos necesita patrocinio, que GSK concede habitualmente en estos roles pero que no esta verificado aqui. Sin salario publicado en lo que pude leer.</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Plazas de genetica estadistica en farma grande con alcance mundial y sin restriccion geografica de candidatos; base cualitativa, no hay datos de solicitantes.</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>No aplicar ahora. Reintentar la ficha con navegador o a mano para leer requisitos y ubicacion; anadir jobs.gsk.com a la vigilancia semanal filtrando por genetics; reabrir esta linea de plazas en 2028 con el doctorado defendido.</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>https://jobs.gsk.com/en-gb/jobs/223316?lang=en-us</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Rama 4, carril 1. La existencia del puesto y su URL proceden de una busqueda acotada al dominio propio del empleador (jobs.gsk.com), no de un agregador; la ficha en si devolvio solo el armazon del portal, asi que fechas, requisitos, ubicacion y salario quedan expresamente sin verificar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>J-0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Medical Writer (Oxford o remoto en Reino Unido) y familia de plazas de redaccion y edicion medica</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Oxford PharmaGenesis Ltd</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Comunicacion cientifica / MedComms</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Oxford y Londres</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Reino Unido</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Remote-UK o hibrido segun plaza</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Permanent</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>No detallados en el listado; la agencia declara buscar tanto comunicadores medicos con experiencia como recien titulados. Doce vacantes vivas en el portal, entre ellas tres Medical Writer (ref. 1421 Oxford/Remote-UK, 1420 USA, 1400 UK), un Senior Medical Writer (1392, Londres) y un Senior Medical Editor (1383, UK/Londres), todas permanentes</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Es la primera prueba de que el carril 3 existe de forma verificable, despues de dos pasadas en blanco: son plazas Tier 1 leidas en el portal del propio empleador, no anuncios de agregador. Encaja con ella de forma plausible pero no automatica: MD con ingles C2 y dos manuscritos propios en revision es el perfil clasico de entrada a MedComms, y la redaccion medica valora precisamente el criterio clinico que ella tiene; lo que le falta es cualquier experiencia de agencia y un portafolio de materiales (abstracts, slide decks, publication plans), que es lo que la solicitud exige, normalmente con una prueba de escritura cronometrada. Trabajo de solicitud: CV reorientado a comunicacion, carta y prueba de escritura, de ahi M. Dos condiciones que hay que resolver y que impiden puntuar mas alto: (1) el calendario, porque estas doce plazas son permanentes pero se cubriran mucho antes de mayo de 2027, asi que el valor esta en la agencia como empleador recurrente, no en la ref. 1421; (2) el visado, porque tras el Brexit una plaza britanica exige patrocinio y la ruta remota UK tambien requiere derecho a trabajar en Reino Unido. La lectura util es que Oxford PharmaGenesis publica vacantes de forma continua en un portal legible, asi que es el sitio al que volver en 2027 y, si entonces hay sede o plaza remota europea, el punto de entrada. Sin salario publicado.</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Rotacion alta y contratacion continua en MedComms britanico (doce vacantes simultaneas en una sola agencia), lo que abarata la entrada; en contra, la entrada sin experiencia de agencia compite con candidatos ya formados.</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>No aplicar ahora. Revisar el portal cada trimestre a partir de 2027 buscando plazas remotas o europeas y la figura de associate medical writer; durante 2026-2027 construir portafolio (los dos manuscritos publicados, un abstract y una pieza divulgativa) para poder responder a la prueba de escritura sin preparar nada nuevo.</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>https://careers.pharmagenesis.com/vacancies/vacancy-search-results.aspx</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Rama 4, carril 3, metodo nuevo: en vez de esperar anuncios en agregadores, se abrio el portal de vacantes de una agencia MedComms concreta (motor eploy, el mismo que ya usa el repo para Cardiff). Listado leido hoy: doce vacantes con titulo, ubicacion y tipo de contrato; el portal no publica fechas de cierre, por eso la fila no afirma ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>J-0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Candidatura espontanea permanente en Health in Code (genetica clinica y genomica)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Health in Code</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Empresa de genetica clinica y genomica</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>A Coruna y Madrid (multinacional con sedes en Espana)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Espana</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>No hay vacantes publicadas: la pagina de empleo es un formulario permanente de envio de CV, con el mensaje de que como empresa en crecimiento buscan candidatos de forma continua</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Es el unico puente verificado esta semana entre su titulo de laboratorio y el sector privado espanol de genetica clinica, y tiene la ventaja de no depender de un plazo: el canal esta abierto siempre, asi que se puede usar exactamente cuando ella este disponible. Encaja con ELLA porque una empresa de diagnostico genetico necesita justo el cruce que ella tendra en 2027 (medica especialista en Laboratorio Clinico + interpretacion de variantes + capacidad de analisis con R y PLINK), y porque le permite quedarse en Espana sin depender de una bolsa publica. Lo que hay que resolver es que no hay puesto al que optar: una candidatura espontanea sin vacante rinde poco salvo que vaya dirigida a una persona concreta y con un gancho, asi que el trabajo real no es rellenar el formulario sino identificar en 2027 a quien dirigirla (direccion cientifica o responsable de diagnostico genetico) y escribirle con un caso concreto: residente de Laboratorio Clinico con pipelines GWAS/PRS propios y tesis en genetica estadistica, disponible desde junio de 2027. Esfuerzo XS para el envio. Sin salario ni tipo de contrato publicados, sin visado (empresa espanola, ciudadana UE).</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>No hay vacante publicada ni proceso competitivo visible: la empresa solo mantiene un buzon de CV.</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Revisar la pagina cada trimestre por si pasa de buzon a listado de vacantes; en Q1 2027 localizar el nombre de la direccion cientifica o del area de diagnostico genetico y enviar la candidatura dirigida, no el formulario generico.</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>https://healthincode.com/trabaja-con-nosotros/</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>Rama 4, carril 1 (empresa). Pagina Tier 1 del propio empleador abierta y leida hoy: no lista ninguna vacante, solo el formulario permanente. La fila registra el canal, no un puesto, y lo dice.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB10"/>
+  <autoFilter ref="A1:AB15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21311,7 +25548,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -21451,7 +25688,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -22732,7 +26969,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -23255,7 +27492,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -24028,7 +28265,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -25043,7 +29280,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -35589,7 +39826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -36384,8 +40621,112 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SUB-0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>University of Queensland - alerta de empleo del portal Workday (Job Alerts)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://uq.wd3.myworkdayjobs.com/uqcareers</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Correo con las vacantes nuevas de UQ que casen con la busqueda guardada (genetics, genomics, statistical, mental health)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>UQ concentra el PCTG (Visscher, Yengo, Zeng) y el Child Health Research Centre (Enda Byrne), el ecosistema mas cercano a su linea 1 y donde ya tiene contactos por la estancia en QIMR Berghofer; los anuncios duran ~4 semanas y se pierden entre pasadas</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Crear la alerta desde la propia interfaz Workday ('Create Job Alert'); requiere cuenta de candidato</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SUB-0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>jobRxiv - alerta por correo de busqueda guardada</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>https://jobrxiv.org/job-alerts/</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aviso por correo de cada vacante nueva que encaje con palabras clave (statistical genetics, GWAS, polygenic, psychiatric genetics, sleep genetics). En jobRxiv publican los propios PI, con contacto nominal en el anuncio.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>jobRxiv ya es fuente (SRC-0035) pero su buscador web NO muestra fecha de publicacion, asi que desde el repo es imposible saber que es nuevo y que lleva meses colgado; esta pasada varias pistas de jobRxiv resultaron ser anuncios caducados. La alerta por correo resuelve exactamente ese punto ciego, y ademas alimenta el buzon que esta rutina ya lee cada lunes.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Comprobado el 2026-09-14 que jobRxiv no figura en subscriptions.tsv. Al darse de alta, crear filtro de Gmail que aplique la etiqueta Research a los correos de jobrxiv.org.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J15"/>
+  <autoFilter ref="A1:J17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -21319,7 +21319,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -21461,7 +21461,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -22258,7 +22258,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -22381,7 +22381,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Espana</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -23967,7 +23967,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Espana</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -24209,7 +24209,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -24330,7 +24330,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Espana</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">

--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -22,18 +22,18 @@
     <sheet name="readme" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$63</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$148</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$200</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$252</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Reloj vivo a 8 dias: la inscripcion anticipada cierra el 15-sep-2026 a las 17:00 ET. Hacerse socia trainee de ASHG antes de inscribirse baja la cuota casi a la mitad; despues del 15-sep solo queda tarifa late/onsite.</t>
+          <t>RELOJ VIVO: la tarifa anticipada sigue abierta hasta manana 15-sep-2026 a las 17:00 ET. Si va, hacerse socia student/trainee de ASHG ANTES de inscribirse: la cuota cae de 775 USD (~713 EUR) a 435 USD (~400 EUR), un ahorro de ~313 EUR que supera de largo la cuota de socia. A partir del 16-sep solo queda late/onsite, y no hay tarifa de un dia ni opcion virtual.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -771,12 +771,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E-0001</t>
+          <t>E-0005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
+          <t>IGES 2026 Annual Meeting &amp; Education Workshop</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -786,21 +786,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Congreso anual</t>
+          <t>Congreso anual + workshop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -810,12 +814,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>La inscripcion sigue ABIERTA a 22 dias del congreso: si va, registrarse esta semana en https://ispg.societyconference.com/v2/ y escribir a info@ispg.net pidiendo la cuota Student/Post-Doc y si hay opcion virtual, porque el portal no muestra tarifas.</t>
+          <t>RELOJ VIVO a 5 dias: la tarifa early de IGES cierra el 19-sep-2026 y desde el 20-sep sube a late. Solo tiene sentido moverla si YA ha decidido ir a ASHG 2026 (misma region, dias consecutivos); el plazo de resumenes cerro el 30-may-2026, asi que iria como oyente. Si no va a ASHG, dejarla pasar y apuntarla como objetivo 2027.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://ispg.net/wcpg-2026/</t>
+          <t>https://www.geneticepi.org/2026-annual-meeting</t>
         </is>
       </c>
     </row>
@@ -827,12 +831,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>E-0005</t>
+          <t>E-0001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IGES 2026 Annual Meeting &amp; Education Workshop</t>
+          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -842,14 +846,21 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Congreso anual + workshop</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -857,10 +868,14 @@
           <t>M</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>La inscripcion sigue ABIERTA a 15 dias del congreso y sin fecha de cierre publicada: si va, inscribirse esta misma semana en https://ispg.societyconference.com/v2/ y escribir a info@ispg.net preguntando por la cuota Student/Post-Doc y por si existe opcion virtual, porque ninguna de las dos cosas esta publicada en ningun sitio accesible.</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://www.geneticepi.org/2026-annual-meeting</t>
+          <t>https://ispg.net/wcpg-2026/</t>
         </is>
       </c>
     </row>
@@ -896,11 +911,11 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>737</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -915,7 +930,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>No reservar todavia: hacer primero el MR introductorio (T-0003) en marzo-2027 y buscar la edicion de finales de 2027 cuando Bristol publique el programa 2027-28</t>
+          <t>NO reservable en la practica para 2026: exige haber hecho antes el curso introductorio de MR, que ella hara en marzo-2027. Objetivo real: la edicion de noviembre-2027. Aun asi, confirmar en octubre-2026 si aceptan 'equivalente' con experiencia propia en MR.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -956,7 +971,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -975,7 +990,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Las reservas del programa 2026-27 abren el 2026-10-07 a mediodia (hora britanica), con registro previo de interes desde el 2026-09-23: poner alarma, porque estos cursos se llenan</t>
+          <t>ACCION INMINENTE Y CON DOS FECHAS: crear o reactivar la cuenta de reservas desde el mediodia del 2026-09-23 (dentro de 9 dias) y reservar plaza el 2026-10-07 a mediodia hora del RU, cuando abren las reservas de todo el programa 2026/27.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1028,7 +1043,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Escribir a IBGworkshop@colorado.edu preguntando por la cuota 2027, la fecha de apertura de inscripcion, el plazo y si habra opcion virtual; vigilar la pagina cada semana porque la inscripcion suele abrirse sin previo aviso</t>
+          <t>La inscripcion 2027 AUN NO ESTA ABIERTA. Revisar colorado.edu/ibg/workshop-2027 a partir de noviembre-2026 (en ediciones previas abrio unos 3 meses antes) y reservar presupuesto propio de ~600 USD de cuota academica.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1069,7 +1084,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1088,7 +1103,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Reservar en cuanto abran las reservas el 2026-10-07 a mediodia; es la puerta de entrada obligatoria al curso avanzado de MR</t>
+          <t>ACCION INMINENTE: cuenta de reservas desde el 2026-09-23 a mediodia y reserva el 2026-10-07 a mediodia. Este va ANTES que T-0007, porque es su prerrequisito.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1123,8 +1138,19 @@
           <t>Curso corto</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2027-03-08</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>175</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>3</t>
@@ -1137,12 +1163,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Solo si sobra presupuesto y tiempo: va justo despues del MR introductorio (15-19 mar 2027), semana siguiente</t>
+          <t>Solo si sobran presupuesto y dias: encadenarlo con T-0003 (MR introductorio) la semana anterior, aprovechando un unico permiso.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/molecular-epidemiology/</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1198,14 @@
           <t>Curso corto</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2027-06-08</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>267</v>
+      </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
@@ -1186,7 +1219,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Abrir la ficha del curso cuando se publiquen cuota y programa, y decidir junto con el resto de la oferta de Bristol de 2027</t>
+          <t>Decidir en primavera-2027 junto con el resto de la oferta de Bristol; la ficha individual del curso aun no esta publicada, asi que la cuota se conocera al abrir reservas el 2026-10-07.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1272,7 +1305,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Abrir el portal qimrberghofer.turborecruit.com.au y filtrar por genetica/postdoc; si no hay nada, mandar el correo en frio de todas formas (es la pista mas calida del conjunto y no depende de que haya anuncio).</t>
+          <t>Mandar YA el correo en frio a Sarah Medland o a Lucia Colodro Conde sin esperar a ningun anuncio: esta confirmado que no lo va a haber a corto plazo y la conexion calida de su estancia en QIMR no depende de el.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1289,12 +1322,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L-0004</t>
+          <t>L-0006</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Generation R - genetica del sueno infantil</t>
+          <t>SGDP Centre / Statistical Genetics Unit</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1317,12 +1350,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Confirmar en Tier 1 el cargo y la sede actual de Kocevska (pagina de personal del NIN, grupo Van Someren, y buscador de investigadores de Erasmus MC) e identificar al PI senior de la linea de sueno infantil antes de escribir.</t>
+          <t>Escribir a Cathryn Lewis (Statistical Genetics Unit) planteando co-patrocinio de beca postdoc, dado que la unidad no publica vacantes propias.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://acamh.onlinelibrary.wiley.com/doi/10.1111/jcpp.13899</t>
+          <t>https://www.kcl.ac.uk/research/sgu</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1367,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L-0006</t>
+          <t>L-0012</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SGDP Centre / Statistical Genetics Unit</t>
+          <t>Grupo de genetica estadistica psiquiatrica de Wouter Peyrot (proyecto ERC PersonalRiskProfile)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1362,12 +1395,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Escribir a Cathryn Lewis (Statistical Genetics Unit) planteando co-patrocinio de beca postdoc, dado que la unidad no publica vacantes propias.</t>
+          <t>Escribir correo en frio a Peyrot antes de fin de 2026 presentando disponibilidad desde mediados de 2027 y pidiendo una videollamada de 20 minutos; en paralelo, localizar su direccion institucional exacta en pure.amsterdamumc.nl y revisar la bolsa de empleo de Amsterdam UMC por si sale la plaza del ERC.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://www.kcl.ac.uk/research/sgu</t>
+          <t>https://www.amsterdamumc.org/en/research/institutes/amsterdam-public-health/news/wouter-peyrot-awarded-erc-starting-grant-for-personalized-genetic-risk-profiles-in-psychiatry-1</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1412,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L-0012</t>
+          <t>L-0013</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Grupo de genetica estadistica psiquiatrica de Wouter Peyrot (proyecto ERC PersonalRiskProfile)</t>
+          <t>Grupo de Kelli Lehto, Instituto de Genomica (proyecto ERC AT-TENSION)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1407,12 +1440,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Escribir correo en frio a Peyrot antes de fin de 2026 presentando disponibilidad desde mediados de 2027 y pidiendo una videollamada de 20 minutos; en paralelo, localizar su direccion institucional exacta en pure.amsterdamumc.nl y revisar la bolsa de empleo de Amsterdam UMC por si sale la plaza del ERC.</t>
+          <t>Correo en frio a Kelli Lehto con CV y las dos fechas de disponibilidad; preguntar si AT-TENSION prevee contratar en 2027 y ofrecer la vertiente de fenotipado clinico. Confirmar antes su direccion institucional en la ficha de personal de ut.ee.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://www.amsterdamumc.org/en/research/institutes/amsterdam-public-health/news/wouter-peyrot-awarded-erc-starting-grant-for-personalized-genetic-risk-profiles-in-psychiatry-1</t>
+          <t>https://ut.ee/en/news/erc-grant-helps-explore-innovative-approaches-improve-diagnosis-adhd-adults</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1457,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L-0013</t>
+          <t>L-0014</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Grupo de Kelli Lehto, Instituto de Genomica (proyecto ERC AT-TENSION)</t>
+          <t>Grupo de Psiquiatria Infantil y Genetica del Comportamiento de Christel Middeldorp</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1452,12 +1485,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Correo en frio a Kelli Lehto con CV y las dos fechas de disponibilidad; preguntar si AT-TENSION prevee contratar en 2027 y ofrecer la vertiente de fenotipado clinico. Confirmar antes su direccion institucional en la ficha de personal de ut.ee.</t>
+          <t>Preparar un correo en frio con una propuesta de una pagina sobre genetica del sueno en primera infancia dentro de sus cohortes; antes, verificar en pure.amsterdamumc.nl su financiacion vigente y sus publicaciones de 2025-2026 sobre sueno.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://ut.ee/en/news/erc-grant-helps-explore-innovative-approaches-improve-diagnosis-adhd-adults</t>
+          <t>https://www.amsterdamumc.org/en/research/researchers/christel-middeldorp.htm</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1502,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L-0014</t>
+          <t>L-0020</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Grupo de Psiquiatria Infantil y Genetica del Comportamiento de Christel Middeldorp</t>
+          <t>KI Psychiatric Genomics Institute (KI-PGI)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1492,17 +1525,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Preparar un correo en frio con una propuesta de una pagina sobre genetica del sueno en primera infancia dentro de sus cohortes; antes, verificar en pure.amsterdamumc.nl su financiacion vigente y sus publicaciones de 2025-2026 sobre sueno.</t>
+          <t>Correo en frio a lu.yi@ki.se proponiendo co-solicitar MSCA o postdoc del Swedish Research Council con el KI-PGI como host; no esperar a que salga plaza.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://www.amsterdamumc.org/en/research/researchers/christel-middeldorp.htm</t>
+          <t>https://ki.se/en/meb/research/ki-psychiatric-genomics-institute/about-ki-pgi</t>
         </is>
       </c>
     </row>
@@ -1514,24 +1547,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>E-0011</t>
+          <t>L-0021</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BGA 2028 - 58th Annual Meeting of the Behavior Genetics Association</t>
+          <t>PsychGen Centre for Genetic Epidemiology and Mental Health</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Conference</t>
-        </is>
-      </c>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
@@ -1541,17 +1570,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Revisar la pagina de BGA Future Meetings en enero-2028 para fechas exactas y plazo de resumenes; apuntarla ya como objetivo post-tesis.</t>
+          <t>Confirmar la direccion de Havdahl en su ficha de fhi.no y escribirle con una propuesta de una pagina: sueno infantil en MoBa con diseno intrafamiliar. Preguntar por MSCA o postdoc del Research Council of Norway.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567675</t>
+          <t>https://www.fhi.no/en/me/the-psychgen-centre-for-genetic-epidemiology-and-mental-health/about-the-psychgen-centre/</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1592,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>E-0014</t>
+          <t>E-0011</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>XXXV Reunion Anual de la Sociedad Espanola de Sueno (SES 2027)</t>
+          <t>BGA 2028 - 58th Annual Meeting of the Behavior Genetics Association</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1585,22 +1614,22 @@
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Consultar congreso-ses.com/ses2027 en octubre-2026 para fechas exactas de marzo-2027, plazo de comunicaciones y cuota de residente; si cae en marzo, hay que pedir dias en el hospital con antelacion.</t>
+          <t>Revisar la pagina de BGA Future Meetings en enero-2028 para fechas exactas y plazo de resumenes; apuntarla ya como objetivo post-tesis.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://congreso-ses.com/ses2027/bienvenida</t>
+          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567675</t>
         </is>
       </c>
     </row>
@@ -1612,12 +1641,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>E-0015</t>
+          <t>E-0016</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jornada AEGH 2027 (Asociacion Espanola de Genetica Humana)</t>
+          <t>EMGM 2027 - 55a European Mathematical Genetics Meeting</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1627,34 +1656,185 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Congreso anual</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>La 54a edicion (Davos, 14-15 abr 2026) ya paso y la de 2027 sigue sin anfitrion. Vigilar sites.google.com/site/emgmhome a partir de noviembre-2026; si en enero-2027 sigue TBA, escribir a los organizadores de Davos 2026 (emgm2026.sciencesconf.org) preguntando por sede y fechas de 2027, que es justo lo que la propia web pide hacer.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/site/emgmhome/future-meetings</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>T-0011</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Genetic and Epigenetic Epidemiology (curso especializado del EEPE)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Curso especializado residencial</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>1575</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Revisar eepe.org en enero-2027: la edicion 2027 se anunciara con el curso residencial (mediados de junio a principios de julio) y los especializados la semana siguiente. Compararla entonces con el MR de Bristol de marzo-2027, que cubre parte del mismo terreno mas barato.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://www.eepe.org/courses-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>E-0014</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>XXXV Reunion Anual de la Sociedad Espanola de Sueno (SES 2027)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>XS</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Mirar aegh.org/congresos-y-jornadas-aegh a finales de 2026 para ver que sede gano la candidatura y que fechas tiene la Jornada 2027.</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Consultar congreso-ses.com/ses2027 en octubre-2026 para fechas exactas de marzo-2027, plazo de comunicaciones y cuota de residente; si cae en marzo, hay que pedir dias en el hospital con antelacion.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://congreso-ses.com/ses2027/bienvenida</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>E-0015</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Jornada AEGH 2027 (Asociacion Espanola de Genetica Humana)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Volver a aegh.org/congresos-y-jornadas-aegh en diciembre-2026 o enero-2027 para ver sede y fechas adjudicadas.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>https://aegh.org/congresos-y-jornadas-aegh/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L23"/>
+  <autoFilter ref="A1:L26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1665,7 +1845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J137"/>
+  <dimension ref="A1:J148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8792,8 +8972,580 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SRC-0137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PGC - indice de working groups (lista de chairs por subpagina)</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://pgc.unc.edu/for-researchers/working-groups/</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Mapa directo de quien dirige hoy el GWAS psiquiatrico: 17 working groups, cada subpagina nombra a sus chairs con institucion y se actualiza cuando hay relevo (la de Cross Disorder dice literalmente 'stepped in as co-chairs in 2026'). De aqui salieron Yi Lu, Barbara Franke, Anders Borglum, Fabian Streit y Laramie Duncan.</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Abrir cada subpagina y leer el bloque de liderazgo del inicio. Quedan 11 sin abrir: esquizofrenia, bipolar, TEPT, TOC/Tourette, sustancias, suicidio, alimentarios, Alzheimer, CNV, genomica funcional, pedigree sequencing.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Fuente nueva del 2026-09-14 y la mas rentable de la pasada. Material ya cribado para la siguiente rotacion sin repetir angulo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SRC-0138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>PsychGen Centre (FHI) - Latest research</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.fhi.no/en/me/the-psychgen-centre-for-genetic-epidemiology-and-mental-health/latest-research/</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Resultados nuevos sobre la cohorte MoBa con los nombres de quien firma; util para detectar a los junior del centro que se independizan y montan grupo propio.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Seccion 'Latest findings'</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Alta del 2026-09-14, junto con la ficha del grupo L-0020.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>SRC-0139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Sleep Research Society - liderazgo y comites</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/about/leadership/</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Junta y comites de la SRS.</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Pagina de liderazgo</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>BAJA</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Alta del 2026-09-14 CON ADVERTENCIA: no se encontro ningun comite de genetica dentro de la SRS y la junta 2026-2027 (Goldschmied, Saletin, Reynolds) es de sueno conductual/clinico, no de genetica. Rendimiento bajo previsible para su perfil: no gastar mucho aqui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>SRC-0140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>EMGM - European Mathematical Genetics Meeting, futuras sedes</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/site/emgmhome/future-meetings</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Sede y fechas de las proximas ediciones de la reunion europea anual de genetica matematica y estadistica: el congreso pequeno y barato que mejor describe su linea 1.</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Seccion 'Future Meetings'; la de 'past-meetings' da el historico de sedes y ayuda a estimar el pais siguiente.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Fuente nueva del 2026-09-14, origen del E-0016. Consulta que la encontro: 'European Mathematical Genetics Meeting EMGM 2027 statistical genetics'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>SRC-0141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>AEGH - adjudicacion de sede de la Jornada 2027</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://aegh.org/jornada-aegh-2027-presentacion-de-candidaturas/</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Sede y fechas adjudicadas de la Jornada AEGH 2027 (E-0015). Mas precisa que el indice general de congresos de la AEGH.</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Pagina de presentacion de candidaturas</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Alta del 2026-09-14. El plazo de candidaturas cerro a finales de oct-2025 y la adjudicacion sigue sin publicarse: revisar en dic-2026 o ene-2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>SRC-0142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>EEPE - catalogo anual de cursos de epidemiologia (Toscana)</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://www.eepe.org/courses-2/</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Catalogo anual de la escuela de epidemiologia de la Toscana: curso residencial de 3 semanas mas modulos especializados de 5 dias, con profesorado nominal (MRC IEU de Bristol) y cuotas exactas.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Seccion 'Specialised courses' y tabla de fees en eepe.org/registration-2-2/</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Fuente nueva del 2026-09-14, origen de T-0011. La edicion 2027 se anuncia hacia enero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>SRC-0143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SMARTbiomed (Aarhus) - escuela de verano</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://smartbiomed.dk/news-and-events/summer-school</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Escuela de verano danesa que combina genetica estadistica, inferencia causal y machine learning en Python, mas desarrollo de paquetes en R; la pagina documenta modulos, cuota en DKK y plazo de la ultima edicion.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Pagina de la summer school</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Fuente nueva del 2026-09-14, origen de T-0012. No hay edicion posterior a 2025 anunciada: contacto smartbiomed_info@au.dk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SRC-0144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Bristol Medical School - criterios de voucher packs y calendario de reservas</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/fees/</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Criterios completos de los voucher packs (quien tiene 50% o gratuidad) y las fechas de apertura de cuentas y reservas. Es lo que permite descartar financiacion para ella con certeza.</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Tabla de fees y criterios de elegibilidad</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Alta del 2026-09-14. AVISO DE RUTA: el catalogo cambio de direccion, bristol.ac.uk/medical-school/study/short-courses/ redirige a /short-courses-and-cpd/short-courses/courses/ -- usar la nueva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>SRC-0145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Aarhus University - portal de vacantes Emply</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://au.career.emply.com/en/vacant-positions</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Unico listado real de vacantes de toda Aarhus, incluidas las de QGG (L-0003), ahora que qgg.au.dk/en/vacancies e international.au.dk estan caidos o bloqueados.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Listado de vacant positions</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Alta del 2026-09-14. BLOQUEO: requiere navegador real, el lector automatico rebota al dominio generico del proveedor. international.au.dk devuelve 403.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>SRC-0146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Grotzinger - web propia del laboratorio (p-badger-lab)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://www.p-badger-lab.com/</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Web propia del laboratorio de Andrew Grotzinger (L-0007), que la ficha no conocia. Hoy no tiene seccion de contratacion, pero es donde apareceria.</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Web del laboratorio</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>MEDIA</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Alta del 2026-09-14; sustituye a la URL que se daba por rota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>SRC-0147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>NIH - codigo de actividad T32 (elegibilidad)</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://grants.nih.gov/funding/activity-codes/T32</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Referencia de elegibilidad, no portal de empleo: las T32 exigen ciudadania estadounidense, nacionalidad no ciudadana o residencia permanente legal. Calibra de golpe toda la rama estadounidense.</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Activity code T32 y NIH Grants Policy Statement 11.2.2</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Alta del 2026-09-14. REGLA PRACTICA: cualquier plaza descrita como T32, NRSA o 'training grant' esta fuera de su alcance y no admite patrocinio de visado.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J137"/>
+  <autoFilter ref="A1:J148"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8924,7 +9676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -17185,8 +17937,2192 @@
         </is>
       </c>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>L-0020</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>KI Psychiatric Genomics Institute (KI-PGI)</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Alta por descubrimiento (rama 1, angulo working groups del PGC). Fit 5, VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://ki.se/en/meb/research/ki-psychiatric-genomics-institute/about-ki-pgi</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>L-0021</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>PsychGen Centre for Genetic Epidemiology and Mental Health</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Alta por descubrimiento (rama 1, angulo working groups del PGC). Fit 5, VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://www.fhi.no/en/me/the-psychgen-centre-for-genetic-epidemiology-and-mental-health/about-the-psychgen-centre/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>L-0022</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Molecular Psychiatry research group (Cognitive Neuroscience / Human Genetics)</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Alta por descubrimiento (rama 1, angulo working groups del PGC). Fit 4, VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://www.radboudumc.nl/en/people/barbara-franke</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>L-0023</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>iPSYCH - The Lundbeck Foundation Initiative for Integrative Psychiatric Research</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Alta por descubrimiento (rama 1, angulo working groups del PGC). Fit 4, VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://ipsych.dk/en/about-ipsych</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>L-0024</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Department of Genetic Epidemiology in Psychiatry (grupo de Fabian Streit)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Alta por descubrimiento (rama 1, angulo working groups del PGC). Fit 4, UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://pgc.unc.edu/for-researchers/working-groups/mdd/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>L-0025</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>PGC Cross-Population Analyses Working Group (grupo de Laramie Duncan)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Alta por descubrimiento (rama 1, angulo working groups del PGC). Fit 3, LIKELY.</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://pgc.unc.edu/for-researchers/working-groups/cross-population-analyses-working-group/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>E-0016</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>EMGM 2027 - 55a European Mathematical Genetics Meeting</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Alta por descubrimiento (rama 2). Fit 5, VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/site/emgmhome/future-meetings</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>E-0017</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>GAW 2027 - Genetic Analysis Workshop (convocatoria de ideas abierta)</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Alta por descubrimiento (rama 2). Fit 4, UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>E-0018</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>XXIX Congreso Nacional de Psiquiatria 2026</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Alta por descubrimiento (rama 2). Fit 2, LIKELY.</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://congresonacionaldepsiquiatria.es/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>T-0011</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Genetic and Epigenetic Epidemiology (curso especializado del EEPE)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Alta por descubrimiento (rama 3). Fit 4, VERIFIED.</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://www.eepe.org/courses-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>T-0012</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>SMARTbiomed Summer School: Causal inference, statistical genetics and machine learning in common disease epidemiology and biology</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Alta por descubrimiento (rama 3). Fit 4, UNVERIFIED.</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://smartbiomed.dk/news-and-events/summer-school</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>T-0013</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Polygenic scores and the PGS Catalog</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Alta por descubrimiento (rama 3). Fit 2, LIKELY.</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://www.ebi.ac.uk/training/online/courses/polygenic-scores-pgs-catalog/</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>L-0011</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Population Genetics of Human Communication (PGHC) - Departamento de Language &amp; Genetics, Max Planck</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Plaza reconfirmada abierta, pero se anade la reserva de calendario: piden doctorado en mano o inminente y su defensa es feb-2028. El correo antes del 8-oct cambia de objetivo: posicionarse para la ronda 2027-2028.</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://www.mpi.nl/career-education/vacancies/vacancy/3-year-postdoctoral-research-scientist-position-statistical-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>L-0004</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Generation R - genetica del sueno infantil</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>CORRECCION DE CALADO: Kocevska no es jefa de grupo y no puede contratar. PI reasignado a Henning Tiemeier (Generation R). Fit baja de 5 a 4 por estructura, no por competencia.</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://hsph.harvard.edu/profile/henning-tiemeier/</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>L-0007</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Grotzinger Lab (genomica psiquiatrica multivariante)</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>URL reparada (no estaba rota) y via T32 descartada: el NIH exige ciudadania o residencia permanente. Solo sirve contrato con fondos de proyecto. Aviso: figura como Adjunct Professor.</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://www.colorado.edu/ibg/andrew-grotzinger</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>L-0010</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Grupo de Neurogenetica (Depto de Genetica, UB)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>URL rota sustituida por la ficha institucional de la UB (sira.ub.edu). Sigue UNVERIFIED: la ficha solo renderiza con JavaScript.</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://sira.ub.edu/fitxes/Biologia/es/bcormand.ub.edu</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>L-0003</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Center for Quantitative Genetics and Genomics (grupo Speed)</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Sin nueva ronda. La plaza caducada tenia ademas incorporacion el 1-oct-2026. Localizado el portal real de vacantes de Aarhus (Emply).</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/12856703/</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>L-0002</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Psychiatric Genetics Group</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Resuelto el pendiente: abierto el ATS propio de QIMR, ninguna plaza de genetica en todo el instituto. La unica via es el correo en frio, ya sin esperar anuncio.</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>L-0006</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>SGDP Centre / Statistical Genetics Unit</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Correo institucional de Cathryn Lewis localizado en la pagina de la unidad. Sin vacantes ni cambios de personal.</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/research/sgu</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>L-0001</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Complex Trait Genetics (CTG) Lab</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Sin plazas cientificas. Aviso de fiabilidad: la pagina no se actualiza desde 2025-2026, no es canal de vigilancia fiable.</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://cncr.nl/ctg/</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>L-0008</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Saxena Lab (genomica del sueno y circadiana)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Sin cambios: la pagina de empleo sigue diciendo 'Coming Soon!'.</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://saxena.mgh.harvard.edu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>E-0001</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Inscripcion confirmada abierta a 15 dias del congreso, sin fecha de cierre. Cuotas siguen UNVERIFIED tras segundo intento por otra puerta: escribir a info@ispg.net.</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://ispg.net/wcpg-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>E-0002</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>ASHG 2026 Annual Meeting</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>RELOJ VIVO: tarifa anticipada abierta hasta el 15-sep-2026 17:00 ET. Hacerse socia antes de inscribirse ahorra ~313 EUR. Deadline fijado en esa fecha.</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://ashgmeeting.ashg.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>E-0003</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>ESHG Conference 2027 (European Human Genetics Conference)</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Plazo de resumenes verificado en Tier 1: 2027-02-04 23:59 CET, congreso 12-15 jun 2027 en Rotterdam. Posible formato hibrido (Tier 2, sin confirmar).</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://2027.eshg.org/abstracts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>E-0004</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Behavior Genetics Association (BGA) 2027 Annual Meeting</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Sin cambios: plazo de resumenes, cuotas y becas siguen TBA. Program chair es Sarah Medland, la PI de L-0002.</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://bga.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>E-0005</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>IGES 2026 Annual Meeting &amp; Education Workshop</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>RELOJ VIVO no detectado hasta ahora: la tarifa early cierra el 19-sep-2026. Cuotas completas verificadas. Cae justo antes de ASHG y en la misma region: un vuelo, dos congresos.</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/2026-annual-meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>E-0006</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>SOBP 2027 Annual Meeting</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>No verificable: sobp.org/meetings no publica fechas y /future-meetings da 404. Fechas 2027 siguen apoyadas solo en fuentes secundarias.</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://sobp.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>E-0008</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>SLEEP 2027 (APSS Annual Meeting)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>CONFLICTO DE FECHAS RESUELTO: el 5-jun era el inicio de los cursos de posgrado, no del congreso. Se adopta 6-9 jun 2027.</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://www.sleepmeeting.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>E-0011</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>BGA 2028 - 58th Annual Meeting of the Behavior Genetics Association</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Sin cambios: 2028 en Tartu, fecha TBA.</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567675</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>E-0015</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Jornada AEGH 2027 (Asociacion Espanola de Genetica Humana)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Sin cambios: la AEGH sigue sin publicar sede ni fechas de la Jornada 2027. Confirmado que 2027 es ano de Jornada.</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://aegh.org/congresos-y-jornadas-aegh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>T-0001</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Fechas 2027 confirmadas en Tier 1 (1-5 mar). La inscripcion AUN no esta abierta y no hay cuota publicada. El curso de marzo se imparte cada tres anos: si se pierde 2027, la siguiente es 2030.</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://www.colorado.edu/ibg/workshop-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>T-0002</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Genetic Epidemiology (short course)</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Fechas verificadas y, sobre todo, calendario de reservas confirmado: cuenta desde el 23-sep-2026, reservas el 7-oct-2026 a mediodia. Sin beca aplicable para ella.</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>T-0003</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Mendelian Randomization (short course)</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Fechas verificadas (15-19 mar 2027). Sin beca aplicable. Es prerrequisito de T-0007.</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>T-0007</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Advanced Mendelian Randomization</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Cuota confirmada (630 GBP) y prerrequisito explicito: exige el curso introductorio de MR. No reservable para 2026; objetivo real, nov-2027.</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/advanced-mr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>T-0008</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Machine Learning with Omics Data</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Fechas verificadas en el catalogo. La ficha del curso aun no existe (404 en dos rutas): la cuota se conocera el 7-oct-2026.</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>T-0009</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Molecular Epidemiology</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Cuota confirmada (750 GBP). Detalle de calendario util: va la semana siguiente al MR introductorio, encadenables con un solo permiso.</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/molecular-epidemiology/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>T-0004</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Genetic Analysis of Population-based Association Studies</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Sin edicion 2026 ni 2027 en el catalogo de Wellcome. Sigue en vigilancia; revisar en enero-2027.</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://coursesandconferences.wellcomeconnectingscience.org/event/genetic-analysis-of-population-based-association-studies-20240902/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>T-0005</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>CAJAL Course: Neurobiology of Sleep</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Confirmado CERRADO: el listado de CAJAL no llega mas alla de diciembre de 2026, sin edicion 2027 de ningun curso.</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://cajal-training.org/courses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>T-0006</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Statistical Analysis of Genome Scale Data</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Sin edicion 2027 en CSHL. Revisar en primavera-2027.</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://meetings.cshl.edu/courses.aspx?course=C-DATA</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>T-0010</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>From Genetic Variants to Risk Prediction (UniTartu Summer School)</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>CORRECCION: la fila no tenia fechas y parecia viva; era la edicion 2026, ya celebrada, con plazo cerrado el 20-abr-2026. Marcada CLOSED.</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://ut.ee/en/content/genetic-variants-risk-prediction</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>SRC-0137</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>PGC - indice de working groups (lista de chairs por subpagina)</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Nueva fuente de vigilancia.</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://pgc.unc.edu/for-researchers/working-groups/</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>SRC-0138</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>PsychGen Centre (FHI) - Latest research</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Nueva fuente de vigilancia.</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://www.fhi.no/en/me/the-psychgen-centre-for-genetic-epidemiology-and-mental-health/latest-research/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>SRC-0139</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Sleep Research Society - liderazgo y comites</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Nueva fuente de vigilancia.</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/about/leadership/</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>SRC-0140</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>EMGM - European Mathematical Genetics Meeting, futuras sedes</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Nueva fuente de vigilancia.</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/site/emgmhome/future-meetings</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>SRC-0141</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>AEGH - adjudicacion de sede de la Jornada 2027</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Nueva fuente de vigilancia.</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://aegh.org/jornada-aegh-2027-presentacion-de-candidaturas/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>SRC-0142</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>EEPE - catalogo anual de cursos de epidemiologia (Toscana)</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Nueva fuente de vigilancia.</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://www.eepe.org/courses-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>SRC-0143</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>SMARTbiomed (Aarhus) - escuela de verano</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Nueva fuente de vigilancia.</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://smartbiomed.dk/news-and-events/summer-school</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>SRC-0144</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Bristol Medical School - criterios de voucher packs y calendario de reservas</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Nueva fuente de vigilancia.</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/fees/</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>SRC-0145</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Aarhus University - portal de vacantes Emply</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Nueva fuente de vigilancia.</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://au.career.emply.com/en/vacant-positions</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>SRC-0146</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Grotzinger - web propia del laboratorio (p-badger-lab)</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Nueva fuente de vigilancia.</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://www.p-badger-lab.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>SRC-0147</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>NIH - codigo de actividad T32 (elegibilidad)</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Nueva fuente de vigilancia.</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://grants.nih.gov/funding/activity-codes/T32</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>SUB-0017</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Bristol Medical School - cuenta de reservas de cursos cortos</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Propuesta de alta, Status TODO. No es un boletin sino la puerta de entrada, y tiene dos relojes: la cuenta se crea o reactiva desde el mediodia del 2026-09-23 y las reservas del programa 2026/27 abren el 2026-10-07 a mediodia hora del RU. Sin cuenta creada antes, no se puede reservar el dia que abren, y estos cursos se llenan.</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H200"/>
+  <autoFilter ref="A1:H252"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18375,7 +21311,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-452</v>
+        <v>-453</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -18521,7 +21457,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -18663,7 +21599,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-135</v>
+        <v>-136</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -18928,7 +21864,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-206</v>
+        <v>-207</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -19320,7 +22256,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -19458,7 +22394,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -19592,7 +22528,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -19722,7 +22658,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -19852,7 +22788,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -20109,7 +23045,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -20815,7 +23751,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -21358,7 +24294,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -21496,7 +24432,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -21638,7 +24574,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -21768,7 +24704,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -21902,7 +24838,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -22036,7 +24972,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -23740,7 +26676,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -25548,7 +28484,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -25688,7 +28624,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -26969,7 +29905,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -27492,7 +30428,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -28265,7 +31201,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -29280,7 +32216,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -32542,7 +35478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -32798,7 +35734,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -32808,7 +35744,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -32829,7 +35765,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Abri yo misma cncr.nl/ctg/jobs/ el 2026-09-07 (Tier 1): sin vacantes cientificas listadas.</t>
+          <t>cncr.nl/ctg/jobs/ reabierta el 2026-09-14: sigue sin plazas cientificas, solo practicas de grado y master. AVISO DE FIABILIDAD DE LA FUENTE: la pagina no se ha tocado y mantiene los plazos de 2025-2026, senal de que NO es un canal fiable de vigilancia semanal -- la ausencia de plaza aqui no prueba que el grupo no contrate.</t>
         </is>
       </c>
     </row>
@@ -32876,7 +35812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Revisado qimrb.edu.au/careers el 2026-09-07 (Tier 1): la pagina institucional NO lista vacantes, deriva todo al portal de seleccion qimrberghofer.turborecruit.com.au. No pude abrir ese portal esta semana, asi que no hay confirmacion ni desmentido de plazas en el grupo de Medland. La via del correo en frio a su antiguo anfitrion sigue siendo la principal.</t>
+          <t>RESUELTO lo que quedo pendiente el 2026-09-07: abierto el portal de seleccion real de QIMR (ATS propio del instituto) y NO hay ninguna plaza de genetica. El instituto entero tiene UNA sola vacante publicada hoy, 'Research Officer / Senior Research Officer' (ref. BV000085), un postdoc de datos sanitarios vinculados para politica de prevencion cardiovascular, sin relacion con genetica psiquiatrica ni con el grupo de Medland. Confirmado: no hay anuncio al que optar y la unica via es el correo en frio.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -32926,7 +35862,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -32936,7 +35872,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -32946,7 +35882,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Abrir el portal qimrberghofer.turborecruit.com.au y filtrar por genetica/postdoc; si no hay nada, mandar el correo en frio de todas formas (es la pista mas calida del conjunto y no depende de que haya anuncio).</t>
+          <t>Mandar YA el correo en frio a Sarah Medland o a Lucia Colodro Conde sin esperar a ningun anuncio: esta confirmado que no lo va a haber a corto plazo y la conexion calida de su estancia en QIMR no depende de el.</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -32961,7 +35897,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Abri qimrb.edu.au/careers yo misma el 2026-09-07; de ahi sale la direccion del portal de seleccion, que no llegue a abrir.</t>
+          <t>qimrberghofer.turborecruit.com.au abierto el 2026-09-14 (Tier 1, el ATS propio del instituto; la pagina institucional de careers solo redirige aqui): una unica vacante listada. Sube de VERIFIED parcial a VERIFIED pleno en cuanto al estado de vacantes.</t>
         </is>
       </c>
     </row>
@@ -33008,7 +35944,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OJO, DATO CADUCADO CORREGIDO: el plazo del 1-may-2026 YA PASO. El anuncio sigue apareciendo indexado en la pagina oficial de vacantes de Aarhus (international.au.dk, 'Postdoc position in method development in human statistical genetics, with a focus on classification of complex diseases'), con inicio 1-oct-2026 o lo antes posible y duracion de 2 anos, pero NO pude abrir la pagina de vacantes del centro (qgg.au.dk/en/vacancies devuelve 404), asi que no se si sigue viva o es un residuo. Hay que preguntarlo directamente.</t>
+          <t>Sin nueva ronda localizada el 2026-09-14. El anuncio de Nature Careers sigue siendo el mismo, con plazo 1-may-2026 ya caducado E INICIO PREVISTO EL 1-OCT-2026, o sea dentro de dos semanas: si la plaza se cubrio, ya esta ocupada. Las unicas vacantes de QGG visibles esta semana son de mejora genetica vegetal y animal (avena ecologica, cria sostenible, seleccion genomica en trucha), ninguna de genetica humana.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -33018,7 +35954,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Correo directo a doug@qgg.au.dk - gancho: su genetica estadistica aplicada (PLINK/R) mas la mirada clinica/MD sobre heterogeneidad de enfermedad, que es justo el objeto de su ERC. Como el plazo publicado ya paso, el correo debe preguntar explicitamente si la plaza sigue abierta y si habra nuevas incorporaciones al proyecto ERC en 2027-2028.</t>
+          <t>Sin cambios de destinatario pero con mas urgencia: correo directo a doug@qgg.au.dk. Con la fecha de incorporacion encima, el estado real de la plaza solo lo puede decir el.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -33053,12 +35989,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -33068,7 +36004,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -33078,7 +36014,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Escribir a doug@qgg.au.dk preguntando por el estado de la plaza y por futuras rondas de la ERC CoG, indicando su disponibilidad (mediados de 2027 / feb-2028).</t>
+          <t>Escribir a doug@qgg.au.dk esta misma semana preguntando si la plaza se cubrio y si la ERC Consolidator preve nuevas incorporaciones en 2027-2028.</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -33093,7 +36029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>El anuncio original de Nature Careers se abrio en la pasada anterior. Esta semana: qgg.au.dk/en/vacancies da 404 y la existencia continuada del anuncio en international.au.dk mas el detalle de la ERC Consolidator vienen de resultados de busqueda, no de abrir la pagina - por eso baja a LIKELY.</t>
+          <t>DATO NUEVO util: el portal de vacantes real de Aarhus es au.career.emply.com/en/vacant-positions (sistema Emply). No se pudo leer automaticamente (redirige al dominio generico del proveedor) e international.au.dk devolvio 403 en el unico intento, asi que la ausencia de plaza NO esta verificada: es ausencia de evidencia, no evidencia de ausencia. qgg.au.dk/en/vacancies sigue sin servir.</t>
         </is>
       </c>
     </row>
@@ -33110,12 +36046,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Desana (Desi) Kocevska - ATENCION, CORRECCION PENDIENTE DE CONFIRMAR: las fuentes secundarias la describen como investigadora POSTDOCTORAL en el Netherlands Institute for Neuroscience (Amsterdam), grupo Sleep &amp; Cognition de Eus van Someren, con afiliacion secundaria a Erasmus MC (Psiquiatria Infantil y del Adolescente). Si es postdoc y no jefa de grupo, NO puede contratar: seria una puerta de entrada y una posible colaboradora, no la PI que ofrece la plaza.</t>
+          <t>Henning Tiemeier (PI senior de Generation R). CORRECCION: Desana Kocevska NO es jefa de grupo y no puede contratar; queda como contacto cientifico secundario.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Erasmus MC University Medical Center</t>
+          <t>Erasmus MC, Departamento de Psiquiatria Infantil y del Adolescente (Sophia) / estudio Generation R; Tiemeier tiene ademas catedra en Harvard T.H. Chan School of Public Health</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -33140,7 +36076,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>desconocido - y ademas la premisa de la fila esta en duda. No hay anuncio. Antes de tratarla como grupo contratante hay que averiguar quien es el PI senior con capacidad de contratar en la linea de sueno infantil (dentro de Generation R / Erasmus MC, o el grupo de Van Someren en el NIN).</t>
+          <t>Ninguna plaza anunciada. La via es el correo en frio al PI senior, no a Kocevska.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -33150,7 +36086,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Correo en frio a Kocevska como CONTACTO CIENTIFICO, no como jefa de grupo - gancho: su review en revision en Journal of Sleep Research encaja casi exactamente con el articulo de JCPP 2024 de Kocevska. Pedirle orientacion sobre quien lidera la linea de genetica del sueno pediatrico en Rotterdam/Amsterdam y si ve encaje para una postdoc; ese correo cuesta poco y puede abrir la puerta al PI real.</t>
+          <t>Correo en frio a Henning Tiemeier como PI de Generation R, proponiendo genetica del sueno en primera infancia sobre Generation R / Generation R Next y ofreciendo el pipeline GWAS-PRS mas la mirada clinica. Su direccion institucional NO esta verificada: sacarla de la ficha de Erasmus MC o de Pure antes de escribir. Kocevska baja a contacto secundario opcional, solo para orientacion.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -33160,12 +36096,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>El solapamiento cientifico mas raro del conjunto y por eso mantengo el 5: su nicho exacto de linea 3 (genetica del sueno infantil) ejecutado con metodos PRS de linea 1/2, en un entorno UE sin visado y sobre una infraestructura de cohorte de nacimiento enorme (Generation R). Muy pocos grupos en el mundo hacen sueno pediatrico mas genetica y este es uno. PERO el encaje estructural es peor de lo que decia esta ficha: Kocevska parece ser postdoc, no jefa de grupo, asi que el primer acercamiento no debe pedirle una plaza sino conocimiento y contacto - citar su review de sueno, nombrar el articulo de JCPP 2024, proponer extender el trabajo de PRS a fenotipos de sueno mas tempranos (lactantes) que ella conoce de su revision sistematica, y preguntar quien dirige esa linea y si habria via para una postdoc o para co-solicitar una beca.</t>
+          <t>Baja de 5 a 4, y el motivo NO es competencia sino estructura: el 5 se sostenia sobre la premisa de que Kocevska dirigia una linea contratable de genetica del sueno infantil, y esa premisa es falsa. Lo que queda sigue siendo valioso y raro: la cohorte de nacimiento Generation R, con fenotipado de sueno repetido desde la lactancia y PRS ya aplicados, en un entorno UE sin visado -- literalmente el sustrato de su linea 3 ejecutado con los metodos de su linea 1. Pero la persona con experiencia especifica en genetica del sueno pediatrico dentro de esa cohorte ya no es localizable alli, asi que ella entraria a CONSTRUIR esa linea con un PI cuyo foco declarado es la epidemiologia psiquiatrica del desarrollo en general y no el sueno. Eso es mas trabajo de venta y mas riesgo de que el proyecto todavia no exista. La accion correcta no cambia de destino, cambia de destinatario.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -33185,12 +36121,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -33200,7 +36136,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -33210,7 +36146,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Confirmar en Tier 1 el cargo y la sede actual de Kocevska (pagina de personal del NIN, grupo Van Someren, y buscador de investigadores de Erasmus MC) e identificar al PI senior de la linea de sueno infantil antes de escribir.</t>
+          <t>Localizar la direccion institucional de Tiemeier en Erasmus MC o Pure y escribirle con una propuesta de una pagina sobre determinantes geneticos del sueno en los primeros anos dentro de Generation R. NO escribir a Kocevska como si fuera PI.</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -33220,12 +36156,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://acamh.onlinelibrary.wiley.com/doi/10.1111/jcpp.13899</t>
+          <t>https://hsph.harvard.edu/profile/henning-tiemeier/</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Intentado el 2026-09-07: erasmusmc.nl/en/research/researchers/kocevska-desana devuelve 404 y no aparece ficha propia en nin.nl. Solo fuentes secundarias (ResearchGate la da como postdoc en el NIN / grupo Van Someren, articulos con doble afiliacion). Por eso baja de LIKELY a UNVERIFIED: el dato de 'grupo con PI propia' que daba esta fila NO esta sostenido.</t>
+          <t>Tier 1 abierto el 2026-09-14: perfil oficial de Harvard Chan, que confirma su catedra de Epidemiologia Psiquiatrica en Erasmus MC y su liderazgo de Generation R. Salvedad honesta: ese perfil NO nombra el sueno entre sus temas; el vinculo con la linea de sueno de Generation R se deduce de su coautoria en Kocevska 2024, Koopman-Verhoeff 2020 y Mulder 2019 (JCPP), es decir del registro de publicaciones, no de una declaracion institucional -- por eso LIKELY. La URL apunta a Harvard porque no hay ficha suya viva verificada en erasmusmc.nl. Ademas: Kocevska NO figura entre los 28 miembros listados del grupo Sleep &amp; Cognition de Van Someren en el NIN (Tier 1), asi que su situacion actual esta sin confirmar en ningun sitio.</t>
         </is>
       </c>
     </row>
@@ -33414,7 +36350,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Correo en frio a Lewis (Statistical Genetics Unit) o Breen - gancho: geneticista estadistica (PLINK/R) con formacion clinica MD, interesada en PRS de trastornos del animo; su review de depresion + trabajo en revision son relevantes</t>
+          <t>DATO NUEVO: direccion de correo publicada en la propia pagina de la unidad, cathryn.lewis@kcl.ac.uk. Ya no hace falta buscarla antes de escribir.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -33454,7 +36390,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -33464,7 +36400,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -33489,7 +36425,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Abri yo misma kcl.ac.uk/research/sgu el 2026-09-07 (Tier 1): confirma a Lewis al frente de la Statistical Genetics Unit y su cargo de Head of School of Mental Health &amp; Psychological Sciences. Gerome Breen NO aparece en esa pagina concreta - su vinculo al SGDP viene de otras fuentes y queda sin reconfirmar.</t>
+          <t>kcl.ac.uk/research/sgu reabierta el 2026-09-14 (Tier 1): sigue sin seccion de vacantes, sin noticias ni cambios de personal fechados en 2026, y confirma a Lewis al frente con su correo institucional.</t>
         </is>
       </c>
     </row>
@@ -33536,7 +36472,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Revisada la pagina de plazas del IBG (colorado.edu/ibg/join-ibg/positions) el 2026-09-07: no hay postdoc especifico del laboratorio de Grotzinger. Lo que hay es una beca postdoctoral del programa de formacion NIMH T32 y la mencion de tres programas de formacion federales (NIMH, NIDA, NIA) que financian postdocs. AVISO IMPORTANTE: las becas T32 del NIH suelen exigir ciudadania o residencia permanente estadounidense - hay que confirmarlo, porque si es asi esa via le queda cerrada y solo le sirve un postdoc pagado con fondos de proyecto. La pagina ademas esta desactualizada (mantiene un anuncio de profesorado con plazo de dic-2024).</t>
+          <t>Sin plaza propia del laboratorio. La via de FORMACION del IBG queda CERRADA para ella: las becas T32 (NRSA institucional del NIH) exigen ciudadania estadounidense, nacionalidad no ciudadana o residencia permanente legal en el momento de la concesion. Es requisito de elegibilidad del NIH, no una preferencia del centro, y no admite patrocinio de visado. Solo le sirve un contrato pagado con fondos de proyecto del propio laboratorio.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -33546,7 +36482,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Correo en frio a Grotzinger - gancho: geneticista estadistica MD+PhD que quiere aplicar Genomic SEM a fenotipos psiquiatricos transdiagnosticos / de sueno; los PIs junior responden mas a correos en frio y suelen estar montando equipo</t>
+          <t>Correo en frio a Andrew.Grotzinger@colorado.edu (direccion confirmada en su ficha oficial del IBG) con la pregunta de financiacion POR DELANTE: si tiene fondos de proyecto que permitan contratar a alguien sin ciudadania ni residencia permanente estadounidense, porque la via T32 esta descartada. De paso, pedirle que confirme su cargo actual.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -33581,12 +36517,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -33596,7 +36532,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -33606,7 +36542,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Correo en frio directo a Andrew.Grotzinger@colorado.edu (correo publicado en fuentes del IBG) proponiendo una aplicacion concreta de Genomic SEM; preguntar de paso si sus fondos de proyecto permiten contratar a alguien sin ciudadania estadounidense, porque la via T32 probablemente no.</t>
+          <t>Escribir a Grotzinger preguntando primero por la financiacion (fondos de proyecto vs T32) y por su cargo actual. Si la respuesta es que solo hay T32, la puerta se cierra y conviene saberlo antes de invertir en la candidatura.</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -33621,7 +36557,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>CORRECCION: la URL que traia esta ficha (colorado.edu/behavioral-genetics/andrew-grotzinger) devuelve 404 el 2026-09-07, igual que colorado.edu/lab/grotzinger. La nueva URL sale de resultados de busqueda y aun no la he abierto. Si abri (Tier 1) la pagina de plazas del IBG, de donde salen los datos de T32 y programas de formacion. Sigue en LIKELY porque no he abierto ninguna pagina propia del laboratorio.</t>
+          <t>CORRECCION: la URL que la ficha daba por rota SI funciona; abierta el 2026-09-14 (Tier 1), de ahi sube a VERIFIED. De ella salen su correo y la web nueva del laboratorio, p-badger-lab.com, tambien abierta (Tier 1): describe psiquiatria, neurodesarrollo, salud inmune y envejecimiento cognitivo, pero NO tiene seccion ni texto de contratacion. La regla de elegibilidad T32 procede de la documentacion oficial del NIH (grants.nih.gov, activity code T32, y NIH Grants Policy Statement 11.2.2), Tier 1. AVISO: su ficha del IBG lo lista como Adjunct Professor; un cargo adjunto puede ser afiliacion de cortesia y suele implicar menor capacidad de contratar con fondos propios -- preguntarselo.</t>
         </is>
       </c>
     </row>
@@ -33718,7 +36654,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -33728,12 +36664,12 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -33753,7 +36689,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Abri yo misma la homepage del Saxena Lab y su pagina de empleo el 2026-09-07 (Tier 1). Sube de LIKELY a VERIFIED.</t>
+          <t>saxena.mgh.harvard.edu/our-lab/jobs-in-the-lab/ reabierta el 2026-09-14: literal 'Coming Soon!', sin plazas.</t>
         </is>
       </c>
     </row>
@@ -33982,7 +36918,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -33992,7 +36928,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -34002,7 +36938,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Localizar la pagina actual del grupo de Cormand (probablemente via el directorio de la Facultat de Biologia de la UB, el IBUB o CIBERER) y sustituir la URL rota antes de escribirle. No mandar el correo con esta ficha sin verificar.</t>
+          <t>Abrir a mano sira.ub.edu/fitxes/Biologia/es/bcormand.ub.edu en un navegador real (la ficha necesita JavaScript) para sacar correo y cargo; reintentar la pagina del grupo en ub.edu/ibub dentro de una semana.</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -34012,12 +36948,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://www.ub.edu/genetica/</t>
+          <t>https://sira.ub.edu/fitxes/Biologia/es/bcormand.ub.edu</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>CORRECCION: la URL que traia esta ficha (ub.edu/genetica) devuelve HTTP 404 el 2026-09-07, o sea que el enlace publicado esta roto. No me dio el presupuesto para buscar la pagina de sustitucion, asi que la fila baja a UNVERIFIED hasta que alguien abra una pagina Tier 1 del grupo. El resto de la fila sigue apoyandose solo en fuentes secundarias de la pasada anterior.</t>
+          <t>La URL rota anterior (ub.edu/genetica) se sustituye por la ficha oficial de personal de la UB: webgrec.ub.edu redirige con 301 permanente a sira.ub.edu, portal institucional de investigadores de la UB, dominio Tier 1 y enlace que resuelve. Salvedad: el contenido se genera con JavaScript y el lector automatico solo recupero encabezados vacios, asi que la ficha NO se ha leido y la fila sigue UNVERIFIED. El otro candidato, ub.edu/ibub/research-group/genetics-and-genomics-of-human-disorders, devolvio 'Pagina temporalment no disponible' en el unico intento. ATENCION AL NOMBRE: fuentes secundarias de la UB e IBUB llaman al grupo tanto 'Grup de Recerca de Neurogenetica' como 'Genetics and Genomics of Human Disorders', y situan a Cormand como catedratico del Departament de Genetica, Microbiologia i Estadistica e investigador ICREA Academia 2021 -- ninguno de esos datos esta confirmado en Tier 1.</t>
         </is>
       </c>
     </row>
@@ -34064,7 +37000,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>CONFIRMADA Y ABIERTA: 'Postdoctoral Research Scientist Position in Statistical Genomics/Genetic Epidemiology', 3 anos, jornada completa (39 h/semana), Departamento de Language and Genetics, grupo PGHC, supervisada por Beate St Pourcain. Candidaturas revisadas de forma rodante desde el 8-oct-2026 hasta cubrir. Inicio previsto 1-dic-2026, NEGOCIABLE. Piden doctorado en genomica estadistica, epidemiologia genetica, bioestadistica o bioinformatica (o estar a punto de obtenerlo) y solvencia computacional en R, Python, Perl o shell. AVISO DE CALENDARIO: el inicio en dic-2026 es incompatible con su disponibilidad (mediados de 2027 como pronto, feb-2028 para puestos que exigen el doctorado terminado); hay que preguntar hasta donde llega ese 'negociable'.</t>
+          <t>ABIERTA Y CONFIRMADA el 2026-09-14: '3-year Postdoctoral Research Scientist Position in Statistical Genomics/Genetic Epidemiology', revision rodante desde el 8-oct-2026 'until the position is filled', inicio propuesto 1-dic-2026 'although the start date is negotiable'. Requisito literal: 'hold, or expect to obtain shortly, a PhD'.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -34089,7 +37025,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Sube de 3 a 4 porque al abrir el anuncio el encaje resulta mucho mejor de lo que parecia: no es 'genetica del lenguaje' sin mas, es epidemiologia genetica del desarrollo sobre cohortes de nacimiento (EAGLE), con trayectorias de salud mental y condiciones del neurodesarrollo entre los fenotipos. Eso toca a la vez su linea 1 (genetica estadistica de rasgos complejos, que es literalmente el titulo del puesto), su linea 2 (salud mental/neurodesarrollo) y su linea 3 (fenotipos infantiles medidos desde la primera infancia, el mismo tipo de cohorte que ha revisado para el Journal of Sleep Research). Requisitos tecnicos exactamente los suyos: R, Python, shell, analisis de datos omicos - nada que necesite electrofisiologia ni neuroimagen, que son sus tecnicas supervisadas y no desplegables. Paises Bajos, UE, sin visado, contrato de 3 anos con financiacion nuclear Max Planck: colchon estable, sin depender de que le concedan una beca. El unico problema serio es el calendario: inicio 1-dic-2026 frente a una disponibilidad de mediados de 2027 en el mejor caso, y este puesto exige doctorado (feb-2028). Por eso el primer acercamiento no debe ser una candidatura ciega sino un correo a St Pourcain antes del 8-oct-2026 que diga tres cosas: que su perfil MD mas genetica estadistica encaja con la parte de fenotipado clinico y salud mental del proyecto, que su revision sistematica de genetica del sueno en lactantes le da conocimiento directo de fenotipos de primera infancia en cohortes tipo EAGLE, y la pregunta directa de si el inicio puede desplazarse a 2027-2028 o si convendria mas apuntar a la siguiente plaza del grupo.</t>
+          <t>El encaje cientifico no cambia: genomica estadistica y epidemiologia genetica sobre comportamiento social desde la primera infancia, trayectorias de salud mental y el consorcio EAGLE de cohortes de nacimiento, es decir sus lineas 1 y 3 a la vez, en la UE y sin visado. Lo que cambia esta semana es la lectura del calendario, y conviene decirla sin adornos: el anuncio exige doctorado en mano o 'a punto de obtenerlo' y su defensa esta prevista para feb-2028, catorce meses despues del inicio propuesto. 'Negociable' en un anuncio Max Planck suele significar semanas o pocos meses, no mas de un ano, y el anuncio no cuantifica el margen. Analisis, no dato verificado: esta convocatoria concreta probablemente NO es alcanzable para ella. Su valor real es abrir la puerta a la SIGUIENTE plaza del grupo PGHC, asi que el correo antes del 8-oct sigue siendo la accion correcta pero con otro objetivo: presentarse como candidata de la ronda 2027-2028, no competir por esta.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -34114,7 +37050,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -34124,7 +37060,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -34134,7 +37070,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Escribir a beate.stpourcain@mpi.nl ANTES del 8-oct-2026 preguntando si la fecha de inicio admite desplazarse a 2027-2028 y presentando el perfil; segun la respuesta, decidir si solicitar esta plaza o esperar a la siguiente.</t>
+          <t>Escribir a beate.stpourcain@mpi.nl antes del 8-oct-2026 con la pregunta en los dos sentidos: hasta donde llega el margen del inicio, y si el grupo preve nuevas plazas en 2027-2028. Presentarse como candidata de la siguiente ronda.</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -34149,7 +37085,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Abri yo misma el anuncio completo en mpi.nl el 2026-09-07 (Tier 1). Sube de UNVERIFIED a VERIFIED: la plaza que la pasada anterior solo vio en el tablon BGA existe, es real, y el PI NO es Simon Fisher sino Beate St Pourcain dentro de su departamento.</t>
+          <t>Anuncio completo releido en mpi.nl el 2026-09-14 (Tier 1): sigue publicado y sin cambios respecto al 2026-09-07. La reserva de calendario es lectura propia del texto del anuncio, no una declaracion del grupo.</t>
         </is>
       </c>
     </row>
@@ -35177,8 +38113,776 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>L-0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KI Psychiatric Genomics Institute (KI-PGI)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Yi Lu (Lu Yi), co-director Patrick F. Sullivan</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Karolinska Institutet, Department of Medical Epidemiology and Biostatistics (MEB)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Estocolmo</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Suecia</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>statistical genetics of complex traits; GWAS/PRS of schizophrenia and depression; treatment-resistant depression; gene-environment interplay; molecular and cellular effects of psychiatric risk loci</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>genome-wide SNP arrays, CNV analysis, whole exome/genome sequencing, analisis de registros sanitarios nacionales suecos, PRS</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Ninguna plaza publicada localizada el 2026-09-14; el instituto describe programa activo con doctorandos y colaboraciones. La entrada natural es el correo en frio.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Vetenskapsradet (Swedish Research Council) como financiador principal, mas proyectos UE (COSYN, CoMorMent, REALMENT) y NIMH de EE. UU.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Escribir a Yi Lu (lu.yi@ki.se, direccion publicada en la pagina Tier 1 del KI-PGI) como directora del instituto. Gancho: MD con pipeline GWAS-PRS propio en PLINK/R y dos primeros autores en revision, interesada en depresion y resistencia al tratamiento; proponer co-solicitar una MSCA o un postdoc del Swedish Research Council con el instituto como host, en vez de preguntar por una plaza.</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Yi Lu co-preside el MDD Working Group del PGC; produccion reciente del entorno en GWAS de depresion de inicio temprano/tardio y depresion resistente al tratamiento.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Es su linea 1 y su linea 2 combinadas -- genetica estadistica de rasgos complejos aplicada a trastornos psiquiatricos -- en el MEB, el departamento de referencia europeo en epidemiologia genetica. Lo que lo vuelve especifico para ELLA y no para cualquier postdoc: trabajan con registros clinicos nacionales suecos y con fenotipos de resistencia al tratamiento, que se construyen leyendo historia clinica, asi que su titulo de Medicina y su residencia de Laboratorio son un activo operativo y no un adorno biografico. La financiacion esta diversificada (VR + tres proyectos UE + NIMH), que es el margen que permite incorporar a alguien sin plaza publicada. Suecia es EEE: sin visado. El primer correo debe caber en dos parrafos: que pipeline GWAS-PRS ha montado ella sola, que tiene dos primeros autores en revision (Nature Mental Health y Journal of Sleep Research), su disponibilidad real (mediados de 2027 sin doctorado terminado, feb-2028 con el) y una propuesta explicita de co-solicitar financiacion propia.</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Instituto insignia co-dirigido con Patrick Sullivan, uno de los nombres mas citados del campo; atrae candidaturas internacionales y las plazas se cubren por la red del PGC.</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Correo en frio a lu.yi@ki.se proponiendo co-solicitar MSCA o postdoc del Swedish Research Council con el KI-PGI como host; no esperar a que salga plaza.</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://ki.se/en/meb/research/ki-psychiatric-genomics-institute/about-ki-pgi</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Pagina institucional Tier 1 de KI leida el 2026-09-14; liderazgo de Yi Lu confirmado en paralelo en la pagina del MDD Working Group del PGC. Aviso: ki.se/en/people/yi-lu da 404, la ficha viva es ki.se/en/people/lu-yi (indexada, no abierta).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>L-0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PsychGen Centre for Genetic Epidemiology and Mental Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Alexandra Havdahl</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Norwegian Institute of Public Health (FHI) con Lovisenberg Diaconal Hospital</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Oslo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>genetic epidemiology of neurodevelopmental and psychiatric conditions across the lifespan; within-family genomic analyses; co-occurrence and comorbidity; risk and resilience factors; sleep and fatigue; prediction models</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>analisis genomicos intrafamiliares (trios), PRS, epidemiologia genetica sobre cohortes y registros, machine learning; datos de MoBa (la mayor cohorte genotipada del mundo de ninos y ambos progenitores) y registros noruegos</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>No consta convocatoria abierta en la pagina del centro el 2026-09-14; centro en expansion con consorcios activos (PGC, EAGLE, Within Family Consortium, FAMILY).</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>No especificado en la pagina del centro; participa en el proyecto europeo FAMILY y en COVIDMENT, lo que implica financiacion UE en curso.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Correo en frio a Alexandra Havdahl como directora del centro (confirmar antes su direccion en su ficha de personal de fhi.no: la pagina 'about' del centro no nombra a nadie). Gancho: proponer un analisis intrafamiliar (trios) de sueno infantil en MoBa que separe efectos geneticos directos de los indirectos parentales -- es lo que ese centro sabe hacer y casi nadie ha aplicado al sueno de 0-3 anos.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Linea publicada sobre desarrollo de condiciones de salud mental a lo largo de la vida y procesos intrafamiliares; miembro de EAGLE y del Within Family Consortium.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Es el unico sitio de toda la cosecha de esta semana donde convergen sus TRES lineas a la vez, y no por casualidad: MoBa tiene fenotipos de sueno repetidos en los primeros anos de vida con genotipado de madre, padre e hijo, que es exactamente el material de su revision en Journal of Sleep Research, y el centro lo explota con metodologia de genetica estadistica. El diseno intrafamiliar es ademas la pregunta abierta de su linea 3: separar lo que hereda el nino de lo que aporta el ambiente parental. La cultura del centro es metodologica y open-source (publican sus pipelines), lo que encaja con alguien que llega con PLINK/R propios y no con una tecnica de banco. Noruega es EEE: sin visado. El primer correo debe abrir con la revision sistematica de sueno en menores de 3 anos como carta de presentacion, proponer en tres frases un analisis intrafamiliar concreto sobre MoBa y preguntar por la VIA DE FINANCIACION (postdoc del Research Council of Norway o MSCA con FHI como host), no por una plaza.</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Centro de alto perfil pero joven y en crecimiento, fuera del circuito anglosajon mas saturado; la barrera real es llegar con una idea concreta sobre MoBa, no el numero de candidatos.</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Confirmar la direccion de Havdahl en su ficha de fhi.no y escribirle con una propuesta de una pagina: sueno infantil en MoBa con diseno intrafamiliar. Preguntar por MSCA o postdoc del Research Council of Norway.</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://www.fhi.no/en/me/the-psychgen-centre-for-genetic-epidemiology-and-mental-health/about-the-psychgen-centre/</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Pagina Tier 1 del centro (fhi.no) leida el 2026-09-14 para lineas, metodos y socios. Salvedad: esa pagina NO nombra a la directora; el rol de Havdahl consta en su ficha de personal de fhi.no y en LinkedIn (Tier 2). Confirmar antes de encabezar el correo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>L-0022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Molecular Psychiatry research group (Cognitive Neuroscience / Human Genetics)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Barbara Franke</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Radboud university medical center, Donders Institute</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Nimega</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Paises Bajos</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>complex genetics of neurodevelopmental and stress-related psychiatric conditions and their comorbidities; ADHD across the lifespan; imaging genetics</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>analisis conjunto de variantes comunes y raras, epigenetica y multi-omica, bioinformatica, neuroimaging genetics (ENIGMA)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>No localizada convocatoria abierta el 2026-09-14; grupo grande con historial continuado de consorcios financiados por la UE.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Ha liderado consorcios UE (Aggressotype, MiND, PRIME); co-lidera la red ECNP de TDAH a lo largo de la vida.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Correo en frio a Barbara Franke presentandose como MD con pipeline GWAS-PRS independiente Y formacion supervisada en neuroimagen por RM, diciendo con precision cual es cual. Ofrecerse para la interseccion PRS-neuroimagen dentro de ENIGMA y preguntar por vias de entrada tipo MSCA o postdoc de Radboud con ella como supervisora.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Co-preside el ADHD Working Group del PGC junto a Joanna Martin; fundadora de IMpACT y miembro fundador del consorcio ENIGMA.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Encaje fuerte en su linea 2 con una particularidad que no se repite en ningun otro grupo de la tabla: es el unico sitio donde su formacion SUPERVISADA en neuroimagen por RM deja de ser un adorno y se vuelve argumento, porque el grupo hace imaging genetics dentro de ENIGMA y necesita gente que entienda a la vez el PRS y la RM -- una combinacion escasa incluso entre quienes dominan una de las dos. El TDAH a lo largo de la vida roza ademas el desarrollo infantil, puente natural hacia su linea 3. Paises Bajos es UE, sin visado, y el grupo tiene tradicion de captar postdocs via MSCA. La regla del primer correo es no sobrevender: decir explicitamente que la neuroimagen la aprendio en formacion supervisada y que su autonomia real esta en el lado estadistico-genetico, proponiendo un analisis PRS sobre fenotipos de imagen ya existentes. Si la vende como tecnica propia, la primera reunion tecnica la desmonta.</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>PI muy visible internacionalmente, grupo grande y co-chair de working group del PGC; recibe candidaturas espontaneas de forma habitual.</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Correo en frio a Franke ofreciendo la interseccion PRS x neuroimagen dentro de ENIGMA, declarando el nivel supervisado de la RM sin inflarlo.</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>https://www.radboudumc.nl/en/people/barbara-franke</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Ficha institucional Tier 1 de Radboudumc leida el 2026-09-14. La pagina del grupo (radboudumc.nl/en/research/research-groups/molecular-psychiatry) no se abrio en esta pasada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>L-0023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>iPSYCH - The Lundbeck Foundation Initiative for Integrative Psychiatric Research</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Anders Borglum (con Preben Bo Mortensen como director cientifico; Merete Nordentoft, Thomas Werge, Ole Mors)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Aarhus University con Statens Serum Institut y Region Hovedstaden Psykiatri</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aarhus</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dinamarca</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>interaccion entre herencia y ambiente en la enfermedad mental; genetica de autismo, TDAH, esquizofrenia, trastorno bipolar y depresion, desde el desarrollo prenatal hasta el paciente adulto</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>GWAS y secuenciacion sobre mas de 130.000 participantes daneses, integracion con registros poblacionales nacionales y muestras de sangre neonatal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>No consta convocatoria abierta en la pagina institucional el 2026-09-14; iniciativa grande y estable cuya puerta de entrada habitual es el contacto directo.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Financiacion de la Fundacion Lundbeck desde 2012, renovada por fases; una de las mayores iniciativas del mundo en su campo.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Correo en frio a Anders Borglum como co-chair del Autism Working Group del PGC y responsable genomico de iPSYCH; alternativa institucional ipsych@ipsych.dk. Gancho: la combinacion MD + pipeline GWAS-PRS y el interes por fenotipos del neurodesarrollo medidos pronto en la vida, que es el eje prenatal-a-adulto de iPSYCH.</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Co-preside el Autism Working Group del PGC; iPSYCH sostiene la cohorte de casos-controles psiquiatricos basada en registros mas explotada de Europa.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Genetica estadistica pura aplicada a psiquiatria sobre una cohorte nacional con datos desde el nacimiento, incluidas muestras de sangre neonatal. Para ELLA hay dos ganchos concretos: su formacion medica sirve de verdad para trabajar fenotipos de registro clinico danes, y el eje prenatal-infancia abre la puerta a colar su linea de sueno temprano como proyecto propio en lugar de llegar como par de manos a un GWAS ya montado -- que es la diferencia entre un postdoc que construye curriculo y uno que lo alquila. Es UE, sin visado. Atencion a no confundirlo con el grupo de QGG de Aarhus (L-0003, Doug Speed): es otro departamento y otra via. El primer correo debe pedir algo concreto -- entrar en el analisis de un fenotipo del neurodesarrollo infantil de iPSYCH -- y mencionar que puede venir con financiacion propia via MSCA o postdoc de la Lundbeck Foundation.</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Iniciativa de referencia mundial con financiacion de la Fundacion Lundbeck; capta postdocs internacionales de forma constante.</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Correo en frio a Borglum (o ipsych@ipsych.dk) proponiendo un fenotipo del neurodesarrollo infantil concreto y ofreciendo venir con MSCA o beca de la Lundbeck Foundation.</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>https://ipsych.dk/en/about-ipsych</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Pagina institucional Tier 1 de iPSYCH leida el 2026-09-14; el rol de Borglum se confirmo en paralelo en la pagina del Autism Working Group del PGC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>L-0024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Department of Genetic Epidemiology in Psychiatry (grupo de Fabian Streit)</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Fabian Streit</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Central Institute of Mental Health (ZI Mannheim), Medical Faculty Mannheim, Heidelberg University</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Mannheim</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>genetic epidemiology of psychiatric disorders; GWAS de trastorno limite de la personalidad; depresion y ansiedad; interaccion entre trauma temprano e historia familiar; epigenetica cerebral</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>GWAS y PRS, EWAS y transcriptomica en tejido cerebral, analisis sobre cohortes poblacionales europeas y la cohorte nacional alemana NAKO</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Desconocido: no se pudo abrir la pagina del departamento (dos URL de zi-mannheim.de dieron 404).</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Desconocido; lidera el International Borderline Genomics Consortium, lo que implica financiacion de consorcio activa.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Correo en frio a Fabian Streit citando su co-presidencia del MDD Working Group del PGC como referencia compartida. Gancho: capacidad independiente en PLINK/R para GWAS-PRS y disponibilidad para trabajo sobre NAKO o sobre los datos del consorcio de personalidad limite. Proponer explicitamente co-escribir una solicitud Humboldt o MSCA con el como host.</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Co-chair del MDD Working Group del PGC; trabajos recientes sobre vias geneticas directas e indirectas entre neuroticismo parental y problemas emocionales de la descendencia en siete cohortes europeas.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Encaje fuerte y, a diferencia de los cuatro anteriores, notablemente menos disputado: es un PI de mediana carrera recien ascendido a co-chair del PGC, el perfil que suele tener hueco y ganas de construir equipo en vez de limitarse a recibir becarios. El contenido encaja por partida doble: genetica estadistica psiquiatrica en un instituto clinico aleman, donde un MD que ademas maneja sus propios pipelines es una combinacion escasa; y su linea publicada sobre transmision parental de rasgos emocionales a la descendencia es el puente natural hacia el interes de ella por fenotipos infantiles. El obstaculo previsible en Alemania es la financiacion del puesto, no el numero de candidatos, asi que el correo debe llegar con la solucion puesta: ofrecer co-escribir una Humboldt o una MSCA con el como host, y adjuntar una pagina con el diseno de su pipeline GWAS-PRS.</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>PI de mediana carrera, menos expuesto internacionalmente que los directores de instituto; la barrera habitual en Alemania es financiar la plaza, no la competencia.</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Localizar a mano la pagina del Department of Genetic Epidemiology in Psychiatry del ZI Mannheim y su direccion de correo antes de escribir; la adscripcion es Tier 2 y esta sin confirmar.</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>https://pgc.unc.edu/for-researchers/working-groups/mdd/</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Su co-presidencia del MDD WG SI esta verificada en la pagina Tier 1 del PGC (2026-09-14). La adscripcion al Department of Genetic Epidemiology in Psychiatry del ZI Mannheim procede de fuentes Tier 2 y dos intentos de URL en zi-mannheim.de devolvieron 404: por eso la fila es UNVERIFIED y la URL apunta al PGC, que es lo unico comprobado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>L-0025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PGC Cross-Population Analyses Working Group (grupo de Laramie Duncan)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Laramie Duncan (co-chairs Hailiang Huang y Roseann Peterson)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Stanford University</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Stanford, California</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>cross-population and multi-ancestry analyses in psychiatric genetics; transferibilidad de PRS entre ancestrias</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>meta-analisis GWAS multi-ancestria, PRS cross-population, metodologia estadistica sobre datos del PGC</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Desconocido.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Desconocido.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Dos vias: correo en frio a Laramie Duncan en Stanford, o -- mucho mas barata -- solicitar unirse al Cross-Population Working Group del PGC (mas de 100 miembros, llamadas mensuales por Zoom), que da acceso a la red sin plaza, sin visado y sin mudanza.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Working group formado en mayo de 2018, con mas de 100 miembros y reuniones mensuales.</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Plausible pero hay que reencuadrarlo: el tema multi-ancestria no es ninguna de sus tres lineas declaradas y EE. UU. exige patrocinio de visado, asi que la via realista no es el postdoc sino apuntarse al working group para construir red y coautorias mientras termina la tesis.</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stanford y el atractivo del tema multi-ancestria, hoy prioridad de financiacion en EE. UU.</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Solicitar el alta en el Cross-Population Working Group del PGC: coste casi nulo y acceso a llamadas mensuales con el nucleo del campo.</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>https://pgc.unc.edu/for-researchers/working-groups/cross-population-analyses-working-group/</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Pagina Tier 1 del PGC leida el 2026-09-14 (chairs e instituciones). No se abrio la pagina de Stanford de Duncan, de ahi LIKELY.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z20"/>
+  <autoFilter ref="A1:Z26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -35189,15 +38893,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -35441,7 +39145,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -35451,7 +39155,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -35461,7 +39165,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>La inscripcion sigue ABIERTA a 22 dias del congreso: si va, registrarse esta semana en https://ispg.societyconference.com/v2/ y escribir a info@ispg.net pidiendo la cuota Student/Post-Doc y si hay opcion virtual, porque el portal no muestra tarifas.</t>
+          <t>La inscripcion sigue ABIERTA a 15 dias del congreso y sin fecha de cierre publicada: si va, inscribirse esta misma semana en https://ispg.societyconference.com/v2/ y escribir a info@ispg.net preguntando por la cuota Student/Post-Doc y por si existe opcion virtual, porque ninguna de las dos cosas esta publicada en ningun sitio accesible.</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -35476,7 +39180,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Tier 1, ispg.net/wcpg-2026 el 2026-09-07: 'Registration for WCPG 2026 is now OPEN', sin fecha de cierre publicada y sin mencion alguna a asistencia virtual/online. Plazos ya vencidos: simposios 19 y 26-mar-2026, orales/posters y ECIP 14-may-2026, premios Reich y Todd 31-may-2026, registro obligatorio de ponentes 1-jul-2026. Las cuotas quedan UNVERIFIED: el portal ispg.societyconference.com/v2 solo devuelve 'Loading...' (carga por JavaScript) y la pagina ispg.net/registration muestra todavia contenido de WCPG 2022 Florencia. Categoria Student/Post-Doc incluye residentes, con verificacion documental al inscribirse. Sede: Scottish Event Campus, Glasgow, 29-sep a 3-oct-2026.</t>
+          <t>Tier 1, ispg.net/wcpg-2026 el 2026-09-14: sigue diciendo 'Registration for WCPG 2026 is now OPEN!' sin fecha de cierre, sin tabla de cuotas y SIN mencion alguna a asistencia virtual. ECIP Travel Award confirmado CERRADO (14-may-2026); su elegibilidad incluia literalmente 'medical student, post-doctoral researcher, or less than five years out of a doctoral program'. Cuotas 2026 siguen UNVERIFIED tras un segundo intento por otra puerta: ispg.societyconference.com/conf solo devuelve botones 'Register Now' sin tabla de precios (carga por JavaScript) e ispg.net/registration SIGUE mostrando el WCPG 2022 de Florencia. ANCLA HISTORICA, NO es la tarifa de 2026: en Florencia 2022 la categoria Student/Post-Doc fue 396 EUR early, 462 regular, 506 on-site, y el Education Day suelto 198 EUR. No insistir mas por via automatica.</t>
         </is>
       </c>
     </row>
@@ -35573,7 +39277,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -35583,7 +39287,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -35593,7 +39297,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Reloj vivo a 8 dias: la inscripcion anticipada cierra el 15-sep-2026 a las 17:00 ET. Hacerse socia trainee de ASHG antes de inscribirse baja la cuota casi a la mitad; despues del 15-sep solo queda tarifa late/onsite.</t>
+          <t>RELOJ VIVO: la tarifa anticipada sigue abierta hasta manana 15-sep-2026 a las 17:00 ET. Si va, hacerse socia student/trainee de ASHG ANTES de inscribirse: la cuota cae de 775 USD (~713 EUR) a 435 USD (~400 EUR), un ahorro de ~313 EUR que supera de largo la cuota de socia. A partir del 16-sep solo queda late/onsite, y no hay tarifa de un dia ni opcion virtual.</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -35608,7 +39312,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Tier 1, ashgmeeting.ashg.org/attend/register el 2026-09-07. Cuotas en USD: no socio trainee 775 anticipada / 825 late; socio student-trainee 435 anticipada / 460 late; no socio 1.250 / 1.400. Cost_EUR 715 = 775 USD al cambio aproximado 0,92 (si se hace socia, ~400 EUR). Ventana anticipada 13-ago a 15-sep-2026 17:00 ET; despues late/onsite. No hay inscripcion de un solo dia ni opcion virtual anunciada. El plazo de resumenes late-breaking (26-ago-2026) ya paso, asi que el unico reloj que queda es el de inscripcion.</t>
+          <t>Tier 1, ashgmeeting.ashg.org/attend/register el 2026-09-14: la ventana anticipada (13-ago a 15-sep, 17:00 ET) NO ha cerrado todavia. Tabla completa en USD, anticipada/late: socio ASHG o Early Career 785/920; socio student-trainee 435/460; no socio 1.250/1.400; no socio student-trainee 775/825; emerito 290/290; RLC renta baja 0/0; RLC renta media-baja 310/310. Cost_EUR 715 se mantiene sobre la base no-socio trainee anticipada (775 USD x 0,92); por la via de socia serian ~400 EUR. Literal: 'Registration is for the full meeting; there is no one-day or exhibits-only registration.' El plazo de resumenes late-breaking (26-ago-2026) ya paso: el unico reloj vivo es el de inscripcion, y por eso la columna Deadline lleva esa fecha y no una de resumenes.</t>
         </is>
       </c>
     </row>
@@ -35701,30 +39405,34 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Plazo de resumenes abierto de par en par y a casi cinco meses vista: es el envio europeo mas planificable que tiene. Preparar el resumen en enero-2027 (notificacion a principios de abril, congreso en junio, ya fuera de la residencia). Vigilar 2027.eshg.org para cuotas y bursaries de jovenes investigadores, aun sin anunciar.</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>https://2027.eshg.org/abstracts/</t>
@@ -35732,7 +39440,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Fechas/plazo de las paginas oficiales 2027.eshg.org de resumenes y registro via busqueda. Registro abre feb 2027; tarifas aun no publicadas. ESHG 2026 ya celebrado.</t>
+          <t>Tier 1, 2027.eshg.org/abstracts el 2026-09-14: plazo regular literal 'Thursday, February 04, 2027 at 23:59 hrs CET', notificacion 'beginning of April 2027', congreso 12-15 jun 2027 en Rotterdam. La pagina NO anuncia todavia ronda late-breaking, ni cuotas, ni becas para 2027 (las que aparecen son las de 2026). Tier 2 (erdera.org) indica que esta planificado como evento HIBRIDO, lo que abriria una via barata de asistencia remota: sin confirmar en la web oficial.</t>
         </is>
       </c>
     </row>
@@ -35817,22 +39525,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -35852,7 +39560,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Tier 1: pagina oficial BGA Current Meeting el 2026-09-07: '2027 BGA Annual Meeting, Minneapolis, Minnesota, USA, 29 June - 2 July 2027', local host Scott Vrieze, program chair Sarah Medland. Siguen TBA: plazo de resumenes, web, programa, cuotas y plazo de becas de estudiante y de early career award. La pagina de Future Meetings de la BGA anuncia ademas Tartu (Estonia) para 2028.</t>
+          <t>bga.org reabierta el 2026-09-14: 29-jun a 2-jul-2027 en Minneapolis, local host Scott Vrieze, program chair Sarah Medland (la misma PI de L-0002, conexion calida de su estancia en QIMR). Plazo de resumenes, web del congreso, cuotas y becas de estudiante siguen TBA.</t>
         </is>
       </c>
     </row>
@@ -35902,8 +39610,16 @@
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>Si - apoyo de viaje/trainee de IGES (no verificado)</t>
@@ -35921,7 +39637,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Fuerte encaje de metodos para la linea (1): IGES es donde se discute la metodologia de genetica estadistica en un grupo pequeno y senior, y su workshop educativo esta pensado para alguien de su nivel. El plazo de resumenes (30-may-2026) ya paso y va pegado a ASHG en Quebec, asi que realistamente es objetivo 2027 salvo que ya vaya a ASHG. Registrar y revisar para 2027.</t>
+          <t>Fuerte encaje de metodos para su linea 1: IGES es la sociedad pequena donde se discute la metodologia de genetica estadistica cara a cara y con gente senior accesible, y su Education Workshop (85 USD) esta pensado justo para su nivel. Novedad de esta pasada, y es la que decide: cae 18-20-oct en Esterel, a una hora de Montreal, e inmediatamente ANTES de ASHG (20-24-oct, Montreal), asi que un solo vuelo transatlantico le compraria las dos salas. El freno es el dinero, no el encaje: sumar las dos inscripciones ronda los 1.400 EUR sin vuelo ni hotel, inasumible para una residente que paga de su bolsillo. Si tiene que elegir una sola, ASHG le da mas contactos y IGES mas metodo.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -35936,35 +39652,39 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>RELOJ VIVO a 5 dias: la tarifa early de IGES cierra el 19-sep-2026 y desde el 20-sep sube a late. Solo tiene sentido moverla si YA ha decidido ir a ASHG 2026 (misma region, dias consecutivos); el plazo de resumenes cerro el 30-may-2026, asi que iria como oyente. Si no va a ASHG, dejarla pasar y apuntarla como objetivo 2027.</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y6" t="inlineStr">
         <is>
           <t>https://www.geneticepi.org/2026-annual-meeting</t>
@@ -35972,7 +39692,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Fechas/plazo de geneticepi.org y listados via busqueda (no fetch directo). Adyacente a ASHG 2026 en Quebec.</t>
+          <t>Tier 1, geneticepi.org/2026-annual-meeting el 2026-09-14 (primera apertura DIRECTA; antes solo se habia leido via buscador). Cuotas en USD, early/late-onsite: socio academia 826/918; socio jubilado-estudiante-renta baja 662/772; no socio academia 1.033/1.125; no socio estudiante-renta baja 772/882; Education Workshop 85. Ventana: early hasta el 19-sep, late del 20-sep al 20-oct. Cost_EUR 710 = 772 USD (no socio estudiante, early) x 0,92. La columna Deadline lleva el cierre de la tarifa early porque el plazo de resumenes ya vencio. AVISO DE FIABILIDAD: esa misma pagina devolvio al extraerla una linea suelta 'June 1-2, 2026' que contradice todo lo demas; las fechas 18-20-oct-2026 en Esterel estan confirmadas por la ficha oficial via buscador y por la propia ventana de inscripcion (que cierra el 20-oct), asi que la linea de junio se descarta como error de la pagina, no se adopta en silencio.</t>
         </is>
       </c>
     </row>
@@ -36052,35 +39772,39 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Revisar sobp.org en noviembre-2026 buscando la convocatoria de resumenes de 2027; entrar por sobp.org/meetings, porque la ruta /meetings/future-meetings NO existe.</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
           <t>https://sobp.org/</t>
@@ -36088,7 +39812,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Fechas (6-8 may 2027, Chicago) de sobp.org via busqueda. Plazo de resumenes aun no anunciado. Tarifas en USD.</t>
+          <t>Intento de verificacion el 2026-09-14 fallido: sobp.org/meetings solo muestra un indice con enlaces a 'Future Meetings' y a la reunion de 2017, sin fechas ni plazos, y sobp.org/meetings/future-meetings devuelve 404. Las fechas 6-8 may 2027 en Chicago siguen apoyadas SOLO en fuentes secundarias. La convocatoria de resumenes de 2027 sigue sin publicarse (en ediciones previas abre hacia oct-nov del ano anterior).</t>
         </is>
       </c>
     </row>
@@ -36297,7 +40021,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -36307,7 +40031,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -36317,7 +40041,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>La convocatoria de resumenes de SLEEP 2027 aun no esta abierta: revisar sleepmeeting.org/call-for-abstracts en noviembre-2026, porque en la edicion 2026 el plazo cerro el 8-dic-2025 y el de 2027 caera previsiblemente en el mismo tramo.</t>
+          <t>Conflicto de fechas resuelto, no hace falta volver sobre el. Queda un solo reloj: la convocatoria de resumenes de SLEEP 2027, aun sin abrir. Revisar sleepmeeting.org/call-for-abstracts en noviembre-2026 (en la edicion 2026 cerro el 8-dic-2025). La inscripcion abre en enero-2027.</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -36332,7 +40056,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>CONFLICTO DE FECHAS: la ficha de aasm.org/event/sleep-2027 da 6-9 jun 2027 en Denver (Colorado Convention Center) frente al 5-jun-2027 que teniamos registrado; adopto 6-9 jun y lo dejo senalado. sleepmeeting.org solo muestra todavia contenido de SLEEP 2026 (plazo de resumenes 8-dic-2025), y su pagina call-for-abstracts devolvio contenido vacio al abrirla el 2026-09-07: la fecha de resumenes 2027 sigue sin publicar y no se inventa.</t>
+          <t>CONFLICTO RESUELTO el 2026-09-14, y las dos fechas eran ciertas: describian cosas distintas. Los cursos de posgrado con entrada aparte son sabado y domingo 5 y 6 de junio, y la sesion general va de domingo a miercoles, 6 a 9 de junio de 2027; el 5-jun que teniamos era el arranque de los CURSOS, no del congreso. Se adopta 6-9 jun 2027 como congreso. Sede: Colorado Convention Center, Denver; 41a reunion anual de la APSS. LIKELY y no VERIFIED porque sleepmeeting.org devolvio contenido vacio al abrirla directamente (segunda pasada consecutiva: dejar de abrirla directamente) y el texto se obtuvo via buscador, coincidiendo con la ficha aasm.org/event/sleep-2027.</t>
         </is>
       </c>
     </row>
@@ -36657,22 +40381,22 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -36688,7 +40412,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Tier 1: pagina oficial BGA Future Meetings consultada el 2026-09-07: lista 2028 Tartu (Estonia) con fecha TBA y 2029 TBA. Sin fechas ni cuotas publicadas todavia.</t>
+          <t>Verificado indirectamente en la misma consulta a bga.org del 2026-09-14: sigue listada 2028 en Tartu con fecha TBA.</t>
         </is>
       </c>
     </row>
@@ -37105,27 +40829,27 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Mirar aegh.org/congresos-y-jornadas-aegh a finales de 2026 para ver que sede gano la candidatura y que fechas tiene la Jornada 2027.</t>
+          <t>Volver a aegh.org/congresos-y-jornadas-aegh en diciembre-2026 o enero-2027 para ver sede y fechas adjudicadas.</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -37136,12 +40860,344 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>La web de la AEGH (2026-09-07) confirma que en 2027 toca Jornada AEGH porque en 2026 se celebra el V Congreso Interdisciplinar en Genetica Humana, y que la presentacion de candidaturas de sede se cerraba a finales de octubre de 2025; sede y fechas siguen sin anunciarse en la pagina, por eso UNVERIFIED.</t>
+          <t>Re-comprobado el 2026-09-14 en aegh.org (paginas 'Congresos y Jornadas AEGH' y 'Jornada AEGH 2027 - Presentacion de candidaturas'): SIGUE sin anunciarse sede ni fechas. Se confirma el encaje del calendario: en 2026 toca el V Congreso Interdisciplinar en Genetica Humana (15-17 abr 2026, Granada) y por eso 2027 es ano de Jornada. El plazo de candidaturas de sede cerro a finales de octubre de 2025 y la adjudicacion no se ha publicado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>E-0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EMGM 2027 - 55a European Mathematical Genetics Meeting</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>European Mathematical Genetics Meeting (comunidad EMGM, sede rotatoria)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Por anunciar</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Europa (sede rotatoria, por anunciar)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>UNVERIFIED (no se anuncian becas en la web general de la EMGM)</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Genetistas estadisticos, matematicos y epidemiologos geneticos europeos; reunion pequena de dos dias</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Es la reunion europea que mejor describe su linea 1 sin rodeos: el alcance declarado de la EMGM nombra literalmente genetica de rasgos complejos, inferencia causal, prediccion de rasgos y salud personalizada, fine-mapping e imputacion, metodos multirrasgo y variantes raras -- el temario exacto de su tesis. Lo que le aporta frente a WCPG o ASHG es PROPORCION: dos dias y aforo pequeno, asi que una doctoranda presenta ante la misma sala en la que estan los metodologos en vez de competir por atencion entre 8.000 asistentes, y la conversacion de pasillo con un jefe de grupo es realista y no un golpe de suerte. Y es la opcion mas barata que va a encontrar para su linea principal: sede europea (sin visado, vuelo corto desde Espana), dos dias de permiso en vez de una semana -- lo cual importa de verdad mientras siga en residencia -- y cuotas de reunion pequena, muy por debajo de los ~700 EUR de ASHG o IGES. El pero real: la sede de 2027 todavia no tiene quien la organice, asi que hoy es vigilancia, no accion.</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>La 54a edicion (Davos, 14-15 abr 2026) ya paso y la de 2027 sigue sin anfitrion. Vigilar sites.google.com/site/emgmhome a partir de noviembre-2026; si en enero-2027 sigue TBA, escribir a los organizadores de Davos 2026 (emgm2026.sciencesconf.org) preguntando por sede y fechas de 2027, que es justo lo que la propia web pide hacer.</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/site/emgmhome/future-meetings</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Tier 1, pagina oficial de Future Meetings de la EMGM abierta el 2026-09-14. Texto literal para 2027: '2027 TBA - please contact the organisers of the 2025 or 2026 EMGM if you are interested in hosting the meeting'. Serie anual ininterrumpida desde el 10-abr-1973 en Sheffield. No se publican cuotas ni plazos de resumenes en la web general: dependen de cada sede anual (emgm2025.sciencesconf.org, emgm2026.sciencesconf.org, emgm2024.ista.ac.at en IST Austria).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>E-0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GAW 2027 - Genetic Analysis Workshop (convocatoria de ideas abierta)</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Workshop colaborativo de analisis (reunion cientifica, no curso)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>International Genetic Epidemiology Society (IGES)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Por anunciar</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Por anunciar</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Metodologos de genetica estadistica y epidemiologia genetica que analizan en paralelo un mismo conjunto de datos y contrastan resultados</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>El GAW no es un congreso de escaparate sino el formato en el que varios grupos analizan EL MISMO dataset con metodos distintos y comparan resultados en sala, que es precisamente donde una doctoranda de genetica estadistica demuestra criterio metodologico sin necesitar todavia un hallazgo propio espectacular. Eso importa para ella en concreto: sus dos manuscritos siguen en revision y no le dan aun peso de autora senior, pero un analisis bien hecho sobre datos comunes si la pone al nivel de la conversacion. Ademas lo organiza la IGES, la misma sociedad pequena del E-0005, asi que los contactos se acumulan en vez de dispersarse entre circulos distintos. Hoy esta abierta la convocatoria de ideas para el tema de datos de 2027: es una ventana de participacion temprana, aunque ni fechas ni sede ni plazo esten publicados.</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Abrir la noticia 'Call for Ideas: Genetic Analysis Workshop (GAW) 2027' en geneticepi.org para ver el plazo exacto de la convocatoria de ideas y quien coordina; despues vigilar geneticepi.org/meetings para sede, fechas y plazo de resumenes.</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Detectado el 2026-09-14 como titular de 'latest news' en la portada de geneticepi.org mientras se verificaba el E-0005, y confirmado como entrada existente en el buscador. UNVERIFIED de forma deliberada: NO se abrio la noticia, asi que no se conocen plazo de la convocatoria, sede, fechas ni cuotas, y ninguno de esos datos se inventa aqui. Lo unico que se afirma es que la convocatoria de ideas para GAW 2027 existe y esta publicada por la IGES. La URL apunta a la portada y no al enlace largo de la noticia porque ese enlace lleva parametros de sesion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>E-0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>XXIX Congreso Nacional de Psiquiatria 2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Congreso anual nacional</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Psiquiatria y Salud Mental (SEPSM)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Espana</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-11-14</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Psiquiatras clinicos y profesionales de salud mental de Espana</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Es barato y esta en Espana, pero es psiquiatria clinica y no genetica estadistica, y ella es residente de Medicina de Laboratorio: se registra solo para no volver a descubrirlo cada semana.</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ninguna accion. Revisar solo si alguna vez quiere red clinica de psiquiatria en Espana.</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>https://congresonacionaldepsiquiatria.es/</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Tier 2, resultados de busqueda del 2026-09-14 (ficha de la Comunidad de Madrid y sepsm.org): 12-14 nov 2026 en Sevilla, organizado por la SEPSM. No se abrio la web oficial del congreso, de ahi LIKELY; cuotas y plazo de comunicaciones sin verificar. Descartado en la misma busqueda el XXXV Congreso Nacional de Psiquiatria Legal (Zaragoza, 20-22 may 2027) por no tener relacion con sus lineas.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Z16"/>
+  <autoFilter ref="A1:Z19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -37152,13 +41208,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="51" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -37341,7 +41397,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ISCEP (patrocinio de Regeneron Genetics Center) sigue vivo, PERO solo para nacionales y residentes de paises de renta baja o media-baja: ella, como espanola, NO es elegible. No consta ninguna otra exencion de cuota general.</t>
+          <t>Solo el ISCEP (Regeneron Genetics Center), restringido a nacionales Y residentes de paises de renta baja o media-baja: ella NO es elegible. Ninguna otra exencion publicada.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -37371,7 +41427,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -37381,7 +41437,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -37391,7 +41447,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Escribir a IBGworkshop@colorado.edu preguntando por la cuota 2027, la fecha de apertura de inscripcion, el plazo y si habra opcion virtual; vigilar la pagina cada semana porque la inscripcion suele abrirse sin previo aviso</t>
+          <t>La inscripcion 2027 AUN NO ESTA ABIERTA. Revisar colorado.edu/ibg/workshop-2027 a partir de noviembre-2026 (en ediciones previas abrio unos 3 meses antes) y reservar presupuesto propio de ~600 USD de cuota academica.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -37406,7 +41462,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Pagina oficial de la edicion 2027 y pagina oficial del ISCEP leidas el 2026-09-07. Confirmadas fechas 1-5 marzo 2027 en Boulder, Colorado, presencial; el foco anunciado es el modelado genetico latente (modelos de gemelos, OpenMx, genomic SEM, MR). La cuota 2027 NO esta publicada: los 550 EUR son una estimacion a partir de la tarifa academica de 600 USD de la edicion 2024 y hay que confirmarla. Tampoco hay plazo de solicitud publicado ni confirmacion de opcion virtual (existe una pagina de recursos online con materiales de ediciones pasadas). La pagina menciona un programa de inscripcion temprana para quien necesite visado. El aviso del ISCEP 2027 estaba previsto para mayo de 2026 y las condiciones publicadas dejan fuera a los paises de renta alta.</t>
+          <t>Pagina oficial del taller 2027 leida el 2026-09-14: confirma 'March 1 - March 5, 2027' en Boulder y advierte que 'the syllabus has yet to be decided upon'; NO publica cuota, plazo ni formulario. La pagina general (colorado.edu/ibg/workshop) confirma que la semana de marzo en Boulder es el Latent Genetics Course, que se imparte cada tres anos (2024, 2027, 2030) -- si se pierde 2027, la siguiente es 2030. Cost_EUR 550 sigue siendo ESTIMACION a partir de los 600 USD de cuota academica de 2024, no un dato de 2027.</t>
         </is>
       </c>
     </row>
@@ -37458,7 +41514,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>No consta beca ni exencion; coste integro a su cargo</t>
+          <t>Sin beca aplicable: los voucher packs de Bristol cubren solo a doctorandos y personal de la propia Bristol Medical School, profesionales de salud publica del suroeste de Inglaterra, empleados de organizaciones beneficas medicas del RU y residentes de paises de renta baja o media-baja. Ella no encaja en ninguno: coste integro a su cargo.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -37488,7 +41544,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -37498,7 +41554,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -37508,7 +41564,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Las reservas del programa 2026-27 abren el 2026-10-07 a mediodia (hora britanica), con registro previo de interes desde el 2026-09-23: poner alarma, porque estos cursos se llenan</t>
+          <t>ACCION INMINENTE Y CON DOS FECHAS: crear o reactivar la cuenta de reservas desde el mediodia del 2026-09-23 (dentro de 9 dias) y reservar plaza el 2026-10-07 a mediodia hora del RU, cuando abren las reservas de todo el programa 2026/27.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -37523,7 +41579,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Ficha oficial del curso y catalogo de Bristol leidos el 2026-09-07. Confirmado: 27-29 de enero y 1-3 de febrero de 2027, seis dias lectivos a jornada completa, formato online en directo, 1.250 GBP (~1.450 EUR), reservas cerradas hasta dos semanas antes del inicio (2027-01-13, coincide con lo ya fichado). Temario: tipos de datos geneticos, estructura poblacional, heredabilidad, GWAS y GWAS multiancestral, construccion y uso de puntuaciones poligenicas, anotacion funcional, estudios de expresion y metilacion y MR. No menciona explicitamente LDSC ni fine-mapping. Ojo: seis dias a jornada completa en plena residencia exigen permiso, aunque hay acceso a grabaciones durante 5 meses.</t>
+          <t>Catalogo oficial de cursos cortos de Bristol leido el 2026-09-14: confirma '27-29 January and 1-3 February 2027' (dos bloques). Confirmado tambien el dato clave de la rama, literal: 'From midday on Wednesday 23 September 2026 you will be able to register/re-register a short course booking account' y 'Bookings for the 2026/27 short course programme open midday Wednesday 7 October 2026'. La politica general es 'bookings close two weeks before the start of each course', coherente con el plazo 2027-01-13. AVISO DE RUTA: el catalogo ha cambiado de direccion; bristol.ac.uk/medical-school/study/short-courses/ redirige a /short-courses-and-cpd/short-courses/courses/.</t>
         </is>
       </c>
     </row>
@@ -37575,7 +41631,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>No consta beca ni exencion; coste integro a su cargo</t>
+          <t>Sin beca aplicable (mismos criterios de voucher pack que T-0002, ninguno le encaja); coste integro a su cargo.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -37605,7 +41661,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -37615,7 +41671,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -37625,7 +41681,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Reservar en cuanto abran las reservas el 2026-10-07 a mediodia; es la puerta de entrada obligatoria al curso avanzado de MR</t>
+          <t>ACCION INMINENTE: cuenta de reservas desde el 2026-09-23 a mediodia y reserva el 2026-10-07 a mediodia. Este va ANTES que T-0007, porque es su prerrequisito.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -37640,7 +41696,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Ficha oficial leida el 2026-09-07. Confirmado: 15-19 de marzo de 2027, cinco dias, online en directo, 880 GBP (~1.020 EUR), reservas cerradas dos semanas antes (2027-03-01, coincide con lo ya fichado). No exige experiencia previa en MR, pero si epidemiologia etiologica, regresion multivariable y soltura con Stata 17+ o R: ella cumple. Acceso a materiales y grabaciones 5 meses.</t>
+          <t>Catalogo oficial de Bristol leido el 2026-09-14: 'Mendelian Randomization, 15-19 March 2027'. Plazo derivado de la politica publicada 'bookings close two weeks before the start of each course'.</t>
         </is>
       </c>
     </row>
@@ -37710,22 +41766,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -37745,7 +41801,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Corregido un dato de la pasada anterior: ademas de la edicion de sep-2024 hubo una edicion el 2025-09-01, de modo que el curso siguio vivo hasta 2025 (histórico: 2019, 2020 virtual, 2022, 2023, 2024, 2025). Revisado el listado oficial de cursos de Wellcome Connecting Science el 2026-09-07: los unicos cursos listados son Accelerating Translation of Biodata to Impact (22-24 sep 2026) y Scalable Genomics and Pangenomics (11-16 oct 2026), ambos con plazo cerrado. NO hay convocatoria 2026 ni 2027 de este curso publicada a dia de hoy.</t>
+          <t>Catalogo de Wellcome Connecting Science reabierto el 2026-09-14: solo lista dos cursos ('Accelerating Translation of Biodata to Impact', 22-24 sep 2026, y 'Scalable Genomics and Pangenomics', 11-16 oct 2026), ambos con plazos ya cerrados. NO hay edicion 2026 ni 2027 de 'Genetic Analysis of Population-based Association Studies'. Sigue como elemento de vigilancia; proxima comprobacion en enero-2027.</t>
         </is>
       </c>
     </row>
@@ -37827,19 +41883,19 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>CLOSED</t>
@@ -37862,7 +41918,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Pagina oficial de CAJAL leida el 2026-09-07: edicion 2026 del 19 de noviembre al 8 de diciembre de 2026 en la Bordeaux School of Neuroscience, plazo cerrado el 27 de agosto, 4.500 EUR con matricula, alojamiento y comidas incluidos. NO hay edicion 2027 anunciada. Tres semanas presenciales en Burdeos con registros, optogenetica y modelos animales: es formacion de laboratorio humedo que no cierra ninguno de sus huecos reales, que son metodologicos y computacionales.</t>
+          <t>cajal-training.org/courses/ reabierta el 2026-09-14: el listado solo llega hasta diciembre de 2026 y NO hay ninguna edicion 2027 anunciada, ni de Neurobiology of Sleep ni del resto del programa. Sigue cerrado.</t>
         </is>
       </c>
     </row>
@@ -37932,22 +41988,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -37963,7 +42019,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Edicion 2026: 5-19 jun 2026, plazo 20-abr-2026 (ambos PASADOS); 4.790 USD incl. pension completa -&gt; ~4.420 EUR. Recurre anualmente; fechas 2027 aun no publicadas.</t>
+          <t>meetings.cshl.edu/courseshome.aspx reabierta el 2026-09-14: 'Statistical Analysis of Genome Scale Data' no aparece con edicion 2027 ni con fechas. El unico curso proximo de genomica humana computacional es 'Computational Genomics' (14-21 nov 2026), cuyo plazo vencio el 2026-09-11 y cuyo encaje es genomica computacional, no GWAS/PRS. Proxima comprobacion en primavera-2027, cuando CSHL suele publicar el calendario del ano siguiente.</t>
         </is>
       </c>
     </row>
@@ -38010,12 +42066,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>737</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>No consta ninguna beca ni exencion de cuota; el coste corre por cuenta del asistente</t>
+          <t>Sin beca ni exencion aplicable; coste integro a su cargo.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -38045,27 +42101,27 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>No reservar todavia: hacer primero el MR introductorio (T-0003) en marzo-2027 y buscar la edicion de finales de 2027 cuando Bristol publique el programa 2027-28</t>
+          <t>NO reservable en la practica para 2026: exige haber hecho antes el curso introductorio de MR, que ella hara en marzo-2027. Objetivo real: la edicion de noviembre-2027. Aun asi, confirmar en octubre-2026 si aceptan 'equivalente' con experiencia propia en MR.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -38076,7 +42132,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Pagina oficial del curso leida el 2026-09-07. Cuota original 630 GBP (~730 EUR). Duracion 2,5 dias, formato online en directo, acceso a materiales y grabaciones 5 meses. Las reservas del programa 2026-27 abren el 2026-10-07 a mediodia. Requisitos: MR introductorio o equivalente, experiencia previa en analisis MR y soltura con R.</t>
+          <t>Ficha oficial leida el 2026-09-14: 25-27 nov 2026, cuota 630 GBP (= 737 EUR a 1,17), reservas abren el 2026-10-07 a mediodia y cierran dos semanas antes del inicio. Prerrequisito EXPLICITO: haber completado el curso introductorio de MR o equivalente y tener experiencia haciendo analisis de MR. Se trabaja en R, con Posit Cloud como alternativa.</t>
         </is>
       </c>
     </row>
@@ -38116,7 +42172,11 @@
           <t>2027-06-24</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2027-06-08</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
@@ -38145,32 +42205,32 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Abrir la ficha del curso cuando se publiquen cuota y programa, y decidir junto con el resto de la oferta de Bristol de 2027</t>
+          <t>Decidir en primavera-2027 junto con el resto de la oferta de Bristol; la ficha individual del curso aun no esta publicada, asi que la cuota se conocera al abrir reservas el 2026-10-07.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -38181,7 +42241,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Fechas tomadas del catalogo oficial de cursos cortos de Bristol Medical School el 2026-09-07; no abri la ficha individual, asi que cuota y plazo estan sin verificar. Por el patron del resto del catalogo, el plazo suele ser dos semanas antes del inicio.</t>
+          <t>Fechas confirmadas en el catalogo oficial de Bristol el 2026-09-14 ('22-24 June 2027'). Plazo derivado de la politica publicada de cierre dos semanas antes. La ficha propia del curso todavia no existe: /machine-learning-with-omics-data/ y /machine-learning-omics/ devuelven 404. Referencia de precio: los otros cursos de 3 dias del programa estan en 630-750 GBP.</t>
         </is>
       </c>
     </row>
@@ -38221,11 +42281,19 @@
           <t>2027-03-24</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2027-03-08</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Desconocida; no consta beca en el catalogo</t>
+          <t>Sin beca ni exencion aplicable; coste integro a su cargo.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -38235,7 +42303,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Datos omicos y multiomicos con enfoque causal, util para su hueco de bioinformatica omica, pero cae en plena residencia y solapa parcialmente con el curso de epidemiologia genetica que ya tiene fichado.</t>
+          <t>Datos omicos a gran escala (metilacion, metabolomica, expresion, proteomica) con inferencia causal y MR aplicada, es decir su hueco de omicas. Dos peros concretos: cae en plena residencia y solapa en parte con epidemiologia genetica. A favor, un detalle de calendario que si cambia la decision: va la semana siguiente al MR introductorio (15-19 mar 2027), asi que ambos se encadenarian con un unico permiso.</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -38250,43 +42318,43 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Solo si sobra presupuesto y tiempo: va justo despues del MR introductorio (15-19 mar 2027), semana siguiente</t>
+          <t>Solo si sobran presupuesto y dias: encadenarlo con T-0003 (MR introductorio) la semana anterior, aprovechando un unico permiso.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr">
         <is>
-          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/molecular-epidemiology/</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Fechas del catalogo oficial de Bristol leido el 2026-09-07; cuota no verificada porque no abri la ficha individual.</t>
+          <t>Ficha oficial leida el 2026-09-14: 22-24 marzo 2027, 750 GBP (= 878 EUR a 1,17), online en directo, practicas en R via Posit Cloud, acceso a grabaciones 5 meses. Temario: diseno de estudios moleculares, interpretacion biologica de metilacion/metabolitos/expresion/proteinas, biomarcadores, inferencia causal y MR.</t>
         </is>
       </c>
     </row>
@@ -38316,9 +42384,21 @@
           <t>Tartu, Estonia (presencial)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>750</t>
@@ -38326,7 +42406,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>La pagina menciona becas pero sin detallar importes ni criterios</t>
+          <t>No consta beca; ademas de la cuota de 750 EUR hay 25 EUR no reembolsables de tasa de solicitud, y alojamiento, comidas y viaje van aparte.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -38341,7 +42421,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -38351,32 +42431,32 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Revisar en marzo-2027 si se convoca la edicion 2027: por el patron anual caeria a finales de julio, ya sin residencia, con plazo hacia el 20 de abril</t>
+          <t>La edicion 2026 ya se celebro y su plazo cerro el 2026-04-20. Revisar la pagina en marzo-2027: la convocatoria 2026 se abrio el 20-mar y cerro el 20-abr, con resolucion antes del 30-abr y pago antes del 31-may.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -38387,12 +42467,315 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Pagina oficial leida el 2026-09-07: la edicion documentada es la de 2026 (27 jul - 7 ago 2026, plazo 2026-04-20, 750 EUR mas 25 EUR de tasa de solicitud, 3 ECTS, 10 dias lectivos). La edicion 2027 NO esta anunciada todavia; las fechas se dejan vacias a proposito para no inventar. Requisitos: nivel basico de R o Python y preferiblemente Unix/Bash. Descubierta via el agregador summerschoolsineurope.eu.</t>
+          <t>Pagina oficial de la UniTartu Summer School leida el 2026-09-14: 10 dias lectivos del 27-jul al 7-ago-2026, 750 EUR de matricula mas 25 EUR de solicitud, requiere carta de motivacion, expediente y copia del pasaporte. Contenido: EDA y visualizacion de datos genotipo-fenotipo, control de calidad, GWAS y PRS. No hay anuncio de edicion 2027. CORRECCION: la fila no tenia fechas y parecia una convocatoria viva; era la edicion 2026, ya celebrada y con plazo vencido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T-0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Genetic and Epigenetic Epidemiology (curso especializado del EEPE)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>European Educational Programme in Epidemiology (EEPE)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Curso especializado residencial</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Toscana, Italia (presencial, residencial)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1575</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>No consta beca ni exencion en la pagina de inscripcion; la cuota incluye docencia, materiales, alojamiento compartido y comidas, y baja 250-345 EUR en modalidad no residencial.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Cierra de lleno DOS de sus huecos declarados -- inferencia causal / aleatorizacion mendeliana y datos omicos a gran escala (epigenetica, metilacion) -- y lo hace con el profesorado de la MRC IEU de Bristol (David Evans, Gibran Hemani, Matthew Suderman, Paul Yousefi), que es exactamente la sala donde le interesa estar. El tercer argumento es el formato: residencial una semana entera, con alojamiento y comidas compartidos, que es el tipo de curso que genera contactos de verdad, y la visibilidad en la comunidad es un hueco tan real en su perfil como los tecnicos. La contrapartida hay que decirla clara: no hay financiacion identificada, son 1.575 EUR integros de su bolsillo, y el temario solapa en parte con el MR de Bristol, que es mas barato y online.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Revisar eepe.org en enero-2027: la edicion 2027 se anunciara con el curso residencial (mediados de junio a principios de julio) y los especializados la semana siguiente. Compararla entonces con el MR de Bristol de marzo-2027, que cubre parte del mismo terreno mas barato.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>https://www.eepe.org/courses-2/</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>eepe.org/courses-2/ y eepe.org/registration-2-2/ leidas el 2026-09-14 (Tier 1). Edicion 2026: curso residencial de 3 semanas del 15-jun al 3-jul-2026 (3.965 EUR, fuera de alcance por duracion) y cursos especializados de 5 dias del 6 al 10 de julio de 2026, entre ellos este, a 1.575 EUR en regimen residencial compartido; habitacion individual +595 a +750 EUR. Cuotas en euros, sin conversion. La edicion 2027 NO esta anunciada: las fechas se dejan vacias a proposito en vez de extrapolar. La web no publica fechas limite ni becas; el contacto es eepe@eepe.org.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T-0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SMARTbiomed Summer School: Causal inference, statistical genetics and machine learning in common disease epidemiology and biology</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SMARTbiomed (Universidad de Aarhus)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Escuela de verano</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sonderborg, Dinamarca (presencial, residencial)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>No consta beca ni exencion.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Es la unica formacion encontrada que ataca TRES de sus huecos en un solo bloque de cinco dias: inferencia causal, genetica estadistica y machine learning aplicado en Python. El cuarto modulo, desarrollo de paquetes en R, va directo a algo que el perfil admite sin rodeos -- que su Python es asistido por IA y su autonomia de programacion es el limite real de su independencia tecnica. Ademas es la cuota mas baja de toda la rama (unos 633 EUR) y esta en la UE, sin visado. El problema no es el encaje sino la existencia: la web solo documenta la edicion de 2025 y no anuncia 2026 ni 2027, asi que hoy es una pregunta que hacer, no un curso al que apuntarse.</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>No hay convocatoria abierta. Escribir a smartbiomed_info@au.dk en enero-2027 preguntando si habra edicion y en que fechas; si la hay, es candidata de primera linea.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://smartbiomed.dk/news-and-events/summer-school</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Pagina oficial leida el 2026-09-14 (ultima revision del sitio: 2026-08-04, sin anuncio posterior a 2025). Edicion 2025: 23-27 jun 2025 en Sandbjerg Gods, cuota 4.718,75 DKK con IVA (= 633 EUR a 7,46 DKK/EUR), plazo 19-abr-2025, cuatro modulos en paralelo (Introduction to Statistical Genetics, R Package Development, Introduction to Causal Inference, Applied Machine Learning with Python). Fechas de una edicion futura: NO anunciadas, no se extrapolan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T-0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Polygenic scores and the PGS Catalog</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMBL-EBI Training</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Curso online autoformativo gratuito</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Gratuito, no aplica.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Gratuito y directamente sobre PRS, pero es material introductorio sobre una tecnica que ella ya despliega sola: se registra para no volver a descubrirlo, y su unico valor real es familiarizarse con el PGS Catalog como repositorio.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Recurso de consulta, no accion: hojearlo si alguna vez necesita depositar o reutilizar scores del PGS Catalog.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>https://www.ebi.ac.uk/training/online/courses/polygenic-scores-pgs-catalog/</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Localizado en busqueda web el 2026-09-14; NO se abrio la pagina del curso (el listado de eventos de EBI, ebi.ac.uk/training/events/, entro en bucle de mas de 10 redirecciones), de ahi LIKELY y no VERIFIED.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W11"/>
+  <autoFilter ref="A1:W14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39826,7 +44209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -40725,8 +45108,60 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SUB-0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bristol Medical School - cuenta de reservas de cursos cortos</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>La cuenta de reservas del programa de cursos cortos de Bristol: es el mecanismo por el que se reserva plaza en Genetic Epidemiology, Mendelian Randomization, Molecular Epidemiology y Machine Learning with Omics Data (T-0002, T-0003, T-0008, T-0009), los cuatro cursos que mas huecos suyos cierran.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>No es un boletin sino la puerta de entrada, y tiene dos relojes: la cuenta se crea o reactiva desde el mediodia del 2026-09-23 y las reservas del programa 2026/27 abren el 2026-10-07 a mediodia hora del RU. Sin cuenta creada antes, no se puede reservar el dia que abren, y estos cursos se llenan.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ALTA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Alta del 2026-09-14. Era la candidata que el tope de 2 dejo fuera la semana pasada. Verificado el calendario en la pagina oficial de fees el 2026-09-14.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J17"/>
+  <autoFilter ref="A1:J18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -23,17 +23,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$63</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$158</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$276</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
@@ -1845,7 +1845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J148"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -8963,7 +8963,7 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -9544,8 +9544,528 @@
         </is>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>SRC-0148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>EURAXESS Worldwide - digests regionales de postdocs recien publicados</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/worldwide/north-america/news/europe-22-postdoctoral-positions</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Recopilaciones editoriales que publican las oficinas regionales de EURAXESS (north-america, lac, japan, china, asean, india, africa) con 20-90 ofertas concretas del portal, cada una con titulo, institucion, pais, PLAZO y enlace directo a la ficha /jobs/NNNNNN. Es la unica via encontrada que devuelve contenido real de EURAXESS filtrado y fechado, porque el buscador del portal no filtra nada.</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Navegar https://euraxess.ec.europa.eu/worldwide/&lt;region&gt;/news/ y abrir los items cuyo titulo empiece por 'Europe:' (postdocs, PhD, funding). Leer la tabla y quedarse con genetica/genomica/psiquiatria/neurociencia/sueno.</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Punto debil: son digests esporadicos y con retraso. Los dos localizados el 2026-09-21 son de 2024-11-15 (lac) y 2026-05-15 (north-america), y NINGUNO traia nada de genetica estadistica ni psiquiatrica. Util como red de barrido mensual, inutil para plazos urgentes. Fuente NUEVA en esta pasada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>SRC-0149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>NIH Office of Intramural Training &amp; Education (OITE) - tablon de empleo intramural</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://www.training.nih.gov/jobs/</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Plazas postdoctorales del programa intramural del NIH (NIMH, NHGRI, NLM, NIA, NIEHS...), con fichas por instituto. En esta pasada aparecian, entre otras, 'Postdoctoral Fellow (Genetic Epidemiology and Bioinformatics)' (doctorado en genetica estadistica/epidemiologia genetica, PRS y datos omicos) y 'Postdoctoral Fellow (NLM &amp; NIMH)' sobre tipos celulares del cerebro humano y trastornos psiquiatricos con genomica de celula unica.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>El indice y las fichas devuelven HTTP 403 al fetch automatico: hay que atacarlo por busqueda web restringida (allowed_domains=training.nih.gov, nimh.nih.gov, irp.nih.gov) con 'postdoctoral fellow statistical genetics', 'genetic epidemiology polygenic', 'psychiatric genomics'; las fichas tienen la forma training.nih.gov/jobs/&lt;codigo&gt;/ y las abre la dueña a mano</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Mensual (y semanal a partir de 2027, cuando su reloj se acerque)</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Fuente nueva para el repo, encontrada el 2026-09-21. Ojo a la elegibilidad: el programa PIRA del NIMH exige ciudadania o residencia permanente en EE.UU., mientras que la via de Visiting Fellow si admite extranjeros con visado; hay que mirarlo ficha por ficha. Anadir 403 de training.nih.gov a la lista de bloqueos conocidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>SRC-0150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>IiSGM - Instituto de Investigacion Sanitaria Gregorio Maranon, ofertas de empleo</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://www.iisgm.com/ofertas-de-empleo/</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Convocatorias propias de un IIS grande de Madrid con nodo CIBERSAM: genetistas, ayudantes de investigacion, tecnicos y contratos ligados a proyecto</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Listado completo; filtrar por estado Abierta y leer los titulos con genetica / genomica / bioinformatica</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Se lee sin bloqueo por WebFetch y muestra referencia, grupo y fecha limite en el propio listado. FUENTE NUEVA de la pasada 2026-09-21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>SRC-0151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>IIS-FJD Fundacion Jimenez Diaz, ofertas de empleo</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>https://www.fjd.es/iis-fjd/es/formacion-empleo/ofertas-empleo</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Llamadas de acogida a candidatos postdoctorales por area (incluida un Area de Genomica y Genetica) para concurrir a contratos publicos tipo Sara Borrell</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Abrir a mano; el area de interes es Genomica y Genetica</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>BLOQUEO: fjd.es devuelve HTTP 403 al fetch automatico. Solo utilizable a mano por la duena. Es el mejor ejemplo encontrado del patron espanol grupo-acoge-para-Sara-Borrell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>SRC-0152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>INCLIVA (Instituto de Investigacion Sanitaria, Valencia), convocatorias de empleo</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>https://www.incliva.es/en/rrhh/job-offers/employment-opportunities/</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Convocatorias numeradas del IIS de Valencia con estado Plazo abierto/cerrado</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Listado completo, mirar las de Plazo abierto</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Se lee sin bloqueo, pero en esta pasada las 4 convocatorias abiertas eran enfermeria de investigacion, desarrollo de aplicaciones y gestion: rendimiento bajo para su perfil. Contacto empleo@incliva.es.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>SRC-0153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Porterhouse Medical - portal de vacantes de la agencia</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://www.porterhousemedical.com/careers/</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Vacantes reales y legibles de una agencia MedComms britanica con tres oficinas (Londres, Nottingham, Reading) y division estadounidense: Senior Medical Writer, Senior Medical Editor y, sobre todo, las dos vias de entrada nombradas para quien no tiene experiencia de agencia, el Pathfinders PhD Internship Programme y el Pathfinders Graduate Internship Programme, esta ultima con calendario anual declarado</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Abrir la pagina entera y leer el bloque 'Current Vacancies'; buscar 'Medical Writer' sin el prefijo Senior y la reapertura del programa Pathfinders</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Trimestral, y con un vistazo extra a finales del cuarto trimestre de 2026 por la reapertura anunciada del programa de graduados</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>HTML plano, sin JavaScript, perfectamente legible por un agente; metadatos con fecha de ultima modificacion 2026-08-26, o sea listado mantenido. No publica salarios ni fechas de cierre. La solicitud es por correo a careers@porterhousemedical.com, no hay formulario. Segunda agencia del metodo 'portal de agencia' tras Oxford PharmaGenesis (SRC-0134)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>SRC-0154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Evidenze - portal de empleo (motor Personio)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>https://evidenze.jobs.personio.com/</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Vacantes de un CRO europeo que declara divisiones propias de medical writing y de comunicacion cientifica, ademas de bioestadistica y gestion de datos: cubre a la vez el carril 1 (investigacion por contrato) y el carril 3 (comunicacion cientifica)</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Buscar en el campo 'Position' los terminos medical writer, scientific communication y biostatistics</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>OJO, FUENTE A MEDIO VERIFICAR: la pagina https://evidenze.com/careers carga y contiene un buscador 'Open positions', y el enlace real de las vacantes es el portal Personio de arriba, pero ese portal no devuelve nada a un agente (el feed XML de Personio vino vacio y la pagina se pinta con JavaScript), asi que NO se ha podido leer ni una sola vacante ni confirmar en la web que la sede este en Espana. Tiene que abrirla ella a mano. Se registra como fuente y no como fila de empleo precisamente por eso</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>SRC-0155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>IGES - Position Openings (International Genetic Epidemiology Society)</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/position-openings</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Tablon de plazas de la sociedad de epidemiologia genetica: postdocs y research associates en genetica estadistica y epidemiologia genetica, publicados por los propios PI. CADA ENTRADA LLEVA FECHA DE PUBLICACION VISIBLE, lo que lo hace fiable para detectar altas nuevas (a diferencia de jobRxiv).</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Abrir la pagina entera y filtrar por la fecha 'Posted' de cada entrada; son pocas (5 vivas el 2026-09-21).</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Fuente nueva de esta pasada (rama 5). Es exactamente la linea 1-2 del perfil. OJO: el indice NO esta en iges.memberclicks.net (ahi /job-postings y /jobs dan 404); el dominio bueno es geneticepi.org. Las fichas individuales si viven en iges.memberclicks.net/&lt;slug&gt;. El 2026-09-21 la mas reciente era del 2026-06-17: rotacion lenta, no esperar altas todas las semanas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>SRC-0156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>AEGH - Ofertas de empleo (Asociacion Espanola de Genetica Humana)</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://aegh.org/empleo/</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Bolsa de ofertas de genetica clinica y de laboratorio en hospitales y empresas espanolas (facultativos especialistas, genetistas clinicos, citogenetistas), mas alguna europea. Carril 2 del perfil: sistema publico espanol como especialista de Laboratorio/Genetica.</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Indice /empleo/; para fechar cada oferta hay que abrir la ficha individual.</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Quincenal</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Fuente nueva de esta pasada (rama 5). Complementa SRC-0094 (blog de convocatorias) y SRC-0115 (cursos), que no cubren la bolsa de empleo. LIMITACION IMPORTANTE: el indice NO muestra fechas de publicacion, solo las fichas individuales; el buscador web sí las expone. La mas reciente detectada el 2026-09-21 era del 2026-07-23, nada dentro de la ventana de 7-14 dias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>SRC-0157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>PGC Careers (Psychiatric Genomics Consortium)</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://pgc.unc.edu/about-us/pgc-careers/</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Plazas que los grupos del PGC publican para early career researchers (postdocs en genomica psiquiatrica, GWAS, PRS). Linea 2 del perfil, y es la red de contactos donde ella querria estar.</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Pagina unica, lista corta. Sin fechas de publicacion: usar el plazo de solicitud para saber si sigue viva.</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Fuente nueva de esta pasada (rama 5); distinta de SRC-0027 (portal general) y SRC-0137 (working groups). Rotacion MUY lenta y se queda rancia: el 2026-09-21 la unica entrada era un postdoc del Karolinska (Lisa Dinkler) con plazo 2026-02-17, caducado hace siete meses. Por eso cadencia mensual y no semanal.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J148"/>
+  <autoFilter ref="A1:J158"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9676,7 +10196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20121,8 +20641,1016 @@
         </is>
       </c>
     </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>P-0036</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Research Scientist - Maternal Sleep</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Toca su tercera linea (sueno) y admite perfil medico, pero lo esencial es polisomnografia y desenlaces perinatales -nada de genetica- y exige experiencia postdoctoral ya hecha, mientras ella no estara disponible hasta 2027-2028.</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/158385-research-scientist-maternal-sleep</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>P-0037</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow (Genetic Epidemiology and Bioinformatics)</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>En tema es lo mas cercano a su nucleo que ha aparecido esta semana: epidemiologia genetica + PRS es exactamente su linea 1-2 y su stack real (PLINK, R, pipelines GWAS-PRS a nivel independiente), y el NIH valora el perfil MD+PhD para fenotipado clinico. Se queda en 3, no en 4, por tres condiciones si</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://www.training.nih.gov/jobs/pd-010127/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>P-0038</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Ayudante de Investigacion Postdoctoral - Unidad de Investigacion Clinica en Inmunoterapia del Cancer CNIO-HMarBCN (AIPOSCNIO-HMarBCN)</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Inmunologia experimental humeda (vectores lentivirales, citometria, experimentacion animal) con 6 anos de experiencia exigidos y doctorado de hace menos de un ano: ni la tecnica ni el reloj encajan, y ella no estaria disponible antes de mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>https://www.cnio.es/empleo/ayudante-de-investigacion-postdoctoral-para-la-unidad-de-investigacion-clinica-en-inmunoterapia-del-cancer-cnio-hmarbcn-aiposcnio-hmarbcn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>P-0039</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Genetista en Servicio de Apoyo a la Investigacion de Farmacogenomica (ref. 98_2026)</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>La farmacogenomica hospitalaria toca su especialidad de Medicina de Laboratorio, pero la convocatoria pide Grado en Genetica y ella es medica, asi que probablemente no sea elegible por titulacion; ademas cierra el 2026-09-26 y ella no esta disponible hasta mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://www.iisgm.com/ofertas-de-empleo/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>P-0040</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Busqueda de candidatos con perfil postdoctoral - Area de Genomica y Genetica (contratos postdoctorales publicos)</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>El mecanismo es exactamente la via espanola que le interesa (un grupo que te acoge para presentarte a un Sara Borrell), pero el grupo concreto es genetica del desarrollo ocular, no genetica estadistica ni psiquiatrica, y su doctorado no estara defendido hasta feb-2028 (ETA), fuera del ciclo actual.</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://www.fjd.es/iis-fjd/es/formacion-empleo/ofertas-empleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>P-0002</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Scientist in Statistical Genomics / Genetic Epidemiology</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Deadline, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://recruitingapp-5569.de.umantis.com/Vacancies/496/Description/2?lang=eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>P-0033</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Postdoctoral researcher in genome stability and neurotoxicity</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Deadline, Last_Updated, Last_Verified, Next_Action, Salary_EUR_Year, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://www.werkenbijerasmusmc.nl/vacature/1307326/postdoctoral-researcher-genome-stability-and-neurotoxicity-3-years-3416</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>P-0032</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Research Associate at the Human Functional Genomics Initiative</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/155527-research-associate-at-the-human-functional-genomics-initiative</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>P-0014</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Research Assistant (Moondance Dementia Laboratory)</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://cardiffuniweb.eploy.net/vacancies/vacancy-search-results.aspx?culture=en-GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>P-0018</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Clinical Research Fellow (Psychological Medicine)</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DST268/clinical-research-fellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>P-0031</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Associate (proyecto Youth Endowment Fund, CRIS)</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Salary_EUR_Year, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/157565-postdoctoral-research-associate</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>P-0028</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Bioinformatician</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Salary_EUR_Year, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSU830/bioinformatician</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>P-0030</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Research Assistant - estudio CONNECT</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Salary_EUR_Year, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>https://cardiffuniweb.eploy.net/vacancies/447/research-assistant.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>P-0027</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Research Fellow (Genetic Analysis)</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSW126/research-fellow-genetic-analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>P-0029</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Fellow/Research Fellow in Statistical Genomics (R-68861)</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Deadline, Duration, Fit_1_5, Fit_Rationale, Group_or_Lab, Last_Updated, Last_Verified, Next_Action, Open_Date, PI, Requirements_Key, Salary_EUR_Year, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>https://uq.wd3.myworkdayjobs.com/uqcareers/job/St-Lucia-Campus/Postdoctoral-Research-Fellow-Research-Fellow-in-Statistical-Genomics_R-68861-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>P-0034</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Computational Scientist II - Karczewski Lab (ref 44894)</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>https://broadinstitute.avature.net/en_US/careers/JobDetail/Computational-Scientist-II-Karczewski-Lab/22501</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>P-0035</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Postdoctoral Associate - Computational Biology (ref 44829)</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, City, Confidence, Group_or_Lab, Last_Updated, Last_Verified, Open_Date, PI, Requirements_Key, Salary_EUR_Year, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>https://broadinstitute.avature.net/en_US/careers/JobDetail/Postdoctoral-Associate-Computational-Biology/22430</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>P-0008</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Computational Scientist I - McCarroll Lab</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>https://broadinstitute.avature.net/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>P-0016</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Clinical Research Fellow (IoPPN)</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Deadline, Last_Updated, Last_Verified, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/155765-clinical-research-fellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>P-0020</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow - Statistical Genetics and Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Updated, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>https://jobrxiv.org/job/postdoctoral-fellow-statistical-genetics-and-artificial-intelligence/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>J-0015</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Familia de vacantes de Porterhouse Medical: Senior Medical Writer (Reino Unido), Senior Medical Writer (Remote-US) y programas Pathfinders de entrada a MedComms</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Encaja con ELLA por lo que MedComms compra de verdad en un writer junior: criterio clinico y capacidad de leer, jerarquizar y resumir literatura. Es MD con ingles C2 y lleva dos manuscritos propios como primera autora, uno de revision en Journal of Sleep Research y uno empirico en Nature Mental Heal</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>https://www.porterhousemedical.com/careers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>J-0010</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Bolsa de Empleo Abierta y Permanente (BAPE) de Sacyl - categoria Licenciados Especialistas (incluye Analisis Clinicos y Bioquimica Clinica)</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Effort_Estimate, Fit_1_5, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Requirements_Key, Source_Note</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>https://www.saludcastillayleon.es/profesionales/es/bolsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>J-0003</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Via transitoria al titulo de especialista en Genetica Medica y en Genetica de Laboratorio (dos reales decretos separados, aun sin publicar)</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>https://www.sanidad.gob.es/normativa/audiencia/home.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>J-0012</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Statistical Geneticist Investigator (Human Genetics / Genomic Sciences)</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, City, Confidence, Last_Updated, Last_Verified, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>https://jobs.gsk.com/en-gb/jobs/223316?lang=en-us</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H252"/>
+  <autoFilter ref="A1:H276"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -20528,22 +22056,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD36"/>
+  <dimension ref="A1:AD41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
     <col width="52" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="52" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="52" customWidth="1" min="13" max="13"/>
     <col width="52" customWidth="1" min="14" max="14"/>
     <col width="11" customWidth="1" min="15" max="15"/>
     <col width="52" customWidth="1" min="16" max="16"/>
@@ -20556,7 +22084,7 @@
     <col width="15" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
-    <col width="52" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
     <col width="52" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="52" customWidth="1" min="29" max="29"/>
@@ -20912,7 +22440,11 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>sin fecha de cierre publicada; la pagina institucional marca 'DEADLINE HAS PASSED' en las demas vacantes y esta NO lo lleva, luego sigue abierta sin plazo</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>PhD en genomica estadistica, epidemiologia genetica, bioestadistica o campo cuantitativo afin; metodos omicos para arquitectura genetica de fenotipos humanos; R, Python, Perl, shell. Deseable: SEM, meta-analisis, neuroimagen. SIN PLAZO FIJO: revision continua de candidaturas a partir del 2026-10-08 y hasta cubrir la plaza. Encuadre en el consorcio EAGLE.</t>
@@ -20945,12 +22477,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -20960,17 +22492,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>DEADLINE_INFO: la plaza sigue publicada y aparece la ventana de revision de candidaturas, que la fila no tenia</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Revision continua de candidaturas a partir del 2026-10-08; sin fecha de cierre dura (plaza ROLLING). Preparar CV y carta antes del 2026-10-08 y escribir a la Language and Genetics group del MPI explicando que defiende en feb-2028 y no esta disponible hasta el 22-05-2027; confirmar si el contrato de 3 anos admite inicio diferido</t>
+          <t>Sigue viva tras un mes. Es la unica ROLLING de su linea exacta: escribir a Language and Genetics (MPI Nijmegen) presentandose como MD con pipeline GWAS/PRS propio y preguntar si aceptan incorporacion en 2028 (defensa ETA feb-2028); si contestan que no esperan tanto, pedir que la avisen de la siguiente convocatoria.</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -20985,7 +22517,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Tablon de la ISPG (ispg.net/resources/job-postings) anuncia revision continua desde el 2026-10-08; la pagina oficial de vacantes del MPI (mpi.nl/career-education/vacancies) confirma el 2026-09-14 que la plaza de 3 anos en Statistical Genomics/Genetic Epidemiology del grupo Language and Genetics sigue publicada, pero no reproduce la fecha</t>
+          <t>Reverificada 2026-09-21 en Tier 1: www.mpi.nl/career-education/vacancies la sigue listando como unica vacante sin 'DEADLINE HAS PASSED'. Ficha: https://www.mpi.nl/career-education/vacancies/vacancy/3-year-postdoctoral-research-scientist-position-statistical-0 ; la solicitud se envia por el formulario umantis de la columna URL.</t>
         </is>
       </c>
     </row>
@@ -21311,7 +22843,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-453</v>
+        <v>-459</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -21457,7 +22989,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -21599,7 +23131,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-136</v>
+        <v>-142</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -21764,39 +23296,39 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Abrir a mano el buscador de broadinstitute.avature.net y filtrar por McCarroll para confirmar si la plaza sigue viva; el listado no es navegable por agente dentro de presupuesto.</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>No aplicar ahora (publicado en jun 2026; ella no esta disponible hasta mediados de 2027 como pronto). Desde mediados de 2027, revisar el portal del Broad mensualmente; en paralelo, redactar un correo especulativo a Steven McCarroll para finales de 2027 encabezado por la combinacion MD+PhD y el articulo QIMR/Nature Mental Health. La proxima pasada: capturar la URL directa del anuncio y su fecha de cierre abriendo la ficha del portal.</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>https://broadinstitute.avature.net/careers</t>
@@ -21804,7 +23336,7 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Rama 3 (institucion directa). Leido en el portal Avature propio del Broad (Tier 1) el 2026-08-23, con 6 vacantes visibles. La vista de listado solo muestra titulo y fecha de publicacion: no expone URL por anuncio, ni cierre, ni salario, de ahi los campos vacios en vez de inventados.</t>
+          <t>Intento de re-verificacion el 2026-09-21 SIN exito: el portal Avature del Broad pagina de 6 en 6 (6 paginas) y el parametro searchKeyword se ignora, asi que la pagina 1 solo devuelve las ofertas mas recientes y el puesto McCarroll no aparece ni se puede descartar. NO es prueba de cierre. Se baja a UNVERIFIED por honestidad: la ultima verificacion real es del 2026-08-23.</t>
         </is>
       </c>
     </row>
@@ -21864,7 +23396,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-207</v>
+        <v>-213</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -22256,7 +23788,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>-11</v>
+        <v>-17</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -22394,7 +23926,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-8</v>
+        <v>-14</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -22518,7 +24050,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -22528,7 +24060,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -22562,12 +24094,12 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -22577,17 +24109,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>CONFLICTO PARCIALMENTE RESUELTO: NO son la misma plaza. La ref 459 de Cardiff es 'Research Assistant/Associate (Statistics)' del Centre for Trials Research (confirmada, cierre 17-09-2026), mientras que el puesto Moondance descrito en fuentes externas es de banco humedo (microglia en Alzheimer, procesado y tincion de cortes de tejido, edificio Hadyn Ellis), perfil incompatible con un puesto de estadistica. Ademas el texto Moondance coincide con un anuncio de Bright Network fechado en 2024, asi que esta fila puede venir de un anuncio caduco. El portal eploy ignora el parametro ?keywords= (devuelve los mismos 12 resultados de la pagina 1 para 'research assistant' y para 'dementia') y sigue sin servir las paginas 2 y 3, asi que no se puede confirmar ni descartar desde el portal. Proxima pasada: intentar la ficha de vacante por ID directo o el listado de la School of Medicine; si no aparece, cerrar la fila como caducada. Nota: el puesto Moondance es de laboratorio humedo y por tanto de bajo interes para ella aunque estuviera vivo.</t>
+          <t>Ninguna; plaza retirada.</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -22602,7 +24134,7 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>Rama 2, 2026-09-07: NO CONFIRMADO. El portal eploy de Cardiff responde en https://cardiffuniweb.eploy.net/vacancies/ pero solo devuelve la pagina 1 de 3 y la paginacion (?page=2) reenvia a la 1, asi que no se pudo ver el listado completo. En esa pagina 1 no hay nada de Moondance ni del MRC Centre for Neuropsychiatric Genetics; si hay un 'Research Assistant/Associate (Statistics)' del Centre for Trials Research, ref 459, con cierre 17-09-2026, la MISMA fecha de P-0014: posible confusion de identidad, sin resolver.</t>
+          <t>Re-verificado el 2026-09-21 en el portal eploy de Cardiff (cardiffuniweb.eploy.net, Tier 1): el listado completo son 12 vacantes y el Research Assistant del Moondance Dementia Laboratory ya no aparece. Su plazo era 2026-09-17.</t>
         </is>
       </c>
     </row>
@@ -22658,7 +24190,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-18</v>
+        <v>-24</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -22784,11 +24316,11 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>-13</v>
+        <v>-2</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -22822,12 +24354,12 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -22837,12 +24369,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -22862,7 +24394,7 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>Rama 2, 2026-09-07: plazo 01-09-2026 vencido. OJO: KCL Psychological Medicine tiene ahora un Clinical Research Fellow con cierre 18-09-2026 (DST268) que podria ser su reedicion; se registra como fila nueva y queda por confirmar si es el mismo puesto.</t>
+          <t>Re-verificado el 2026-09-21 en el buscador propio de KCL (Tier 1): la oferta 155765 Clinical Research Fellow (IoPPN, School of Academic Psychiatry, Denmark Hill) figura con cierre el 2026-09-18, NO el 2026-09-01 que teniamos. El plazo se extendio. CONFLICTO A VIGILAR: por titulo, centro y fecha de cierre, esta fila y P-0018 (jobs.ac.uk DST268) parecen la MISMA plaza duplicada desde dos fuentes.</t>
         </is>
       </c>
     </row>
@@ -23035,7 +24567,7 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -23045,7 +24577,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -23084,7 +24616,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -23094,17 +24626,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>No solicitar: exige titulo medico britanico o equivalente CON registro completo en el GMC y licencia en vigor, mas practica clinica activa (ECG e induccion de puncion lumbar), y arranca antes del fin de su residencia (22-05-2027). PI Prof Dag Aarsland, Centre for Healthy Brain Ageing; contrato de 12 meses, 45.943 GBP sin London Weighting. Guardar a Aarsland como contacto si le interesa el eje envejecimiento cerebral.</t>
+          <t>Comprobar si es la misma plaza que P-0016 y fusionar; si el IoPPN la reabre, merece la pena porque es de las pocas de Fit 3 que aceptan perfil clinico.</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -23119,7 +24651,7 @@
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>Rama 2 (tablones academicos). Leido en la pagina de resultados de jobs.ac.uk (busqueda 'psychiatric genetics', 2026-09-07); no se abrio el anuncio individual, de ahi LIKELY y no VERIFIED.</t>
+          <t>Re-verificado el 2026-09-21: su plazo (2026-09-18) ya ha vencido, y el buscador de KCL confirma esa misma fecha de cierre para la oferta 155765. Muy probablemente duplicado de P-0016.</t>
         </is>
       </c>
     </row>
@@ -23360,7 +24892,7 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -23370,7 +24902,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>Conflicto sin resolver: decode.com/careers no lista NINGUNA vacante concreta y solo remite al portal 50skills, que es JavaScript puro y llega vacio tanto por WebFetch como por curl. Confirmar la plaza de Reikiavik escribiendo directamente a deCODE (careers) en vez de seguir raspando el portal.</t>
+          <t>Abrir a mano careers.amgen.com y filtrar por localizacion Reykjavik; el portal no es legible por agente.</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -23385,7 +24917,7 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>Rama 5 (buzon y novedad), barrido de jobRxiv (SRC-0035) el 2026-09-07. Anuncio leido en jobRxiv (publicado 2026-08-22) y confirmado de forma independiente por researchersjob.com y por la pagina del programa de postdocs de Amgen; no se abrio la ficha del portal Workday de Amgen, de ahi LIKELY y no VERIFIED. CONFLICTO A VIGILAR: la pagina del programa Amgen R&amp;D solo lista Thousand Oaks, San Francisco, Burnaby y Copenhague como sedes de postdocs, no Reykjavik, mientras el anuncio situa la plaza en Amgen deCODE genetics (Reykjavik); no se pudo reconciliar.</t>
+          <t>Intento de re-verificacion el 2026-09-21 SIN exito, y CORRECCION AL BRIEF: careers.amgen.com NO funciona bien para un agente. Responde 200 pero sirve una landing de tipo SPA sin ninguna oferta en el HTML; dos formas de URL de busqueda distintas (keywords=deCODE statistical genetics y keywords=Reykjavik) devolvieron la misma landing sin listados. Last_Verified se deja como estaba porque no se verifico nada.</t>
         </is>
       </c>
     </row>
@@ -23751,7 +25283,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>-105</v>
+        <v>-111</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -24280,7 +25812,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -24294,7 +25826,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -24333,27 +25865,27 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>No solicitar. Guardar a Andre Altmann (UCL) como contacto para 2027: su grupo une genetica estadistica y neuroimagen, combinacion que ella busca.</t>
+          <t>Si aun interesara (Fit 2), que ella compruebe a mano el portal propio de UCL: el anuncio se ha retirado antes del plazo publicado y eso suele significar plaza cubierta o convocatoria suspendida</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -24364,7 +25896,7 @@
       </c>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>Rama 2, jobs.ac.uk (SRC-0002), busqueda 'statistical genetics' el 2026-09-14. Ficha individual abierta y leida: fechas, salario, PIs y criterios tomados del anuncio.</t>
+          <t>Re-verificado el 2026-09-21: la URL DSW126 de jobs.ac.uk ya no muestra la ficha ('The job you're looking for is no longer being advertised') y redirige al listado general. CONFLICTO declarado: el plazo publicado era el 2026-10-04, dos semanas por delante, asi que el anuncio se ha retirado antes de tiempo; no se ha verificado en el portal propio de UCL.</t>
         </is>
       </c>
     </row>
@@ -24412,7 +25944,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>53100</t>
+          <t>53100-58800 aprox (GBP 46189-51174 incl. London Weighting)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -24432,7 +25964,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -24471,22 +26003,22 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -24502,7 +26034,7 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Rama 2, jobs.ac.uk (SRC-0002), busqueda 'polygenic risk score' el 2026-09-14. Datos leidos en la pagina de resultados; no se abrio la ficha individual, de ahi LIKELY.</t>
+          <t>Re-verificado el 2026-09-21 por DOS ramas y con una discrepancia de confianza que se deja escrita en vez de resolverse en silencio. Rama 2 abrio la ficha DSU830 de jobs.ac.uk (Tier 2): sigue abierta, cierre 2026-09-23, publicada el 2026-09-03 por Medical &amp; Molecular Genetics de KCL, salario GBP 46.189-51.174 con London Weighting, y aparece ademas bajo la palabra clave 'polygenic'. Rama 3 vio en el buscador propio de KCL (Tier 1) un Bioinformatician (oferta 157045, Faculty of Life Sciences &amp; Medicine, Guy's Hospital) con la MISMA fecha de cierre, casi con seguridad la misma plaza, pero no abrio la ficha individual. Se fija Confidence = LIKELY (dos fuentes independientes coinciden) y no VERIFIED, porque nadie llego a leer la ficha Tier 1 completa.</t>
         </is>
       </c>
     </row>
@@ -24524,12 +26056,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Institute for Molecular Bioscience - Program in Complex Trait Genomics (PCTG)</t>
+          <t>Institute for Molecular Bioscience (IMB) - entorno de genomica estadistica de Loic Yengo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Loic Yengo</t>
+          <t>Prof. Loic Yengo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -24549,12 +26081,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Hasta 2.5 anos</t>
+          <t>hasta 2,5 anos, jornada completa</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>~60000-80000 (AUD 106294-113660 Level A / AUD 119463-141545 Level B, + 17% superannuation)</t>
+          <t>61700-82100 aprox (AUD 106294-113660 nivel A / AUD 119463-141545 nivel B, mas 17% de superannuacion)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -24574,11 +26106,11 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>PhD en genetica estadistica/cuantitativa, biologia computacional, estadistica o data science; estadistica bayesiana; modelizacion matematica; programacion en C/C++, Python o R; datasets genomicos a gran escala y single-cell omics valorados; productividad investigadora acorde a la etapa</t>
+          <t>Doctorado (se admiten tanto recien doctorados como postdocs con recorrido); desarrollo de metodos estadisticos para datos genomicos y omicos de celula unica a gran escala, identificacion de variacion causal, prediccion de fenotipos y priorizacion de genes en poblaciones geneticamente diversas; se espera transitar hacia laboratorio propio en 5 anos y, en nivel B, liderar solicitudes de financiacion; supervision de estudiantes</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -24588,7 +26120,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Es su linea 1 literal (genetica estadistica de rasgos complejos) en el grupo de referencia mundial del area, el PCTG que ella ya conoce de oidas por su estancia en QIMR Berghofer (mismo ecosistema de Brisbane), y el perfil MD le daria valor en la interpretacion clinica de fenotipos; pero NO es elegible por calendario: el plazo cierra el 13-10-2026, ella sigue de residente en Malaga hasta el 22-05-2027 y no defiende tesis hasta feb-2028, y el anuncio exige doctorado concedido. Ademas el puesto es de DESARROLLO de metodos (bayesiano, C/C++, track record de publicaciones y de solicitudes de financiacion) y ella es usuaria aplicada de PLINK/R sin publicaciones destacadas: hoy no competiria. Valor real de la fila: es el arquetipo exacto de plaza a la que debe poder optar en 2028 y el anuncio dice que el grupo capta 'recent PhD graduates'; ademas fija dos datos utiles, el rango salarial y que Yengo esta construyendo equipo. Australia exige patrocinio de visado (no es UE). Accion: escribir a Loic Yengo (IMB/PCTG) en 2027 presentandose como MD-PhD en genetica estadistica con contactos previos en QIMR Berghofer y preguntando por vacantes o por un esquema NHMRC/fellowship con fecha de inicio 2028.</t>
+          <t>Es genetica estadistica de rasgos complejos pura -su linea 1- en el grupo de Loic Yengo en el IMB, uno de los sitios de referencia mundiales, y ella ya tiene vinculo australiano vivo (estancia en QIMR Berghofer) y stack propio (PLINK, R, pipelines GWAS-PRS a nivel independiente). Lo que la deja en 3 y no en 5 es el reloj, no el tema: la plaza se cierra el 12-13 de octubre de 2026 y arranca de inmediato, mientras ella no defiende hasta febrero de 2028 (ETA) y no esta libre hasta el fin de la residencia el 22-05-2027; ademas el anuncio esta escrito para 'recien doctorados o postdocs' con recorrido publicable, y ella solo tiene dos primeros autores en revision. Condiciones publicadas: 2,5 anos, AUD 106.294-113.660 (nivel A) o 119.463-141.545 (nivel B) mas 17% de superannuacion, campus de St Lucia; el anuncio no menciona patrocinio de visado, que ella necesitaria por no ser ciudadana australiana. Accion util: escribir a Yengo presentandose para la siguiente ronda (2027-2028) con el gancho del manuscrito de QIMR en revision en Nature Mental Health y el perfil MD+PhD.</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -24613,27 +26145,27 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>No aplicable ahora por calendario: guardar el anuncio como plantilla y contactar a Loic Yengo a finales de 2027 para vacantes con inicio 2028</t>
+          <t>No presentarse a R-68861 (el reloj no cuadra). Escribir a Loic Yengo en otono de 2027 y vigilar cnsgenomics.com/content/recruitment y la API Workday de UQ para la siguiente convocatoria</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -24644,7 +26176,7 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Portal Workday oficial de UQ consultado por su API publica (POST a /wday/cxs/uq/uqcareers/jobs y GET de la ficha): titulo, fechas 2026-09-11/2026-10-13, salario y criterios leidos integros. La pagina de reclutamiento del PCTG (cnsgenomics.com/content/recruitment) enlaza a UQ jobs.</t>
+          <t>Re-verificado el 2026-09-21 por la API publica Workday de UQ (SRC-0127), porque la ficha HTML es una SPA vacia para el fetch: canApply=true, postedOn 'Posted 9 Days Ago', startDate 2026-09-11, endDate 2026-10-13. CONFLICTO de plazo declarado: el cuerpo del anuncio dice 'Applications close Monday 12 October 2026 at 11.00pm AEST' mientras el campo endDate de Workday marca 2026-10-13; se mantiene 2026-10-13 en la columna pero el limite real para la dueña es el 12 de octubre AEST.</t>
         </is>
       </c>
     </row>
@@ -24688,7 +26220,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>~39000-42000 (GBP 33951-36636)</t>
+          <t>GBP 33951-36636 (Grade 5)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -24704,7 +26236,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -24739,22 +26271,22 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -24770,7 +26302,7 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Portal oficial eploy de Cardiff (30 vacantes en total, unica coincidencia con psiquiatria/genetica); fecha de cierre leida en el listado oficial</t>
+          <t>Re-verificado el 2026-09-21 en cardiffuniweb.eploy.net (vacante ID 447, Division of Psychological Medicine and Clinical Neurosciences): sigue abierta, cierra el 2026-09-25, salario Grade 5 GBP 33.951-36.636.</t>
         </is>
       </c>
     </row>
@@ -24822,7 +26354,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>~52000-56000 (GBP 45031-48607 incl. London Weighting)</t>
+          <t>51800-55900 aprox (GBP 45031-48607 incl. London Weighting)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -24838,7 +26370,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -24873,27 +26405,27 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Ninguna; fuera de linea y fuera de plazo para ella</t>
+          <t>Cierra HOY 2026-09-21: con Fit 2 y sin disponibilidad hasta 2027 no procede presentarse; la semana que viene ya se podra cerrar la fila</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -24904,7 +26436,7 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Ficha oficial de KCL leida entera (salario, duracion y cierre); localizada con la busqueda por termino del portal, que si expone los puestos del IoPPN</t>
+          <t>Re-verificado el 2026-09-21 en la ficha Tier 1 de KCL (157565): sigue abierta, publicada el 2026-09-07, cierre 2026-09-21, salario GBP 45.031-48.607 incl. London Weighting</t>
         </is>
       </c>
     </row>
@@ -24962,7 +26494,7 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
@@ -24972,7 +26504,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -25007,27 +26539,27 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Ninguna</t>
+          <t>Ninguna: plazo vencido el 2026-09-16 y la ficha ya no existe</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -25038,7 +26570,7 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>Ficha oficial de KCL leida entera</t>
+          <t>Re-verificado el 2026-09-21: la ficha de KCL (155527) devuelve HTTP 404, es decir retirada del portal; el plazo publicado (2026-09-16) ya habia vencido</t>
         </is>
       </c>
     </row>
@@ -25084,7 +26616,11 @@
           <t>3 anos</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>70404</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
@@ -25092,7 +26628,14 @@
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>5</v>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Doctorado; estabilidad del genoma y neurotoxicidad (perfil de laboratorio molecular)</t>
@@ -25126,27 +26669,27 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Ninguna</t>
+          <t>Ninguna. Cierra el 2026-09-25 (4 dias) y ella no esta disponible hasta mediados de 2027; ademas es estabilidad del genoma y neurotoxicidad, no genetica estadistica. Se mantiene la fila solo para no redescubrirla.</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr"/>
@@ -25157,7 +26700,7 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Listado oficial werkenbijerasmusmc (131 vacantes; unica coincidencia con genetica); ficha individual no abierta por presupuesto, sin fecha de cierre publicada en el listado</t>
+          <t>Re-verificado el 2026-09-21 en werkenbijerasmusmc.nl (Tier 1): sigue publicada. En todo el portal de Erasmus MC solo hay dos postdocs ahora mismo (este y uno de artrosis de rodilla); nada de epidemiologia genetica ni de genetica del sueno.</t>
         </is>
       </c>
     </row>
@@ -25207,7 +26750,7 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -25253,27 +26796,27 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Abrir la ficha la proxima pasada para leer requisitos y confirmar si hay linea de genetica psiquiatrica asociada</t>
+          <t>Ninguna; la ficha ha desaparecido del portal.</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
@@ -25284,7 +26827,7 @@
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>Listado en el portal oficial Avature del Broad con fecha de publicacion 10-09-2026; ficha individual no abierta por presupuesto</t>
+          <t>Re-verificado el 2026-09-21: la ficha Avature .../JobDetail/Computational-Scientist-II-Karczewski-Lab/22501 devuelve HTTP 404 y la ref 44894 tampoco aparece en el listado de careers. Dos senales coincidentes: se da por cerrada.</t>
         </is>
       </c>
     </row>
@@ -25306,10 +26849,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>No indicado en el listado</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>Haber Lab / Klarman Cell Observatory</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Dr. Haber</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>Cambridge, MA</t>
@@ -25326,7 +26873,11 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>aprox. 65000-86000 (convertido de USD 70.000-92.667 publicados)</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
@@ -25341,7 +26892,7 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>No leidos (ficha individual no abierta); postdoc de biologia computacional, presencial</t>
+          <t>Doctorado en biologia computacional, machine learning, ciencia de datos o campo cuantitativo afin; valorable experiencia con ensayos genomicos tipo RNA-seq y conocimiento de biologia pulmonar / inmunologia de mucosas; presencial en Cambridge MA</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -25376,22 +26927,22 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -25407,12 +26958,728 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>Listado en el portal oficial Avature del Broad con fecha de publicacion 04-09-2026; ficha individual no abierta por presupuesto</t>
+          <t>Re-verificado el 2026-09-21 abriendo la ficha Avature (Tier 1): sigue publicada, sin fecha de cierre. Se anade lo que faltaba: es el Haber Lab / Klarman Cell Observatory, salario USD 70.000-92.667, publicada el 2026-09-04, presencial. Confirma el Fit bajo: el contenido es inmunologia de mucosas y biologia pulmonar, no genetica estadistica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P-0036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Research Scientist - Maternal Sleep</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Faculty of Life Sciences &amp; Medicine - AI &amp; Personalised Health</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Josip Car (Josip.car@kcl.ac.uk)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>London (Guy's Campus)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Research Scientist (duracion determinada, jornada completa)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>4 anos</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>62000-72800 aprox (GBP 53947-63350 incl. London Weighting)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>29</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Doctorado en fisiologia del sueno o respiratoria, epidemiologia, ingenieria biomedica o afin; experiencia postdoctoral relevante y publicaciones; ESENCIAL experiencia con medicion objetiva del sueno (PSG y/o test domiciliario de apnea); conocimiento de desenlaces maternos y perinatales; analisis longitudinal en R o Python; el puesto NO incluye actividad clinica pero admite perfil medico</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Toca su tercera linea (sueno) y admite perfil medico, pero lo esencial es polisomnografia y desenlaces perinatales -nada de genetica- y exige experiencia postdoctoral ya hecha, mientras ella no estara disponible hasta 2027-2028.</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Perfil muy especifico (PSG + salud materno-perinatal) que estrecha mucho el campo, pero es Londres, 4 anos y salario alto</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>No presentarse; sirve para no redescubrirla y como senal de que el grupo de Josip Car (AI &amp; Personalised Health) contrata en sueno: guardar el contacto por si sale algo de genetica del sueno en 2027</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/158385-research-scientist-maternal-sleep</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Ficha Tier 1 del portal de KCL, alcanzada desde /jobs/search?term=sleep el 2026-09-21; tambien aparece listada en jobs.ac.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P-0037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow (Genetic Epidemiology and Bioinformatics)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>National Institutes of Health (NIH), programa intramural</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No identificado: la ficha del tablon OITE devuelve 403 al fetch automatico</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>no identificado</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bethesda, Maryland (por confirmar)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow (intramural NIH)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>no publicado en la fuente accesible</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>no publicado en la fuente accesible</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>verano de 2026 segun el extracto indexado (fecha ya pasada: probable anuncio caducado o renovado)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>no publicado: el anuncio del tablon OITE no muestra fecha de cierre en el extracto disponible y la ficha completa devuelve 403</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Doctorado en epidemiologia genetica, genetica estadistica o bioinformatica; experiencia analizando datos omicos de alto rendimiento y puntuaciones de riesgo poligenico (PRS); programas intramurales del NIH aplican reglas de nacionalidad o visado que NO se han podido verificar en esta pasada</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>En tema es lo mas cercano a su nucleo que ha aparecido esta semana: epidemiologia genetica + PRS es exactamente su linea 1-2 y su stack real (PLINK, R, pipelines GWAS-PRS a nivel independiente), y el NIH valora el perfil MD+PhD para fenotipado clinico. Se queda en 3, no en 4, por tres condiciones sin resolver: (a) la ficha Tier 1 devuelve 403 y no he podido leer requisitos, plazo ni estipendio -el extracto indexado habla de inicio en verano de 2026, que ya paso, asi que puede estar caducado-; (b) la fecha objetivo de inicio es incompatible con su disponibilidad (mediados de 2027 sin doctorado, feb-2028 con el); (c) EE.UU. exige patrocinio de visado y el NIH intramural lo canaliza por la figura de Visiting Fellow, mientras que el programa PIRA del NIMH si exige ciudadania o residencia permanente. Si la plaza le interesa, lo accionable no es esta ficha concreta sino vigilar el tablon OITE a partir de mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Los postdocs intramurales del NIH se anuncian globalmente y compiten con candidatos estadounidenses sin friccion de visado</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>Que ella abra la ficha a mano en el navegador (training.nih.gov devuelve 403 a agentes) y confirme plazo, estipendio, laboratorio y regla de nacionalidad; si esta caducada, dejar el tablon OITE en seguimiento para 2027</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>https://www.training.nih.gov/jobs/pd-010127/</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Tier 1 localizado por busqueda web restringida a dominios nih.gov; la ficha y el indice del tablon devuelven HTTP 403 al fetch automatico (un solo intento, no reintentado). Datos tomados del extracto indexado, por eso UNVERIFIED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P-0038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ayudante de Investigacion Postdoctoral - Unidad de Investigacion Clinica en Inmunoterapia del Cancer CNIO-HMarBCN (AIPOSCNIO-HMarBCN)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CNIO (Centro Nacional de Investigaciones Oncologicas)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Unidad de Investigacion Clinica en Inmunoterapia del Cancer CNIO-Hospital del Mar Barcelona (Programa de Investigacion Clinica)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>no publicado; contacto empleo@cnio.es</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Contrato laboral por obra/proyecto de investigacion</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>no publicada (ligada al proyecto)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>30758-35669</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>no publicada</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>6</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Doctorado en Biomedicina/Inmunologia obtenido hace menos de 1 ano; preferible formacion sanitaria especializada (MIR/BIR/FIR) en Inmunologia; minimo 6 anos de experiencia en investigacion en inmunologia; cultivo celular, transfeccion, citometria de flujo, vectores lentivirales, modificacion de linfocitos; certificado de experimentacion animal; ingles C1</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Inmunologia experimental humeda (vectores lentivirales, citometria, experimentacion animal) con 6 anos de experiencia exigidos y doctorado de hace menos de un ano: ni la tecnica ni el reloj encajan, y ella no estaria disponible antes de mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Convocatoria abierta del CNIO con perfil muy especifico (inmunologia + MIR/BIR/FIR), lo que estrecha mucho el campo</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>Ninguna: se registra solo para no volver a descubrirlo. Util como prueba de que el canal del CNIO esta vivo y publica postdocs con salario.</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>https://www.cnio.es/empleo/ayudante-de-investigacion-postdoctoral-para-la-unidad-de-investigacion-clinica-en-inmunoterapia-del-cancer-cnio-hmarbcn-aiposcnio-hmarbcn/</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Tier 1, pagina propia del CNIO (https://www.cnio.es/acerca-del-cnio/ofertas-de-empleo/), abierta sin bloqueo el 2026-09-21. Es el unico postdoc del listado del CNIO en esta pasada; el resto son predoctorales, tecnicos y administracion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P-0039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Genetista en Servicio de Apoyo a la Investigacion de Farmacogenomica (ref. 98_2026)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>IiSGM - Instituto de Investigacion Sanitaria Gregorio Maranon</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Grupo de Farmacia Hospitalaria y Farmacogenomica</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>no publicado en el listado</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Contrato de servicio de apoyo a la investigacion (convocatoria del IiSGM)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>no publicada en el listado</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>no publicado en el listado</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>no publicada</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>no publicada (convocatoria listada como Abierta el 2026-09-21)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>6</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Grado Universitario en Genetica; trabajo de genetista en una unidad de apoyo de farmacogenomica hospitalaria</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>La farmacogenomica hospitalaria toca su especialidad de Medicina de Laboratorio, pero la convocatoria pide Grado en Genetica y ella es medica, asi que probablemente no sea elegible por titulacion; ademas cierra el 2026-09-26 y ella no esta disponible hasta mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Convocatoria publica de un IIS grande de Madrid con requisito de titulacion estrecho</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>No presentarse ahora. Valor real: el IiSGM saca convocatorias de este tipo con regularidad y su listado se lee sin bloqueo; conviene revisarlo cada pasada y mirar si alguna admite titulacion en Medicina.</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>https://www.iisgm.com/ofertas-de-empleo/</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Tier 1, listado propio del IiSGM leido el 2026-09-21 (tres convocatorias abiertas: 94_2026, 96_2026 y 98_2026). Fuente NUEVA para esta rama.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P-0040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Busqueda de candidatos con perfil postdoctoral - Area de Genomica y Genetica (contratos postdoctorales publicos)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>IIS-FJD - Instituto de Investigacion Sanitaria Fundacion Jimenez Diaz</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Area de Genomica y Genetica, grupo de Genetica del Desarrollo Ocular</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Dra. Marta Corton</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Acogida de candidatos para solicitar contratos postdoctorales publicos (tipo Sara Borrell / Juan de la Cierva)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>la del contrato publico que se consiga</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>no publicado (el del programa publico correspondiente)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ligada a la resolucion de la convocatoria publica</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>no confirmada</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>sin fecha confirmada: fjd.es devuelve 403 al fetch automatico, asi que no se pudo leer la ficha; un resultado de buscador menciona un plazo de 2026-07-17 con inicio 2026-09-01 que parece ser el ciclo YA pasado, no el vigente</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Doctorado en Biomedicina o disciplinas afines; interes en concurrir a convocatorias publicas de contratos postdoctorales; area de genomica y genetica</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>El mecanismo es exactamente la via espanola que le interesa (un grupo que te acoge para presentarte a un Sara Borrell), pero el grupo concreto es genetica del desarrollo ocular, no genetica estadistica ni psiquiatrica, y su doctorado no estara defendido hasta feb-2028 (ETA), fuera del ciclo actual.</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>No se pudo leer la ficha (403); la competencia real la marca la convocatoria publica, no el centro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>Abrir a mano la pagina de ofertas del IIS-FJD (el 403 es solo contra agentes) y comprobar si el area de genomica repite la llamada para el ciclo 2027-2028; si repite, es el patron a replicar con grupos CIBERSAM que si hagan genetica psiquiatrica.</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>https://www.fjd.es/iis-fjd/es/formacion-empleo/ofertas-empleo</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Existencia y descripcion via resultado de buscador; la ficha propia (Tier 1) devolvio HTTP 403 en un unico intento, no se reintento. Fuente NUEVA para esta rama. NUEVO BLOQUEO A REGISTRAR: fjd.es = 403.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD36"/>
+  <autoFilter ref="A1:AD41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -25423,7 +27690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB15"/>
+  <dimension ref="A1:AB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -25437,7 +27704,7 @@
     <col width="52" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="52" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
@@ -25913,7 +28180,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sin movimiento esta semana y con el expediente ahora mucho mejor fechado. El listado de audiencia e informacion publica de Sanidad, abierto hoy, tiene dos proyectos vivos (formulas infantiles y cereales, DG/73/26, plazo 8 a 29-09-2026; dependencia electromedica, DG/72/26, hasta 11-09-2026) y ninguno de Genetica: los dos reales decretos siguen sin llegar a audiencia publica. Dos hallazgos Tier 1 nuevos ordenan la cronologia y CIERRAN el conflicto con la AEGH que quedo abierto la pasada anterior. Primero, la nota de prensa 6697 del Ministerio, de 13-06-2025, dice que lo aprobado es la CREACION de las dos especialidades en respuesta al acuerdo de la Comision de Recursos Humanos del SNS de diciembre de 2024: eso es un acuerdo ministerial, no un real decreto publicado en el BOE, y es lo que la AEGH llama aprobacion. Segundo, existe el documento de consulta publica previa del proyecto de real decreto del titulo de especialista en Genetica de Laboratorio, fechado el 01-07-2025 y tramitado al amparo del articulo 133 de la Ley 39/2015: confirma que a julio de 2025 el expediente estaba todavia en el escalon anterior a la audiencia publica. La nota de prensa confirma tambien lo que esta fila ya sostenia: seran dos reales decretos independientes, ambas especialidades duraran cuatro anos, Genetica Medica quedara reservada a Medicina y Genetica de Laboratorio se abrira a Medicina, Farmacia, Biologia, Quimica y Veterinaria. Lo que sigue sin existir en ningun texto oficial es la disposicion transitoria: ni la nota de prensa ni el documento de consulta previa la mencionan, asi que la hipotesis de que exigira anos de ejercicio al modo de Pediatria y Urgencias sigue siendo hipotesis, y el riesgo para ella es el mismo: al acabar la residencia en mayo de 2027 no tendra anos de ejercicio en genetica que acreditar. Balance temporal: 15 meses desde la consulta publica previa y 21 desde el acuerdo de la Comision de RRHH sin borrador en audiencia publica.</t>
+          <t>Sigue sin haber movimiento y la espera ya es el dato. Listado de audiencia e informacion publica del Ministerio abierto hoy: solo dos proyectos vivos, DG/79/26 (orden de actualizacion de la cartera comun de servicios y de la prestacion ortoprotesica, del 15-09 al 06-10-2026) y DG/73/26 (real decreto de promocion y publicidad de formulas infantiles, del 08 al 29-09-2026); ha cerrado el DG/72/26 que figuraba la pasada anterior. Ninguno es de Genetica: los dos reales decretos no han entrado en audiencia publica. Lo nuevo de esta pasada es que la cronologia queda fechada hasta el ultimo escalon conocido. Las resoluciones de la Direccion General de Ordenacion Profesional que acordaron iniciar el procedimiento de elaboracion de ambos reales decretos son de junio de 2025; la consulta publica previa del titulo de Genetica de Laboratorio es de 01-07-2025; y el 23-12-2025 la propia Direccion General declaro que los borradores y las memorias de analisis de impacto normativo estaban practicamente ultimados y que los textos saldrian en breve a informacion y audiencia publica. Desde ese en breve han pasado NUEVE MESES sin que aparezcan en el listado, quince desde la consulta publica previa y veintiuno desde el acuerdo de la Comision de Recursos Humanos del SNS de diciembre de 2024. Esa declaracion de diciembre de 2025 es prensa sectorial, Tier 2, no una fuente oficial, y como tal se registra. La misma prensa sostiene que Sanidad apunta a ofertar las primeras plazas de Genetica en la convocatoria MIR de 2027, lo que exigiria publicar los reales decretos con bastante antelacion; no lo confirma ningun documento oficial y no se da por bueno, pero es el unico indicio de calendario que existe y conviene vigilarlo porque, de cumplirse, el borrador tendria que salir a audiencia en los proximos meses. Para ELLA nada cambia en lo esencial y ese es el riesgo: lo que sigue sin existir en ningun texto oficial es la disposicion transitoria de acceso excepcional al titulo. Ni la nota de prensa de 13-06-2025, ni el documento de consulta publica previa, ni las declaraciones de diciembre la mencionan. La hipotesis de que exigira acreditar anos de ejercicio en el area al modo de Pediatria y Urgencias sigue siendo hipotesis, y si se confirma ella no cumplira al terminar la residencia de Laboratorio Clinico en mayo de 2027. Cada mes de retraso empeora su posicion por partida doble: retrasa la via y aumenta la probabilidad de que el periodo de ejercicio exigible se cuente hacia atras desde una fecha en la que ella todavia no ejercia</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -25938,7 +28205,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -25948,7 +28215,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -25958,7 +28225,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Seguir revisando cada semana el listado de audiencia publica de Sanidad; a partir de ahora vigilar tambien el paso previo, la consulta publica previa, y el buzon proyectosnormativos-dgorden@sanidad.gob.es como via de alegaciones cuando aparezca el borrador; en el BOE buscar por titulo cada mes. Si en 2027 sigue sin haber borrador, escribir a la AEGH preguntando si la disposicion transitoria acreditara anos de ejercicio y si computara la residencia de Laboratorio Clinico.</t>
+          <t>Seguir revisando cada semana el listado de audiencia publica de Sanidad y tambien el escalon previo de consulta publica; en el BOE buscar por titulo cada mes. Novedad a vigilar con prioridad: si la prensa sectorial acierta y Sanidad quiere plazas de Genetica en el MIR 2027, el borrador tiene que salir a audiencia en los proximos meses, asi que un vistazo semanal al listado es ahora mas rentable que nunca. Cuando aparezca el borrador, alegar por el buzon proyectosnormativos-dgorden@sanidad.gob.es sobre el computo de la residencia de Laboratorio Clinico. Si en 2027 sigue sin haber borrador, escribir a la AEGH preguntando por la disposicion transitoria</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -25973,7 +28240,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>Rama 4, pasada del 2026-09-07. Verificado en Tier 1: listado de audiencia publica del Ministerio de Sanidad (SRC-0055) abierto y leido hoy, con un solo proyecto vivo y ninguno de Genetica. La ausencia en el BOE se comprobo por busqueda acotada al dominio boe.es (el formulario GET de boe.es/buscar/legislacion.php devuelve 'Los valores de busqueda enviados son incorrectos', bloqueo nuevo que conviene anotar): esa parte es LIKELY, no VERIFIED. CONFLICTO AEGH: SIGUE ABIERTO Y NO LO CIERRO. Abri hoy aegh.org y su portada NO contiene ninguna afirmacion de aprobacion en Consejo de Ministros ni de publicacion en BOE; solo un anuncio del Secretario de Estado de que las especialidades podrian ver la luz en julio. Es decir, no he podido reproducir el texto conflictivo ni localizar la pagina exacta que lo contiene. La hipotesis de la pasada anterior sigue en pie y ahora tiene un candidato concreto: el RD 203/2025, de 18 de marzo (BOE-A-2025-5405), que modifica el RD 589/2022 sobre formacion sanitaria especializada, si fue aprobado en Consejo de Ministros y publicado en BOE, y es la norma que la nota de prensa 6637 del Ministerio presenta como aprobada. No hay prueba de que sea el referente del texto de la AEGH, asi que el conflicto queda escrito, no resuelto.</t>
+          <t>Rama 4, pasada del 2026-09-21. Tier 1 abierto y leido hoy: listado de audiencia e informacion publica del Ministerio de Sanidad (SRC-0055), con los dos unicos proyectos vivos identificados por codigo y plazo y ninguno de Genetica. La ausencia en el BOE se comprobo por busqueda acotada al dominio boe.es, que sigue sin devolver ningun real decreto de Genetica Medica ni de Genetica de Laboratorio y si el RD 101/2025 de Laboratorio Clinico: esa parte es LIKELY, no VERIFIED, y se mantiene anotado que el formulario GET de boe.es/buscar/legislacion.php esta bloqueado para un agente. Las fechas de junio de 2025 (resoluciones de inicio) y de 23-12-2025 (borradores practicamente ultimados, salida en breve a audiencia) y la referencia al MIR 2027 proceden de prensa sectorial concordante (Gaceta Medica, ConSalud, iSanidad, Infobae/Europa Press, Genotipia), varios medios independientes que coinciden: Tier 2, registrado como tal. CONFLICTO AEGH: sigue abierto y no se reabrio esta semana por presupuesto; la hipotesis viva sigue siendo que el texto de la AEGH se refiera al RD 203/2025 de formacion sanitaria especializada y no a un real decreto de Genetica</t>
         </is>
       </c>
     </row>
@@ -26676,7 +28943,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-49</v>
+        <v>-55</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -26805,7 +29072,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Titulo de especialista de la categoria (Analisis Clinicos / Bioquimica Clinica, previsiblemente Laboratorio Clinico tras el RD 101/2025); nacionalidad UE; inscripcion telematica en la aplicacion BAPE con autobaremo, sin aportar documentacion en el momento del alta; los meritos se acreditan despues, cuando lo requiera la resolucion; los cortes de baremacion son anuales (ultima resolucion de corte publicada el 14-01-2026)</t>
+          <t>Titulo de especialista de la categoria (Analisis Clinicos / Bioquimica Clinica, previsiblemente Laboratorio Clinico tras el RD 101/2025); nacionalidad UE; inscripcion telematica en la aplicacion BAPE con autobaremo, sin aportar documentacion en el momento del alta. PLAZO ESPECIFICO CONFIRMADO PARA QUIEN TERMINA RESIDENCIA: el articulo 15 de la ORDEN SAN/713/2016, de 29 de julio (BOCyL de 25-08-2016), da a los especialistas DOS DIAS HABILES desde el dia siguiente a la finalizacion oficial de la formacion especializada para registrarse en la aplicacion de bolsa. El dia de finalizacion cuenta como dia de formacion, y tener el certificado de fin de residencia antes de esa fecha, por vacaciones u otras razones, NO adelanta el computo: la fecha que vale es la que fija el Ministerio de Sanidad en sus guias del residente. Quien termine con posterioridad a la fecha oficial debe comunicarlo al Servicio de Seleccion de la Direccion General de Personal y Desarrollo Profesional (Paseo de Zorrilla n 1, 47007 Valladolid) y dispone igualmente de dos dias habiles. Los cortes de baremacion son anuales (ultima resolucion de corte publicada el 14-01-2026)</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -26815,7 +29082,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Es una via PERMANENTE, del tipo que sobrevive a su calendario: ella no puede presentarse a nada que se cierre antes del 22-05-2027, y esta bolsa admite altas en cualquier momento con cortes anuales de baremacion, asi que basta con inscribirse el mismo dia que acabe la residencia. La categoria existe y esta viva: la pagina de convocatorias abiertas de Sacyl nombra literalmente Licenciado Especialista en Analisis Clinicos y en Bioquimica Clinica, que son los titulos que el RD 101/2025 sustituye por Laboratorio Clinico, el que ella obtendra. La solicitud es ligera (alta telematica y autobaremo; la documentacion se aporta despues), de ahi el esfuerzo XS-S, pero conviene tener el expediente de meritos ordenado antes de mayo de 2027 porque el autobaremo decide el orden en la lista. No hay sueldo publicado en la pagina: seria el de FEA estatutario temporal de Castilla y Leon. Sin visado ni homologacion (ciudadana UE con titulo espanol). Una regla vista en un PDF de Sacyl y NO confirmada por mi: quien termina el MIR tendria dos dias habiles desde el fin de la formacion para inscribirse en la bolsa; si se confirma, es critico, porque significa inscribirse el 25-05-2027 y no cuando le venga bien. Hay que abrir ese PDF antes de 2027. A quien escribir: al Servicio de Seleccion de Personal de la Gerencia Regional de Salud, preguntando a que categoria de bolsa se mapea el nuevo titulo de Laboratorio Clinico.</t>
+          <t>Es una via PERMANENTE, del tipo que sobrevive a su calendario: ella no puede presentarse a nada que se cierre antes del 22-05-2027, y esta bolsa admite altas en cualquier momento con cortes anuales de baremacion. La categoria existe y esta viva: la pagina de convocatorias abiertas de Sacyl nombra literalmente Licenciado Especialista en Analisis Clinicos y en Bioquimica Clinica, los titulos que el RD 101/2025 sustituye por Laboratorio Clinico, que es el que ella obtendra. La solicitud es ligera (alta telematica y autobaremo, la documentacion se aporta despues), de ahi el esfuerzo XS-S, pero el autobaremo decide el orden en la lista, asi que el expediente de meritos tiene que estar ordenado antes. EL ENCARGO PENDIENTE QUEDA RESUELTO Y LA REGLA ERA REAL: abierto hoy el PDF de procedimiento de inscripcion FIN MIR/EIR de Sacyl, confirma que el plazo son DOS DIAS HABILES contados desde el dia siguiente a la finalizacion oficial de la residencia, por el articulo 15 de la ORDEN SAN/713/2016. Esto convierte la fila en una tarea con reloj de precision y no en una gestion tranquila: si se pasa esos dos dias, pierde la via especifica de alta como fin de residencia. Un matiz critico que el PDF obliga a anotar: la fecha que cuenta no es la de su contrato sino la fecha oficial de finalizacion del programa que publica el Ministerio en la guia del residente, y las fechas de 2025 que el propio PDF tabula lo demuestran, porque los R4 terminaron el 19-07-2025 y los R2/EIR el 22-05-2025, es decir el dia de fin varia por promocion y no coincide necesariamente con el aniversario del contrato. Si su fecha oficial fuera el 22-05-2027, que cae en sabado, los dos dias habiles serian el lunes 24 y el martes 25 de mayo de 2027, y su limite real de inscripcion seria el 25-05-2027. Si el Ministerio fija julio, como a los R4 de 2025, todo el calculo se desplaza. Sin sueldo publicado en la pagina: seria el de FEA estatutario temporal de Castilla y Leon. Sin visado ni homologacion, ciudadana UE con titulo espanol. A quien escribir: Servicio de Seleccion de la Direccion General de Personal y Desarrollo Profesional, Paseo de Zorrilla n 1, Valladolid, con dos preguntas, a que categoria de bolsa se mapea el nuevo titulo de Laboratorio Clinico y cual es su fecha oficial de fin de formacion</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -26830,7 +29097,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XS</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -26840,27 +29107,27 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Antes de que acabe 2026 abrir el PDF de procedimiento de inscripcion FIN MIR de Sacyl y confirmar si el plazo es realmente de dos dias habiles tras finalizar la residencia; en abril de 2027 preparar el autobaremo y la documentacion de meritos; inscribirse en BAPE el 25-05-2027 como muy tarde.</t>
+          <t>Confirmado el plazo de dos dias habiles, quedan dos cosas y ninguna es opcional. Primero, en enero de 2027 comprobar en la guia del residente del Ministerio la fecha OFICIAL de finalizacion de su promocion, porque de ella y no de su contrato cuelga el computo; si coincide con el 22-05-2027 el limite de inscripcion es el 25-05-2027. Segundo, en abril de 2027 tener el autobaremo y la documentacion de meritos ya montados para poder registrarse el mismo dia habil siguiente al fin de la residencia. Si por cualquier causa terminase despues de la fecha oficial, comunicarlo al Servicio de Seleccion en Valladolid, que reabre los mismos dos dias habiles</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr"/>
@@ -26871,7 +29138,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Rama 4, carril 2 (sistema publico). Abierta y leida hoy la ficha Tier 1 de convocatorias abiertas de la categoria Licenciados Especialistas de Sacyl, donde figuran Analisis Clinicos y Bioquimica Clinica y el corte con resolucion de 14-01-2026. El plazo de dos dias habiles para quien termina el MIR procede del titulo de un PDF de Sacyl visto en resultados de busqueda y NO abierto: queda como no confirmado dentro de la fila.</t>
+          <t>Rama 4, carril 2 (sistema publico). Encargo prioritario de la pasada anterior, RESUELTO: abierto y leido hoy el PDF Tier 1 'Procedimiento de inscripcion en la bolsa de empleo de personal estatutario de la Gerencia Regional de Salud de los residentes/especialistas en ciencias de la salud (A1/A2) que finalicen la formacion especializada en el ano 2025', alojado en el propio dominio de Sacyl (https://www.saludcastillayleon.es/profesionales/es/bolsa.ficheros/3019518-Procedimiento%20inscripcion%20FIN%20MIR_EIR%202025.%20BOLSA%20EMPLEO.pdf). El PDF no se pudo leer ni por fetch normal ni con las herramientas de PDF del entorno (falta poppler y libreria de python): hubo que descomprimir a mano los flujos del fichero, y de ahi salen citas literales, incluido el articulo 15 de la ORDEN SAN/713/2016 y la tabla de fechas oficiales de fin de formacion de 2025 (R5 24-09-2025, R4 19-07-2025, R3 Radiofisica 30-05-2025, R2/EIR 22-05-2025). El documento es la edicion de 2025; la de 2027 aun no existe, asi que el plazo esta confirmado como regla vigente y con base normativa, no como fecha de su promocion</t>
         </is>
       </c>
     </row>
@@ -27019,7 +29286,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Multiple locations (no verificado)</t>
+          <t>Multiples ubicaciones: asi lo titula literalmente el propio portal de GSK ('Statistical Geneticist Investigator in Multiple Locations'); cuales no se ha podido leer</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -27082,27 +29349,27 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>No aplicar ahora. Reintentar la ficha con navegador o a mano para leer requisitos y ubicacion; anadir jobs.gsk.com a la vigilancia semanal filtrando por genetics; reabrir esta linea de plazas en 2028 con el doctorado defendido.</t>
+          <t>No aplicar ahora y NO volver a intentar la ficha con herramientas automaticas: el bloqueo es estructural y gastar presupuesto en el es tirarlo. La lectura de requisitos, ubicacion y salario tiene que hacerla ella a mano abriendo https://jobs.gsk.com/en-gb/jobs/223316 en un navegador; merece la pena aunque no vaya a presentarse, porque fija el estandar de requisitos de la familia entera de plazas a la que si optara en 2028. Mantener jobs.gsk.com en la vigilancia semanal filtrando por genetics y reabrir esta linea en 2028 con el doctorado defendido</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr"/>
@@ -27113,7 +29380,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>Rama 4, carril 1. La existencia del puesto y su URL proceden de una busqueda acotada al dominio propio del empleador (jobs.gsk.com), no de un agregador; la ficha en si devolvio solo el armazon del portal, asi que fechas, requisitos, ubicacion y salario quedan expresamente sin verificar.</t>
+          <t>Rama 4, carril 1. Encargo prioritario de la pasada anterior, intentado y NO resuelto, con el motivo ya establecido. El puesto SIGUE EXISTIENDO: una busqueda acotada al dominio del propio empleador devuelve hoy la ficha 223316 activa y titulada 'Statistical Geneticist Investigator in Multiple Locations', asi que la vacante lleva al menos dos semanas viva. Pero la ficha en si es ilegible para un agente: se intento dos veces, con la URL en-gb y con una variante de idioma distinta (de-de), y las dos devuelven unicamente el armazon del portal, sin titulo, requisitos, fechas ni salario. Queda confirmado que jobs.gsk.com es un portal que solo se pinta con JavaScript y pertenece a la lista de bloqueos conocidos del repo: no se debe reintentar. Por eso la fila se mantiene expresamente en UNVERIFIED pese a que la existencia del puesto si esta respaldada por el dominio del empleador y no por un agregador</t>
         </is>
       </c>
     </row>
@@ -27359,8 +29626,133 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>J-0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Familia de vacantes de Porterhouse Medical: Senior Medical Writer (Reino Unido), Senior Medical Writer (Remote-US) y programas Pathfinders de entrada a MedComms</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Porterhouse Medical Group (Porterhouse Medical UK, Porterhouse Medical US, Porterhouse Insights)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Comunicacion cientifica / MedComms</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Londres, Nottingham y Reading (oficinas britanicas); una plaza remota con base en Estados Unidos</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Reino Unido / Estados Unidos</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Onsite o hibrido en las tres oficinas britanicas; la plaza de Senior Medical Writer de la division estadounidense se anuncia expresamente como Remote-US</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Plazas permanentes de plantilla y, aparte, programas de practicas Pathfinders (graduados, doctores e insights)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>El portal no publica fecha de cierre de ninguna vacante: se solicita por correo y las plazas se retiran cuando se cubren. La unica fecha propia de toda la pagina es la del programa Pathfinders de graduados, que declara estar lleno para 2026 y que reabrira solicitudes a finales del cuarto trimestre de 2026 para la edicion de 2027</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>El listado no detalla titulaciones. Las dos plazas de Senior Medical Writer (una UK, una Remote-US) piden experiencia previa en comunicacion medica, que ella no tiene. La via de entrada documentada para su perfil es el Pathfinders PhD Internship Programme in Medical Communications, que figura abierto, y el Pathfinders Graduate Internship Programme, lleno para 2026. Solicitud por correo a careers@porterhousemedical.com con CV y carta de presentacion; no hay formulario ni plazo</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Encaja con ELLA por lo que MedComms compra de verdad en un writer junior: criterio clinico y capacidad de leer, jerarquizar y resumir literatura. Es MD con ingles C2 y lleva dos manuscritos propios como primera autora, uno de revision en Journal of Sleep Research y uno empirico en Nature Mental Health, es decir ya ha escrito en el registro que la agencia vende; y Porterhouse tiene una via de entrada explicitamente pensada para doctorados, el Pathfinders PhD Internship Programme, lo que evita el circulo vicioso de pedir experiencia de agencia. Lo que le falta y lo que pide la solicitud: no hay formulario, se envia CV y carta a careers@porterhousemedical.com, asi que el trabajo real es reorientar el CV de investigadora a comunicacion y construir un portafolio; por el estandar del sector cabe esperar una prueba de escritura cronometrada, aunque Porterhouse NO la menciona en su pagina y no la afirmo. De ahi Effort M. Salario: no publicado en ninguna de las vacantes. Tres condiciones impiden puntuar mas alto y son las que convierten esto en un 3 y no en un 4. (1) Visado: tras el Brexit cualquier plaza britanica exige patrocinio, y un programa de practicas casi nunca se patrocina; la plaza Remote-US exige autorizacion de trabajo en Estados Unidos, que no tiene. (2) Calendario: la unica fecha propia, la reapertura del programa de graduados a finales del cuarto trimestre de 2026 para la edicion de 2027, cae cuando ella sigue en residencia hasta el 22-05-2027, de modo que no podria incorporarse a una edicion que arranque antes de esa fecha. (3) Nivel: las plazas realmente abiertas son de Senior, para las que no es candidata hoy. El valor de la fila no es una vacante concreta sino confirmar por segunda vez que el metodo de portal de agencia funciona y que existe un empleador con puerta de entrada nombrada para doctores, al que volver en otono de 2027. Contacto: careers@porterhousemedical.com, buzon nombrado en la propia pagina, no persona; el gancho seria MD espanola con doctorado en genetica estadistica y dos primeras autorias en revision buscando la via PhD de Pathfinders.</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>La entrada a MedComms es la salida de academia mas concurrida para doctores; el propio portal es la prueba: el programa de practicas para graduados ya estaba lleno para 2026 en septiembre y no reabre hasta el cuarto trimestre. Las plazas vivas son todas de nivel Senior, es decir el embudo esta abierto sobre todo para gente con experiencia de agencia</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>No aplicar ahora. Anotar un aviso para finales de noviembre de 2026 y comprobar si la reapertura del Pathfinders de graduados trae fechas concretas y si el PhD Internship sigue abierto; antes de invertir esfuerzo, resolver por correo a careers@porterhousemedical.com la unica pregunta que decide todo, si patrocinan visado britanico en practicas y en plazas junior. Volver al portal en otono de 2027 buscando Medical Writer sin el prefijo Senior</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>https://www.porterhousemedical.com/careers/</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>Rama 4, carril 3. Repeticion deliberada del metodo de portal de agencia estrenado con Oxford PharmaGenesis (J-0013): en vez de esperar anuncios en agregadores se abre el portal de una agencia MedComms concreta. Pagina leida hoy en el dominio del propio empleador, HTML plano y legible, con fecha de ultima modificacion 2026-08-26 en sus metadatos estructurados, lo que confirma que el listado esta mantenido. Todas las vacantes y la frase sobre la reapertura del programa de graduados son cita literal del portal. El portal no publica salarios ni fechas de cierre, por eso esta fila no afirma ninguno</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB15"/>
+  <autoFilter ref="A1:AB16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28484,7 +30876,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -28624,7 +31016,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -29905,7 +32297,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -30428,7 +32820,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -31201,7 +33593,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -32216,7 +34608,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -44209,7 +46601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -45160,8 +47552,60 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SUB-0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EURAXESS Jobs - alerta por email desde perfil de investigador</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>https://euraxess.ec.europa.eu/jobs</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Avisos por correo de ofertas nuevas que casen con los criterios guardados (campo de investigacion, perfil R2, paises) en cuanto se publican en el portal.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Es el unico rodeo real al problema estructural de esta rama: el buscador de EURAXESS no filtra para un agente (devuelve siempre las ~6.616 ofertas genericas por cualquier parametro, incluida la URL de faceta que ya teniamos registrada), pero el motor de alertas del lado del servidor SI filtra. Con la alerta configurada por ella, las ofertas de genetica estadistica/psiquiatrica llegarian al correo y la rutina podria trabajar sobre fichas concretas en vez de pelearse con el portal.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Requiere que ella cree cuenta con su correo y guarde la busqueda; un agente no puede hacerlo. Sugerencia OPCIONAL, es la unica que propone esta rama.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J18"/>
+  <autoFilter ref="A1:J19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -22,18 +22,18 @@
     <sheet name="readme" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$169</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$276</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$331</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>URGENTE, 30 dias. 1) Comprobar hoy si es socia de SEMEDLAB y, si no, tramitar el alta. 2) Esta semana, correo al laboratorio receptor pidiendo carta de aceptacion. 3) En paralelo, pedir al jefe de servicio la firma del acuerdo. 4) Enviar antes del 30-09-2026.</t>
+          <t>NUEVE DIAS. En este orden y hoy mismo: 1) Escribir a secretaria@fundacionjlc.es Y a la secretaria de SEMEDLAB preguntando (a) si consta como socia y (b) si un alta tramitada esta semana permite solicitar antes del 30-09; si no es socia, darse de alta en https://semedlab.es/alta-de-socio/ (cuota anual 85 EUR + 15 de inscripcion, 60 EUR residentes segun fuente secundaria, sin verificar) y pedir por escrito la confirmacion de condicion de socia, que es lo que la Fundacion exige. 2) Hoy tambien: correo al laboratorio receptor de fuera de Espana (QIMR Berghofer es la via mas rapida por contacto previo) pidiendo carta de aceptacion y fechas dentro de la ventana marzo 2027 - marzo 2028, preferiblemente posterior al 22-05-2027. 3) Manana: pedir al jefe de servicio del Hospital Regional de Malaga el documento de aceptacion y apoyo y la firma del acuerdo entre laboratorios. 4) Redactar la memoria siguiendo el Anexo 1 (https://www.fundacionjlc.es/wp-content/uploads/2025/07/Anexo-1.pdf, maximo 10 paginas, Arial 12, A4) y la carta al presidente de SEMEDLAB. 5) Rellenar el formulario PEP de la IFCC y marcar la checklist (https://www.fundacionjlc.es/wp-content/uploads/2025/07/Checklist-documentacion-presentar-INTERCAMBIO-DE-PROFESIONALES.pdf), que hay que adjuntar firmada. 6) Enviar todo a secretaria@fundacionjlc.es antes del 30-09-2026 con el asunto exigido. SI EL ALTA DE SOCIA NO PUEDE RESOLVERSE ESTA SEMANA, LA OPERACION ES INVIABLE PARA 2026: en ese caso, darse de alta igualmente y apuntar a la convocatoria de 2027.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -658,12 +658,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>F-0054</t>
+          <t>F-0004</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>III Convocatoria de Becas Fulbright-Fundacion Seneca de investigacion posdoctoral en los Estados Unidos</t>
+          <t>Ayudas para contratos Juan de la Cierva (JDC)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -673,33 +673,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Regional-bilateral postdoctoral research fellowship (Espana - EE. UU.)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>POSTDOC_FELLOWSHIP</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>73</v>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3200 al mes para alojamiento y manutencion + ayuda de desplazamiento</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Revisar https://fseneca.es/web/convocatorias en la primera semana de septiembre de 2026, cuando termine el mes inhabil, y capturar las bases de la III convocatoria: ventana de anos post-doctorado y definicion exacta de 'vinculacion con la Region de Murcia'.</t>
+          <t>Vigilar el BOE entre el 20 de octubre y el 20 de noviembre de 2026 para el extracto de la Resolucion de la Presidencia de la AEI que aprueba la convocatoria JdC 2026, y extraer UNA sola cosa: la redaccion literal de la ventana de fecha de obtencion del titulo de doctor. Con esa frase se fija de una vez si su primera convocatoria es la de 2028 o la de 2029, y todo el calendario de la defensa depende de ello.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://fseneca.es/web/convocatorias</t>
+          <t>https://www.fibao.es/convocatoria/b-b-17782-ayudas-juan-de-la-cierva-2026/</t>
         </is>
       </c>
     </row>
@@ -711,40 +718,33 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>E-0002</t>
+          <t>F-0054</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ASHG 2026 Annual Meeting</t>
+          <t>III Convocatoria de Becas Fulbright-Fundacion Seneca de investigacion posdoctoral en los Estados Unidos</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Fellowships</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Congreso anual</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>-5</v>
-      </c>
+          <t>Regional-bilateral postdoctoral research fellowship (Espana - EE. UU.)</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>3200 al mes para alojamiento y manutencion + ayuda de desplazamiento</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -754,12 +754,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>RELOJ VIVO: la tarifa anticipada sigue abierta hasta manana 15-sep-2026 a las 17:00 ET. Si va, hacerse socia student/trainee de ASHG ANTES de inscribirse: la cuota cae de 775 USD (~713 EUR) a 435 USD (~400 EUR), un ahorro de ~313 EUR que supera de largo la cuota de socia. A partir del 16-sep solo queda late/onsite, y no hay tarifa de un dia ni opcion virtual.</t>
+          <t>Revisar https://fseneca.es/web/convocatorias en la primera semana de septiembre de 2026, cuando termine el mes inhabil, y capturar las bases de la III convocatoria: ventana de anos post-doctorado y definicion exacta de 'vinculacion con la Region de Murcia'.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://ashgmeeting.ashg.org/</t>
+          <t>https://fseneca.es/web/convocatorias</t>
         </is>
       </c>
     </row>
@@ -771,12 +771,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E-0005</t>
+          <t>E-0002</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>IGES 2026 Annual Meeting &amp; Education Workshop</t>
+          <t>ASHG 2026 Annual Meeting</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -786,25 +786,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Congreso anual + workshop</t>
+          <t>Congreso anual</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>715</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>RELOJ VIVO a 5 dias: la tarifa early de IGES cierra el 19-sep-2026 y desde el 20-sep sube a late. Solo tiene sentido moverla si YA ha decidido ir a ASHG 2026 (misma region, dias consecutivos); el plazo de resumenes cerro el 30-may-2026, asi que iria como oyente. Si no va a ASHG, dejarla pasar y apuntarla como objetivo 2027.</t>
+          <t>RELOJ VIVO: la tarifa anticipada sigue abierta hasta manana 15-sep-2026 a las 17:00 ET. Si va, hacerse socia student/trainee de ASHG ANTES de inscribirse: la cuota cae de 775 USD (~713 EUR) a 435 USD (~400 EUR), un ahorro de ~313 EUR que supera de largo la cuota de socia. A partir del 16-sep solo queda late/onsite, y no hay tarifa de un dia ni opcion virtual.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://www.geneticepi.org/2026-annual-meeting</t>
+          <t>https://ashgmeeting.ashg.org/</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>E-0001</t>
+          <t>E-0005</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
+          <t>IGES 2026 Annual Meeting &amp; Education Workshop</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -846,21 +846,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Congreso anual</t>
+          <t>Congreso anual + workshop</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -870,12 +874,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>La inscripcion sigue ABIERTA a 15 dias del congreso y sin fecha de cierre publicada: si va, inscribirse esta misma semana en https://ispg.societyconference.com/v2/ y escribir a info@ispg.net preguntando por la cuota Student/Post-Doc y por si existe opcion virtual, porque ninguna de las dos cosas esta publicada en ningun sitio accesible.</t>
+          <t>RELOJ VIVO a 5 dias: la tarifa early de IGES cierra el 19-sep-2026 y desde el 20-sep sube a late. Solo tiene sentido moverla si YA ha decidido ir a ASHG 2026 (misma region, dias consecutivos); el plazo de resumenes cerro el 30-may-2026, asi que iria como oyente. Si no va a ASHG, dejarla pasar y apuntarla como objetivo 2027.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://ispg.net/wcpg-2026/</t>
+          <t>https://www.geneticepi.org/2026-annual-meeting</t>
         </is>
       </c>
     </row>
@@ -887,55 +891,51 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T-0007</t>
+          <t>E-0001</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Advanced Mendelian Randomization</t>
+          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Curso corto avanzado</t>
+          <t>Congreso anual</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>52</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>737</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>NO reservable en la practica para 2026: exige haber hecho antes el curso introductorio de MR, que ella hara en marzo-2027. Objetivo real: la edicion de noviembre-2027. Aun asi, confirmar en octubre-2026 si aceptan 'equivalente' con experiencia propia en MR.</t>
+          <t>La inscripcion sigue ABIERTA a 15 dias del congreso y sin fecha de cierre publicada: si va, inscribirse esta misma semana en https://ispg.societyconference.com/v2/ y escribir a info@ispg.net preguntando por la cuota Student/Post-Doc y por si existe opcion virtual, porque ninguna de las dos cosas esta publicada en ningun sitio accesible.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/advanced-mr/</t>
+          <t>https://ispg.net/wcpg-2026/</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T-0002</t>
+          <t>T-0007</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Genetic Epidemiology (short course)</t>
+          <t>Advanced Mendelian Randomization</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -962,20 +962,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Short course</t>
+          <t>Curso corto avanzado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>737</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ACCION INMINENTE Y CON DOS FECHAS: crear o reactivar la cuenta de reservas desde el mediodia del 2026-09-23 (dentro de 9 dias) y reservar plaza el 2026-10-07 a mediodia hora del RU, cuando abren las reservas de todo el programa 2026/27.</t>
+          <t>NO reservable en la practica para 2026: exige haber hecho antes el curso introductorio de MR, que ella hara en marzo-2027. Objetivo real: la edicion de noviembre-2027. Aun asi, confirmar en octubre-2026 si aceptan 'equivalente' con experiencia propia en MR.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/advanced-mr/</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T-0001</t>
+          <t>T-0002</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
+          <t>Genetic Epidemiology (short course)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1022,33 +1022,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Workshop</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+          <t>Short course</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>114</v>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XS</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>La inscripcion 2027 AUN NO ESTA ABIERTA. Revisar colorado.edu/ibg/workshop-2027 a partir de noviembre-2026 (en ediciones previas abrio unos 3 meses antes) y reservar presupuesto propio de ~600 USD de cuota academica.</t>
+          <t>ACCION INMINENTE Y CON DOS FECHAS: crear o reactivar la cuenta de reservas desde el mediodia del 2026-09-23 (dentro de 9 dias) y reservar plaza el 2026-10-07 a mediodia hora del RU, cuando abren las reservas de todo el programa 2026/27.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://www.colorado.edu/ibg/workshop-2027</t>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1067,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T-0003</t>
+          <t>T-0001</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mendelian Randomization (short course)</t>
+          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1075,40 +1082,33 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Short course</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2027-03-01</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>162</v>
-      </c>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>550</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>ACCION INMINENTE: cuenta de reservas desde el 2026-09-23 a mediodia y reserva el 2026-10-07 a mediodia. Este va ANTES que T-0007, porque es su prerrequisito.</t>
+          <t>La inscripcion 2027 AUN NO ESTA ABIERTA. Revisar colorado.edu/ibg/workshop-2027 a partir de noviembre-2026 (en ediciones previas abrio unos 3 meses antes) y reservar presupuesto propio de ~600 USD de cuota academica.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
+          <t>https://www.colorado.edu/ibg/workshop-2027</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T-0009</t>
+          <t>T-0003</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Molecular Epidemiology</t>
+          <t>Mendelian Randomization (short course)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1135,40 +1135,40 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Curso corto</t>
+          <t>Short course</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2027-03-08</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XS</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Solo si sobran presupuesto y dias: encadenarlo con T-0003 (MR introductorio) la semana anterior, aprovechando un unico permiso.</t>
+          <t>ACCION INMINENTE: cuenta de reservas desde el 2026-09-23 a mediodia y reserva el 2026-10-07 a mediodia. Este va ANTES que T-0007, porque es su prerrequisito.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/molecular-epidemiology/</t>
+          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T-0008</t>
+          <t>T-0009</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Machine Learning with Omics Data</t>
+          <t>Molecular Epidemiology</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1200,13 +1200,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2027-06-08</t>
+          <t>2027-03-08</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>261</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>3</t>
@@ -1219,12 +1223,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Decidir en primavera-2027 junto con el resto de la oferta de Bristol; la ficha individual del curso aun no esta publicada, asi que la cuota se conocera al abrir reservas el 2026-10-07.</t>
+          <t>Solo si sobran presupuesto y dias: encadenarlo con T-0003 (MR introductorio) la semana anterior, aprovechando un unico permiso.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/molecular-epidemiology/</t>
         </is>
       </c>
     </row>
@@ -1236,25 +1240,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>L-0001</t>
+          <t>T-0008</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Complex Trait Genetics (CTG) Lab</t>
+          <t>Machine Learning with Omics Data</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Groups</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Curso corto</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2027-06-08</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>260</v>
+      </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1262,10 +1277,14 @@
           <t>S</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Decidir en primavera-2027 junto con el resto de la oferta de Bristol; la ficha individual del curso aun no esta publicada, asi que la cuota se conocera al abrir reservas el 2026-10-07.</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://cncr.nl/ctg/</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1296,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L-0002</t>
+          <t>L-0001</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Psychiatric Genetics Group</t>
+          <t>Complex Trait Genetics (CTG) Lab</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1303,14 +1322,10 @@
           <t>S</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Mandar YA el correo en frio a Sarah Medland o a Lucia Colodro Conde sin esperar a ningun anuncio: esta confirmado que no lo va a haber a corto plazo y la conexion calida de su estancia en QIMR no depende de el.</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
+          <t>https://cncr.nl/ctg/</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1337,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L-0006</t>
+          <t>L-0002</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SGDP Centre / Statistical Genetics Unit</t>
+          <t>Psychiatric Genetics Group</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1350,12 +1365,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Escribir a Cathryn Lewis (Statistical Genetics Unit) planteando co-patrocinio de beca postdoc, dado que la unidad no publica vacantes propias.</t>
+          <t>Mandar YA el correo en frio a Sarah Medland o a Lucia Colodro Conde sin esperar a ningun anuncio: esta confirmado que no lo va a haber a corto plazo y la conexion calida de su estancia en QIMR no depende de el.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://www.kcl.ac.uk/research/sgu</t>
+          <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1382,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L-0012</t>
+          <t>L-0006</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Grupo de genetica estadistica psiquiatrica de Wouter Peyrot (proyecto ERC PersonalRiskProfile)</t>
+          <t>SGDP Centre / Statistical Genetics Unit</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1395,12 +1410,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Escribir correo en frio a Peyrot antes de fin de 2026 presentando disponibilidad desde mediados de 2027 y pidiendo una videollamada de 20 minutos; en paralelo, localizar su direccion institucional exacta en pure.amsterdamumc.nl y revisar la bolsa de empleo de Amsterdam UMC por si sale la plaza del ERC.</t>
+          <t>Escribir a Cathryn Lewis (Statistical Genetics Unit) planteando co-patrocinio de beca postdoc, dado que la unidad no publica vacantes propias.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://www.amsterdamumc.org/en/research/institutes/amsterdam-public-health/news/wouter-peyrot-awarded-erc-starting-grant-for-personalized-genetic-risk-profiles-in-psychiatry-1</t>
+          <t>https://www.kcl.ac.uk/research/sgu</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1427,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L-0013</t>
+          <t>L-0012</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Grupo de Kelli Lehto, Instituto de Genomica (proyecto ERC AT-TENSION)</t>
+          <t>Grupo de genetica estadistica psiquiatrica de Wouter Peyrot (proyecto ERC PersonalRiskProfile)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1440,12 +1455,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Correo en frio a Kelli Lehto con CV y las dos fechas de disponibilidad; preguntar si AT-TENSION prevee contratar en 2027 y ofrecer la vertiente de fenotipado clinico. Confirmar antes su direccion institucional en la ficha de personal de ut.ee.</t>
+          <t>Escribir correo en frio a Peyrot antes de fin de 2026 presentando disponibilidad desde mediados de 2027 y pidiendo una videollamada de 20 minutos; en paralelo, localizar su direccion institucional exacta en pure.amsterdamumc.nl y revisar la bolsa de empleo de Amsterdam UMC por si sale la plaza del ERC.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://ut.ee/en/news/erc-grant-helps-explore-innovative-approaches-improve-diagnosis-adhd-adults</t>
+          <t>https://www.amsterdamumc.org/en/research/institutes/amsterdam-public-health/news/wouter-peyrot-awarded-erc-starting-grant-for-personalized-genetic-risk-profiles-in-psychiatry-1</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1472,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L-0014</t>
+          <t>L-0013</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Grupo de Psiquiatria Infantil y Genetica del Comportamiento de Christel Middeldorp</t>
+          <t>Grupo de Kelli Lehto, Instituto de Genomica (proyecto ERC AT-TENSION)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1485,12 +1500,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Preparar un correo en frio con una propuesta de una pagina sobre genetica del sueno en primera infancia dentro de sus cohortes; antes, verificar en pure.amsterdamumc.nl su financiacion vigente y sus publicaciones de 2025-2026 sobre sueno.</t>
+          <t>Correo en frio a Kelli Lehto con CV y las dos fechas de disponibilidad; preguntar si AT-TENSION prevee contratar en 2027 y ofrecer la vertiente de fenotipado clinico. Confirmar antes su direccion institucional en la ficha de personal de ut.ee.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://www.amsterdamumc.org/en/research/researchers/christel-middeldorp.htm</t>
+          <t>https://ut.ee/en/news/erc-grant-helps-explore-innovative-approaches-improve-diagnosis-adhd-adults</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1517,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L-0020</t>
+          <t>L-0014</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KI Psychiatric Genomics Institute (KI-PGI)</t>
+          <t>Grupo de Psiquiatria Infantil y Genetica del Comportamiento de Christel Middeldorp</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1525,17 +1540,17 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Correo en frio a lu.yi@ki.se proponiendo co-solicitar MSCA o postdoc del Swedish Research Council con el KI-PGI como host; no esperar a que salga plaza.</t>
+          <t>Preparar un correo en frio con una propuesta de una pagina sobre genetica del sueno en primera infancia dentro de sus cohortes; antes, verificar en pure.amsterdamumc.nl su financiacion vigente y sus publicaciones de 2025-2026 sobre sueno.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://ki.se/en/meb/research/ki-psychiatric-genomics-institute/about-ki-pgi</t>
+          <t>https://www.amsterdamumc.org/en/research/researchers/christel-middeldorp.htm</t>
         </is>
       </c>
     </row>
@@ -1547,12 +1562,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L-0021</t>
+          <t>L-0020</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PsychGen Centre for Genetic Epidemiology and Mental Health</t>
+          <t>KI Psychiatric Genomics Institute (KI-PGI)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1575,12 +1590,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Confirmar la direccion de Havdahl en su ficha de fhi.no y escribirle con una propuesta de una pagina: sueno infantil en MoBa con diseno intrafamiliar. Preguntar por MSCA o postdoc del Research Council of Norway.</t>
+          <t>Correo en frio a lu.yi@ki.se proponiendo co-solicitar MSCA o postdoc del Swedish Research Council con el KI-PGI como host; no esperar a que salga plaza.</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://www.fhi.no/en/me/the-psychgen-centre-for-genetic-epidemiology-and-mental-health/about-the-psychgen-centre/</t>
+          <t>https://ki.se/en/meb/research/ki-psychiatric-genomics-institute/about-ki-pgi</t>
         </is>
       </c>
     </row>
@@ -1592,24 +1607,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>E-0011</t>
+          <t>L-0021</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BGA 2028 - 58th Annual Meeting of the Behavior Genetics Association</t>
+          <t>PsychGen Centre for Genetic Epidemiology and Mental Health</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Conference</t>
-        </is>
-      </c>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
@@ -1619,17 +1630,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Revisar la pagina de BGA Future Meetings en enero-2028 para fechas exactas y plazo de resumenes; apuntarla ya como objetivo post-tesis.</t>
+          <t>Confirmar la direccion de Havdahl en su ficha de fhi.no y escribirle con una propuesta de una pagina: sueno infantil en MoBa con diseno intrafamiliar. Preguntar por MSCA o postdoc del Research Council of Norway.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567675</t>
+          <t>https://www.fhi.no/en/me/the-psychgen-centre-for-genetic-epidemiology-and-mental-health/about-the-psychgen-centre/</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1652,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>E-0016</t>
+          <t>E-0011</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EMGM 2027 - 55a European Mathematical Genetics Meeting</t>
+          <t>BGA 2028 - 58th Annual Meeting of the Behavior Genetics Association</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1656,7 +1667,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Congreso anual</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
@@ -1668,17 +1679,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>La 54a edicion (Davos, 14-15 abr 2026) ya paso y la de 2027 sigue sin anfitrion. Vigilar sites.google.com/site/emgmhome a partir de noviembre-2026; si en enero-2027 sigue TBA, escribir a los organizadores de Davos 2026 (emgm2026.sciencesconf.org) preguntando por sede y fechas de 2027, que es justo lo que la propia web pide hacer.</t>
+          <t>Revisar la pagina de BGA Future Meetings en enero-2028 para fechas exactas y plazo de resumenes; apuntarla ya como objetivo post-tesis.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://sites.google.com/site/emgmhome/future-meetings</t>
+          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567675</t>
         </is>
       </c>
     </row>
@@ -1690,48 +1701,44 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>T-0011</t>
+          <t>E-0016</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Genetic and Epigenetic Epidemiology (curso especializado del EEPE)</t>
+          <t>EMGM 2027 - 55a European Mathematical Genetics Meeting</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Curso especializado residencial</t>
+          <t>Congreso anual</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>1575</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XS</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Revisar eepe.org en enero-2027: la edicion 2027 se anunciara con el curso residencial (mediados de junio a principios de julio) y los especializados la semana siguiente. Compararla entonces con el MR de Bristol de marzo-2027, que cubre parte del mismo terreno mas barato.</t>
+          <t>La 54a edicion (Davos, 14-15 abr 2026) ya paso y la de 2027 sigue sin anfitrion. Vigilar sites.google.com/site/emgmhome a partir de noviembre-2026; si en enero-2027 sigue TBA, escribir a los organizadores de Davos 2026 (emgm2026.sciencesconf.org) preguntando por sede y fechas de 2027, que es justo lo que la propia web pide hacer.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.eepe.org/courses-2/</t>
+          <t>https://sites.google.com/site/emgmhome/future-meetings</t>
         </is>
       </c>
     </row>
@@ -1743,44 +1750,48 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>E-0014</t>
+          <t>T-0011</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>XXXV Reunion Anual de la Sociedad Espanola de Sueno (SES 2027)</t>
+          <t>Genetic and Epigenetic Epidemiology (curso especializado del EEPE)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Curso especializado residencial</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1575</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Consultar congreso-ses.com/ses2027 en octubre-2026 para fechas exactas de marzo-2027, plazo de comunicaciones y cuota de residente; si cae en marzo, hay que pedir dias en el hospital con antelacion.</t>
+          <t>Revisar eepe.org en enero-2027: la edicion 2027 se anunciara con el curso residencial (mediados de junio a principios de julio) y los especializados la semana siguiente. Compararla entonces con el MR de Bristol de marzo-2027, que cubre parte del mismo terreno mas barato.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://congreso-ses.com/ses2027/bienvenida</t>
+          <t>https://www.eepe.org/courses-2/</t>
         </is>
       </c>
     </row>
@@ -1792,12 +1803,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>E-0015</t>
+          <t>E-0014</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jornada AEGH 2027 (Asociacion Espanola de Genetica Humana)</t>
+          <t>XXXV Reunion Anual de la Sociedad Espanola de Sueno (SES 2027)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1824,17 +1835,66 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t>Consultar congreso-ses.com/ses2027 en octubre-2026 para fechas exactas de marzo-2027, plazo de comunicaciones y cuota de residente; si cae en marzo, hay que pedir dias en el hospital con antelacion.</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://congreso-ses.com/ses2027/bienvenida</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>E-0015</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Jornada AEGH 2027 (Asociacion Espanola de Genetica Humana)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>Volver a aegh.org/congresos-y-jornadas-aegh en diciembre-2026 o enero-2027 para ver sede y fechas adjudicadas.</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>https://aegh.org/congresos-y-jornadas-aegh/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L26"/>
+  <autoFilter ref="A1:L27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1845,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J158"/>
+  <dimension ref="A1:J169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10064,8 +10124,580 @@
         </is>
       </c>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>SRC-0158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>MSCA - seccion de noticias y resultados de convocatoria</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/whats-new/news</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Los anuncios oficiales de apertura y CIERRE de cada convocatoria MSCA, el recuento de propuestas recibidas, el presupuesto indicativo, el numero de proyectos que se espera financiar y la fecha de notificacion de resultados. Es donde se confirma en Tier 1 que una convocatoria ha cerrado de verdad, cosa que la pagina de la accion no dice.</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Filtrar por 'Postdoctoral Fellowships'; leer la noticia de resultados de cada edicion (p. ej. /whats-new/news/postdoctoral-fellowships-2026-call-results)</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Usada por primera vez en la pasada del 2026-09-21 para confirmar el cierre de la MSCA PF 2026 (21.627 propuestas). Distinta de SRC-0011 y SRC-0097, que apuntan a la pagina de la accion y a las fichas por ano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>SRC-0159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>MSCA - pagina de la convocatoria Postdoctoral Fellowships 2027</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/funding/msca-postdoctoral-fellowships-2027</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>El calendario provisional de la ultima edicion de PF de Horizonte Europa 2021-2027: lanzamiento 07-04-2027 y cierre 08-09-2027, ambos marcados TBC. Es la pagina donde esas dos fechas pasaran de TBC a confirmadas.</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Leer la seccion de calendario y comprobar si las fechas siguen marcadas '(TBC)'</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>URL distinta de SRC-0098 (que es la de MSCA COFUND 2027) y de SRC-0097 (node/1496). El paso de TBC a fecha firme es el disparador de la decision sobre adelantar la defensa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>SRC-0160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Faculty of Law, University of Oxford - pagina de plazos de Wellcome Early-Career Awards</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://www.law.ox.ac.uk/wellcome-early-career-awards</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Espejo britanico que reproduce el calendario de rondas de los Wellcome Early-Career Awards: plazo del financiador, mes de preseleccion y mes de entrevistas de cada ronda, separados de los plazos internos del centro. Es la unica via encontrada hasta ahora para leer fechas de Wellcome mientras wellcome.org devuelve 403.</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Abrir la pagina entera y leer las tablas por termino academico (Michaelmas, Hilary, Trinity); quedarse con la fila rotulada 'Advised Latest Submission Deadline for Applicants (including Organisation Approval)' y contrastarla con otro espejo universitario antes de darla por buena.</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Tier 2. Abre sin bloqueo. OJO: en la pasada del 2026-09-21 su fecha para la ronda de otono de 2026 (16-11-2026) NO coincide con la que la propia Wellcome publica (10-11-2026) para la misma ronda. Usarla para el patron de rondas, no como fecha unica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SRC-0161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>FIBAO - buscador de convocatorias (espejo de fichas de la BDNS)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://www.fibao.es/convocatoria/</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Fichas completas de convocatorias estatales y andaluzas copiadas de la Base de Datos Nacional de Subvenciones: plazos, numero de ayudas, importes, duracion y codigo BDNS. Sirve de sustituto operativo mientras aei.gob.es da 503 y mientras subvenciones.gob.es se renderiza por JavaScript y devuelve cuerpo vacio al fetch automatico.</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Buscar por nombre del programa (Juan de la Cierva, Ramon y Cajal, Sara Borrell, Rio Hortega) y abrir la ficha del ano en curso. Leer SIEMPRE el ano dentro de la ficha: las fichas arrastran del ano anterior la referencia de BOE y a veces las fechas de plazo.</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Tier 2. Descubierta en la pasada del 2026-09-21. Resuelve el bloqueo de aei.gob.es (503 en cuatro URLs) y el de subvenciones.gob.es (SPA con cuerpo vacio). Falso positivo comprobado: la ficha de la JdC 2026 mostraba en detalle fechas de plazo de 2025 y una referencia de BOE de 31-10-2025; contrastar siempre con una segunda fuente antes de escribir una fecha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>SRC-0162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Fundacion Alicia Koplowitz - Ayudas de Formacion (estancias de 6-12 meses y Formacion Avanzada)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://fundacionaliciakoplowitz.org/lineas-de-accion/ayudas-formacion/</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Bases en PDF y calendario de las dos lineas de formacion de la fundacion, distintas de las Ayudas a Proyectos ya fichadas; los PDF anuales cuelgan de /wp-content/uploads/&lt;ano&gt;/01/</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Enlaces a Bases_Ayudas-Estancias-Cortas_&lt;ano&gt;.pdf y Bases-Ayudas-Formacion-Avanzada_&lt;ano&gt;.pdf; descargar con curl y extraer el texto, la pagina HTML solo lista beneficiarios</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Anual, bases publicadas en enero</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Verificado el 2026-09-21: ambas lineas exigen titulo de Especialista en Psiquiatria (MIR) o Psicologia Clinica (PIR), que la excluye. Se conserva la fuente para no volver a investigarla desde cero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>SRC-0163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>FENS Job Market (Federation of European Neuroscience Societies)</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://www.fens.org/careers/job-market/</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Convocatorias de becas y estancias de neurociencia republicadas por los financiadores; sirve de via de rescate cuando la web del financiador esta bloqueada</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Buscar por nombre del financiador o de la convocatoria; ejemplo util: la Research Stay Grant de CINET/Fundacion Tatiana aparece en /careers/job-market/job/122150 con las bases que fundaciontatiana.com no sirve</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Alta el 2026-09-21. Distinta de la ficha generica de fens.org y de /careers/grants ya presentes en el fichero: esta es la seccion de anuncios, y es la que rescato F-0050.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>SRC-0164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>L'Oreal-UNESCO For Women in Science - portal de convocatorias</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://www.forwomeninscience.com/</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Bases legales de la modalidad espanola y de los International Awards, y los portales de candidatura numerados por edicion</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Bases de Espana en /statics/filemanager/Spain/&lt;ano&gt;/; portal de la XXI edicion espanola en /challenge/show/169 y de los International Awards 2027 en /challenge/show/158</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Anual, la modalidad espanola abre en septiembre</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Alta el 2026-09-21. AVISO: el PDF de bases de Espana es un escaneo sin capa de texto y no se puede leer de forma automatica; hay que abrirlo a mano.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>SRC-0165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>AEGH - archivo de ayudas y becas</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://aegh.org/ayudas-y-becas/</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Listado paginado con TODAS las convocatorias de ayudas de la AEGH y sus resoluciones, incluida la nominacion a la Beca Nacional de la ESHG, que no aparece en el blog general. Es donde se vio primero la convocatoria ESHG 2027 con plazo 15-11-2026.</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Recorrer las paginas 1 a 3 y leer los titulos con beca, bolsa, premio o ayuda</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>mensual; semanal entre enero y marzo</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Mas completo que SRC-0094 (aegh.org/blog-2/). Ojo: https://aegh.org/categoria/convocatorias/ devuelve 404.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>SRC-0166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SENC - Requisitos para solicitudes de ayudas y becas (PDF oficial)</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://www.senc.es/wp-content/uploads/2024/09/Requisitos-solicitudes-de-ayudas-y-becas-SENC.pdf</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>El documento de la Junta Directiva que fija a que ayudas se aplica la regla de los dos anos consecutivos de cuota. Delimita el alcance: ayudas de viaje y de organizacion de actividades si; premios no.</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Descargar con curl y extraer texto; revisar si la SENC publica una version posterior a la de 2024</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>anual</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Resuelve la duda que bloqueaba F-0039 y F-0040. Enlazado desde https://www.senc.es/ayudas-de-la-senc/ como 'Requisitos para solicitudes de ayudas y becas'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>SRC-0167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>NHMRC - Funding schemes and calendar</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://www.nhmrc.gov.au/funding/calendar</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>El calendario oficial de todos los esquemas de la NHMRC con fechas de apertura, datos minimos y cierre; es donde apareceran las fechas de la ronda de Investigator Grants que cierra hacia julio de 2027 antes que en la ficha del esquema</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Investigator Grants - proxima ronda (apertura junio, cierre julio)</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Trimestral, y mensual de abril a agosto</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Distinta de SRC-0076, que es la ficha del esquema. AVISO: nhmrc.gov.au empezo a devolver 403 a curl y a WebFetch en esta pasada (bloqueo no registrado hasta ahora); la URL sirve para abrirla a mano y los datos hay que sacarlos por buscador restringido al dominio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>SRC-0168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Fundacion Seneca - Convocatorias Abiertas</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>FELLOWSHIPS</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://fseneca.es/web/convocatorias-abiertas</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>La lista de convocatorias de la Fundacion Seneca efectivamente abiertas en cada momento, que es lo que faltaba para saber si la III Fulbright-Seneca ha salido; el catalogo anual (SRC-0091) las lista aunque no esten abiertas</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Ver si aparece la III Convocatoria Fulbright-Fundacion Seneca</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Semanal en septiembre y octubre de 2026</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Comprobada hoy: responde 200 por curl (con User-Agent de navegador) pero el listado se renderiza por JavaScript y el cuerpo llega VACIO, igual que las fichas de sede de la Junta de Andalucia. Queda registrada para que la duena la abra a mano y para que nadie vuelva a gastar presupuesto esperando texto de ella.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J158"/>
+  <autoFilter ref="A1:J169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10196,7 +10828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -21649,8 +22281,2318 @@
         </is>
       </c>
     </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>F-0063</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Ayudas para estancias de 6 a 12 meses en el extranjero para Psiquiatras (MIR) o Psicologos Clinicos (PIR) (Ayudas de Formacion)</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Ineligible de forma permanente: las bases 2026 exigen literalmente el titulo de Especialista en Psiquiatria (MIR) o Psicologia Clinica (PIR) y el suyo sera de Medicina de Laboratorio, de modo que ni la modalidad de superespecializacion ni la de centros de excelencia le estan abiertas por mucho que e</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>https://fundacionaliciakoplowitz.org/wp-content/uploads/2026/01/Bases_Ayudas-Estancias-Cortas_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>F-0064</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Beca Nacional de la ESHG 2027 - nominacion de la AEGH</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Seria el atajo ideal a su congreso natural, pero es INELEGIBLE por triple partida en 2027: no es socia de la AEGH (y hacen falta mas de dos anos de antiguedad), es MD de 2019 y por tanto supera los 4 anos de experiencia postuniversitaria, y no presento comunicacion en el congreso de Granada de 2026.</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>https://aegh.org/beca-eshg-2027-para-asistir-a-la-eshg-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>F-0065</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>SENC-J Ambassador Distinction</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Inelegible durante anos: exige doctorado ya obtenido (el suyo llegaria en febrero de 2028 segun ETA) y ademas dos anos acumulados de postdoc en el extranjero, que no tendria antes de 2030.</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>https://www.senc.es/wp-content/uploads/2026/03/SENC-J_Ambassador_Call_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>F-0009</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>MSCA Postdoctoral Fellowships (European Fellowship; variante Global)</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Competition_Basis, Competition_Level, Confidence, Deadline, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Open_Date, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/actions/postdoctoral-fellowships</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>F-0007</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>HFSP Postdoctoral Fellowships (Long-Term Fellowship, LTF)</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>https://www.hfsp.org/funding/hfsp-funding/postdoctoral-fellowships</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>F-0008</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>EMBO Postdoctoral Fellowships</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Eligibility_Key_Conditions, Last_Updated, Last_Verified</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/postdoctoral-fellowships/eligibility/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>F-0019</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>FENS/IBRO-PERC Exchange Fellowships</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Verified</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>https://www.fens.org/careers/grants-and-stipends/grant/fens-ibro-perc-exchange-fellowships</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>F-0018</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>ERC Starting Grant</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Verified</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>https://erc.europa.eu/apply-grant/starting-grant</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>F-0058</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>BGA Early Career Award (antes Fuller and Scott Award)</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Eligibility_Key_Conditions, Last_Updated, Last_Verified, Next_Action, Source_Note, Years_PostPhD_Window</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567677</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>F-0001</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Contratos Rio Hortega (ISCIII, Accion Estrategica en Salud)</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Verified</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>F-0002</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Contratos Sara Borrell (ISCIII, Accion Estrategica en Salud)</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Verified</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>F-0003</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Contratos Miguel Servet (ISCIII, Accion Estrategica en Salud)</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Verified</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>F-0004</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Ayudas para contratos Juan de la Cierva (JDC)</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>columnas: Amount_EUR, Change_Flag, Confidence, Deadline, Duration, Eligibility_Key_Conditions, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Open_Date, Source_Note, Status, URL, Years_PostPhD_Window</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>https://www.fibao.es/convocatoria/b-b-17782-ayudas-juan-de-la-cierva-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>F-0005</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Ayudas para contratos Ramon y Cajal (RYC) 2026</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Deadline, Duration, Eligibility_Key_Conditions, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Open_Date, Source_Note, Status, URL</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>https://www.fibao.es/convocatoria/b-b-17784-ayudas-ram-xc3-x93n-y-cajal-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>F-0010</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Humboldt Research Fellowship for Postdoctoral Researchers</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Competition_Basis, Confidence, Deadline, Eligibility_Key_Conditions, Fit_Rationale, Host_Requirement, Last_Updated, Last_Verified, Next_Action, Open_Date, Source_Note, Status, Years_PostPhD_Window</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>https://www.humboldt-foundation.de/en/apply/sponsorship-programmes/humboldt-research-fellowship</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>F-0011</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>DFG Walter Benjamin Programme</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Eligibility_Key_Conditions, Fit_Rationale, Host_Requirement, Last_Updated, Last_Verified, Next_Action, Source_Note, Years_PostPhD_Window</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>https://www.dfg.de/en/research-funding/funding-opportunities/programmes/individual/walter-benjamin</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>F-0012</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Wellcome Early-Career Awards</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Eligibility_Key_Conditions, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>https://wellcome.org/research-funding/schemes/early-career-awards</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>F-0017</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>BBRF Young Investigator Grant (antes NARSAD Young Investigator)</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Eligibility_Key_Conditions, Fit_1_5, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>https://bbrfoundation.org/grants-prizes/bbrf-young-investigator-grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>F-0024</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Premios L'Oreal-UNESCO For Women in Science Espana (XXI edicion, bases 2026)</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Deadline, Fit_1_5, Fit_Rationale, Last_Updated, Last_Verified, Name, Next_Action, Open_Date, Source_Note, Status, URL</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>https://www.forwomeninscience.com/statics/filemanager/Spain/2026/20260714_Bases%20Legales%20Premios%20For%20Women%20in%20Science%202026-2027%20Espan%CC%83a.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>F-0035</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>L'Oreal-UNESCO For Women in Science International Awards / International Rising Talents</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Eligibility_Key_Conditions, Last_Updated, Last_Verified, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>https://www.forwomeninscience.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>F-0051</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>SRSF Small Research Grant</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Eligibility_Key_Conditions, Last_Updated, Last_Verified, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/foundation/small-research-grant/</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>F-0046</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Ayuda para la Investigacion y el Intercambio de Conocimiento (SES)</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>https://ses.org.es/profesionales/becas-y-premios/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>F-0048</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Becas de Investigacion SES (incluye beca especial para investigadores jovenes)</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>https://ses.org.es/wp-content/uploads/2025/11/bases_becas_investigacion_2026-1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>F-0050</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Research Stay Grant for Interdisciplinary Training in Neuroscience (CINET)</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Eligibility_Key_Conditions, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>https://www.cinetcenter.com/convocatoria/research-stay-grant-for-interdisciplinary-training-in-neuroscience-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>F-0034</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Stanley Center Sklar Program (Sklar Research Award / Sklar BSRP Fellowship)</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>https://www.broadinstitute.org/stanley-center-sklar-program</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>F-0037</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Beca Internacional de Intercambio Cientifico Profesional 2026 (Programa de Intercambio Profesional SEMEDLAB)</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Competition_Basis, Competition_Level, Confidence, Deadline, Effort_Estimate, Eligibility_Key_Conditions, Fit_1_5, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>https://www.fundacionjlc.es/becapremio-convocado/beca-internacional-de-intercambio-cientifico-profesional-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>F-0023</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>ESHG 2027 - conference fellowships / early career awards</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Competition_Basis, Competition_Level, Confidence, Deadline, Effort_Estimate, Eligibility_Key_Conditions, Fit_1_5, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>https://2027.eshg.org/abstracts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>F-0029</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>The Company of Biologists Travelling Fellowships</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Competition_Level, Confidence, Deadline, Effort_Estimate, Eligibility_Key_Conditions, Fit_1_5, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>https://www.biologists.com/travelling-fellowships/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>F-0039</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Excellent Student Rita Levi-Montalcini Award (SENC)</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Competition_Basis, Competition_Level, Confidence, Eligibility_Key_Conditions, Fit_1_5, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>https://www.senc.es/wp-content/uploads/2025/04/1_Rita-Levi-Montalcini-Award-Call-2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>F-0040</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>SENC Travel Awards Program (SENC / FENS / ENCODS / SfN)</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Eligibility_Key_Conditions, Fit_1_5, Fit_Rationale, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>https://www.senc.es/wp-content/uploads/2026/01/03_SENC-TRAVEL-GRANTS-PROGRAM_WEB_EN_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>F-0038</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>ISPG Early Career Investigator Program (ECIP) Travel Award - World Congress of Psychiatric Genetics</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Confidence, Last_Updated, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>https://ispg.net/ecip-program/</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>F-0020</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>EMBO Scientific Exchange Grants</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Verified, Source_Note</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/scientific-exchange-grants/eligibility/</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>F-0041</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Beca Estancia Profesional AEGH (modalidad junior)</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Verified, Source_Note</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>https://aegh.org/convocatoria-de-becas-estancia-profesional-aegh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>F-0042</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Premio Joven en Investigacion de la AEGH (XXVI edicion)</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Verified, Source_Note</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>https://aegh.org/convocatoria-xxvi-edicion-del-premio-joven-en-investigacion-de-la-aegh/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>F-0043</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Bolsas de Viaje AEGH (congreso nacional AEGH / Congreso Interdisciplinar en Genetica Humana)</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>columnas: Change_Flag, Last_Verified, Next_Action, Source_Note</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>https://aegh.org/convocatoria-de-bolsas-de-viaje-aegh-xxx-congreso-aegh-y-v-congreso-interdisciplinar-en-genetica-humana-del-15-al-17-de-abril-de-2026-granada/</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>W-0001</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>HFSP Postdoctoral Fellowships - convocatoria del ano 2027</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>https://www.hfsp.org/funding/hfsp-funding/postdoctoral-fellowships</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>W-0002</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Contratos Rio Hortega - edicion AES 2026</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>W-0003</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Contratos Sara Borrell - edicion AES 2026</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>W-0004</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Contratos Miguel Servet - edicion AES 2026</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>https://www.isciii.es/documents/d/guest/report_aes_2026?download=true</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>W-0006</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>NHMRC Investigator Grants - ronda con cierre en julio de 2027</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>columnas: Expected_Reopen, Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>https://www.nhmrc.gov.au/funding/find-funding/investigator-grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>W-0007</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>BBRF Young Investigator Grant - ciclo 2026</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>https://bbrfoundation.org/grants-prizes/bbrf-young-investigator-grants</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>W-0008</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Postdoctoral Junior Leader - modalidad Incoming, convocatoria 2027</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>columnas: Expected_Reopen, Last_Checked, Notes, Reopen_Confidence</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>https://lacaixafoundation.org/en/postdoctoral-junior-leader-fellowships-incoming-call</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>W-0009</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>ISPG Early Career Investigator Program (ECIP) - ayuda de viaje al WCPG</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>https://ispg.net/ecip-program/</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>W-0010</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>SRS Trainee Awards del congreso SLEEP (Trainee Merit, Diversity Travel, First-Time Attendee)</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>https://sleepresearchsociety.org/awards/conference-awards/</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>W-0011</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Premio de Investigacion del Instituto de Neurociencias Federico Oloriz (UGR) - edicion 2026</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>https://ineurociencias.ugr.es/instituto/noticias/premio-instituto-neurociencias-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>W-0012</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Becas de Investigacion de la SES (Sociedad Espanola de Sueno)</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>https://ses.org.es/blog-post/becas-2022-2-5-3-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>W-0013</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>ESRS Meetings and Courses Fellowship</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>columnas: Notes</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>https://esrs.eu/grants-awards/meetings-and-courses-fellowship/</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>W-0015</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>MSCA Postdoctoral Fellowships - convocatoria 2027 (HORIZON-MSCA-2027-PF-01-01) y el acantilado posterior</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>https://marie-sklodowska-curie-actions.ec.europa.eu/funding/msca-postdoctoral-fellowships-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>W-0016</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>EMBO Postdoctoral Fellowships - ronda de otono de 2027</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>https://www.embo.org/funding/fellowships-grants-and-career-support/postdoctoral-fellowships/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>W-0017</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Becas de Investigacion SES - edicion 2027</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>https://ses.org.es/becas-y-premios/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>W-0018</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Convocatorias anuales de la AEGH (estancia profesional, bolsas de viaje y premio joven)</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>columnas: Expected_Reopen, Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>https://aegh.org/blog-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>W-0019</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Convocatorias anuales de la SENC (travel grants y premio Rita Levi-Montalcini)</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>https://www.senc.es/ayudas-de-la-senc/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>W-0020</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Contratos postdoctorales de la Junta de Andalucia (Linea 2, EIDIA) - edicion 2027</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>https://www.juntadeandalucia.es/boja/</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>W-0021</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Ayudas a Proyectos de la Fundacion Alicia Koplowitz - convocatoria 2027</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>columnas: Last_Checked, Notes</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>https://fundacionaliciakoplowitz.org/lineas-de-accion/ayudas-investigacion/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>fellowships</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>watchlist_closed</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>W-0022</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>III Convocatoria de Becas Fulbright-Fundacion Seneca de investigacion posdoctoral en EE. UU.</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>columnas: Expected_Reopen, Last_Checked, Notes, Reopen_Confidence</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>https://fseneca.es/web/convocatorias</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H276"/>
+  <autoFilter ref="A1:H331"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22843,7 +25785,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-459</v>
+        <v>-460</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -22989,7 +25931,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -23131,7 +26073,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-142</v>
+        <v>-143</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -23396,7 +26338,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-213</v>
+        <v>-214</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -23788,7 +26730,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -23926,7 +26868,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -24060,7 +27002,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -24190,7 +27132,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -24320,7 +27262,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -24577,7 +27519,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -25283,7 +28225,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>-111</v>
+        <v>-112</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -25826,7 +28768,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -25964,7 +28906,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -26106,7 +29048,7 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -26236,7 +29178,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -26370,7 +29312,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -26504,7 +29446,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -26634,7 +29576,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -27030,7 +29972,7 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -27315,7 +30257,7 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -27461,7 +30403,7 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -28943,7 +31885,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -29763,7 +32705,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB63"/>
+  <dimension ref="A1:AB66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -30028,22 +32970,22 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -30157,22 +33099,22 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -30282,22 +33224,22 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -30354,25 +33296,40 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>ANNOUNCED</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-11-12</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-12-03</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>73</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>35000</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2 anos</t>
+          <t>3 anos</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Segun fuentes secundarias: doctorado en posesion en el momento de la solicitud, obtenido como maximo 3 anos antes de la fecha de cierre. SIN VERIFICAR.</t>
+          <t>NO VERIFICADA para la edicion 2026: las bases no estan aun en el BOE (busqueda en boe.es el 2026-09-21: solo aparecen los extractos de la JdC 2024, BOE-B-2024-44727, y de la JdC 2025, BOE-B-2025-39640). La JdC exige haber obtenido el titulo de doctor dentro de una ventana cerrada de unos 2-3 anos que termina poco antes de la convocatoria; el borde superior (si admite doctorados obtenidos durante el propio ano de la convocatoria) es el dato que decide su primera oportunidad y NO esta verificado.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Ultima convocatoria realmente publicada: la de 2025 (Resolucion de 29-10-2025, BOE-B-2025-39640), con plazo del 25-11-2025 al 10-12-2025 a las 14:00 para las personas candidatas y hasta el 17-12-2025 para las entidades. Ventana de doctorado de esa edicion: defensa entre el 01-01-2024 y el 31-12-2025 (turno general), ampliable por bajas y cuidados. La fecha que cuenta es la 'fecha del acto de defensa y aprobacion de la tesis doctoral'.</t>
+          <t>Convocatoria 2026 anunciada por la AEI: 500 ayudas, 35.000 EUR/ano para cofinanciar salario y Seguridad Social mas 15.000 EUR para gastos de investigacion y movilidad, 3 anos. Plazo de solicitud de la persona candidata del 12-11-2026 00:00 al 03-12-2026 14:00 (hora peninsular). BDNS MINECO-PTE-RRHH-CJ-2026. Condicion estructural confirmada en varias fichas institucionales: el centro de acogida debe ser DISTINTO de aquel en el que realizo la formacion predoctoral, lo que para ella excluye la Universidad de Murcia como centro receptor. Incompatible con solicitar a la vez Ramon y Cajal en la misma convocatoria.</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -30382,7 +33339,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Encaje alto por contenido (contrato posdoctoral de la AEI en cualquier centro espanol, compatible con su linea de genetica estadistica) y ventana de aproximadamente dos anos desde la defensa, que con feb-2028 la situa en la convocatoria de 2028 (cierre previsible en diciembre de 2028), no en ninguna anterior. Elegibilidad punto por punto: doctorado en posesion al solicitar, que en 2028 cumpliria; ventana de anos, holgada; centro espanol de acogida, por conseguir. Sigue sin verificarse un extremo: si la AEI admite certificado de defensa o exige titulo expedido en el momento de acreditar (a diferencia del ISCIII, que si lo aclara). Para ella es secundario, porque hasta diciembre de 2028 tiene margen de sobra. Trabajo: M.</t>
+          <t>Encaja con ella por la linea 1 (genetica estadistica de rasgos complejos) y por el instrumento: es la via estandar de primer contrato posdoctoral en Espana, con carta de compromiso de un centro espanol y sin exigencia de movilidad internacional previa, lo que neutraliza su punto debil (residencia continuada en Espana salvo dos estancias de ~3 meses). RELOJES, uno a uno: (a) exige doctorado YA OBTENIDO en el momento que fijen las bases, y su defensa es feb-2028 (ETA), asi que la convocatoria 2026 (cierre 03-12-2026) esta CERRADA para ella sin discusion; (b) su primera oportunidad realista es la convocatoria JdC de 2028 (que por el patron de 2024, 2025 y 2026 se publicaria en otono de 2028 con cierre en diciembre de 2028), y solo SI la ventana de fecha de doctorado admite titulos obtenidos durante el propio ano de la convocatoria; si el borde superior se cierra el 31 de diciembre del ano anterior, su primera convocatoria seria la JdC de 2029. Ese unico dato hay que extraerlo del BOE en cuanto salga el extracto de la 2026, previsiblemente entre octubre y noviembre de 2026. (c) Su defensa en feb-2028 cae comodamente dentro de cualquier ventana de 2-3 anos que se use en 2029, asi que el riesgo no es quedarse corta sino perder un ano por el borde. TRABAJO REAL: la solicitud es de esfuerzo medio (memoria de la candidata, CV normalizado, historial del grupo receptor y carta del centro), pero el centro de acogida tiene que estar cerrado antes: contar 3-6 meses para negociarlo, y NO puede ser la Universidad de Murcia.</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -30402,12 +33359,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>LIKELY para plazo, numero de ayudas, importe y duracion de la convocatoria 2026 (fichas de la BDNS reproducidas por FIBAO y por guias independientes, concordantes; aei.gob.es sigue dando 503 y el extracto no esta aun en el BOE). UNVERIFIED para la ventana de fecha de doctorado.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -30417,7 +33374,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -30427,7 +33384,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>CORRECCION DE MATIZ: la JDC 2026 no esta retrasada. La convocatoria mas reciente sigue siendo la de 2025 (BOE-B-2025-39640, extracto de la Resolucion de 29-10-2025, plazo del 25-11-2025 al 17-12-2025 a las 14:00, BDNS 857452). Por el patron de 2025 (extracto en BOE el 31-10-2025), el extracto de la JDC 2026 deberia publicarse a finales de octubre de 2026: su ausencia hoy es lo esperable, no una anomalia. Vigilar el BOE esas semanas. Se mantiene la advertencia sobre fibao.es y tesify.es, que siguen sin respaldo oficial.</t>
+          <t>Vigilar el BOE entre el 20 de octubre y el 20 de noviembre de 2026 para el extracto de la Resolucion de la Presidencia de la AEI que aprueba la convocatoria JdC 2026, y extraer UNA sola cosa: la redaccion literal de la ventana de fecha de obtencion del titulo de doctor. Con esa frase se fija de una vez si su primera convocatoria es la de 2028 o la de 2029, y todo el calendario de la defensa depende de ello.</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -30437,12 +33394,12 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>https://www.boe.es/diario_boe/txt.php?id=BOE-B-2025-39640</t>
+          <t>https://www.fibao.es/convocatoria/b-b-17782-ayudas-juan-de-la-cierva-2026/</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>aei.gob.es acumula CUATRO URLs con 503 entre esta pasada y la anterior, incluido su endpoint de PDF: el dominio se da por inaccesible al rastreo automatico y se sustituye por el BOE como fuente Tier 1.</t>
+          <t>Rama 2, pasada 2026-09-21. aei.gob.es sigue en 503 (bloqueo ya fichado): se sustituye por la ficha de la BDNS reproducida en fibao.es y por guias independientes concordantes. Busqueda en boe.es acotada al dominio: NO hay todavia extracto de la JdC 2026; los ultimos son BOE-B-2025-39640 (JdC 2025) y BOE-B-2024-44727 (JdC 2024). OJO: la ficha de FIBAO arrastra del ano anterior la referencia de BOE (31-10-2025) y, en la vista de detalle, fechas de plazo de 2025; las fechas de 2026 (12-11-2026 a 03-12-2026) proceden del anuncio de la propia AEI recogido por varias fuentes secundarias. Tratar la referencia de BOE de esa ficha como obsoleta hasta que se publique el extracto de 2026.</t>
         </is>
       </c>
     </row>
@@ -30479,11 +33436,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>ANNOUNCED</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-11-10</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-12-10</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>80</v>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>38270 al ano en la primera fase segun fuentes secundarias; presupuesto total de la convocatoria 132346140 para 494 contratos</t>
@@ -30491,7 +33459,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Hasta 5 anos, mas incentivo a la creacion de plaza estable</t>
+          <t>5 anos (fase inicial de 3 anos mas hasta 2 anos de segunda fase)</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -30501,7 +33469,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Exige doctorado. La edicion de 2026 introduce, segun fuentes secundarias, una entrevista con las comisiones tecnicas de la AEI y financia ademas un proyecto liderado por la solicitante. Regla exacta de fecha de doctorado sin verificar.</t>
+          <t>Convocatoria RyC 2026 anunciada: 494 ayudas, de las cuales 80 reservadas a la linea de atraccion de talento del extranjero. Plazo del 10-11-2026 00:00 al 10-12-2026 14:00 (hora peninsular). Retribucion de 38.270 a 47.500 EUR/ano segun tramo, mas 50.000 EUR adicionales (100.000 EUR en la linea de atraccion). BDNS MINECO-PT-RRHH-RYC-2026. Incompatible con solicitar Juan de la Cierva en la misma convocatoria. La ventana de fecha de doctorado (en ediciones recientes, un tramo ancho de varios anos posteriores al doctorado) NO se ha podido verificar en esta pasada: las bases no estan en el BOE y aei.gob.es da 503.</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -30511,7 +33479,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>La puerta de entrada a la carrera estable en Espana y el final del carril academico que dice querer, pero es un esquema para quien ya tiene trayectoria independiente, no para una recien doctorada. Punto por punto: (a) exige doctorado leido antes del cierre, asi que 2026 y 2027 quedan fuera; (b) incluso desde 2028 estaria en el ultimo escalon del grupo de candidatos, compitiendo con gente con 4-8 anos de produccion posdoctoral, y su expediente actual (dos manuscritos en revision, ningun articulo destacado) no sobreviviria al baremo curricular; (c) la entrada realista es hacia 2031-2033, despues de un Rio Hortega/Sara Borrell o de un posdoc internacional. LINEA CON LA QUE ENCABEZAR cuando llegue el momento: un programa propio de genetica estadistica, ya que la reforma de 2026 financia el proyecto de la IP y eso favorece una linea metodologicamente distintiva frente a una prestada. Se registra ahora porque el calendario (noviembre-diciembre cada ano) es estable y conviene que conozca el esquema al planificar los anos posdoctorales, no porque sea accionable.</t>
+          <t>Es el escalon siguiente al de Juan de la Cierva, no el inmediato: la RyC busca trayectoria posdoctoral consolidada y ella defiende en feb-2028 (ETA) sin publicaciones destacadas todavia (dos manuscritos en revision como primera autora). La convocatoria 2026 esta CERRADA para ella por el reloj del doctorado. Sigue en la base como horizonte: la linea de atraccion de talento del extranjero (80 de las 494 plazas) seria su mejor entrada SI antes hace un posdoc fuera de Espana, que es exactamente lo que abren Humboldt, Walter Benjamin o un Sara Borrell en otro centro. Reevaluar hacia 2032-2033, no antes.</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -30531,47 +33499,47 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>LIKELY para plazo, numero de ayudas, importes y duracion de la convocatoria 2026 (ficha de la BDNS reproducida por FIBAO, concordante con el anuncio de la AEI recogido en fuentes secundarias). UNVERIFIED para la ventana de fecha de doctorado.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Ninguna accion por su parte. Cuando en otono de 2026 salga el extracto en el BOE, capturar solo la ventana de fecha de doctorado, para tener fijado el horizonte y no volver a abrir la fila cada pasada.</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Ninguna ahora. Reverificar la ventana de fecha de doctorado en otono de 2028, cuando decida entre un posdoc espanol y salir fuera.</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>https://www.aei.gob.es/convocatorias/buscador-convocatorias/ayudas-contratos-ramon-cajal-ryc-2026</t>
+          <t>https://www.fibao.es/convocatoria/b-b-17784-ayudas-ram-xc3-x93n-y-cajal-2026/</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>Rama 2. URL tomada de un listado de resultados (pagina propia de la AEI para RYC 2026); no se pudo abrir (HTTP 503). Cifras de paginas secundarias de oficinas de investigacion y de noticias del MICIU.</t>
+          <t>Rama 2, pasada 2026-09-21. Sustituye la URL anterior de aei.gob.es, que llevaba dos pasadas dando 503, por la ficha de la BDNS reproducida en fibao.es, que si abre. La misma ficha arrastra una referencia de BOE de 31-10-2025 que corresponde al ano anterior: no usarla.</t>
         </is>
       </c>
     </row>
@@ -30794,7 +33762,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -30804,7 +33772,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -30814,7 +33782,7 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>El calendario AY2028 SIGUE SIN PUBLICARSE (comprobado en Tier 1: la pagina anuncia todavia el AY2027). Se espera entre enero y marzo de 2027. Depositar un preprint del empirico australiano sigue siendo la accion mas barata y de mayor rendimiento, pero hay que planificar la aceptacion para la propuesta completa de septiembre, no solo el LOI.</t>
+          <t>Confirmado en Tier 1 el 2026-09-21: el ciclo AY2027 sigue en pie tal cual -LOI cerrada el 12-05-2026 y propuesta completa de las invitadas el 24-09-2026 a las 9:00-, asi que ese plazo de dentro de tres dias no le afecta: no presento LOI en mayo y no esta en el circuito de invitadas. El calendario AY2028 SIGUE SIN PUBLICARSE (la pagina oficial solo anuncia el AY2027); se espera entre enero y marzo de 2027. DATO NUEVO Y RELEVANTE PARA SU RELOJ: las seleccionadas del AY2027 deben incorporarse entre el 01-04-2027 y el 01-01-2028; si el AY2028 conserva la misma estructura, la incorporacion caeria entre abril de 2028 y enero de 2029, justo despues de su defensa prevista de febrero de 2028, y la LOI de ese ciclo seria hacia mayo de 2027. Eso convierte el AY2028 en el ciclo HFSP realista para ella. Preparacion: la busqueda de host fuera de Espana tendria que estar en marcha a finales de 2026, y para la propuesta completa de septiembre de 2027 hace falta el manuscrito ACEPTADO (en propuesta completa el preprint ya no vale), asi que el empirico de Nature Mental Health es el cuello de botella.</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -30876,7 +33844,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -30895,7 +33863,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>PDF de guidelines extraido localmente (15 paginas, 35.847 caracteres), no por resumen automatico. CINCO reglas, dos de ellas nuevas: (1) PHD NO EXIGIDO AL SOLICITAR: 'Applicants must hold a PhD degree or equivalent at the start of the fellowship, but not necessarily at the time the application is submitted'; si ya lo tiene, elegible dentro de los dos anos previos. ELLA PUEDE SOLICITAR SIENDO AUN DOCTORANDA. (2) PUBLICACION, que es el verdadero cuello de botella: exige 'at least one first (or joint first) author PRIMARY RESEARCH PAPER accepted for publication or published' al presentar; un preprint solo vale con revisiones publicas en profundidad de un servicio independiente y verificable (Peer Community In, Review Commons). OJO: 'primary research paper' significa que su REVISION en Journal of Sleep Research NO SERVIRIA aunque se aceptara; solo cuenta el empirico de Nature Mental Health. (3) Nota explicita sobre MD: 'Candidates with a medical degree (M.D.) may be eligible... provided they hold a PhD (MD-PhD programme)'. (4) MOVILIDAD, buena noticia: maximo 6 meses en el pais de acogida durante los 18 previos; excluido el pais del doctorado (Espana fuera); excluido volver a un laboratorio donde haya trabajado mas de 6 meses, de modo que QIMR Berghofer y el laboratorio japones (~3 meses cada uno) NO quedan vetados como destino. (5) Plazo maximo de incorporacion: ronda de primavera, entre el 1 de julio del ano del premio y el 15 de febrero del siguiente; ronda de otono, entre el 1 de enero y el 15 de agosto del siguiente; solo se empieza dia 1 o dia 15. RIESGO ADICIONAL: 'Applications in which the postdoctoral project is a direct continuation of the PhD project will not be considered', y EMBO excluye trabajo aplicado o clinico sin pregunta biologica clara: tendria que reencuadrar hacia una pregunta biologica distinta de su tesis.</t>
+          <t>PDF de guidelines extraido localmente (15 paginas, 35.847 caracteres), no por resumen automatico. CINCO reglas, dos de ellas nuevas: (1) PHD NO EXIGIDO AL SOLICITAR: 'Applicants must hold a PhD degree or equivalent at the start of the fellowship, but not necessarily at the time the application is submitted'; si ya lo tiene, elegible dentro de los dos anos previos. ELLA PUEDE SOLICITAR SIENDO AUN DOCTORANDA. (2) PUBLICACION, que es el verdadero cuello de botella: exige 'at least one first (or joint first) author PRIMARY RESEARCH PAPER accepted for publication or published' al presentar; un preprint solo vale con revisiones publicas en profundidad de un servicio independiente y verificable (Peer Community In, Review Commons). OJO: 'primary research paper' significa que su REVISION en Journal of Sleep Research NO SERVIRIA aunque se aceptara; solo cuenta el empirico de Nature Mental Health. (3) Nota explicita sobre MD: 'Candidates with a medical degree (M.D.) may be eligible... provided they hold a PhD (MD-PhD programme)'. (4) MOVILIDAD, buena noticia: maximo 6 meses en el pais de acogida durante los 18 previos; excluido el pais del doctorado (Espana fuera); excluido volver a un laboratorio donde haya trabajado mas de 6 meses, de modo que QIMR Berghofer y el laboratorio japones (~3 meses cada uno) NO quedan vetados como destino. (5) Plazo maximo de incorporacion: ronda de primavera, entre el 1 de julio del ano del premio y el 15 de febrero del siguiente; ronda de otono, entre el 1 de enero y el 15 de agosto del siguiente; solo se empieza dia 1 o dia 15. RIESGO ADICIONAL: 'Applications in which the postdoctoral project is a direct continuation of the PhD project will not be considered', y EMBO excluye trabajo aplicado o clinico sin pregunta biologica clara: tendria que reencuadrar hacia una pregunta biologica distinta de su tesis. (6) REGLA NUEVA, verificada el 2026-09-21 por la rama de watchlist en la pagina de EMBO, cita literal: 'Effective from the Autumn 2027 selection round (i.e., for all applications submitted after January 22, 2027, 14:00 CET), re-applications will no longer be permitted. Researchers may submit only one EMBO Fellowship Proposal.' Consecuencia practica grande: a partir del corte de julio de 2027 tiene UN SOLO intento en toda su carrera, de modo que NO cabe usar una solicitud temprana como ensayo. Como su cuello de botella es la aceptacion del empirico de Nature Mental Health, la decision es esperar a tenerlo aceptado en vez de gastar el unico disparo. El corte del 22-01-2027 14:00 CET es el ultimo que todavia admitiria repeticion.</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -30930,7 +33898,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -30940,7 +33908,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -31002,22 +33970,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>-11</v>
-      </c>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>No publicado en las paginas de la CE leidas (asignaciones de manutencion, movilidad, familia, investigacion y gestion como costes unitarios corregidos por pais). No citar cifras sin consultar el Portal de Financiacion y Licitaciones.</t>
@@ -31045,7 +34002,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>El programa es contenido puro suyo y en abstracto seria un 4, pero se baja a 3 porque hay una condicion estructural sin resolver y conviene que la fila lo diga: NO ES ELEGIBLE PARA NINGUNA EDICION PUBLICADA. La convocatoria 2026 cierra el 09-09-2026, mucho antes de su defensa. La de 2027 (HORIZON-MSCA-2027-PF-01-01, lanzamiento 07-04-2027 y cierre 08-09-2027, ambos marcados TBC en origen, 388,57 M EUR) TAMPOCO le llega por cinco meses. Y ahi esta el problema serio: la convocatoria de 2027 es la ultima del actual marco financiero, porque Horizonte Europa cubre 2021-2027, de modo que NO HAY CERTEZA DE QUE EXISTA UNA CONVOCATORIA PF CON ESTAS REGLAS EN 2028 (dependeria del programa sucesor, FP10, sin diseno ni calendario fijados). PALANCA ACCIONABLE: la regla oficial exige HABER DEFENDIDO, no tener el titulo expedido; si adelantara la defensa a antes del 08-09-2027 entraria en la ultima convocatoria de Horizonte Europa. El choque es con el MIR, que termina el 22-05-2027: quedarian ~3,5 meses, apretado pero no imposible si la tesis esta madura. Es una decision con consecuencias economicas concretas, no una preferencia de calendario, y toca hablarla con la direccion de tesis este otono, no en 2027.</t>
+          <t>CONVOCATORIA 2026 CERRADA: el plazo del 09-09-2026 paso y la Comision ya ha publicado el recuento de propuestas (21.627), asi que no hay prorroga ni segunda ronda. Encaje de fondo con ella: alto (movilidad europea, estadistica genetica y GWAS/PRS entran de lleno en el panel LIF/SOC, y el perfil MD+PhD es raro), pero el encaje REAL lo decide un reloj que hoy no cumple. Elegibilidad reloj a reloj: (1) doctorado exigido EN LA FECHA DE CIERRE -basta con haber defendido aunque no este expedido el titulo-, y su defensa prevista es febrero de 2028 (ETA no confirmada); (2) ventana de 8 anos de experiencia investigadora desde el doctorado: sobradamente dentro; (3) regla de movilidad, no haber residido ni tenido actividad principal en Espana mas de 12 meses en los 36 anteriores al cierre: la INCUMPLE con el MIR en Malaga (22-05-2023 a 22-05-2027) salvo que las dos estancias de ~3 meses (QIMR Berghofer y Japon) y un traslado posterior cambien el computo; como las fechas exactas de esas estancias no estan fijadas, esto se puntua LIKELY y nunca VERIFIED, y en la practica obliga a mirar hacia un pais de acogida distinto de Espana. PROXIMA EDICION: convocatoria 2027, lanzamiento previsto el 07-04-2027 y cierre el 08-09-2027, AMBAS FECHAS MARCADAS COMO TBC EN LA PAGINA OFICIAL. Es la ULTIMA edicion segura del actual Horizonte Europa (2021-2027) y su cierre del 08-09-2027 cae unos cinco meses ANTES de su defensa prevista: solo la alcanzaria si la defensa se adelanta a antes del 08-09-2027. Esa es la decision estrategica del otono. ACANTILADO POST-2027: el sucesor propuesto por la Comision el 17-07-2025 se llama tambien Horizonte Europa (2028-2034), FP10, con 175.000 M EUR propuestos; el Consejo fijo su posicion el 26-06-2026; las MSCA siguen previstas dentro del Pilar I junto al ERC y el objetivo declarado es que la financiacion llegue sin interrupcion desde enero de 2028, con una convocatoria puente en 2027. Todo esto es Tier 2 (briefings parlamentarios y prensa especializada; las paginas del Consejo y de la Commons Library devolvieron 403), asi que NO se puede dar por hecha una convocatoria PF en 2028 ni su calendario. Conclusion practica: hay una edicion 2027 casi segura y una probable continuidad posterior con fechas desconocidas; planificar contra el 08-09-2027 y no contra una hipotetica de 2028.</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -31055,7 +34012,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Convocatoria 2026 con 399,05 M EUR y expectativa de financiar 'nearly 1600 projects' sobre varias veces esa cifra de solicitudes; es el instrumento posdoctoral mas solicitado de Europa</t>
+          <t>Cifras oficiales de la convocatoria 2026, ya cerrada: 21.627 propuestas presentadas (20.131 European Fellowships, 93,1%; 1.496 Global Fellowships, 6,9%), un 26,7% mas que las 17.066 de 2025 y el mayor numero de propuestas jamas recibido por una accion de los programas marco de la UE. Con 399,05 M EUR se espera financiar unos 1.600 proyectos: tasa de exito implicita en torno al 7%.</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -31070,7 +34027,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -31080,17 +34037,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>No hay nada que presentar. La accion es estrategica: decidir con la direccion de tesis, este otono, si la defensa puede adelantarse a antes del 08-09-2027 para alcanzar la ultima convocatoria MSCA de Horizonte Europa. Ver W-0015.</t>
+          <t>Dos acciones, en este orden. (1) Estrategica y urgente este otono: decidir con la direccion de tesis si la defensa puede adelantarse a antes del 08-09-2027 para alcanzar la convocatoria MSCA PF 2027 (lanzamiento ~07-04-2027, cierre ~08-09-2027, ambas TBC), que es la ultima edicion segura de Horizonte Europa 2021-2027. Adelantarla exige ademas tener host europeo fuera de Espana comprometido a comienzos de 2027, porque la propuesta la firma la institucion de acogida. (2) Vigilar la publicacion del programa de trabajo MSCA 2027 y la confirmacion de las dos fechas TBC; y, por separado, la aparicion del primer calendario de convocatorias del nuevo Horizonte Europa 2028-2034. Ver W-0015.</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -31105,7 +34062,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>Anuncio oficial: la convocatoria 2026 'is open as of 9 April 2026' y 'will close on 9 September 2026'. Fuentes: https://marie-sklodowska-curie-actions.ec.europa.eu/node/1575 y /actions/postdoctoral-fellowships. Convocatoria 2027 en /funding/msca-postdoctoral-fellowships-2027. La afirmacion de que 2027 es la ultima del marco es LIKELY (Tier 2); la pagina oficial no la contiene.</t>
+          <t>Tier 1 verificado el 2026-09-21: https://marie-sklodowska-curie-actions.ec.europa.eu/whats-new/news/postdoctoral-fellowships-2026-call-results da el cierre el 09-09-2026, las 21.627 propuestas, el reparto European/Global, los 399,05 M EUR, los ~1.600 proyectos y la notificacion de resultados a mediados de febrero de 2027. Fechas de la edicion 2027 (07-04-2027 y 08-09-2027, TBC) leidas en Tier 1 en https://marie-sklodowska-curie-actions.ec.europa.eu/funding/msca-postdoctoral-fellowships-2027. FP10: solo Tier 2 (consilium.europa.eu y commonslibrary.parliament.uk devolvieron 403 a WebFetch; epthinktank.eu respondio pero sin cifras).</t>
         </is>
       </c>
     </row>
@@ -31137,15 +34094,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OBLIGATORIA: un anfitrion aleman debe confirmar la acogida y co-desarrollar el plan de investigacion antes de presentar. Humboldt espera un compromiso sustantivo, no una carta de formulario.</t>
+          <t>SI, y bloqueante antes de enviar: hace falta un acogimiento en una institucion academica alemana que aporte un mentoring agreement y la confirmacion por escrito de que hay medios de investigacion disponibles. La solicitud no se da por recibida hasta que la persona anfitriona sube su documentacion.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ROLLING</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
@@ -31159,12 +34120,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Doctorado completado hace menos de cuatro anos en la fecha de solicitud (segun fuentes secundarias).</t>
+          <t>Doctorado (o cualificacion academica equivalente) completado dentro de los ULTIMOS CUATRO ANOS. La fecha que cuenta es aquella en que la fundacion RECIBE la solicitud completa, no la de envio en el portal.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>DOCTORADO EXIGIDO AL SOLICITAR: el reloj de cuatro anos corre del doctorado a la fecha de solicitud, asi que no se puede presentar una tesis sin defender. Ademas, regla de residencia: quien viene del extranjero debe haber vivido fuera de Alemania al menos 12 meses en total durante los 18 anteriores a la presentacion. Sin plazo fijo; el comite de seleccion se reune en marzo, julio y noviembre.</t>
+          <t>CAMBIO IMPORTANTE FRENTE A LO QUE TENIAMOS FICHADO: el programa NO es de presentacion continua. Tiene TRES convocatorias al ano con fecha de apertura fija; en 2026 abren el 15 de marzo, el 15 de julio y el 15 de noviembre. Cada convocatoria se cierra en cuanto acumula 800 solicitudes, de modo que no hay fecha de cierre publicada y en la practica funciona por orden de llegada. Requisito de anfitrion aleman previo (mentoring agreement mas confirmacion de medios).</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -31174,7 +34135,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Un plazo rodante es especialmente valioso para alguien cuya fecha de defensa es una estimacion: no tiene que acertar una ventana, solicita cuando la tesis este de verdad terminada. Punto por punto: (a) doctorado al solicitar: elegible desde su defensa (ETA febrero de 2028) hasta aproximadamente febrero de 2032, una pista de cuatro anos que absorbe cualquier retraso, que es exactamente la propiedad que necesita; (b) la regla de 12 de los ultimos 18 meses fuera de Alemania se cumple trivialmente -ha estado en Espana todo el tiempo, con estancias cortas en Australia y Japon-, asi que, a diferencia de las reglas tipo MSCA, esta se puede puntuar sin conocer sus fechas exactas; (c) ciudadania de la UE, sin problema de visado. LINEA CON LA QUE ENCABEZAR: GWAS/PRS de trastornos psiquiatricos, porque la capacidad alemana en genetica psiquiatrica (Instituto Central de Salud Mental de Mannheim, MPI de Psiquiatria de Munich, Bonn) es un hogar natural para su segunda linea y una fuente realista de un anfitrion que co-escriba el plan; la genetica estadistica de rasgos complejos es el encuadre metodologico. EL PROBLEMA: Humboldt puntua con fuerza el expediente de publicaciones y la posicion cientifica independiente, hoy su dimension mas debil, asi que los dos manuscritos deben estar aceptados antes de solicitar. La duracion de 6-24 meses la convierte en un puente mas que en un puesto de carrera, lo que encaja bien con un primer movimiento al extranjero despues de la residencia y la tesis. TRABAJO: M, 1-2 semanas una vez acordada la acogida.</t>
+          <t>Sigue siendo una de sus dos mejores vias alemanas y ahora esta verificada en primera fuente. Encaja por la linea 1 (genetica estadistica de rasgos complejos) y por la 2 (GWAS/PRS en psiquiatria), donde Alemania tiene grupos de primer nivel, y como ciudadana de la UE no necesita permiso de trabajo. RELOJES: (a) la ventana de cuatro anos desde el doctorado, contada a la fecha de RECEPCION de la solicitud, le da margen desde feb-2028 (ETA) hasta ~feb-2032, muy holgado incluso si la defensa se desplaza unos meses; (b) exige doctorado ya completado, asi que no puede presentarse antes de feb-2028 y la convocatoria de noviembre de 2026 no le sirve; (c) la primera ventana util seria la que abra a mediados de 2028. LO QUE CAMBIA SU PLANIFICACION: al cerrarse cada convocatoria a las 800 solicitudes, no basta con llegar dentro del ano: hay que estar listo el dia de la apertura, lo que obliga a tener el anfitrion y el mentoring agreement cerrados ANTES. Negociar un anfitrion aleman lleva tipicamente entre 3 y 6 meses, asi que el trabajo util empieza a finales de 2027, no despues de la defensa. TRABAJO REAL: propuesta de investigacion, CV, publicaciones y dos cartas de referencia mas la documentacion del anfitrion; esfuerzo de dos a cuatro semanas una vez el anfitrion esta comprometido.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -31184,7 +34145,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Esquema de prestigio con tres rondas de seleccion al ano en todas las disciplinas; tasa de exito no leida en esta pasada.</t>
+          <t>Cada convocatoria se cierra al llegar a 800 solicitudes, dato publicado por la propia fundacion: da una idea directa del volumen por ronda, tres veces al ano.</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -31194,39 +34155,39 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Dos cosas, ninguna urgente pero ambas con fecha: (1) a finales de 2027, cerrar anfitrion aleman y mentoring agreement, porque la convocatoria se agota por cupo y no por calendario; (2) confirmar entonces que el calendario de tres aperturas anuales (marzo, julio, noviembre) sigue vigente en 2028, ya que es una practica publicada ano a ano, no una regla permanente.</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Verificar en humboldt-foundation.de en una pasada posterior si el reloj de cuatro anos se cuenta desde la fecha de solicitud o desde el inicio de la beca, y si las candidatas espanolas MD+PhD necesitan el acuerdo de acogida ya al presentar. No urgente antes de mediados de 2027.</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>https://www.humboldt-foundation.de/en/apply/sponsorship-programmes/humboldt-research-fellowship</t>
@@ -31234,7 +34195,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>Rama 2. Agregacion Tier 2 (base de datos de becas del DAAD, Max Planck Society, DAAD Norteamerica) coherente entre fuentes, pero la pagina propia de la fundacion aun debe leerse una vez.</t>
+          <t>Rama 2, pasada 2026-09-21. Tier 1 leido directamente en humboldt-foundation.de: calendario de las tres convocatorias de 2026, tope de 800 solicitudes por convocatoria, ventana de cuatro anos contada a la fecha de recepcion y exigencia de anfitrion aleman con mentoring agreement. Corrige la ficha anterior, que estaba construida sobre agregadores (DAAD, Max Planck) y la daba por ROLLING.</t>
         </is>
       </c>
     </row>
@@ -31266,7 +34227,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>OBLIGATORIA: hay que identificar institucion y persona de acogida, y no haber trabajado en esa institucion mas de un ano en el momento de solicitar.</t>
+          <t>SI. Hace falta institucion de acogida que respalde el proyecto. Puede estar en Alemania o en el extranjero, pero la modalidad EN EL EXTRANJERO tiene un filtro de arraigo aleman que ella no cumple (ver condiciones), de modo que para ella la unica via practicable es la de acogida EN ALEMANIA.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -31284,12 +34245,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>No publica un numero fijo de anos: exige doctorado completado y estar en la fase posdoctoral temprana de cualificacion.</t>
+          <t>La pagina del programa no fija un maximo numerico de anos desde el doctorado: describe a las personas destinatarias como 'postdoctoral researchers at an early career phase'. El limite duro, si lo hay, estaria en el PDF de bases 50-10, no leido en esta pasada.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Doctorado EXIGIDO al solicitar; fase posdoctoral temprana; no haber trabajado en la institucion de acogida elegida mas de un ano. Como la DFG no publica techo numerico de anos posdoctorales, una defensa en febrero de 2028 no acarrea riesgo de reloj, algo poco habitual y util.</t>
+          <t>VERIFICADO en la pagina del programa: 'Proposals may be submitted at any time', es decir presentacion realmente continua, sin plazos. Destinado a personal posdoctoral en fase temprana. FILTRO QUE LA AFECTA DE LLENO: para financiar una estancia FUERA de Alemania hay que haber trabajado como investigador o investigadora en Alemania de forma continuada al menos tres anos durante la etapa doctoral o posdoctoral, o bien haber cursado en Alemania la mayor parte de la escolarizacion y la educacion superior con no mas de tres anos fuera tras el doctorado. Ella no cumple ninguna de las dos, asi que la modalidad de estancia en el extranjero le esta vedada y solo le queda la acogida en Alemania.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -31299,7 +34260,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>La otra opcion alemana rodante, y la mas flexible de las dos: sin plazo y sin techo publicado de anos posdoctorales, su fecha de defensa incierta no le cuesta nada, y la beca puede incluso disfrutarse fuera de Alemania. Punto por punto: (a) exige doctorado, asi que la bloquea hasta febrero de 2028 y luego se abre sin caducidad dura; (b) la regla del ano en la institucion de acogida le es irrelevante, no tiene vinculacion alemana; (c) ciudadania de la UE, sin permisos; (d) el fin de la residencia en mayo de 2027 le deja nueve meses limpios de preparacion. LINEA CON LA QUE ENCABEZAR: genetica estadistica de rasgos complejos formulada como proyecto propio e independiente - Walter Benjamin financia el plan de investigacion de la solicitante y no el proyecto de un anfitrion, lo que encaja con quien elige deliberadamente una linea en vez de sumarse a otra, y le permite escribir ella misma la aplicacion a genomica psiquiatrica. La evaluacion de la DFG es una revision cientifica completa de la propuesta, asi que se escribe mas pesado que Humboldt (2-4 semanas) y lo que la sostiene es la calidad de la propuesta y no solo el CV, lo que en su caso ayuda dado un expediente de publicaciones fino. Util sobre todo como alternativa si se le pasa el reloj de cuatro anos de Humboldt o una ronda del comite.</t>
+          <t>Es la unica de sus vias nacionales que es de verdad continua: puede presentarla el mes que le convenga despues de defender, sin esperar a una ventana anual, lo que la convierte en el mejor colchon si la defensa de feb-2028 (ETA) se desplaza. Encaja por las lineas 1 y 2, con grupos alemanes fuertes en genetica psiquiatrica, y como ciudadana de la UE no necesita visado. RELOJES: (a) exige doctorado, asi que no antes de feb-2028; (b) no hay maximo de anos post-doctorado publicado en la pagina del programa, solo 'fase temprana', asi que el reloj no la aprieta y ese es precisamente su valor frente a Humboldt; (c) el filtro de tres anos de investigacion en Alemania solo aplica a la modalidad de salida al extranjero, que para ella queda descartada: su candidatura es necesariamente con acogida en Alemania. TRABAJO REAL: propuesta de investigacion propia mas compromiso de la institucion de acogida; esfuerzo de dos a cuatro semanas, mas los 3-6 meses previos de negociar el grupo aleman. Lo mismo que hace para Humboldt sirve aqui, asi que conviene preparar las dos con el mismo anfitrion.</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -31319,39 +34280,39 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED para la presentacion continua, el requisito de acogida y el filtro de arraigo aleman de la modalidad en el extranjero. UNVERIFIED para un posible maximo de anos post-doctorado y para las tarifas, que estan en el PDF de bases 50-10 y no se abrio.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Leer una sola vez https://www.dfg.de/resource/blob/168116/50-10-en.pdf para cerrar dos huecos: si hay un maximo de anos desde el doctorado y cuales son las tarifas. No es urgente, pero deja la fila completa y evita reabrirla cada pasada. Y, a efectos practicos, buscar el anfitrion aleman a la vez que el de Humboldt: es el mismo trabajo.</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Leer https://www.dfg.de/resource/blob/168116/50-10-en.pdf en una pasada posterior para la redaccion exacta de elegibilidad, las tarifas y si las solicitantes no residentes en Alemania necesitan anfitrion aleman ya al presentar.</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>https://www.dfg.de/en/research-funding/funding-opportunities/programmes/individual/walter-benjamin</t>
@@ -31359,7 +34320,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Rama 2. URLs Tier 1 identificadas (pagina del programa, FAQ, PDF de bases) pero el contenido se leyo por resumenes secundarios en esta pasada.</t>
+          <t>Rama 2, pasada 2026-09-21. Tier 1 leido directamente en dfg.de: 'Proposals may be submitted at any time', exigencia de institucion de acogida y las dos alternativas de arraigo aleman para financiar estancias fuera de Alemania. Sustituye a los resumenes secundarios de la pasada anterior.</t>
         </is>
       </c>
     </row>
@@ -31418,7 +34379,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>RESTRICCION DE PAIS DE ACOGIDA, dirimente: 'UK, Republic of Ireland, Low- or middle-income countries (apart from India and mainland China)'. Y desde el 29-10-2026 se estrecha aun mas: solo Reino Unido y paises de renta baja/media de Africa, Asia del Sur y Sudeste Asiatico, es decir Irlanda tambien sale. Ademas, desde el 25-08-2026 el esquema pasa a presentacion CONTINUA con tres cortes al ano (preseleccion en febrero, junio y septiembre), de modo que lo que se registre como 'plazo' son cortes, no cierres duros. Corte inmediato: 10-11-2026.</t>
+          <t>Esquema en presentacion continua con tres rondas de preseleccion y entrevistas al ano. Rondas confirmadas esta pasada a traves de un espejo universitario britanico: solicitud completa con aprobacion de la institucion para la ronda de otono de 2026, con preseleccion en febrero de 2027 y entrevistas en mayo de 2027; ronda siguiente con solicitud el 15-02-2027, preseleccion en junio de 2027 y entrevistas en septiembre de 2027. Todos los plazos de Wellcome cierran a las 15:00 GMT/BST. CONFLICTO DE FECHA SIN RESOLVER en la ronda de otono de 2026, ver Source_Note. Requiere institucion anfitriona en el Reino Unido (o pais elegible) que avale y apruebe la solicitud antes de enviarla.</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -31428,7 +34389,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>HALLAZGO DE LA PASADA, y corrige el mapa: esta ayuda NO se puede llevar a un centro espanol. Solo admite acogida en el Reino Unido y en paises de renta baja/media, y desde el 29-10-2026 ni siquiera Irlanda. Sigue puntuando 4 porque su contenido es exactamente ella (los hubs britanicos de genetica psiquiatrica -King's/SGDP, Cardiff, Edimburgo- son el destino natural de su linea 1-2 y esta abierta a mudarse), pero deja de ser una opcion 'desde Espana' y pasa a ser una decision de traslado al Reino Unido. Elegibilidad punto por punto: doctorado DEFENDIDO en la fecha de cierre, luego nada antes de feb-2028; techo de 3 anos posdoctorales, que cumple de sobra y ademas su residencia MIR cuenta como tiempo fuera de la investigacion y da margen; acogida britanica, obligatoria y por conseguir. El corte del 10-11-2026 NO es suyo: no tendra doctorado. Trabajo: XL, es una solicitud de programa propio con presupuesto, no una beca de formulario.</t>
+          <t>Sigue siendo su mejor via britanica por el contenido: los polos de genetica psiquiatrica del Reino Unido (King's College London, Cardiff, Edinburgh) son exactamente sus lineas 1 y 2, y el esquema premia la independencia temprana, donde su combinacion MD mas PhD pesa mas que un historial de publicaciones que todavia no tiene. RELOJES: (a) exige doctorado obtenido, y su defensa es feb-2028 (ETA), asi que las rondas de noviembre de 2026 y de febrero de 2027 estan CERRADAS para ella; (b) la primera ronda a la que podria presentarse es la de mediados de 2028, ya con el titulo en la mano; (c) al ser continuo con tres cortes anuales, el reloj no la castiga: puede elegir la ronda, que es justo lo que necesita con una fecha de defensa no confirmada. QUE HACE FALTA: una institucion anfitriona britanica que apruebe la solicitud internamente ANTES del plazo del financiador, y los centros britanicos imponen sus propios plazos internos meses antes (en el caso leido, aviso de intencion en agosto para una ronda de noviembre). Eso significa que si quiere la ronda de 2028 tiene que tener el anfitrion britanico comprometido a lo largo de 2027. TRABAJO REAL: propuesta larga, plan de desarrollo de carrera y aval institucional; entre dos y cuatro semanas de escritura efectiva, mas la negociacion previa.</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -31448,12 +34409,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>LIKELY. La estructura de tres rondas, la ronda del 15-02-2027 y la hora de cierre (15:00) estan leidas en un espejo universitario britanico Tier 2, no en wellcome.org, que devuelve 403 de forma persistente.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -31463,7 +34424,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -31473,7 +34434,7 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>Nada hasta 2028, pero condiciona una decision anterior: si quiere esta via, la acogida tiene que ser BRITANICA, asi que los contactos que abra en 2027 (para HFSP, EMBO o esta) conviene sesgarlos hacia King's/SGDP, Cardiff o Edimburgo. Reverificar en 2027 el modelo de cortes rodantes, que acababa de cambiar.</t>
+          <t>Nada por su parte hasta 2027, pero queda una comprobacion barata para una pasada futura: resolver el conflicto del 10 frente al 16 de noviembre de 2026 abriendo un segundo espejo universitario britanico independiente (por ejemplo una oficina de investigacion distinta de Oxford). Y la decision de fondo sigue en pie: si quiere esta via, los contactos que abra en 2027 deben sesgarse hacia el Reino Unido, porque el aval institucional britanico es condicion previa.</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -31488,7 +34449,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>wellcome.org devuelve 403 al fetch automatico dos pasadas seguidas (tambien su pagina de plazos). Verificado a traves de espejos universitarios britanicos que reproducen el texto de Wellcome: https://www.catch.ac.uk/research-grants-and-awards/wellcome-early-career-awards/ y https://www.law.ox.ac.uk/wellcome-early-career-awards . Cambio de paises elegibles del 29-10-2026 documentado aparte.</t>
+          <t>Rama 2, pasada 2026-09-21. wellcome.org confirmado en 403 por tercera vez: NO reintentar. Espejo abierto directamente: https://www.law.ox.ac.uk/wellcome-early-career-awards (Faculty of Law, Universidad de Oxford), que distingue explicitamente plazos internos de la facultad (aviso de intencion 04-08-2026, revision interna 18-08-2026) del plazo del financiador. CONFLICTO NO RESUELTO: esa pagina rotula el 16-11-2026 como 'Advised Latest Submission Deadline for Applicants (including Organisation Approval)', o sea plazo del financiador, mientras que la tabla de plazos de la propia Wellcome, citada en resultados de busqueda pero no abierta por el 403, da el 10-11-2026. Las dos fechas apuntan a la MISMA ronda: ambas fuentes coinciden en preseleccion en febrero de 2027 y entrevistas en mayo de 2027. No se elige entre ellas; se deja el conflicto escrito. Es irrelevante para ella en 2026 (no es elegible hasta feb-2028) pero importa para fijar el patron de fechas.</t>
         </is>
       </c>
     </row>
@@ -32047,17 +35008,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Ciclo 2026 VERIFICADO: apertura miercoles 04-02-2026, cierre miercoles 04-03-2026 a las 23:59 ET. BBRF NO HA PUBLICADO NINGUNA FECHA DE 2027: la fecha 2027-03-05 que llevaba esta fila es una extrapolacion y ademas cae en viernes, cuando el patron de BBRF es cerrar en miercoles. Se retira. ELEGIBILIDAD A VIGILAR (Tier 2, sin confirmar en Tier 1): los postdocs de primer ano son inelegibles y se exige 'M.D. with minimum PGY-IV training' o doctorado mas un puesto de investigacion ya en marcha. Con defensa en febrero de 2028, su primer ano postdoctoral va de febrero de 2028 a febrero de 2029, asi que la primera convocatoria realista seria la de 2029, NO la de 2027.</t>
+          <t>Titulo de nivel doctoral, y las bases admiten expresamente 'M.D. with [minimum PGY-IV training' ademas de Ph.D., Psy.D. o Pharm.D.; hay que estar ya empleada en research training o en un puesto de faculty research; el programa se dirige a advanced post-doctoral fellows, instructors y assistant professors; excluidos quienes hayan sido IP de un NIH R01 o equivalente y quienes esten en el rango de associate professor; obligatorio un mentor o colaborador senior on-site investigador consolidado en areas relevantes para trastornos psiquiatricos</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Cientificamente es el encaje mas proximo de toda esta rama con su linea 2: GWAS/PRS de trastornos psiquiatricos y de salud mental es exactamente el ambito de la BBRF, y el manuscrito de Nature Mental Health del proyecto de QIMR es la pieza con la que encabezar. Es ademas el raro buque insignia sin restriccion de nacionalidad ni de geografia y con una solicitud modesta y escribible (S-M: plan corto, carta del mentor, portada; nada parecido a una MSCA o una HFSP), y 70000 dolares discrecionales son palanca real para un proyecto computacional que apenas necesita mas que computo y su tiempo. EL BLOQUEO ES LA ETAPA DE CARRERA, NO EL CALENDARIO: exige doctorado en mano y empleo actual en un puesto de formacion investigadora o de facultad, y excluye explicitamente a las posdoctorales de primer ano. Punto por punto: no puede solicitar en la ronda de marzo de 2027 porque seguira siendo residente hasta el 22-05-2027 y no estara empleada en un puesto investigador; el caso limite interesante es la ronda de marzo de 2028, cuando ya tendra el titulo de medicina con formacion muy por encima de PGY-IV y, SI ha pasado a un puesto de formacion investigadora desde mediados de 2027, la via del MD significa que no necesitaria que la defensa de febrero de 2028 hubiera ocurrido - aunque 'advanced post-doctoral fellow' es forzado para quien lleva meses en su primer puesto, y los revisores lo leen de forma literal. El objetivo realista es la ronda de 2029, ya como posdoc de segundo ano con un mentor consolidado de genetica psiquiatrica en el mismo centro.</t>
+          <t>Encaja de lleno por tema: la BBRF financia investigacion sobre trastornos psiquiatricos graves y ella lideraria con la linea 2, GWAS/PRS de trastornos mentales, que es exactamente lo que el programa quiere. La duda que arrastraba esta fila queda resuelta contra la fuente Tier 1: las guidelines oficiales de 2026 NO excluyen el primer ano posdoctoral y, lo que es mas importante para ella, aceptan el titulo de M.D. con un minimo de formacion PGY-IV como titulo de nivel doctoral, de modo que no necesita esperar a la tesis (ETA febrero de 2028) para cumplir el requisito de titulacion: su MIR empezo el 22-05-2023, con lo que alcanzo el cuarto ano de residencia el 22-05-2026 y ya lo cumple hoy. El requisito que si tiene que resolver es el otro: hay que estar empleada en research training o en un puesto de investigacion en el momento de solicitar, y su residencia de Medicina de Laboratorio es asistencial, asi que la primera edicion realista es la de 2027 (ventana estimada febrero-marzo, sin publicar) solo si para entonces tiene un encaje institucional de investigacion; si no, la de 2028, ya con la tesis defendida y sin ambiguedad. Hace falta ademas un mentor on-site consolidado en psiquiatria, que es la pieza lenta: conseguir ese compromiso suele llevar meses y conviene cruzarlo con los candidatos de la pestana de grupos. La solicitud en si es de esfuerzo medio: face sheet, presupuesto, plan de investigacion y carta del mentor, sin preregistro ni institucion intermediaria.</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -32077,12 +35038,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -32092,7 +35053,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -32102,7 +35063,7 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>Tratar febrero-marzo de 2027 como ventana estimada, nunca como fecha. Descargar y extraer localmente las guidelines en PDF de la BBRF para verificar la exclusion del primer ano postdoctoral y el requisito PGY-IV: si se confirma, W-0007 hay que reprogramarla de 2027 a 2029 y dejamos de vigilar tres anos en balde.</t>
+          <t>1) Resolver la condicion de estar 'employed in research training' antes de febrero de 2027: hablar con su grupo de la Universidad de Murcia o con IBIMA para tener un vinculo investigador formal. 2) Identificar mentor on-site en psiquiatria o genetica psiquiatrica y pedirle compromiso con meses de antelacion. 3) Vigilar la publicacion del calendario 2027 en bbrfoundation.org/grants-prizes/bbrf-young-investigator-grants; hoy BBRF sigue sin publicar ninguna fecha de 2027.</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
@@ -32117,7 +35078,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>La URL anterior sin el prefijo 'bbrf-' devuelve HTTP 404; corregida. Importe VERIFIED; fechas de 2027 UNVERIFIED.</t>
+          <t>Guidelines oficiales en PDF descargadas con curl y extraidas localmente el 2026-09-21: https://bbrfoundation.org/sites/default/files/pdfs/2026-bbrf-young-investigator-grant-application-guidelines.pdf . Texto literal de elegibilidad: 'Applicants must have a doctoral level degree (e.g., M.D. with [minimum PGY-IV training, Ph.D., Psy.D., Pharm.D., etc.) and already be employed in research training or a faculty research position. The YI Grant is intended to support advanced post-doctoral fellows, instructors and assistant professors (or equivalent).' El face sheet pide a los solicitantes M.D. el ano en que completaron la residencia. Importe VERIFIED (hasta 35.000 USD/ano, 2 anos). CALENDARIO 2027 NO PUBLICADO: el ciclo 2026 fue 04-02-2026 a 04-03-2026 y la pagina no ofrece fechas de 2027; la ventana de febrero-marzo de 2027 es estimacion, nunca fecha.</t>
         </is>
       </c>
     </row>
@@ -32211,22 +35172,22 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -32297,7 +35258,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -32351,22 +35312,22 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -32480,34 +35441,34 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="X21" t="inlineStr">
         <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Abrir los dos PDF de EMBO que no se leyeron (SEG_guidelines_for_applicants.pdf y SEG_subsistence_rates_and_travel_allowance.pdf) para fijar los importes por dia, la estancia minima y el papeleo de acogida; en paralelo, preseleccionar una acogida en un pais EMBC distinto de Espana y sin copublicacion previa.</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Abrir los dos PDF de EMBO que no se leyeron (SEG_guidelines_for_applicants.pdf y SEG_subsistence_rates_and_travel_allowance.pdf) para fijar los importes por dia, la estancia minima y el papeleo de acogida; en paralelo, preseleccionar una acogida en un pais EMBC distinto de Espana y sin copublicacion previa.</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>https://www.embo.org/funding/fellowships-grants-and-career-support/scientific-exchange-grants/eligibility/</t>
@@ -32515,7 +35476,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>Rama 4. Tier 1: paginas propias del esquema y de elegibilidad de EMBO leidas el 2026-08-23. Importes deliberadamente sin cuantificar en vez de inventados.</t>
+          <t>Rama 4. Tier 1: paginas propias del esquema y de elegibilidad de EMBO. Releida el 2026-09-21: el caracter continuo se confirma literalmente ('Applications accepted throughout the year') y el tope de 3 meses sigue igual. Los dos PDF de importes y de plazo minimo de antelacion siguen sin leerse.</t>
         </is>
       </c>
     </row>
@@ -32820,7 +35781,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -32839,7 +35800,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>VIA NACIONAL ADICIONAL DESCUBIERTA, y reduce mucho la competencia: ademas de la solicitud directa a la ESHG, la AEGH (a) concede sus propias 'Becas AEGH para acudir al ESHG' (fueron 3 para el ESHG 2026, Gotemburgo) y (b) NOMINA CANDIDATAS PARA LA 'NATIONAL FELLOWSHIP' DE LA ESHG, que es un cupo por pais. Por la via AEGH la competencia es espanola y no europea. Confianza LIKELY: entradas del blog de la AEGH del 13 y el 15 de enero de 2026 leidas en el indice, no abiertas una a una. PENDIENTE: verificar si el cupo nacional exige tambien 2 anos de antiguedad como socia.</t>
+          <t>ESHG 2027: Rotterdam (Paises Bajos), congreso hibrido del 12 al 15 de junio de 2027. El envio de resumenes abre en diciembre de 2026 y cierra el jueves 04-02-2027 a las 23:59 CET; notificacion a primeros de abril de 2027. LA VIA AEGH QUEDA DESCARTADA PARA 2027, VERIFICADO EL 2026-09-21: la AEGH ya publico su nominacion a la Beca Nacional de la ESHG 2027 (plazo 15-11-2026) y exige tres cosas que ella no cumple: mas de dos anos continuados de antiguedad como socia de la AEGH, no mas de 4 anos de experiencia laboral postuniversitaria (ella es MD de 2019) y haber presentado comunicacion en el congreso interdisciplinar de Granada de 2026. Queda por tanto la via directa de la ESHG, cuyo esquema de fellowships para 2027 aun no esta publicado (2027.eshg.org/fellowships/ devuelve 404 a 2026-09-21); historicamente se solicita dentro del propio sistema de resumenes.</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -32849,7 +35810,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>El mejor objetivo de viaje a congreso dentro de su disciplina real y uno que puede preparar como doctoranda. La ESHG es el congreso europeo de genetica humana: la genetica estadistica de rasgos complejos y el GWAS/PRS de trastornos psiquiatricos (sus lineas 1 y 2) son contenido central del programa, y el trabajo derivado de QIMR es material listo. Punto por punto: (a) la elegibilidad es de 4 anos o menos de experiencia de posgrado, que una doctoranda cumple, y su defensa prevista para febrero de 2028 no es barrera; (b) el congreso cae del 12 al 15 de junio de 2027, es decir TRES SEMANAS DESPUES de que acabe la residencia el 22-05-2027, sin necesidad de negociar permiso, lo que lo convierte en el encaje de calendario mas limpio de toda esta rama; (c) Roterdam, UE, sin visado; (d) el plazo de resumenes del 04-02-2027 cae mientras sigue siendo residente, asi que el trabajo es escribir un resumen, no viajar. TRABAJO: XS-S, un resumen y una casilla. Nada que asegurar con una acogida. SALVEDAD: las condiciones concretas de las ayudas de 2027 aun no estan publicadas; el mecanismo y la regla de los 4 anos se infieren de las ediciones de 2025 y 2026.</t>
+          <t>Es su congreso natural en el carril de genetica clinica y de laboratorio y el escaparate donde esa comunidad espanola la veria; la linea con la que liderar es genetica estadistica aplicada a rasgos complejos con lectura diagnostica. Relojes: el congreso es del 12 al 15 de junio de 2027, tres semanas despues de terminar la residencia MIR el 22-05-2027, asi que no hay conflicto de agenda ni necesidad de permiso; no exige doctorado, por lo que el ETA de febrero de 2028 no la bloquea; sigue siendo predoctoral, que es justamente lo que la hace elegible para los esquemas de estudiante. Trabajo: minimo, un resumen antes del 04-02-2027 y, con el, la solicitud de ayuda cuando la ESHG publique el esquema de 2027. No hace falta acogida. El cambio de esta pasada es negativo y hay que asumirlo: el atajo nacional via AEGH, que era lo que abarataba la competencia, esta cerrado para ella por antiguedad de socia y por los 4 anos maximos de experiencia postuniversitaria.</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -32859,7 +35820,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>La ESHG concede un numero considerable de ayudas cada ano frente a un grupo amplio de resumenes; sin tasa publicada.</t>
+          <t>Via directa europea, sin el cupo nacional que reducia la competencia: se compite con toda la cantera europea de genetica humana.</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -32869,12 +35830,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -32884,7 +35845,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -32894,7 +35855,7 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>Verificar en enero de 2027 si la nominacion espanola a la national fellowship de la ESHG exige 2 anos de antiguedad como socia de la AEGH: si no los exige, es un atajo real a un congreso de su linea (ver SUB-0010).</t>
+          <t>1) Diciembre de 2026: vigilar la apertura del sistema de resumenes de la ESHG 2027 y enviar resumen antes del 04-02-2027 23:59 CET. 2) Al abrirse ese sistema, comprobar si incluye la solicitud de fellowship o premio de inicio de carrera para 2027 (la pagina /fellowships/ aun no existe). 3) Darse de alta en la AEGH igualmente (SUB-0010): arranca el reloj de 2 anos y deja la via nacional disponible para la ESHG 2029, no para la de 2027 ni la de 2028.</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
@@ -32909,7 +35870,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>Rama 4. Fechas, sede y plazo de resumenes VERIFICADOS en el sitio de la ESHG 2027. La elegibilidad y el mecanismo de las ayudas se arrastran de las paginas de 2025/2026 via resultados de busqueda: aun sin confirmar para 2027.</t>
+          <t>Tier 1 doble el 2026-09-21: https://2027.eshg.org/abstracts/ (sede Rotterdam, fechas 12-15 de junio de 2027, apertura en diciembre de 2026 y cierre el 04-02-2027 23:59 CET) y https://aegh.org/beca-eshg-2027-para-asistir-a-la-eshg-2027/ (criterios de la nominacion nacional espanola, plazo 15-11-2026, dotacion: inscripcion gratuita mas 600 EUR de viaje). La pregunta que quedaba abierta desde agosto sobre si el cupo nacional exige 2 anos de antiguedad como socia queda RESUELTA: si los exige.</t>
         </is>
       </c>
     </row>
@@ -32921,7 +35882,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Premios L'Oreal-UNESCO For Women in Science Espana (XXI edicion, prevista)</t>
+          <t>Premios L'Oreal-UNESCO For Women in Science Espana (XXI edicion, bases 2026)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -32946,11 +35907,22 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>28</v>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>15000 por premio (cinco premios)</t>
@@ -32978,7 +35950,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Respuesta a la pregunta abierta de la pasada anterior: un contrato de residencia MIR NO sirve, porque las bases piden un contrato de INVESTIGACION con el centro que presenta la candidatura, y ademas exigen doctorado con 4 anos cumplidos desde la lectura y una estancia previa de 2 anos seguidos fuera (las suyas son de ~3 meses), de modo que no seria elegible hasta ~2032 y la ayuda queda fuera del radar util.</t>
+          <t>La edicion espanola esta abierta ahora mismo y el area de Ciencias de la Vida cubre genetica y neurociencia, pero sigue siendo un premio a proyecto liderado por una investigadora con contrato en vigor en un centro de investigacion espanol, condicion que no cumple mientras sea residente y predoctoral.</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -33003,7 +35975,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -33013,7 +35985,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -33023,7 +35995,7 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>Ninguna. No volver a perseguirla hasta ~2032. No confundirla con los International Awards / International Rising Talents de la UNESCO (F-0035), que son otro programa, por nominacion de terceros.</t>
+          <t>Accion opcional y de bajo coste antes del 19-10-2026: abrir a mano el PDF de bases (es un escaneo, no se puede leer de forma automatica) y comprobar si exige el titulo de doctora; si NO lo exigiera, la convocatoria estaria viva para ella cuatro semanas y habria que reevaluar el Fit. Si lo exige, no volver a perseguirla hasta que tenga contrato posdoctoral.</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
@@ -33033,12 +36005,12 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>https://www.loreal.com/es-es/espana/news/commitment/loreal-unesco-abre-convocatoria-de-premios-for-women-in-science/</t>
+          <t>https://www.forwomeninscience.com/statics/filemanager/Spain/2026/20260714_Bases%20Legales%20Premios%20For%20Women%20in%20Science%202026-2027%20Espan%CC%83a.pdf</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>Bases legales integras (edicion XIX) extraidas de un espejo universitario: https://sgi.unizar.es/sites/sgi/files/convocatorias/2024/12%204%205023_Bases%20Legales%20Premios%20For%20Women%20in%20Science%202024%202025%20Espa%C3%B1a%20TEXTO.pdf . El PDF equivalente en forwomeninscience.com es un escaneado sin capa de texto, ilegible para el rastreo.</t>
+          <t>Bases Tier 1 localizadas y descargadas (2,9 MB) el 2026-09-21: la portada si se lee y dice literalmente 'PREMIOS A LA INVESTIGACION - UNESCO For Women in Science. XXI EDICION - 2026. BASES CONVOCATORIA 2026' y remite a https://www.forwomeninscience.com/challenge/show/169 ; el cuerpo del documento es un escaneo sin capa de texto, asi que los requisitos NO se han podido leer. Ventana 07-09-2026 a 19-10-2026, cinco premios de 15.000 euros y areas de Ciencias de la Vida y Medioambiente: procede de fuentes Tier 2 concordantes (paginas de convocatorias universitarias y nota de loreal.com), de ahi Confidence LIKELY.</t>
         </is>
       </c>
     </row>
@@ -33593,7 +36565,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -33612,7 +36584,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Estudiantes de posgrado e investigadoras posdoctorales; una revista por ronda; el trabajo debe caer dentro del ambito de Development, Journal of Cell Science o Journal of Experimental Biology. La ronda del 07-08-2026 ya paso y las de 2027 no estan publicadas.</t>
+          <t>Estudiantes de posgrado e investigadoras posdoctorales que visiten otro laboratorio; hasta 3000 GBP; sin restriccion de nacionalidad. Una sola revista por ronda y por persona, y una sola candidata por laboratorio y ronda; el trabajo debe caer en el ambito de Development, Journal of Cell Science o Journal of Experimental Biology. El viaje debe realizarse dentro de los 6 meses siguientes a la concesion y no se financian cursos de formacion. Solo se puede recibir una Travelling Fellowship cada dos anos. Documentacion: carta de status de la jefa de departamento, carta de apoyo de la directora de tesis, carta del laboratorio anfitrion, CV y lista de publicaciones, todo en ingles. Rondas de 2026 verificadas: 07-08-2026 (viaje posterior al 21-09-2026) y 23-10-2026 (viaje posterior al 07-12-2026, fecha en que se anuncia la decision). Las rondas de 2027 no estan publicadas.</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -33622,7 +36594,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Genuinamente abierta para ella como doctoranda y uno de los pocos esquemas que podria pagar una vuelta a QIMR Berghofer sin limites de nacionalidad, pero el filtro de ambito de las revistas es el problema: la genetica estadistica humana, el GWAS/PRS y la epidemiologia del sueno infantil quedan fuera de Development, Journal of Cell Science y Journal of Experimental Biology, asi que una solicitud honesta tendria que construirse sobre una visita de biologia celular u organismica que hoy no esta proponiendo.</t>
+          <t>Fit 2 CONFIRMADO, no asumido: el esquema exige trabajar en el ambito de Development, Journal of Cell Science o Journal of Experimental Biology, y su trabajo es genetica estadistica de rasgos complejos, que no cae en ninguno de los tres.</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -33647,34 +36619,34 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>No solicitar la ronda del 23-10-2026: el encaje tematico no da. Volver solo si una estancia futura tiene componente real de biologia celular, del desarrollo o experimental. Nota util para otras filas: The Company of Biologists tiene ademas ECR Visiting Fellowships y Research Partnership Kickstart Travel Grants, esquemas distintos que no se han examinado todavia.</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Volver a ella solo si una estancia futura tiene un componente real de biologia celular, del desarrollo o experimental; si no, dejarla registrada y no redescubrirla.</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>https://www.biologists.com/travelling-fellowships/</t>
@@ -33682,7 +36654,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Rama 4. Tier 1: pagina propia de The Company of Biologists leida el 2026-08-23.</t>
+          <t>Tier 1: https://www.biologists.com/travelling-fellowships/ releida el 2026-09-21 con curl --compressed (el fetch sin --compressed devuelve binario ilegible). Plazo del 23-10-2026 confirmado en la propia pagina.</t>
         </is>
       </c>
     </row>
@@ -34280,27 +37252,27 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Ninguna. No volver a revisarla semanalmente. El Stanley Center no tiene ninguna convocatoria abierta a la que se pueda presentar por si misma; su unica via alli es el empleo (ofertas de postdoc), que corresponde a la pestana de postdocs.</t>
+          <t>Sin novedad al 21-09-2026. Comprobado tambien el Psychiatric Genomics Consortium: no aparece ninguna convocatoria de ayudas o becas propia de los grupos de trabajo del PGC. Ni el Stanley Center ni el PGC tienen hoy nada a lo que ella pueda presentarse por si misma; no revisar semanalmente.</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
@@ -34366,7 +37338,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>NO APLICABLE A ELLA: los International Awards son solo por nominacion y para mujeres cientificas eminentes (cinco laureadas al ano en todo el mundo); las International Rising Talents se seleccionan ENTRE las ganadoras de los programas nacionales o regionales, no por solicitud directa.</t>
+          <t>Programa por NOMINACION, no por solicitud propia: cinco galardones internacionales de 100.000 euros a cientificas consagradas, uno por region del mundo; ciclo 2027 con nominaciones hasta el 30-06-2026</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -34396,39 +37368,39 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Ninguna. Es un premio por nominacion a cientificas de trayectoria consagrada, no una via de solicitud para ella; revisar solo si algun dia gana la edicion espanola.</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>Ninguna. Revisar solo si gana la edicion espanola.</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>https://www.forwomeninscience.com/</t>
@@ -34436,7 +37408,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>Rama 3. La pagina del programa de la UNESCO (unesco.org/en/prizes/women-science) devolvio HTTP 503 el 2026-08-23; la estructura se describe solo desde fuentes secundarias: tratar como pista.</t>
+          <t>Rama 3. Verificado el 2026-09-21 contra un espejo universitario de la convocatoria internacional 2027 (Tier 2): https://convocatoriasinvestigacion.usal.es/convocatoria-del-premio-loreal-unesco-for-women-in-science-2027/ . Cinco premios de 100.000 euros, nominaciones abiertas hasta el 30-06-2026 (ya cerradas) y portal en https://www.forwomeninscience.com/challenge/show/158 . Queda confirmado que es un programa de nominacion y que NO se solapa con la modalidad espanola (F-0024).</t>
         </is>
       </c>
     </row>
@@ -34608,7 +37580,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -34627,7 +37599,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Socia de SEMEDLAB en el momento de solicitar (esta convocatoria NO exige antiguedad, a diferencia de otras ayudas de la misma Fundacion que piden 1 ano); menor de 40 anos; no haber disfrutado antes de este Programa ni de su version IFCC; documentacion a secretaria@fundacionjlc.es con asunto 'BECAS INTERNACIONALES DE LA FUNDACION'; 5 becas; fallo a finales de noviembre de 2026. NO VERIFICADO si ella ya es socia de SEMEDLAB: es el unico punto que puede tumbar la solicitud.</t>
+          <t>Socia de SEMEDLAB en el momento de solicitar (la convocatoria dice literalmente 'El aspirante, socio de SEMEDLAB'); menor de 40 anos; no haber disfrutado antes de este Programa ni de su version IFCC; laboratorio receptor FUERA DE ESPANA; acuerdo firmado entre el jefe del laboratorio espanol donde trabaja y el del receptor; memoria de maximo 10 paginas segun el Anexo 1 (institucion base, institucion anfitriona, objetivos, plan de trabajo con fechas, impacto); carta al presidente de SEMEDLAB; checklist oficial obligatoria adjunta; documentacion a secretaria@fundacionjlc.es con asunto 'BECAS INTERNACIONALES DE LA FUNDACION'; 5 becas; fallo a finales de noviembre de 2026. VENTANA DE EJECUCION VERIFICADA EL 2026-09-21 Y DECISIVA: la estancia debe realizarse entre marzo de 2027 y marzo de 2028. DATO QUE FALTA: si ya es socia de SEMEDLAB y cuanto tarda el alta (semedlab.es bloquea el fetch automatico).</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -34637,7 +37609,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Es lo unico con plazo inminente para lo que HOY es elegible, y entra por su puerta menos explotada: la clinica. Por que encaja con ELLA: la ventana de estancia (marzo 2027 - marzo 2028) se solapa casi exactamente con el hueco entre el fin del MIR (22-05-2027) y su defensa prevista (febrero de 2028), asi que cabe de junio de 2027 en adelante sin tocar ni la residencia ni la tesis. Linea a liderar: genetica estadistica aplicada, encajando el proyecto como implantacion de scores poligenicos y pipelines GWAS-PRS en un laboratorio de genomica clinica, que es donde es INDEPENDIENTE; no proponer electrofisiologia ni neuroimagen, que solo maneja supervisada. Elegibilidad punto por punto: edad menor de 40, cumple; trabaja en laboratorio espanol (HRU de Malaga), cumple; laboratorio receptor fuera de Espana, cumple con QIMR Berghofer (contacto ya existente, pero exige visado australiano: anotar, no descartar) o con un laboratorio de genomica clinica europeo, que evita el visado; no beneficiaria previa, previsiblemente cumple; socia de SEMEDLAB, SIN VERIFICAR y decisivo. Reencuadre necesario: el programa habla de laboratorios clinicos y de tecnologias aplicables al laboratorio de origen, asi que la memoria debe argumentar el retorno al laboratorio de Malaga, no el avance de la tesis. Trabajo real: su parte es S (memoria del Anexo 1 con fechas, carta de motivacion al presidente de la Fundacion, CV), 1-2 dias. El cuello de botella NO es el papeleo sino los avales: necesita en menos de 30 dias la aceptacion escrita del director receptor y la firma de su jefe de servicio; una carta de aceptacion internacional suele tardar de 2 a 4 semanas, de modo que el correo al anfitrion sale esta semana o no sale.</t>
+          <t>Encaja por el carril clinico, no por el investigador: es una beca de la sociedad de su propia especialidad (Medicina de Laboratorio) para una estancia de hasta 3 meses en un laboratorio de fuera de Espana, y la competencia es solo entre socias espanolas de SEMEDLAB para 5 plazas. La linea con la que liderar es genetica de laboratorio / genetica estadistica aplicada al diagnostico, que une su tesis con su especialidad; el destino natural es QIMR Berghofer, donde ya tiene contacto. Relojes, uno a uno: menor de 40 (MD 2019, cumple); no exige doctorado (no la bloquea el ETA de febrero de 2028); NO exige antiguedad como socia, a diferencia de otras ayudas de la misma Fundacion que piden 1 ano; residencia MIR en Malaga hasta el 22-05-2027 y ventana de ejecucion marzo 2027 - marzo 2028, asi que la estancia cabe de forma natural entre junio de 2027 y marzo de 2028, ya terminada la residencia. RIESGO REAL DETECTADO ESTA PASADA: el impreso exige la firma del jefe del laboratorio espanol 'en el que actualmente trabaja' y un acuerdo entre ambos centros; si la estancia cae despues del 22-05-2027 hay que asegurarse de que el Hospital Regional Universitario de Malaga (o el centro donde este entonces) siga avalandola. Trabajo real: bajo, 1-2 dias de escritura (memoria de 10 paginas maximo, CV, DNI, carta de motivacion, formulario PEP de la IFCC y los dos documentos de aceptacion), pero el camino critico NO es escribir sino conseguir tres firmas ajenas en nueve dias. Acogida: obligatoria y previa, con carta de aceptacion del centro receptor.</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -34647,7 +37619,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>5 becas para un colectivo cerrado (socias jovenes menores de 40 de una sociedad nacional de especialidad); se evalua calidad de memoria, no curriculo competitivo</t>
+          <t>5 becas, restringidas a socias de SEMEDLAB menores de 40 anos: bolsa de candidatas nacional y pequena.</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -34662,27 +37634,27 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>URGENTE, 30 dias. 1) Comprobar hoy si es socia de SEMEDLAB y, si no, tramitar el alta. 2) Esta semana, correo al laboratorio receptor pidiendo carta de aceptacion. 3) En paralelo, pedir al jefe de servicio la firma del acuerdo. 4) Enviar antes del 30-09-2026.</t>
+          <t>NUEVE DIAS. En este orden y hoy mismo: 1) Escribir a secretaria@fundacionjlc.es Y a la secretaria de SEMEDLAB preguntando (a) si consta como socia y (b) si un alta tramitada esta semana permite solicitar antes del 30-09; si no es socia, darse de alta en https://semedlab.es/alta-de-socio/ (cuota anual 85 EUR + 15 de inscripcion, 60 EUR residentes segun fuente secundaria, sin verificar) y pedir por escrito la confirmacion de condicion de socia, que es lo que la Fundacion exige. 2) Hoy tambien: correo al laboratorio receptor de fuera de Espana (QIMR Berghofer es la via mas rapida por contacto previo) pidiendo carta de aceptacion y fechas dentro de la ventana marzo 2027 - marzo 2028, preferiblemente posterior al 22-05-2027. 3) Manana: pedir al jefe de servicio del Hospital Regional de Malaga el documento de aceptacion y apoyo y la firma del acuerdo entre laboratorios. 4) Redactar la memoria siguiendo el Anexo 1 (https://www.fundacionjlc.es/wp-content/uploads/2025/07/Anexo-1.pdf, maximo 10 paginas, Arial 12, A4) y la carta al presidente de SEMEDLAB. 5) Rellenar el formulario PEP de la IFCC y marcar la checklist (https://www.fundacionjlc.es/wp-content/uploads/2025/07/Checklist-documentacion-presentar-INTERCAMBIO-DE-PROFESIONALES.pdf), que hay que adjuntar firmada. 6) Enviar todo a secretaria@fundacionjlc.es antes del 30-09-2026 con el asunto exigido. SI EL ALTA DE SOCIA NO PUEDE RESOLVERSE ESTA SEMANA, LA OPERACION ES INVIABLE PARA 2026: en ese caso, darse de alta igualmente y apuntar a la convocatoria de 2027.</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr"/>
@@ -34693,7 +37665,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Tier 1, web oficial de la Fundacion Jose Luis Castano-SEQC. El fetch automatico dio 503; el texto se obtuvo con curl y extraccion local, no por resumen automatico.</t>
+          <t>Tier 1, pagina oficial de la Fundacion Jose Luis Castano-SEQC, releida el 2026-09-21 con curl (WebFetch sigue dando 503; curl con --cacert y reintentos da 200). Plazo del 30-09-2026 CONFIRMADO en el texto vivo. Anexo 1 y checklist descargados y leidos esta pasada. La checklist anade un documento que no figuraba en la ficha: el 'Formulario PEP IFCC cubierto'. semedlab.es responde 202 con 185-249 bytes al fetch automatico (mismo patron de bloqueo que fundaciontatiana.com): el alta de socia no pudo verificarse.</t>
         </is>
       </c>
     </row>
@@ -34787,27 +37759,27 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>Vigilar ispg.net entre enero y marzo de 2027 el anuncio de sede y fechas del WCPG 2027 (ver W-0009); hacerse socia junior de la ISPG antes de solicitar y tener el abstract preparado con antelacion. El plazo ECIP coincide con el cierre de abstracts, hacia mayo de 2027.</t>
+          <t>Sin senal del WCPG 2027 todavia. Volver a mirar en enero-marzo de 2027 (ver W-0009) y no antes: ispg.net/wcpg-2027/ aun no existe y el dominio bloquea curl, asi que habra que abrirlo a mano o por WebFetch. Mientras tanto, hacerse socia junior de la ISPG (SUB-0005 / SUB-0013) y tener el abstract preparado: el plazo ECIP coincide con el cierre de resumenes, hacia mayo de 2027.</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr"/>
@@ -34818,7 +37790,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Tier 1 (ispg.net/ecip-program/ y ispg.net/wcpg-2026/). TRAMPA: ispg.net/abstract-submissions/ sirve contenido obsoleto de 2022 con respuesta 200; la informacion viva esta en la pagina del congreso del ano en curso.</t>
+          <t>Tier 1 (ispg.net/ecip-program/ y ispg.net/wcpg-2026/). TRAMPA: ispg.net/abstract-submissions/ sirve contenido obsoleto de 2022 con respuesta 200. BLOQUEO NUEVO 2026-09-21: ispg.net y ispg.net/wcpg-2027/ devuelven 403 de Cloudflare a curl; via WebFetch la pagina /ecip-program/ sigue sirviendo SOLO el ciclo 2026 (habla del 'travel stipend to the 2026 WCPG' y de la exclusion por premios recibidos en 2022-2025). Sin senal alguna de sede, fechas ni portal de resumenes del WCPG 2027 a 2026-09-21.</t>
         </is>
       </c>
     </row>
@@ -34881,7 +37853,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Ser doctoranda; enviar a secretaria.tecnica@senc.es nombre, afiliacion, nombre de la directora o director de tesis y copia del abstract enviado al congreso SENC como primera autora; 5 preseleccionadas dan una charla de 15 minutos en el simposio 'Young investigators building Neuroscience' y el Comite vota la mejor. Edicion 2025: del 10-04-2025 al 10-06-2025. PUNTO A VERIFICAR: si la regla de 2 anos consecutivos de antiguedad como socia, que aparece redactada para las ayudas de viaje, se aplica tambien a los premios.</t>
+          <t>Ser doctoranda; enviar a secretaria.tecnica@senc.es nombre, afiliacion, nombre de la directora o director de tesis y copia del abstract enviado al congreso SENC como primera autora; 5 preseleccionadas dan una charla de 15 minutos en el simposio 'Young investigators building Neuroscience' y el Comite vota la mejor. Edicion 2025: del 10-04-2025 al 10-06-2025. PUNTO RESUELTO EL 2026-09-21: la regla de los DOS ANOS CONSECUTIVOS de cuota al corriente se aplica, segun el documento oficial 'Requisitos para solicitudes de ayudas y becas SENC', SOLO al 'acceso a ayudas para viajes o para la organizacion de actividades'; los premios no se mencionan y la convocatoria del Rita Levi-Montalcini no exige antiguedad ni, en su texto, membresia. El premio es por tanto alcanzable en 2027 sin esperar dos anos de socia.</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -34891,7 +37863,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Es el caso puro de algo para lo que califica AHORA por ser predoctoral y dejara de calificar despues. Por que encaja con ELLA: el premio esta reservado a doctorandas y el congreso bienal de la SENC de 2027 caeria hacia septiembre de 2027, con ella todavia predoctoral (defensa prevista en febrero de 2028); es probablemente su ULTIMA ventana para este premio. Linea a liderar: aqui conviene el trabajo empirico australiano (neuroimagen mas genetica), porque el auditorio es de neurociencia y no de genetica estadistica; su parte de neuroimagen es supervisada, pero para una charla de 15 minutos eso no es obstaculo y el analisis genetico que si domina es el nucleo del mensaje. Elegibilidad punto por punto: doctoranda matriculada, cumple; abstract como primera autora, lo tiene; carta de la directora de tesis, trivial; socia de la SENC, sin resolver la antiguedad. Trabajo real: XS, un correo con el abstract y los datos, mas 15 minutos de charla si la preseleccionan. Sin anfitrion ni aval externo. Ademas es acumulable: las bases dicen expresamente que los premios son compatibles con las ayudas de viaje de la SENC, asi que puede ir a las dos cosas para el mismo congreso.</t>
+          <t>Es el mejor premio de etapa predoctoral que tiene a tiro y ahora se confirma que esta a tiro: la unica condicion dura es ser doctoranda y presentar abstract como primera autora al congreso bienal de la SENC, y la barrera que se temia (dos anos de antiguedad como socia) NO se aplica a los premios. Relojes: sigue siendo predoctoral hasta la defensa prevista en febrero de 2028, asi que la edicion de 2027 es su ultima oportunidad limpia y la de 2029 ya no; la residencia MIR termina el 22-05-2027 y el congreso bienal de la SENC suele celebrarse en septiembre, sin conflicto. Linea con la que liderar: genetica estadistica y GWAS/PRS en salud mental, encuadrado como neurociencia de rasgos complejos. Trabajo: XS de verdad, un correo con nombre, afiliacion, director de tesis y el abstract ya enviado al congreso, mas preparar una charla de 15 minutos si queda entre las 5 preseleccionadas. No hace falta acogida. Dotacion pequena (600 EUR) pero es visibilidad ante el Comite de Jovenes Investigadores de la SENC.</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -34901,7 +37873,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Sociedad nacional; 5 preseleccionadas y una ganadora sobre un colectivo de pocas decenas de doctorandas socias que presentan abstract al bienal</t>
+          <t>Restringido a doctorandas que presentan abstract al congreso bienal de la SENC; 5 preseleccionadas y un solo premio.</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -34916,27 +37888,27 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>Hacerse socia de la SENC ya (ver SUB-0003: arranca ademas el reloj de 2 anos de las ayudas de viaje); abrir el PDF 'Requisitos para solicitudes de ayudas y becas SENC' para saber si la regla de 2 anos se aplica tambien a los premios; confirmar fechas y sede del SENC 2027 y vigilar senc.es en abril de 2027.</t>
+          <t>1) Alta como socia de la SENC ya (SUB-0003): no la necesita para el premio pero si para las ayudas de viaje, cuyo reloj de 2 anos solo arranca al pagar la primera cuota. 2) Vigilar senc.es a partir del 10-04-2027 (la edicion 2025 abrio el 10-04 y cerro el 10-06) y confirmar sede y fechas del congreso bienal SENC 2027. 3) Planificar el abstract como primera autora para ese congreso.</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr"/>
@@ -34947,7 +37919,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Tier 1: PDF oficial de la convocatoria 2025 descargado con curl y extraido localmente con pypdf, no por resumen automatico. Indice de convocatorias en https://www.senc.es/ayudas-de-la-senc/</t>
+          <t>Tier 1: convocatoria 2025 en PDF, mas el documento oficial https://www.senc.es/wp-content/uploads/2024/09/Requisitos-solicitudes-de-ayudas-y-becas-SENC.pdf descargado y extraido el 2026-09-21, que acota la regla de 2 anos a las ayudas de viaje y de organizacion de actividades y no la extiende a los premios. Indice: https://www.senc.es/ayudas-de-la-senc/</t>
         </is>
       </c>
     </row>
@@ -35010,7 +37982,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Socia de la SENC con 2 o mas anos consecutivos de antiguedad en el momento de solicitar (excepcion: las doctorandas de primer ano pueden solicitar con 1 ano de membresia, excepcion que ella ya no aprovecha); abstract como primera autora presentadora; EL TRABAJO NO PUEDE ESTAR PREVIAMENTE PUBLICADO; carta de la directora de tesis certificando que cursa el doctorado; una sola travel grant por ano; solicitud por el area privada de socias. Ciclo 2026 cerrado: FENS/ENCODS el 31-01-2026 y SfN el 10-05-2026.</t>
+          <t>Socia de la SENC en el momento de la solicitud Y al corriente de pago en los DOS ANOS CONSECUTIVOS ANTERIORES a la solicitud: regla CONFIRMADA el 2026-09-21 en el documento oficial 'Requisitos para solicitudes de ayudas y becas SENC', que la aplica al 'acceso a ayudas para viajes o para la organizacion de actividades' y que la Junta Directiva introdujo precisamente porque la mayoria de altas de socias estudiantes se pedian justo antes de solicitar ayuda. Excepcion para doctorandas de primer ano (1 ano de membresia), que ella ya no aprovecha. Ademas: abstract como primera autora presentadora; el trabajo no puede estar previamente publicado; carta de la directora de tesis; una sola travel grant por ano; solicitud por el area privada de socias. Ciclo 2026 cerrado: FENS/ENCODS el 31-01-2026 y SfN el 10-05-2026.</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -35020,7 +37992,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Encaje real pero bloqueado por reloj de membresia, no por merito. La condicion de 2 anos consecutivos significa que, si se da de alta ahora (agosto de 2026), no sera elegible hasta agosto de 2028: no llega ni al SENC 2027 ni al SfN 2027. No lo pierde, solo lo retrasa, porque tras defender entra por la via de postdoc de primeros anos, abierta hasta 4-8 anos despues del doctorado. Detalle a su favor que conviene registrar: el requisito de que el abstract NO este previamente publicado juega a su favor precisamente porque sus dos manuscritos siguen en revision. La accion util hoy es solo administrativa: alta inmediata para que el contador corra.</t>
+          <t>Ayudas de viaje pequenas y de competencia baja para congresos que si son suyos (FENS, SfN, SENC), pero con un cerrojo temporal: exigen dos anos consecutivos de cuota pagada antes de solicitar, regla ya verificada en el documento oficial. Si se da de alta en 2026, su primera convocatoria elegible es la de 2028, cuando ya habra defendido segun el ETA de febrero de 2028; si se da de alta ahora mismo, llega a tiempo de las convocatorias de finales de 2028 en adelante. Por eso el valor de la fila no esta en solicitar sino en arrancar el reloj hoy.</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -35045,27 +38017,27 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>Alta como socia de la SENC ya (SUB-0003). Revisar el calendario de travel grants que la SENC publica cada diciembre: el de 2026 se publico el 23-12-2025.</t>
+          <t>Alta como socia de la SENC esta semana (SUB-0003): el reloj de 2 anos corre desde la primera cuota y es el unico paso que no se puede recuperar despues. Revisar el calendario de travel grants que la SENC publica cada diciembre (el de 2026 se publico el 23-12-2025).</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr"/>
@@ -35076,7 +38048,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>Tier 1: los dos PDF oficiales (programa 2026 y calendario 2026) descargados con curl y extraidos localmente con pypdf. Calendario: https://www.senc.es/wp-content/uploads/2025/12/04_SENC-Travel-Grants-CALENDAR-2026_WEB_EN.pdf</t>
+          <t>Tier 1: PDF del programa 2026 y del calendario 2026, mas https://www.senc.es/wp-content/uploads/2024/09/Requisitos-solicitudes-de-ayudas-y-becas-SENC.pdf descargado y extraido el 2026-09-21, que es la fuente literal de la regla de los dos anos consecutivos.</t>
         </is>
       </c>
     </row>
@@ -35174,22 +38146,22 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
@@ -35205,7 +38177,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>Tier 1, aegh.org. Las bases completas NO se publican en PDF: solo se envian por secretaria@aegh.org.</t>
+          <t>Tier 1, aegh.org. Revisado el 2026-09-21: la AEGH no ha publicado todavia la edicion 2027 (lo ultimo en su seccion de ayudas es la nominacion a la Beca Nacional de la ESHG 2027, del 15-11-2026). Las bases completas siguen sin publicarse en PDF: solo se envian por secretaria@aegh.org.</t>
         </is>
       </c>
     </row>
@@ -35303,22 +38275,22 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
@@ -35334,7 +38306,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Tier 1, aegh.org.</t>
+          <t>Tier 1, aegh.org. Revisado el 2026-09-21: sin edicion XXVII publicada; se espera mediados de enero de 2027 (ver W-0018).</t>
         </is>
       </c>
     </row>
@@ -35432,27 +38404,27 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>Verificar su edad antes de invertir nada aqui. Alta en la AEGH (SUB-0010).</t>
+          <t>PREGUNTAR A LA DUENA SU FECHA DE NACIMIENTO: sin ese dato no se puede saber si cumple el limite de 35 anos y la fila queda en el aire. Alta en la AEGH (SUB-0010) para arrancar el reloj de 2 anos de antiguedad. Revisar aegh.org a mediados de enero de 2027.</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr"/>
@@ -35463,7 +38435,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>Tier 1, aegh.org.</t>
+          <t>Tier 1, aegh.org. Revisado el 2026-09-21: sin edicion 2027 publicada. DATO QUE FALTA Y QUE DECIDE LA FILA ENTERA: no conocemos su fecha de nacimiento, y la bolsa exige tener menos de 35 anos o estar en paro. No se supone: hay que preguntarselo a la duena antes de invertir nada aqui.</t>
         </is>
       </c>
     </row>
@@ -35807,27 +38779,27 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>Revisar ses.org.es en diciembre de 2026 para la edicion 2027; escribir a secretaria.tecnica@ses.org.es para confirmar si admite predoctorales y que antiguedad de socia exige.</t>
+          <t>Sin novedad al 21-09-2026: no hay bases de 2027 publicadas. Volver a mirar en diciembre de 2026 y escribir a secretaria.tecnica@ses.org.es para confirmar si admite predoctorales. CUIDADO al releer el tablon: el bloque de 2026 sigue rotulado 'CONVOCATORIA ABIERTA' aunque su plazo vencio.</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr"/>
@@ -36057,27 +39029,27 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>1) Darse de alta como socia de la SES YA, en septiembre de 2026 (SUB-0008): es el unico paso que abre la puerta y cada semana de retraso corre contra el ano de antiguedad. 2) Escribir a secretaria.tecnica@ses.org.es para resolver dos ambiguedades: si el ano de antiguedad se cuenta hasta la apertura o hasta el cierre, y si la clausula del medico residente en ultimo ano se aplica a la IP o solo a los colaboradores. 3) Volver al tablon en noviembre de 2026 para la edicion 2027.</t>
+          <t>Sin novedad al 21-09-2026: el tablon de becas y premios de la SES no ha publicado bases de 2027 y su entrada mas reciente sigue siendo la de 2026 (cierre 25-01-2026), pese a estar rotulada 'CONVOCATORIA ABIERTA'. 1) Darse de alta como socia de la SES YA (SUB-0008). 2) Revisar el tablon en noviembre-diciembre de 2026, que es cuando se subieron las bases de 2026.</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr"/>
@@ -36272,7 +39244,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Doctorado; residencia en Espana en el momento de solicitar para la modalidad de salida; admision del centro extranjero; la estancia debe ser de formacion INTERDISCIPLINAR en neurociencia y areas afines (biologia humana, bioetica, psicologia, filosofia, fisica, historia). Criterios de valoracion conocidos: aportacion a la formacion interdisciplinar 30% y prestigio internacional del centro receptor 20%. Ultima edicion documentada: 2025. Calendario de la edicion 2026/2027 SIN CONFIRMAR: web bloqueada.</t>
+          <t>Dirigida a investigadoras que YA esten en posesion del doctorado y quieran reforzar su formacion interdisciplinar en neurociencia y areas afines (biologia humana, bioetica, psicologia, filosofia, fisica o historia); la estancia es en una institucion internacional publica o privada de maximo prestigio, o en una institucion espanola si la solicitante es nacional de otro Estado miembro de la UE; solicitud en un unico PDF a becas.neurociencia@fundaciontatiana.com</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -36307,27 +39279,27 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>Reintentar cinetcenter.com en la pasada de octubre por otra via; si sigue bloqueado, escribir a CINET pidiendo bases y calendario de la edicion 2027, y buscar el PDF republicado por webs universitarias (medicina.us.es adjunta el suyo).</t>
+          <t>Sigue sin convocatoria 2027 publicada y el reloj del doctorado (ETA febrero de 2028) hace que su primera edicion realista sea la de 2028. Paso concreto: escribir a becas.neurociencia@fundaciontatiana.com pidiendo bases y calendario de la proxima edicion, que es mas barato que seguir peleandose con la web. No reintentar fundaciontatiana.com ni cinetcenter.com por fetch automatico.</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr"/>
@@ -36338,7 +39310,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Dos fuentes Tier 2 independientes que concuerdan: anuncio de la Facultad de Medicina de la Universidad de Sevilla (edicion 2025) y ficha de becas.com. BASES TIER 1 NO LEIDAS: fundaciontatiana.com y cinetcenter.com devuelven contenido vacio al fetch y HTTP 202 con 273 bytes a curl.</t>
+          <t>Rama 3, 2026-09-21. Via de rescate NUEVA que funciona con la web del financiador bloqueada: la convocatoria esta republicada en el job market de la FENS, https://www.fens.org/careers/job-market/job/122150 , leida hoy. Confirma financiador, estructura, requisito de doctorado ya obtenido, la regla de institucion internacional (o espanola para no espanoles de la UE) y el correo de solicitud, pero corresponde a la EDICION 2025 (plazo 1 de junio de 2025) y no trae importe ni duracion. NO se ha tocado fundaciontatiana.com (HTTP 202 con 273 bytes, bloqueo ya conocido). Importe y duracion de la fila siguen procediendo de las dos fuentes Tier 2 anteriores.</t>
         </is>
       </c>
     </row>
@@ -36397,7 +39369,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Ser miembro en regla de la Sleep Research Society, de la AASM o con membresia dual EN EL MOMENTO DE PRESENTAR; estar matriculada en un programa de grado o posgrado, o dentro de la ventana de 10 anos; afiliacion institucional. Ciclo 2026 cerrado el 31-08-2026 a las 23:59 CT; notificacion 30-11-2026; periodo de financiacion enero-diciembre de 2027.</t>
+          <t>Ser socia en regla de la Sleep Research Society o de la American Academy of Sleep Medicine (o membresia dual); estar matriculada en un programa de grado o posgrado O estar dentro de los 10 anos siguientes a la obtencion de un titulo terminal (PhD, MD, DO) y en nivel de Assistant Professor o anterior; mantener afiliacion institucional durante toda la ayuda</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -36432,27 +39404,27 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>Valorar el coste de la cuota de socia de la SRS antes de junio de 2027 (ver SUB-0007) y preparar la solicitud para el cierre previsto hacia el 31-08-2027.</t>
+          <t>El ciclo 2026 cerro el 31-08-2026 a las 23:59 CDT y la SRSF anuncia que los detalles del ciclo 2027 se publicaran a finales de junio de 2027: no hay nada que preparar hasta entonces. Lo unico con reloj es la membresia de la SRS (SUB-0007), que es condicion previa dura; tramitarla antes de junio de 2027.</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr"/>
@@ -36463,7 +39435,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>Tier 1, sleepresearchsociety.org.</t>
+          <t>Tier 1 leida el 2026-09-21: https://sleepresearchsociety.org/foundation/small-research-grant/ . Literal: 'The SRSF Small Research Grant application cycle for 2026 is now closed', plazo 'August 31st, 2026 at 11:59pm CDT', 'More details for the 2027 cycle will be shared in late June of 2027', periodo de financiacion enero-diciembre de 2027 y maximo 5.000 USD. Doble via de elegibilidad confirmada: le vale tanto estar matriculada en el doctorado como el reloj de 10 anos desde un titulo terminal, que en su caso corre desde el MD de 2019 y no vence hasta 2029.</t>
         </is>
       </c>
     </row>
@@ -37279,12 +40251,12 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Dentro de 7 anos desde el 'terminal degree' (Ph.D., M.D.). LA DEFINICION ES AMBIGUA Y CRITICA PARA ELLA</t>
+          <t>Siete anos EN EQUIVALENTE A TIEMPO COMPLETO desde el 'terminal degree', con los parentesis de carrera declarables en la carta de nominacion. CONFLICTO NO RESUELTO Y CRITICO PARA ELLA, ahora mejor acotado: la BGA pone 'M.D.' como ejemplo de titulo terminal, lo que empuja a contar desde su MD de 2019 y daria el reloj agotado en 2026; pero el matiz 'full-time equivalent' mas la clausula de interrupciones juegan a favor, porque de 2019 a hoy su dedicacion ha sido en buena parte clinica (MIR de Medicina de Laboratorio 22-05-2023 a 22-05-2027), no investigadora a tiempo completo, y ese tiempo seria descontable. La otra lectura, contar desde el doctorado previsto de febrero de 2028, la dejaria elegible hasta 2035. La diferencia entre las dos lecturas sigue siendo 'expirado' frente a 'abierto hasta 2035' y NO SE DEBE DECIDIR SIN RESPUESTA DE LA BGA.</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Miembro de la BGA en regla; dentro de 7 anos del titulo terminal; se otorga por nominacion (carta breve y CV a behaviorgeneticsassociation@gmail.com). Para el ciclo 2026 el plazo fue el 01-03-2026 (Tier 2). AMBIGUEDAD GRAVE: la BGA enumera 'Ph.D., M.D.' como titulos terminales; si su MD de 2019 cuenta, su reloj expiro en 2026; si cuenta el PhD de febrero de 2028, tendria hasta 2035.</t>
+          <t>Texto localizado el 2026-09-21 (Tier 2, resumen de buscador sobre paginas de la BGA; bga.org sigue devolviendo 403 al acceso automatico, asi que NO esta verificado leyendo la pagina): ser miembro en regla de la BGA y estar 'within seven years full-time equivalent of receiving their terminal degree (e.g., Ph.D., M.D.)'; 'career disruptions or time out-of-role should be noted in the nomination letter'; nomina cualquier miembro de la BGA y las autonominaciones estan expresamente invitadas (carta breve y CV a behaviorgeneticsassociation@gmail.com). Para el ciclo 2026 el plazo fue el 01-03-2026 (Tier 2, sin confirmar).</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -37319,27 +40291,27 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>Un correo a behaviorgeneticsassociation@gmail.com preguntando si el reloj de 7 anos se cuenta desde el MD o desde el PhD. Es barato y aclara ademas su elegibilidad para F-0028.</t>
+          <t>Escribir a behaviorgeneticsassociation@gmail.com con la pregunta concreta y citando su propio texto: si el plazo de 'seven years full-time equivalent of receiving their terminal degree (e.g., Ph.D., M.D.)' se cuenta, en el caso de una MD que despues hace el doctorado, desde el MD o desde el PhD, y si los anos de residencia clinica se descuentan del computo a tiempo completo. Es un correo de diez minutos y ademas aclara su elegibilidad para F-0028. Si se confirma que cuenta desde el PhD o que la residencia se descuenta, la fila pasa de 2 a 4 y hay que buscar el plazo del ciclo 2027.</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr"/>
@@ -37350,7 +40322,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>Pagina Tier 1 de premios de la BGA (confirma el renombrado y la lista de premios, pero NO publica plazos ni importes). La regla de los 7 anos y el plazo del 01-03-2026 vienen de resumen de busqueda Tier 2 sin confirmar.</t>
+          <t>Tier 2 unicamente: el texto de elegibilidad se obtuvo del resumen de buscador sobre paginas de bga.org, que devuelve 403 a cualquier acceso automatico (bloqueo ya conocido, un solo intento). La pagina que la duena puede abrir a mano es https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567677. No se localizaron las bases en PDF ni en actas de la revista Behavior Genetics.</t>
         </is>
       </c>
     </row>
@@ -37858,8 +40830,393 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>F-0063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Ayudas para estancias de 6 a 12 meses en el extranjero para Psiquiatras (MIR) o Psicologos Clinicos (PIR) (Ayudas de Formacion)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Beca de formacion / estancia larga en el extranjero</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Fundacion Alicia Koplowitz</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Nacionalidad espanola; centro de destino en el extranjero, de libre eleccion del solicitante</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Si: carta de aceptacion original firmada y timbrada del centro receptor mas el programa ofertado por el centro de destino, dentro de la propia solicitud</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>-171</v>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>6 a 12 meses; el disfrute debia iniciarse durante 2026</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No aplica: el reloj es el titulo de especialista MIR/PIR, no el doctorado</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Nacionalidad espanola; titulo de Especialista en Psiquiatria (MIR) o Psicologia Clinica (PIR) con formacion acreditada en el area de infancia y adolescencia; modalidad 1 (superespecializacion) para quienes terminaron MIR/PIR en los ultimos 3 anos, modalidad 2 (centros de excelencia) para profesionales senior; memoria cientifica de 2 paginas; carta de aceptacion del centro receptor; retorno obligatorio a un centro espanol al terminar, no retribuido</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Ineligible de forma permanente: las bases 2026 exigen literalmente el titulo de Especialista en Psiquiatria (MIR) o Psicologia Clinica (PIR) y el suyo sera de Medicina de Laboratorio, de modo que ni la modalidad de superespecializacion ni la de centros de excelencia le estan abiertas por mucho que el tema infanto-juvenil encaje con sus lineas 2 y 3.</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Solo dos ayudas por convocatoria; la fundacion no publica el numero de solicitudes recibidas.</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>Ninguna. No volver a sacarla en pasadas futuras: el requisito de titulo MIR de Psiquiatria o PIR la excluye de forma estructural, no por calendario.</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>https://fundacionaliciakoplowitz.org/wp-content/uploads/2026/01/Bases_Ayudas-Estancias-Cortas_2026.pdf</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>Bases 2026 Tier 1 descargadas con curl desde fundacionaliciakoplowitz.org y extraidas localmente (texto literal: 'CONVOCATORIA DE AYUDAS PARA ESTANCIAS DE 6 A 12 MESES EN EL EXTRANJERO PARA PSIQUIATRAS (MIR) O PSICOLOGOS CLINICOS (PIR)' y 'deberan ser enviadas antes del dia 3 de abril de 2026'). La segunda linea de formacion, Ayudas de Formacion Avanzada convocatoria 2026-2028 (https://fundacionaliciakoplowitz.org/wp-content/uploads/2026/01/Bases-Ayudas-Formacion-Avanzada_2026.pdf), exige el mismo titulo MIR de Psiquiatria o PIR obtenido con posterioridad a 2021, asi que tampoco le sirve. La dotacion economica aparece en blanco en la extraccion del PDF y NO se ha estimado. Solicitudes via https://formacionsaludmental.portaleira.com/projects/Ayudas26estancias</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>F-0064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Beca Nacional de la ESHG 2027 - nominacion de la AEGH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Travel award / national fellowship</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Asociacion Espanola de Genetica Humana (AEGH), por cupo nacional de la European Society of Human Genetics</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Espana (cupo nacional espanol para el congreso de la ESHG en Rotterdam)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-11-15</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>55</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>inscripcion gratuita al congreso con almuerzos incluidos + 600 de viaje</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Congreso del 12 al 15 de junio de 2027</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No aplica; el limite es de 4 anos de experiencia laboral postuniversitaria</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Miembro activa de la AEGH con antiguedad continuada SUPERIOR A DOS ANOS a fecha de la convocatoria; excelencia en genetica humana y/o comunicacion presentada en el ultimo congreso interdisciplinar de Genetica Humana de Granada; NO MAS DE 4 ANOS de experiencia laboral postuniversitaria; no haber recibido la beca en la convocatoria ESHG 2026; membresia valida de la ESHG para 2027 para poder disfrutarla. Documentacion a aegh@geyseco.es: CV abreviado con foto indicando la fecha de graduacion, resumen de la comunicacion de Granada con todos los firmantes y certificado de aceptacion. Resuelve la Junta Directiva y es inapelable.</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Seria el atajo ideal a su congreso natural, pero es INELEGIBLE por triple partida en 2027: no es socia de la AEGH (y hacen falta mas de dos anos de antiguedad), es MD de 2019 y por tanto supera los 4 anos de experiencia postuniversitaria, y no presento comunicacion en el congreso de Granada de 2026.</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Una sola persona nominada por la AEGH para el cupo nacional espanol; candidatas solo espanolas.</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>No solicitar: es inelegible en 2027. Se registra para no volver a descubrirla y para dejar escrito el criterio de los 4 anos de experiencia postuniversitaria, que probablemente la excluya tambien en ediciones futuras aunque llegue a tener la antiguedad de socia. Ver F-0023 para la via directa de la ESHG.</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>https://aegh.org/beca-eshg-2027-para-asistir-a-la-eshg-2027/</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>Rama 4. Tier 1, aegh.org, leida el 2026-09-21. Resuelve la duda que F-0023 arrastraba desde agosto: el cupo nacional SI exige dos anos de antiguedad como socia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>F-0065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SENC-J Ambassador Distinction</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Young investigator distinction</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sociedad Espanola de Neurociencia (SENC), Comite de Jovenes Investigadores y Formacion</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Neurociencia espanola; exige experiencia postdoctoral en institucion internacional</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Sin dotacion economica publicada; distincion honorifica por 3 anos, maximo 7 personas al ano</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>3 anos</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Doctorado obtenido en los ultimos 15 anos</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Distincion de nueva creacion; la primera cohorte (2026) se nombro en junio de 2026 y se reconocio en el FENS Forum 2026 de Barcelona. Solo por NOMINACION de una socia de la SENC o de una representante institucional; no se aceptan autocandidaturas. Exige doctorado obtenido en los ultimos 15 anos y un MINIMO ACUMULADO DE DOS ANOS de experiencia postdoctoral en una o varias instituciones internacionales fuera del pais donde hizo el doctorado. No hace falta ser socia al nominarse, pero si al ser nombrada. Documentacion: carta de justificacion de 1 pagina, CV de 5 paginas, compromiso con la SENC de 300 palabras e iniciativa propuesta de 300 palabras.</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Inelegible durante anos: exige doctorado ya obtenido (el suyo llegaria en febrero de 2028 segun ETA) y ademas dos anos acumulados de postdoc en el extranjero, que no tendria antes de 2030.</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Maximo 7 distinciones al ano para toda la neurociencia espanola, y solo por nominacion ajena.</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>Ninguna hasta 2030 como muy pronto. Se registra para que no se redescubra cada pasada y para que conste que existe un carril de reconocimiento SENC al que podria optar despues de dos anos de postdoc en el extranjero.</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>https://www.senc.es/wp-content/uploads/2026/03/SENC-J_Ambassador_Call_2026.pdf</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>Rama 4. Tier 1: PDF oficial de la convocatoria de la cohorte 2026 descargado con curl y extraido localmente el 2026-09-21. Hallazgo nuevo de esta pasada: el esquema no estaba en la base.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB63"/>
+  <autoFilter ref="A1:AB66"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45305,7 +48662,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -45315,7 +48672,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sin cambios: el calendario AY2028 sigue sin publicarse y la pagina de HFSP anuncia todavia el AY2027. Se mantiene la expectativa de publicacion entre enero y marzo de 2027, con LOI hacia mayo de 2027. MATIZ NUEVO Y RELEVANTE (ver F-0007): el preprint solo satisface el requisito de publicacion en fase LOI; en la propuesta completa de septiembre hace falta aceptacion.</t>
+          <t>Verificado hoy en Tier 1 (hfsp.org, HTTP 200 por curl): la pagina sigue siendo la del ciclo 2027 y avisa de que el plazo de LOI del ciclo 2027 ya paso; el calendario AY2028 NO esta publicado. DATO NUEVO VERIFIED que cierra la duda de elegibilidad del ciclo en curso: 'Fellows must begin their fellowship between 1 April 2027 and 1 January 2028' y el doctorado debe estar completado 'before 31 December 2027 at the latest'. Con defensa prevista en febrero de 2028 ella NO es elegible en el ciclo 2027 (ver F-0007). Por extrapolacion del patron (portal abierto 12-03-2026, LOI antes del 05-05-2026, propuesta completa el 24-09-2026), el ciclo AY2028 deberia publicarse entre enero y marzo de 2027 con LOI hacia mayo de 2027 y exigir el doctorado antes del 31-12-2028: ESA seria su primera edicion viable. Es extrapolacion, no dato publicado.</t>
         </is>
       </c>
     </row>
@@ -45367,7 +48724,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -45377,7 +48734,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HALLAZGO DE LA PASADA. Requisito verificado textualmente en el PDF oficial de la AES 2026 (art. 34.2), extraido localmente: la FSE debe finalizar 'con anterioridad a la fecha que se establezca para la finalizacion del plazo de alegaciones a la resolucion provisional de concesion'. La convocatoria no fija esa fecha por adelantado. Precedentes Tier 1 de la sede del ISCIII: Rio Hortega AES 2025, alegaciones 'del 3 al 16 de octubre de 2025' (pub=51490, publicada el 02-10-2025); convocatoria 2022, 'del 19 al 30 de septiembre de 2022'; Sara Borrell y Miguel Servet AES 2025, 'del 11 al 24 de julio de 2025'. Rio Hortega va sistematicamente 2-3 meses mas tarde. Para la AES 2027 cabe esperar el cierre de alegaciones entre finales de septiembre y mediados de octubre de 2027, y el 22-05-2027 cae holgadamente dentro. CONSECUENCIA: LA AES 2027 ES SU PRIMERA EDICION POSIBLE Y SE PREPARA YA, no en 2028. Cabo suelto: no se localizo la resolucion provisional de Rio Hortega AES 2026; puede que aun no este publicada, lo que encajaria con el patron de octubre.</t>
+          <t>HALLAZGO DE LA PASADA ANTERIOR INTACTO (requisito VERIFIED en el PDF de la AES 2026, art. 34.2: la FSE debe finalizar antes del fin del plazo de alegaciones a la resolucion provisional; precedentes de alegaciones: Rio Hortega AES 2025 del 3 al 16 de octubre de 2025, convocatoria 2022 del 19 al 30 de septiembre de 2022; Sara Borrell y Miguel Servet AES 2025 del 11 al 24 de julio de 2025). Conclusion que se mantiene: LA AES 2027 ES SU PRIMERA EDICION POSIBLE Y SE PREPARA YA. Comprobado el 21-09-2026: la AES 2027 sigue SIN publicarse y no hay ninguna senal de adelanto. isciii.es sigue dando 503 al HTML, asi que la verificacion de hoy es indirecta. Anclas de calendario que sostienen la estimacion: la AES 2026 fue autorizada por el Consejo de Ministros el 16-12-2025, y el extracto de la AES 2025 en el BOE (BOE-B-2024-45526) procede de la Resolucion de 10-12-2024. Es decir, autorizacion y publicacion en la segunda quincena de diciembre de 2026 y plazo de Rio Hortega en febrero de 2027 (12-02/05-03 en 2025, 10-02/05-03 en 2026) siguen siendo la mejor estimacion. Cabo suelto de la pasada anterior, sin resolver: no se localiza la resolucion provisional de Rio Hortega AES 2026.</t>
         </is>
       </c>
     </row>
@@ -45429,7 +48786,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -45439,7 +48796,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sin cambios en la estimacion de reapertura: la AES 2027 no esta publicada y nada indica desviacion de la ventana ~10 de febrero a 5 de marzo de 2027. Ancla Tier 1 nueva del calendario interno: resolucion provisional de la AES 2025 publicada el 10-07-2025 con alegaciones 'del 11 al 24 de julio de 2025, ambos inclusive' (sede del ISCIII, pub=51471). Confirmado que su primera edicion realista sigue siendo la AES 2029, porque exige doctorado y defiende en febrero de 2028.</t>
+          <t>Sin cambios el 21-09-2026: la AES 2027 no esta publicada. Estimacion sostenida por las mismas anclas de calendario que W-0002 (AES 2026 autorizada en Consejo de Ministros el 16-12-2025; extracto de la AES 2025 en BOE-B-2024-45526, Resolucion de 10-12-2024) y por el ancla interna de la pasada anterior (resolucion provisional AES 2025 publicada el 10-07-2025, alegaciones del 11 al 24 de julio de 2025). Se mantiene que su primera edicion realista es la AES 2029, porque Sara Borrell exige doctorado y ella defiende en febrero de 2028. Verificacion indirecta: isciii.es sigue con el HTML en 503.</t>
         </is>
       </c>
     </row>
@@ -45491,7 +48848,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -45501,7 +48858,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sin cambios. Mismo ancla Tier 1: resolucion provisional de la AES 2025 del 10-07-2025, alegaciones 'del 11 al 24 de julio de 2025, ambos inclusive' (sede del ISCIII, pub=51470). Sigue fuera de su alcance por trayectoria: Miguel Servet exige varios anos posdoctorales.</t>
+          <t>Sin cambios el 21-09-2026: la AES 2027 no esta publicada y la ventana estimada de 11 de febrero a 4 de marzo de 2027 se mantiene, con las mismas anclas de calendario que W-0002 y W-0003. Sigue fuera de su alcance por trayectoria: Miguel Servet exige varios anos posdoctorales. Verificacion indirecta: isciii.es sigue con el HTML en 503.</t>
         </is>
       </c>
     </row>
@@ -45595,7 +48952,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Apertura hacia junio de 2027 y cierre hacia finales de julio de 2027. CORRECCION DE ETIQUETADO: lo que la NHMRC llama 'ronda 2027' cerro el 29-07-2026 y financia contratos que empiezan en 2028; la ronda siguiente cierra hacia julio de 2027.</t>
+          <t>Apertura hacia junio de 2027 y cierre hacia finales de julio de 2027. CORRECCION DE ETIQUETADO CONFIRMADA: lo que la NHMRC llama 'ronda 2027' abrio el 03-06-2026, cerro el 29-07-2026 a las 17:00 AEST y financia contratos que EMPIEZAN en 2028; la ronda siguiente abre hacia junio de 2027 y cierra hacia finales de julio de 2027.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -45615,7 +48972,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -45625,7 +48982,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>La modalidad Emerging Leadership exige el doctorado ya concedido, asi que con defensa en feb-2028 su primera ronda utilizable es la que cierre hacia julio de 2028. Tiene via de contacto por la estancia en QIMR Berghofer.</t>
+          <t>Corroborada el 21-09-2026 la correccion de etiquetado, con el calendario completo de la ronda que acaba de cerrar: apertura 03-06-2026, datos minimos 01-07-2026 17:00 AEST, cierre 29-07-2026 17:00 AEST, declaraciones de conflicto a finales de agosto de 2026, revision de agosto a noviembre de 2026 y resultados bajo embargo en marzo de 2027. AVISO DE ACCESO: nhmrc.gov.au devuelve 403 tanto a curl como a WebFetch (bloqueo nuevo, no estaba en la lista de bloqueos del briefing), asi que este calendario procede de resultados de buscador restringidos al dominio y NO de una pagina Tier 1 abierta: la confianza se queda en LIKELY. La modalidad Emerging Leadership exige el doctorado ya concedido, asi que con defensa en feb-2028 su primera ronda utilizable sigue siendo la que cierre hacia julio de 2028. Tiene via de contacto por la estancia en QIMR Berghofer.</t>
         </is>
       </c>
     </row>
@@ -45677,7 +49034,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -45687,7 +49044,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>AVISO DE REPROGRAMACION PROBABLE: fuentes Tier 2 indican que los postdocs de primer ano son inelegibles y que se exige 'M.D. with minimum PGY-IV training' o doctorado mas un puesto de investigacion en marcha. Con defensa en febrero de 2028, su primer ano postdoctoral va de febrero de 2028 a febrero de 2029, asi que la primera convocatoria realista seria la de 2029 y no la de 2027. Verificar en las guidelines en PDF antes de seguir vigilando esta fila tres anos en balde.</t>
+          <t>Leida hoy la pagina Tier 1 de la BBRF (HTTP 200 por curl): sigue mostrando UNICAMENTE el ciclo 2026 ('The call for 2026 BBRF Young Investigator Grant Applications is now closed'; 'begins on Wednesday, February 4, 2026 and ends on Wednesday, March 4, 2026 at 11:59 PM ET'). NINGUNA fecha de 2027 publicada: se mantiene la ventana estimada de febrero a marzo de 2027 y se mantiene retirado el 05-03-2027 inventado por la siembra. AVISO DE REPROGRAMACION, sin cambios y aun sin verificar en el PDF de bases: fuentes Tier 2 indican que los postdocs de primer ano son inelegibles y que se exige 'M.D. with minimum PGY-IV training' o doctorado mas un puesto de investigacion en marcha; con defensa en febrero de 2028 su primera convocatoria realista seria la de 2029. Pendiente concreto para otra pasada: descargar 'Download 2026 YI Grant Guidelines' desde esa misma pagina y leer la clausula de elegibilidad.</t>
         </is>
       </c>
     </row>
@@ -45719,12 +49076,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>La convocatoria Incoming 2027 ESTA ABIERTA y cierra el 23-09-2026 a las 14:00 CEST (preseleccion 12-01-2027, entrevistas 24-25 de febrero de 2027, resultados 10-03-2027, incorporacion entre el 01-05-2027 y el 31-12-2027). La de 2028 deberia abrirse hacia junio de 2027 y cerrar hacia septiembre de 2027.</t>
+          <t>La edicion Incoming en curso cierra PASADO MANANA, el 23-09-2026 a las 14:00 (hora peninsular espanola); abrio el 14-07-2026. La edicion siguiente (convocatoria 2028) deberia abrir hacia mediados de julio de 2027 y cerrar hacia finales de septiembre de 2027: es extrapolacion del patron 14-07 / 23-09, no una fecha publicada.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>HIGH para el cierre del 23-09-2026; MEDIUM para la ventana de la edicion 2028, que es extrapolacion</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -45739,7 +49096,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -45749,7 +49106,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Reabierta, pero ella NO es elegible: exige doctorado obtenido entre 2 y 7 anos antes del cierre. Con defensa en feb-2028, su primera edicion posible es la convocatoria de 2029 (cierre previsible hacia septiembre de 2028). Hasta 320.100 EUR por un maximo de 3 anos.</t>
+          <t>DICTAMEN EN FIRME, PARA NO VOLVER A GENERAR FALSA URGENCIA CADA SEPTIEMBRE: ELLA NO PUEDE PRESENTARSE A ESTA EDICION NI A NINGUNA HASTA 2030. La regla es que el doctorado se haya obtenido ENTRE 2 Y 7 ANOS ANTES DE LA FECHA DE CIERRE. Con defensa prevista en febrero de 2028 (ETA), cumple los 2 anos en febrero de 2030, de modo que la primera convocatoria cuyo cierre (finales de septiembre) cae despues de esa fecha es la que cierre en septiembre de 2030, es decir la que la Caixa etiquetaria como convocatoria 2031; el limite superior de 7 anos la deja elegible hasta los cierres de 2034. CORRIGE LA NOTA ANTERIOR, QUE ESTABA MAL: decia 'su primera edicion posible es la convocatoria de 2029 (cierre hacia septiembre de 2028)', y septiembre de 2028 son solo siete meses despues de la defensa, no dos anos. Datos de la edicion en curso: 20 ayudas, hasta 320.100 EUR por un maximo de 3 anos, centros espanoles con sello Severo Ochoa / Maria de Maeztu / ISCIII o centros portugueses con sello FCT, disciplinas STEM, calendario preseleccion 12-01-2027, entrevistas 24-25 de febrero de 2027, resultados 10-03-2027 e incorporacion entre el 01-05-2027 y el 31-12-2027. BLOQUEO NUEVO: hoy lacaixafoundation.org devuelve 403 a curl Y a WebFetch, y fundacionlacaixa.org tambien devuelve 403 al PDF de bases ('junior-leader-incoming-programme-rules-2026-pdf'), asi que el cierre y la regla de 2-7 anos estan confirmados por Tier 2 concordante y no por lectura directa de Tier 1.</t>
         </is>
       </c>
     </row>
@@ -45801,7 +49158,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -45811,7 +49168,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Sin cambios: sede y fechas del WCPG 2027 SIGUEN SIN ANUNCIAR, verificado en dos paginas Tier 1 de ispg.net; la unica futura listada es el WCPG 2026 (Glasgow, 29 de septiembre a 3 de octubre de 2026) y no hay rastro de ECIP 2027. VENTANA DE VIGILANCIA CONCRETA: la sede del congreso siguiente suele anunciarse durante el congreso anterior, asi que la semana del 29 de septiembre de 2026 es el momento natural para que aparezca. El ECIP queda fichado ademas como fila propia en fellowships (Fit 5, la solicitud mas barata de la base).</t>
+          <t>Sin cambios el 21-09-2026: ispg.net/ecip-program/ responde 200 pero solo sirve la navegacion, sigue rotulada 'Early Career Investigator Program (ECIP) 2026' y no hay rastro del ECIP 2027 ni de sede o fechas del WCPG 2027. La unica reunion futura listada sigue siendo el WCPG 2026 (Glasgow, 29 de septiembre a 3 de octubre de 2026). VENTANA DE VIGILANCIA INMINENTE Y CONCRETA: la sede del congreso siguiente suele anunciarse durante el congreso anterior, asi que la pasada del 5 de octubre de 2026 es la que debe mirar esto con prioridad. Recordatorio del briefing: ispg.net/abstract-submissions/ sirve contenido de 2022, no usarla como fuente de fechas.</t>
         </is>
       </c>
     </row>
@@ -45863,7 +49220,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -45873,7 +49230,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cita literal de la Sleep Research Society: 'The application period for SLEEP 2026 is closed. More information regarding the next cycle of the Trainee Awards can be expected in January of 2027.' Fuente Tier 1 nueva que sortea el bloqueo de sleepmeeting.org: https://sleepresearchsociety.org/awards/conference-awards/. Dato adicional util: el Leadership Development Workshop Award se convoca en anos IMPARES, es decir existe en SLEEP 2027 y no existio en 2026; el Grant Writing Workshop Award es de anos pares. AASM confirma la logistica de SLEEP 2027 (Denver, cursos 5-6 de junio, sesion general 6-9 de junio, registro en enero de 2027). SIGUE SIN CONFIRMAR la fecha de apertura del envio de resumenes: la hipotesis de principios de diciembre de 2026 es UNVERIFIED y sleepmeeting.org es el unico sitio que la publicaria.</t>
+          <t>Releida hoy la pagina Tier 1 y la cita sigue literal e inalterada: 'The application period for SLEEP 2026 is closed. More information regarding the next cycle of the Trainee Awards can be expected in January of 2027.' Se confirma tambien que el Leadership Development Workshop Award es de anos IMPARES, luego existe en SLEEP 2027. REQUISITOS VERIFICADOS HOY, utiles para planificar: hay que ser miembro en vigor de la SRS en categoria Postdoctoral Fellow, Predoctoral Student o Undergraduate Student; hay que asistir a las Trainee Symposia Series del domingo; y el Trainee Merit Award exige haber enviado un resumen al congreso, sin que valgan los late-breaking. SIGUE SIN CONFIRMAR la fecha de apertura del envio de resumenes de SLEEP 2027 (hipotesis: principios de diciembre de 2026, UNVERIFIED); sleepmeeting.org es el unico sitio que la publicaria y es una SPA vacia. Congreso confirmado en Denver, 5-6 a 9 de junio de 2027.</t>
         </is>
       </c>
     </row>
@@ -45925,7 +49282,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -45935,7 +49292,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Verificada la edicion 2026: 1.250 EUR, premio unico, articulo publicado en 2023-2025, y abierta a PREDOCTORALES matriculadas, de modo que ella ya es elegible sin haber defendido. Ver F-0030.</t>
+          <t>Comprobado el 21-09-2026 en el indice de noticias del Instituto (ineurociencias.ugr.es/instituto/noticias, HTTP 200): las unicas entradas del premio siguen siendo la CONVOCATORIA 2026 y su RESOLUCION DEFINITIVA; no hay convocatoria 2027 ni anuncio de fechas, que es exactamente lo esperado a estas alturas del ano. Se mantiene la estimacion de mayo-junio de 2027 con ventana de solo 30 dias naturales (la edicion 2026 cerro el viernes 05-06-2026), y por eso esta fila hay que mirarla SIN FALTA en todas las pasadas de abril a junio de 2027: es la que mas facil se escapa. Elegibilidad ya verificada y favorable: 1.250 EUR, premio unico, articulo publicado en 2023-2025 y abierta a PREDOCTORALES matriculadas, o sea que puede optar sin haber defendido. Ver F-0030.</t>
         </is>
       </c>
     </row>
@@ -45987,7 +49344,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -45997,7 +49354,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CORRECCION IMPORTANTE: LA URGENCIA DE LA PASADA ANTERIOR ERA FALSA. Las bases en PDF, descargadas con curl y extraidas localmente, dicen literalmente 'El plazo de solicitud: Desde la apertura de la convocatoria hasta al 25 de enero de 2026'. La edicion 2026 esta CERRADA desde enero, pese a que el tablon de la SES la sigue rotulando 'CONVOCATORIA ABIERTA' a 31-08-2026. NO habia ningun reloj corriendo. El rotulo del tablon de la SES queda marcado como NO FIABLE para todas las pasadas futuras: el estado se saca del PDF, nunca de la etiqueta. RESUELTA TAMBIEN LA REGLA DE ANTIGUEDAD, que pasa de UNVERIFIED a VERIFIED: 'Ser miembro de la SES desde al menos un ano antes a la convocatoria de la beca'. La convocatoria pasa a tener fila propia en fellowships con Fit 4.</t>
+          <t>Comprobado el 21-09-2026: el tablon de la SES SIGUE rotulando la edicion 2026 de las Becas de Investigacion como 'CONVOCATORIA ABIERTA' ocho meses despues de su cierre real del 25-01-2026, junto con la Ayuda para la Investigacion y el Intercambio de Conocimiento y el Premio Joaquin Teran y Mari Luz Alonso. QUEDA CONFIRMADO POR SEGUNDA PASADA CONSECUTIVA QUE EL ROTULO DEL TABLON NO SIRVE: el estado se saca del PDF de bases, nunca de la etiqueta. El desplegable de anos de la pagina solo llega hasta 2026, es decir NO hay todavia bloque 2027. Sigue en pie la regla de antiguedad verificada: ser miembro de la SES desde al menos un ano antes de la convocatoria, lo que obliga a darse de alta ya si quiere optar en 2027 o 2028 (ver SUB-0008).</t>
         </is>
       </c>
     </row>
@@ -46059,7 +49416,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Sin cambios y sigue sin verificar. Via indirecta intentada sin reintentar esrs.eu (403 conocido): los snippets de buscador de la pagina oficial siguen mostrando el ciclo cerrado con plazo del 31 de enero de 2026, lo que es coherente con un plazo hacia el 31 de enero de 2027, pero es cache de Tier 1 leida de segunda mano, no una pagina abierta. Se mantiene LOW-MEDIUM y el dato queda UNVERIFIED por tercera pasada consecutiva.</t>
+          <t>Sin verificar por CUARTA pasada consecutiva y se toma una decision para dejar de gastar presupuesto: esrs.eu devuelve 403 de forma estable y no se ha reintentado hoy. DECISION: esta fila se declara NO VERIFICABLE POR VIA AUTOMATICA. A partir de ahora no se gastan llamadas en esrs.eu; la fecha se dara por buena solo si aparece en una fuente distinta (boletin de la ESRS, programa del congreso, o la propia duena abriendo la pagina en un navegador). La mejor estimacion disponible sigue siendo un plazo hacia el 31 de enero de 2027 por analogia con el ciclo cerrado el 31-01-2026, leido en cache de buscador y por tanto UNVERIFIED. Fit 2: aunque se verificase, no cambia gran cosa. NOTA: no se toca Last_Checked porque hoy NO se ha comprobado nada.</t>
         </is>
       </c>
     </row>
@@ -46169,7 +49526,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -46179,7 +49536,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>La afirmacion de que 2027 es la ultima del marco procede de Tier 2 (Horizon Europe NCP Portal, enlargement-infohub) y NO aparece en la pagina oficial de la MSCA: es coherente con que Horizonte Europa cubra 2021-2027, pero es una inferencia. Confirmarla en el programa de trabajo antes de que nadie tome decisiones sobre la fecha de defensa.</t>
+          <t>VERIFICADO HOY EN TIER 1 (pagina oficial de la MSCA, HTTP 200 por curl) y sin cambios respecto de la pasada anterior: 'Indicative timeline: 7 April 2027 launch of the call for proposals (TBC); 8 September 2027 deadline for submitting proposals (TBC); February 2028 notification of call results (TBC); April 2028 grant agreement signature (TBC); May 2028 first EU-funded projects start (TBC)'. Presupuesto indicativo 388,57 M EUR (TBC). Todo sigue marcado TBC, por eso la confianza se queda en LIKELY y no sube a VERIFIED para las fechas. SIGUE SIENDO INFERENCIA, no dato oficial, que 2027 sea la ultima convocatoria del marco: procede de Tier 2 (Horizon Europe NCP Portal, enlargement-infohub) y es coherente con que Horizonte Europa cubra 2021-2027, pero no aparece en la pagina oficial. Relevancia para ella: con defensa en febrero de 2028, un cierre en septiembre de 2027 le exigiria presentarse ANTES de doctorarse, cosa que la MSCA PF no permite, luego esta convocatoria le queda fuera salvo que la defensa se adelante; el riesgo real es que no haya PF equivalente en 2028 bajo FP10.</t>
         </is>
       </c>
     </row>
@@ -46227,7 +49584,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -46237,7 +49594,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Regla VERIFIED en el PDF de guidelines extraido localmente; la fecha concreta es aritmetica determinista sobre la regla. El desbloqueo real no es esta fecha sino la publicacion: ver F-0008 y la via Review Commons / Peer Community In.</t>
+          <t>Leida hoy la pagina Tier 1 de EMBO (HTTP 200 por curl): 'Applications accepted throughout the year (next cutoff date - hard deadline: Friday 22 January 2027, 14:00 CET)'. Eso confirma la regla del 4o viernes de enero, de modo que el 09-07-2027 (2o viernes de julio) sigue siendo una derivacion aritmetica correcta, pero NO una fecha publicada: EMBO solo publica el corte inmediato. CAMBIO DE REGLA NUEVO Y MUY RELEVANTE, citado literalmente: 'Effective from the Autumn 2027 selection round (i.e., for all applications submitted after January 22, 2027, 14:00 CET), re-applications will no longer be permitted. Researchers may submit only one EMBO Fellowship Proposal.' Es decir, a partir del corte de julio de 2027 solo tendra UN intento en toda su carrera, asi que la solicitud no se puede usar como ensayo. Guidelines vigentes: junio de 2026. El desbloqueo real sigue sin ser la fecha sino la publicacion (ver F-0008).</t>
         </is>
       </c>
     </row>
@@ -46285,7 +49642,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -46295,7 +49652,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>AVISO PERMANENTE: el tablon de la SES NO retira el rotulo 'CONVOCATORIA ABIERTA' al vencer el plazo. El estado hay que sacarlo siempre del PDF de bases, nunca de la etiqueta. Fue esa etiqueta la que genero la falsa urgencia de la pasada anterior.</t>
+          <t>Comprobado el 21-09-2026: en ses.org.es/becas-y-premios/ el desplegable de anos llega solo hasta 2026, no hay bloque 2027 y no hay bases nuevas, lo que es coherente con una apertura en noviembre-diciembre de 2026 y cierre hacia el 25-01-2027 (las bases de 2026 se subieron en noviembre de 2025). Estimacion sin cambios y confianza HIGH. AVISO PERMANENTE REFORZADO HOY: el tablon de la SES no retira el rotulo 'CONVOCATORIA ABIERTA' al vencer el plazo y hoy sigue mostrando como abiertas las tres convocatorias de 2026 ya vencidas; el estado se saca siempre del PDF de bases. ACCION CON RELOJ: la regla de antiguedad exige ser socia desde al menos un ano antes de la convocatoria, asi que para la edicion de enero de 2028 tendria que darse de alta antes de enero de 2027.</t>
         </is>
       </c>
     </row>
@@ -46323,7 +49680,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Premio joven y bolsas de viaje: convocatoria a mediados de enero de 2027, cierre hacia el 2027-02-15. Beca de estancia profesional: convocatoria hacia febrero de 2027, cierre hacia el 2027-03-31.</t>
+          <t>YA HAY UNA REAPERTURA: la Beca Nacional de la AEGH para asistir a la ESHG 2027 se publico el 18-09-2026 y cierra el 15-11-2026 a las 23:59. El resto del paquete anual sigue estimado: premio joven y bolsas de viaje, convocatoria a mediados de enero de 2027 y cierre hacia el 2027-02-15; beca de estancia profesional, convocatoria hacia febrero de 2027 y cierre hacia el 2027-03-31.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -46343,7 +49700,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -46353,7 +49710,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>La AEGH no publica bases completas en PDF: solo las envia por secretaria@aegh.org. Verificar tambien si la nominacion espanola a la national fellowship de la ESHG (ver F-0023) exige la misma antiguedad.</t>
+          <t>NOVEDAD REAL DE ESTA PASADA, verificada en Tier 1 el 21-09-2026 (aegh.org/beca-eshg-2027-para-asistir-a-la-eshg-2027/, publicada el 18-09-2026): la AEGH puede nominar a una persona para la 'Beca Nacional' del ESHG 2027 (Rotterdam, 12-15 de junio de 2027). Requisitos textuales: ser miembro activo de la AEGH con antiguedad continuada superior a dos anos a fecha de la convocatoria; haber demostrado excelencia en genetica humana y/o haber presentado comunicacion o poster en el ultimo Congreso Interdisciplinar de Genetica Humana celebrado en Granada; no tener mas de 4 anos de experiencia laboral postuniversitaria; no haber recibido la beca en la convocatoria ESHG 2026; y tener membresia valida de la ESHG para 2027. Beneficios: inscripcion gratuita al congreso con almuerzos y 600 EUR de viaje. Documentacion a aegh@geyseco.es: CV abreviado con foto indicando fecha de graduacion, resumen de la comunicacion de Granada con todos los firmantes y certificacion de su aceptacion. Resolucion por la Junta Directiva, inapelable. LECTURA PARA ELLA: casi con seguridad NO llega a esta edicion, porque el filtro duro es la antiguedad de socia de mas de dos anos a fecha de convocatoria y no consta que sea socia de la AEGH (ver SUB-0010, aun TODO); ademas hace falta comunicacion en el congreso de Granada. El criterio de 'no mas de 4 anos de experiencia laboral postuniversitaria' es ambiguo en su caso (MD en 2019, pero residencia desde el 22-05-2023, o sea unos 3,5 anos en noviembre de 2026) y conviene preguntarlo por secretaria. CONSECUENCIA ACCIONABLE: darse de alta en la AEGH AHORA es lo que abre esta beca y el resto del paquete AEGH para las ediciones de 2028 y 2029. El resto de convocatorias anuales de la AEGH (premio joven, bolsas de viaje, estancia profesional) siguen sin publicarse para 2027, y la AEGH sigue sin publicar bases completas en PDF: solo las envia por secretaria@aegh.org.</t>
         </is>
       </c>
     </row>
@@ -46401,7 +49758,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -46411,7 +49768,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Pendiente: abrir el PDF 'Requisitos para solicitudes de ayudas y becas SENC' para saber si la regla de 2 anos consecutivos se aplica tambien a los premios o solo a las ayudas de viaje. De eso depende que su mejor premio de predoctoral sea accesible en 2027. Fechas y sede del congreso bienal SENC 2027 sin confirmar.</t>
+          <t>Comprobado el 21-09-2026 en senc.es/ayudas-de-la-senc/ (HTTP 200): la pagina solo lista todavia el ciclo 2026 (convocatoria y resolucion de Becas SENC para SfN 2026, convocatoria y resolucion de ayudas de viaje para FENS y ENCODS 2026) y las de SENC 2025; NO hay calendario 2027. Coherente con la estimacion de publicacion hacia finales de diciembre de 2026 (el calendario de 2026 salio el 23-12-2025), con FENS/ENCODS cerrando el 31 de enero y SfN abriendo el 10 de abril. Se mantiene MEDIUM. PENDIENTE QUE SIGUE SIN RESOLVERSE y que conviene atacar en la pasada de finales de diciembre: abrir el PDF 'Requisitos para solicitudes de ayudas y becas SENC' y averiguar si la regla de dos anos consecutivos de socia se aplica tambien a los premios (Rita Levi-Montalcini, Tatiana Foundation Young Investigator) o solo a las ayudas de viaje; de eso depende que su mejor premio de predoctoral sea accesible en 2027. Fechas y sede del congreso bienal SENC 2027 siguen sin confirmar.</t>
         </is>
       </c>
     </row>
@@ -46459,7 +49816,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -46469,7 +49826,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Antes de la edicion de 2027 hay que abrir la Orden de bases de 24-10-2023 en BOJA y extraer la ventana de anos post-doctorado, que es el dato que aun falta. Las fichas de sede de juntadeandalucia.es devuelven cuerpo vacio (render por JavaScript): usar BOJA, que es HTML plano.</t>
+          <t>Comprobado el 21-09-2026 sin resultado util y con un bloqueo NUEVO que conviene registrar: el buscador del BOJA (juntadeandalucia.es/boja/buscador/) responde 200 pero devuelve solo el armazon de la pagina cuando se le pasa la consulta por GET, es decir la busqueda se ejecuta por POST o por JavaScript y NO es utilizable desde linea de comandos; y juntadeandalucia.es/boja/2026/ es solo un indice de boletines por fecha, sin busqueda por texto. Es decir, el BOJA es HTML plano para leer un boletin concreto, pero NO para buscar. VIA RECOMENDADA PARA LA PASADA DE DICIEMBRE: ir al indice de boletines por fecha del BOJA en los dias habiles alrededor del 17-22 de diciembre de 2026, o buscar el extracto en la BDNS. Nada ha cambiado en la estimacion: apertura hacia el 2026-12-20 y cierre hacia el 2027-01-28 (Res. 17-12-2025 para la edicion 2026, extracto en BOJA num. 246 de 23-12-2025; Res. 21-02-2024 para la de 2024). Sigue pendiente extraer de la Orden de bases de 24-10-2023 la ventana de anos post-doctorado, que es el dato que falta para puntuar bien F-0052.</t>
         </is>
       </c>
     </row>
@@ -46517,7 +49874,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -46527,7 +49884,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Las URL de los PDF de bases son predecibles: /wp-content/uploads/AAAA/MM/Bases_... Pendiente para otra pasada: las 'Ayudas de Formacion' de la misma fundacion, cuya pagina no enlaza bases pero que segun Tier 2 incluyen estancias de 6-12 meses en el extranjero, duracion a la que ya no son ayudas de viaje sino becas de verdad.</t>
+          <t>Comprobado el 21-09-2026 en Tier 1 (fundacionaliciakoplowitz.org, HTTP 200 por curl): la pagina de Ayudas a Proyectos de Investigacion sigue ofreciendo unicamente 'AYUDAS A PROYECTOS DE INVESTIGACION 2026 - Bases - Formulario de solicitud'; NO hay bases de 2027. Es exactamente lo esperado y la estimacion se mantiene sin tocar: bases hacia enero de 2027 y cierre hacia el 2027-04-30, con confianza HIGH (las de 2026 se publicaron en enero con cierre el 30 de abril). Las URL de los PDF de bases siguen siendo predecibles: /wp-content/uploads/AAAA/MM/Bases_... Pendiente para otra pasada, sin avance hoy: las 'Ayudas de Formacion' de la misma fundacion, que segun Tier 2 incluyen estancias de 6-12 meses en el extranjero.</t>
         </is>
       </c>
     </row>
@@ -46555,12 +49912,12 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Septiembre de 2026, inminente: figura ya en el catalogo 2026 de la Fundacion Seneca y agosto es mes inhabil para presentar solicitudes; en la I convocatoria la apertura fue 'a partir del 3 de septiembre'.</t>
+          <t>Septiembre de 2026 sigue siendo la ventana esperada y queda una semana de mes; a 21-09-2026 NO se ha podido confirmar que la III convocatoria este abierta ni localizar fecha de cierre. Figura listada en el catalogo 'CONVOCATORIAS 2026 - Talento Investigador y su Empleabilidad' de la Fundacion Seneca, pero sin pagina de detalle accesible.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>MEDIUM: listada en el catalogo 2026, pero sin texto, sin fechas y sin confirmacion de apertura; baja desde LIKELY porque septiembre se agota sin senal verificable</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -46575,7 +49932,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -46585,7 +49942,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Revisar en la primera semana de septiembre de 2026, cuando termine el mes inhabil. fseneca.es da 503 a WebFetch pero 200 a curl con User-Agent de navegador.</t>
+          <t>Comprobado el 21-09-2026 con curl, que efectivamente sortea el 503 de WebFetch: fseneca.es/web/convocatorias responde 200 y lista 'III Convocatoria de Becas Fulbright-Fundacion Seneca de investigacion posdoctoral en los Estados Unidos' dentro del bloque CONVOCATORIAS 2026. PERO el enlace se construye por JavaScript y no hay href en el HTML; fseneca.es/web/convocatorias-abiertas responde 200 con el cuerpo VACIO por la misma razon; y la pagina del programa en la Comision Fulbright Espana (fulbright.es/programas-y-becas/convocatorias/programa-con-la-fundacion-seneca-region-de-murcia/2026/1955/) responde 200 pero devuelve 'Whoops, no result found'. Conclusion honesta: catalogada si, abierta no confirmada, sin fecha de cierre. AVISO DE ELEGIBILIDAD, PROBABLEMENTE DECISIVO Y PENDIENTE DE VERIFICAR EN LAS BASES DE LA III: segun el resumen del PDF oficial de la II convocatoria alojado en fulbright.es, el programa se dirige a personal docente y/o investigador con vinculacion funcionarial o contractual con universidades y organismos de investigacion DE LA REGION DE MURCIA, a tiempo completo y en servicio activo, y exige carta de invitacion previa del centro estadounidense, para estancias de 9 a 12 meses. Ella no tiene vinculacion contractual con un organismo murciano (su contrato de residencia es del Hospital Regional Universitario de Malaga; su vinculo con la Universidad de Murcia es como doctoranda) y ademas la beca es posdoctoral. Si las bases de la III mantienen ese requisito, esta convocatoria NO le sirve y habria que bajarla de golpe. Es lectura de Tier 2 sobre un PDF Tier 1 que no se pudo extraer (no hay pdftotext en este entorno), asi que queda como aviso, no como hecho.</t>
         </is>
       </c>
     </row>

--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -22,18 +22,18 @@
     <sheet name="readme" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$66</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$331</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$391</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -771,12 +771,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>E-0002</t>
+          <t>E-0019</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ASHG 2026 Annual Meeting</t>
+          <t>EPA 2027 - 35th European Congress of Psychiatry</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -786,40 +786,36 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Congreso anual</t>
+          <t>Congress</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>-6</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>RELOJ VIVO: la tarifa anticipada sigue abierta hasta manana 15-sep-2026 a las 17:00 ET. Si va, hacerse socia student/trainee de ASHG ANTES de inscribirse: la cuota cae de 775 USD (~713 EUR) a 435 USD (~400 EUR), un ahorro de ~313 EUR que supera de largo la cuota de socia. A partir del 16-sep solo queda late/onsite, y no hay tarifa de un dia ni opcion virtual.</t>
+          <t>HOY 21-sep-2026: enviar el abstract por el sistema online (no se aceptan por correo) y marcar la casilla de travel grant en la misma sumision. Notificacion a mediados de diciembre-2026. OJO si la aceptan: el autor presentador debe confirmar e inscribirse antes del 2027-02-01 o cae del programa.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://ashgmeeting.ashg.org/</t>
+          <t>https://epa-congress.org/abstract-submission/</t>
         </is>
       </c>
     </row>
@@ -831,12 +827,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>E-0005</t>
+          <t>E-0001</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IGES 2026 Annual Meeting &amp; Education Workshop</t>
+          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -846,25 +842,21 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Congreso anual + workshop</t>
+          <t>Congreso anual</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -874,12 +866,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>RELOJ VIVO a 5 dias: la tarifa early de IGES cierra el 19-sep-2026 y desde el 20-sep sube a late. Solo tiene sentido moverla si YA ha decidido ir a ASHG 2026 (misma region, dias consecutivos); el plazo de resumenes cerro el 30-may-2026, asi que iria como oyente. Si no va a ASHG, dejarla pasar y apuntarla como objetivo 2027.</t>
+          <t>Empieza en 8 dias. Si quisiera asistir en remoto o de ultima hora, escribir esta semana a la secretaria de ISPG: no hay ninguna tarifa publicada que podamos citar. Vigilar ispg.net/past-congresses el 5-oct-2026, porque la sede de WCPG 2027 suele anunciarse en la asamblea del propio congreso.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://www.geneticepi.org/2026-annual-meeting</t>
+          <t>https://ispg.net/wcpg-2026/</t>
         </is>
       </c>
     </row>
@@ -891,51 +883,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>E-0001</t>
+          <t>T-0014</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
+          <t>SSGAC/CESR Social-Science Genetics Methods Workshop</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Events</t>
+          <t>Training</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Congreso anual</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>8</v>
-      </c>
+          <t>Taller online (serie)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>XS</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>La inscripcion sigue ABIERTA a 15 dias del congreso y sin fecha de cierre publicada: si va, inscribirse esta misma semana en https://ispg.societyconference.com/v2/ y escribir a info@ispg.net preguntando por la cuota Student/Post-Doc y por si existe opcion virtual, porque ninguna de las dos cosas esta publicada en ningun sitio accesible.</t>
+          <t>Entrar en thessgac.org/events y apuntarse a la sesion del 15-oct-2026; comprobar de paso si la serie continua en 2027.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://ispg.net/wcpg-2026/</t>
+          <t>https://www.thessgac.org/events</t>
         </is>
       </c>
     </row>
@@ -947,35 +932,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T-0007</t>
+          <t>E-0005</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Advanced Mendelian Randomization</t>
+          <t>IGES 2026 Annual Meeting &amp; Education Workshop</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Training</t>
+          <t>Events</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Curso corto avanzado</t>
+          <t>Congreso anual + workshop</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-11-11</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>664</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -985,17 +970,17 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>NO reservable en la practica para 2026: exige haber hecho antes el curso introductorio de MR, que ella hara en marzo-2027. Objetivo real: la edicion de noviembre-2027. Aun asi, confirmar en octubre-2026 si aceptan 'equivalente' con experiencia propia en MR.</t>
+          <t>Nada que hacer para 2026: sin abstract y con viaje a Quebec, no sale. Lo que si merece la pena es hacerse socia estudiante de la IGES: es su sociedad natural, da la lista de correo por la que se anunciara la siguiente fase del GAW 2027 y abarata la inscripcion de IGES 2027.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/advanced-mr/</t>
+          <t>https://www.geneticepi.org/2026-annual-meeting</t>
         </is>
       </c>
     </row>
@@ -1007,12 +992,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T-0002</t>
+          <t>T-0007</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Genetic Epidemiology (short course)</t>
+          <t>Advanced Mendelian Randomization</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1022,20 +1007,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Short course</t>
+          <t>Curso corto avanzado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2027-01-13</t>
+          <t>2026-11-11</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>725</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1045,17 +1030,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ACCION INMINENTE Y CON DOS FECHAS: crear o reactivar la cuenta de reservas desde el mediodia del 2026-09-23 (dentro de 9 dias) y reservar plaza el 2026-10-07 a mediodia hora del RU, cuando abren las reservas de todo el programa 2026/27.</t>
+          <t>EL RELOJ MAS CERCANO DE ESTA PESTANA. Crear la cuenta de reservas desde el 23-sep-2026 y reservar el 7-oct-2026 a las 12:00 RU. No puede estar agotado todavia porque las reservas no han abierto.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/advanced-mr/</t>
         </is>
       </c>
     </row>
@@ -1067,12 +1052,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T-0001</t>
+          <t>T-0002</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
+          <t>Genetic Epidemiology (short course)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1082,33 +1067,40 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Workshop</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>Short course</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2027-01-13</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>114</v>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>1450</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XS</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>La inscripcion 2027 AUN NO ESTA ABIERTA. Revisar colorado.edu/ibg/workshop-2027 a partir de noviembre-2026 (en ediciones previas abrio unos 3 meses antes) y reservar presupuesto propio de ~600 USD de cuota academica.</t>
+          <t>Crear YA la cuenta de reservas (disponible desde el 23-sep-2026) y reservar el 7-oct-2026 a las 12:00 hora del RU, que es cuando abren las reservas del programa 2026/27.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://www.colorado.edu/ibg/workshop-2027</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1112,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T-0003</t>
+          <t>T-0001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mendelian Randomization (short course)</t>
+          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1135,40 +1127,33 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Short course</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2027-03-01</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>161</v>
-      </c>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>550</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>ACCION INMINENTE: cuenta de reservas desde el 2026-09-23 a mediodia y reserva el 2026-10-07 a mediodia. Este va ANTES que T-0007, porque es su prerrequisito.</t>
+          <t>La inscripcion NO ha abierto y no hay tarifa publicada. Revisar colorado.edu/ibg/workshop-2027 cada 3-4 semanas desde noviembre-2026, o escribir a IBGworkshop@colorado.edu pidiendo aviso de apertura. Recordar que este taller de marzo se imparte cada TRES anos: perder 2027 significa esperar a 2030.</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
+          <t>https://www.colorado.edu/ibg/workshop-2027</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1165,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T-0009</t>
+          <t>T-0003</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Molecular Epidemiology</t>
+          <t>Mendelian Randomization (short course)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1195,40 +1180,40 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Curso corto</t>
+          <t>Short course</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2027-03-08</t>
+          <t>2027-03-01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>XS</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Solo si sobran presupuesto y dias: encadenarlo con T-0003 (MR introductorio) la semana anterior, aprovechando un unico permiso.</t>
+          <t>Crear la cuenta de reservas ya y reservar el 7-oct-2026 a las 12:00 RU.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/molecular-epidemiology/</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1225,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T-0008</t>
+          <t>T-0009</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Machine Learning with Omics Data</t>
+          <t>Molecular Epidemiology</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1260,13 +1245,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2027-06-08</t>
+          <t>2027-03-08</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>260</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>3</t>
@@ -1279,12 +1268,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Decidir en primavera-2027 junto con el resto de la oferta de Bristol; la ficha individual del curso aun no esta publicada, asi que la cuota se conocera al abrir reservas el 2026-10-07.</t>
+          <t>Solo si sobran presupuesto y dias: encadenarlo con T-0003 (MR introductorio) la semana anterior, aprovechando un unico permiso.</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/molecular-epidemiology/</t>
         </is>
       </c>
     </row>
@@ -1296,25 +1285,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>L-0001</t>
+          <t>T-0008</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Complex Trait Genetics (CTG) Lab</t>
+          <t>Machine Learning with Omics Data</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Groups</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Curso corto</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2027-06-08</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>260</v>
+      </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1322,10 +1322,14 @@
           <t>S</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Decidir en primavera-2027 junto con el resto de la oferta de Bristol; la ficha individual del curso aun no esta publicada, asi que la cuota se conocera al abrir reservas el 2026-10-07.</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://cncr.nl/ctg/</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
         </is>
       </c>
     </row>
@@ -1337,40 +1341,48 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>L-0002</t>
+          <t>T-0011</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Psychiatric Genetics Group</t>
+          <t>Genetic and Epigenetic Epidemiology (curso especializado del EEPE)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Groups</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Training</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Curso especializado residencial</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1575</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Mandar YA el correo en frio a Sarah Medland o a Lucia Colodro Conde sin esperar a ningun anuncio: esta confirmado que no lo va a haber a corto plazo y la conexion calida de su estancia en QIMR no depende de el.</t>
+          <t>La inscripcion abre en NOVIEMBRE-2026 y no hay fecha de cierre publicada: volver a mirar a primeros de noviembre e inscribirse en cuanto abra. Contacto: eepe@eepe.org.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
+          <t>https://www.eepe.org/registration-2-2/</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>L-0006</t>
+          <t>L-0001</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SGDP Centre / Statistical Genetics Unit</t>
+          <t>Complex Trait Genetics (CTG) Lab</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1410,12 +1422,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Escribir a Cathryn Lewis (Statistical Genetics Unit) planteando co-patrocinio de beca postdoc, dado que la unidad no publica vacantes propias.</t>
+          <t>Suscribir la alerta de empleo del CNCR (cncr.nl/cncr/jobs/) para no depender del barrido semanal.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://www.kcl.ac.uk/research/sgu</t>
+          <t>https://cncr.nl/ctg/jobs/</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1439,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>L-0012</t>
+          <t>L-0002</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Grupo de genetica estadistica psiquiatrica de Wouter Peyrot (proyecto ERC PersonalRiskProfile)</t>
+          <t>Psychiatric Genetics Group</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1455,12 +1467,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Escribir correo en frio a Peyrot antes de fin de 2026 presentando disponibilidad desde mediados de 2027 y pidiendo una videollamada de 20 minutos; en paralelo, localizar su direccion institucional exacta en pure.amsterdamumc.nl y revisar la bolsa de empleo de Amsterdam UMC por si sale la plaza del ERC.</t>
+          <t>Mandar YA el correo en frio a Sarah Medland o a Lucia Colodro Conde sin esperar a ningun anuncio: esta confirmado que no lo va a haber a corto plazo y la conexion calida de su estancia en QIMR no depende de el.</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://www.amsterdamumc.org/en/research/institutes/amsterdam-public-health/news/wouter-peyrot-awarded-erc-starting-grant-for-personalized-genetic-risk-profiles-in-psychiatry-1</t>
+          <t>https://www.qimrb.edu.au/researchers-and-labs/psychiatric-genetics</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1484,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L-0013</t>
+          <t>L-0006</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Grupo de Kelli Lehto, Instituto de Genomica (proyecto ERC AT-TENSION)</t>
+          <t>SGDP Centre / Statistical Genetics Unit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1500,12 +1512,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Correo en frio a Kelli Lehto con CV y las dos fechas de disponibilidad; preguntar si AT-TENSION prevee contratar en 2027 y ofrecer la vertiente de fenotipado clinico. Confirmar antes su direccion institucional en la ficha de personal de ut.ee.</t>
+          <t>Escribir a Cathryn Lewis (Statistical Genetics Unit) planteando co-patrocinio de beca postdoc, dado que la unidad no publica vacantes propias.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://ut.ee/en/news/erc-grant-helps-explore-innovative-approaches-improve-diagnosis-adhd-adults</t>
+          <t>https://www.kcl.ac.uk/research/sgu</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1529,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L-0014</t>
+          <t>L-0012</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Grupo de Psiquiatria Infantil y Genetica del Comportamiento de Christel Middeldorp</t>
+          <t>Grupo de genetica estadistica psiquiatrica de Wouter Peyrot (proyecto ERC PersonalRiskProfile)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1545,12 +1557,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Preparar un correo en frio con una propuesta de una pagina sobre genetica del sueno en primera infancia dentro de sus cohortes; antes, verificar en pure.amsterdamumc.nl su financiacion vigente y sus publicaciones de 2025-2026 sobre sueno.</t>
+          <t>Revisar mensualmente tambien el tablon en neerlandes. Contacto en frio a Peyrot en 2027 apoyandose en el ERC recien concedido: los ERC contratan a lo largo de varios anos, no solo al arrancar.</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://www.amsterdamumc.org/en/research/researchers/christel-middeldorp.htm</t>
+          <t>https://werkenbij.amsterdamumc.org/en/vacancies/all-vacancies</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1574,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>L-0020</t>
+          <t>L-0013</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KI Psychiatric Genomics Institute (KI-PGI)</t>
+          <t>Grupo de Kelli Lehto, Instituto de Genomica (proyecto ERC AT-TENSION)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1585,17 +1597,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Correo en frio a lu.yi@ki.se proponiendo co-solicitar MSCA o postdoc del Swedish Research Council con el KI-PGI como host; no esperar a que salga plaza.</t>
+          <t>Buscar el email nominal de Lehto en ut.ee/en/employee/kelli-lehto y escribirle en frio en 2027 con el angulo del ERC AT-TENSION (TDAH adulto, genomica y ciencia de datos).</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://ki.se/en/meb/research/ki-psychiatric-genomics-institute/about-ki-pgi</t>
+          <t>https://genomics.ut.ee/en/research-group-neuropsychiatric-genomics</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1619,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>L-0021</t>
+          <t>L-0014</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PsychGen Centre for Genetic Epidemiology and Mental Health</t>
+          <t>Grupo de Psiquiatria Infantil y Genetica del Comportamiento de Christel Middeldorp</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1630,17 +1642,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Confirmar la direccion de Havdahl en su ficha de fhi.no y escribirle con una propuesta de una pagina: sueno infantil en MoBa con diseno intrafamiliar. Preguntar por MSCA o postdoc del Research Council of Norway.</t>
+          <t>Preparar un correo en frio con una propuesta de una pagina sobre genetica del sueno en primera infancia dentro de sus cohortes; antes, verificar en pure.amsterdamumc.nl su financiacion vigente y sus publicaciones de 2025-2026 sobre sueno.</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://www.fhi.no/en/me/the-psychgen-centre-for-genetic-epidemiology-and-mental-health/about-the-psychgen-centre/</t>
+          <t>https://www.amsterdamumc.org/en/research/researchers/christel-middeldorp.htm</t>
         </is>
       </c>
     </row>
@@ -1652,24 +1664,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>E-0011</t>
+          <t>L-0020</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BGA 2028 - 58th Annual Meeting of the Behavior Genetics Association</t>
+          <t>KI Psychiatric Genomics Institute (KI-PGI)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Conference</t>
-        </is>
-      </c>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
@@ -1679,17 +1687,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Revisar la pagina de BGA Future Meetings en enero-2028 para fechas exactas y plazo de resumenes; apuntarla ya como objetivo post-tesis.</t>
+          <t>Correo en frio a lu.yi@ki.se proponiendo co-solicitar MSCA o postdoc del Swedish Research Council con el KI-PGI como host; no esperar a que salga plaza.</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567675</t>
+          <t>https://ki.se/en/meb/research/ki-psychiatric-genomics-institute/about-ki-pgi</t>
         </is>
       </c>
     </row>
@@ -1701,24 +1709,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>E-0016</t>
+          <t>L-0021</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EMGM 2027 - 55a European Mathematical Genetics Meeting</t>
+          <t>PsychGen Centre for Genetic Epidemiology and Mental Health</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Congreso anual</t>
-        </is>
-      </c>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
@@ -1728,17 +1732,17 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>La 54a edicion (Davos, 14-15 abr 2026) ya paso y la de 2027 sigue sin anfitrion. Vigilar sites.google.com/site/emgmhome a partir de noviembre-2026; si en enero-2027 sigue TBA, escribir a los organizadores de Davos 2026 (emgm2026.sciencesconf.org) preguntando por sede y fechas de 2027, que es justo lo que la propia web pide hacer.</t>
+          <t>Confirmar la direccion de Havdahl en su ficha de fhi.no y escribirle con una propuesta de una pagina: sueno infantil en MoBa con diseno intrafamiliar. Preguntar por MSCA o postdoc del Research Council of Norway.</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://sites.google.com/site/emgmhome/future-meetings</t>
+          <t>https://www.fhi.no/en/me/the-psychgen-centre-for-genetic-epidemiology-and-mental-health/about-the-psychgen-centre/</t>
         </is>
       </c>
     </row>
@@ -1750,48 +1754,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>T-0011</t>
+          <t>L-0026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Genetic and Epigenetic Epidemiology (curso especializado del EEPE)</t>
+          <t>Yao Lab / proyecto CANARY, Department of Medical Epidemiology and Biostatistics</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Training</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Curso especializado residencial</t>
-        </is>
-      </c>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>1575</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>S</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Revisar eepe.org en enero-2027: la edicion 2027 se anunciara con el curso residencial (mediados de junio a principios de julio) y los especializados la semana siguiente. Compararla entonces con el MR de Bristol de marzo-2027, que cubre parte del mismo terreno mas barato.</t>
+          <t>Escribir a Shuyang Yao en octubre-noviembre 2026 felicitando por CANARY y ofreciendo el brazo de genetica estadistica humana. Buscar antes su email institucional en ki.se y comprobar la pagina de vacantes de KI.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://www.eepe.org/courses-2/</t>
+          <t>https://news.ki.se/five-ki-researchers-receive-erc-starting-grants-in-2026</t>
         </is>
       </c>
     </row>
@@ -1803,44 +1799,40 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>E-0014</t>
+          <t>L-0027</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>XXXV Reunion Anual de la Sociedad Espanola de Sueno (SES 2027)</t>
+          <t>Huang Lab, Analytic and Translational Genetics Unit (ATGU)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Events</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Conference</t>
-        </is>
-      </c>
+          <t>Groups</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>XS</t>
+          <t>M</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Consultar congreso-ses.com/ses2027 en octubre-2026 para fechas exactas de marzo-2027, plazo de comunicaciones y cuota de residente; si cae en marzo, hay que pedir dias en el hospital con antelacion.</t>
+          <t>Abrir la pagina 'Opportunities' de huanglab.ac y, si no hay convocatoria, enviar candidatura espontanea a admin@atgu.mgh.harvard.edu citando un paper cross-ancestry concreto.</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://congreso-ses.com/ses2027/bienvenida</t>
+          <t>https://huanglab.ac/home-page/</t>
         </is>
       </c>
     </row>
@@ -1852,12 +1844,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>E-0015</t>
+          <t>E-0011</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jornada AEGH 2027 (Asociacion Espanola de Genetica Humana)</t>
+          <t>BGA 2028 - 58th Annual Meeting of the Behavior Genetics Association</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1874,27 +1866,174 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Revisar la pagina de BGA Future Meetings en enero-2028 para fechas exactas y plazo de resumenes; apuntarla ya como objetivo post-tesis.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://bga.org/content.aspx?page_id=22&amp;club_id=971921&amp;module_id=567675</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>E-0016</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMGM 2027 - 55a European Mathematical Genetics Meeting</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Congreso anual</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>La 54a edicion (Davos, 14-15 abr 2026) ya paso y la de 2027 sigue sin anfitrion. Vigilar sites.google.com/site/emgmhome a partir de noviembre-2026; si en enero-2027 sigue TBA, escribir a los organizadores de Davos 2026 (emgm2026.sciencesconf.org) preguntando por sede y fechas de 2027, que es justo lo que la propia web pide hacer.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://sites.google.com/site/emgmhome/future-meetings</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>E-0014</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>XXXV Reunion Anual de la Sociedad Espanola de Sueno (SES 2027)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>XS</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Consultar congreso-ses.com/ses2027 en octubre-2026 para fechas exactas de marzo-2027, plazo de comunicaciones y cuota de residente; si cae en marzo, hay que pedir dias en el hospital con antelacion.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://congreso-ses.com/ses2027/bienvenida</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>E-0015</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Jornada AEGH 2027 (Asociacion Espanola de Genetica Humana)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Volver a aegh.org/congresos-y-jornadas-aegh en diciembre-2026 o enero-2027 para ver sede y fechas adjudicadas.</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>https://aegh.org/congresos-y-jornadas-aegh/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L27"/>
+  <autoFilter ref="A1:L30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1905,7 +2044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J169"/>
+  <dimension ref="A1:J188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10696,8 +10835,996 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>SRC-0169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>geneticepi.org - latest news</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Las convocatorias del GAW y de la IGES: llamada de ideas, llamada de participacion y plazos. Es la fuente que cerro el pendiente de E-0017.</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>seccion 'latest news' de la portada</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21. Aqui se anunciara la convocatoria de PARTICIPACION del GAW 2027, que es la que si podria usar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>SRC-0170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>ISPG - past and upcoming congresses</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://ispg.net/past-congresses/</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>El anuncio de sede y fechas del WCPG del ano siguiente; el bloque 'Upcoming Congresses' es el que hay que leer.</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>bloque Upcoming Congresses</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Mensual, y obligatorio el 2026-10-05</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21. A 2026-09-21 solo lista WCPG 2026: el 2027 NO esta anunciado. Suele anunciarse en la asamblea del congreso, del 29-sep al 03-oct-2026, de ahi la revision obligatoria del 5-oct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>SRC-0171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>ASHG - registration rates</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://www.ashg.org/registration-rates/</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>La tabla completa de cuotas del congreso de la ASHG por tramo y categoria de socio, que la pagina general del meeting no da.</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>tabla de tarifas</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Anual (agosto)</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21. El tramo Late/Onsite rige desde el 15-sep-2026 hasta el congreso. Hacerse socia estudiante abarata casi a la mitad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>SRC-0172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>EPA - congress abstract submission</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>https://epa-congress.org/abstract-submission/</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Plazo de abstracts y travel grants del congreso europeo de psiquiatria; los travel grants de early career se piden DENTRO de la sumision.</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>pagina de sumision de abstracts</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Anual (agosto-septiembre)</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21, y ha producido el unico plazo vivo de la pasada (E-0019, cierre el propio 2026-09-21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>SRC-0173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Wellcome Connecting Science - conferences</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://coursesandconferences.wellcomeconnectingscience.org/our-events/conferences/</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Conferencias europeas baratas para estudiantes, con modalidad virtual y bursaries de hasta el 50% de la cuota.</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>listado de conferencias</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21. Patron a explotar: las bursaries exigen abstract y cierran ~3 meses antes. Vigilar 'Genomics of Brain Disorders' 2027-2028, que si es su tema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>SRC-0174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>EEPE - registration</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>https://www.eepe.org/registration-2-2/</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Fechas, modulos y tarifas del programa europeo de epidemiologia, incluido el modulo de Genetic and Epigenetic Epidemiology.</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>pagina de inscripcion</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Mensual hasta noviembre-2026</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>La inscripcion 2027 abre en NOVIEMBRE-2026 sin fecha de cierre publicada. Contacto eepe@eepe.org.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>SRC-0175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SSGAC - events</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>https://www.thessgac.org/events</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Talleres online de metodos de genetica estadistica (PRS, inferencia causal) del consorcio de genetica de ciencias sociales, y su summer school cuando la hay.</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>listado de eventos</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21. Formato online y por sesiones sueltas, el unico que le encaja en plena residencia. La summer school presencial no tiene edicion desde julio-2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>SRC-0176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Erasmus Summer Programme (NIHES) - courses</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>https://erasmussummerprogramme.nl/summer-programme-courses/</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Modulos cortos y de media jornada de epidemiologia genetica y de analisis de GWAS en Rotterdam, en el formato modular que a ella le sirve.</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>catalogo de cursos</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21. El catalogo publicado sigue siendo el de 2026 (3-21 ago 2026) con 'Principles of Genetic Epidemiology' (ESP43) y 'Analysis of Genome-wide Association Studies'. El calendario 2027 no esta publicado: revisar enero-marzo 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>SRC-0177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Wellcome Connecting Science - courses</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>TRAINING</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>https://coursesandconferences.wellcomeconnectingscience.org/our-events/courses/</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Cursos avanzados de genomica con plazo de solicitud y becas.</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>listado de cursos</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Revisado el 2026-09-21: NINGUN curso de 2027 anunciado, solo dos de 2026. Negativo verificado que afecta a T-0004.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>SRC-0178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Cardiff University - portal de empleo eploy</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>https://cardiffuniweb.eploy.net/vacancies/</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Todas las vacantes vivas de Cardiff con referencia, departamento y fecha de cierre. Es la unica puerta que funciona.</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>filtrar por School of Medicine y por Division of Psychological Medicine and Clinical Neurosciences; palabras genetics, genomics, bioinformatics, statistics</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>BLOQUEOS: cardiff.ac.uk/jobs/vacancies da 403 y la pagina de vacantes del propio MRC Centre da 403. Y la variante /vacancies/vacancies.aspx da 404: usar la raiz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>SRC-0179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>MPI for Psycholinguistics Nijmegen - vacantes</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://www.mpi.nl/career-education/vacancies</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Las ofertas del MPI, incluidas las del grupo Population Genetics of Human Communication de Beate St Pourcain.</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>revisar el listado entero, son pocas</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>CORRECCION DE URL el 2026-09-21: mpi.nl/career/vacancies da 404. Aqui vive la unica plaza abierta de la pestana de grupos (L-0011).</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>SRC-0180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Amsterdam UMC - tablon de empleo en ingles</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>https://werkenbij.amsterdamumc.org/en/vacancies/all-vacancies</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Postdocs y doctorados de Amsterdam UMC, incluido el grupo de Wouter Peyrot (Psiquiatria, ERC StG).</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>palabras postdoc, genetics, psychiatry</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Quincenal</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21. Cobertura incompleta a proposito: Amsterdam UMC mantiene un tablon APARTE en neerlandes que conviene mirar tambien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>SRC-0181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>CNCR / VU Amsterdam - tablon de empleo</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>https://cncr.nl/cncr/jobs/</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Vacantes por departamento del CNCR, incluido Complex Trait Genetics (Posthuma). Permite suscribir una alerta por email.</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>mirar la fila de CTG</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21. Cambio de ruta: ctg.cncr.nl/jobs ahora es un 301 a cncr.nl/ctg/. La alerta suscribible es SUB nueva de esta pasada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>SRC-0182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Research group of neuropsychiatric genomics, Tartu</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>https://genomics.ut.ee/en/research-group-neuropsychiatric-genomics</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Composicion del grupo de Kelli Lehto, consorcios en los que entra y email de contacto; a veces anuncian plazas.</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>buscar bloque de vacantes y el email genoomika@ut.ee</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21. BLOQUEOS: ut.ee/en/vacancies da 404 y ut.ee/en/content/job-offers da 403, asi que el tablon central de Tartu no entra por ahi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>SRC-0183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>ISPG - Board of Directors</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>https://ispg.net/about-us/board-of-directors/</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>La junta completa de la sociedad de genetica psiquiatrica con roles funcionales (representante de ciencia computacional, clinica, early career), que es un mapa directo de PIs activos y visibles en su campo exacto.</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>listar miembros con rol e institucion</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Anual (la junta rota tras el WCPG)</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21 y la superficie mas rentable de la pasada: junto con la de la IGES dio ~18 nombres de PI en dos llamadas, 5 sin fichar. Nombres identificados y AUN SIN FICHA: Karmel Choi, Emily Olfson, Chunyu Liu, Melanie Carless, Victoria Marshe, Sian Hemmings, Niran Okewole, Daniel Moreno de Luca, Henriette Raventos, J9 Austin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>SRC-0184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>IGES - Board of Directors</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/board-of-directors</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Los directores de la sociedad de epidemiologia genetica con institucion, pais y anos de mandato; util para localizar PIs de metodos en Europa.</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>listar junta y officers con rol, institucion, pais y mandato</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21. La pagina de Officers (geneticepi.org/officers) esta enlazada y NO se abrio: pendiente. Nombres identificados sin ficha: Linda Kachuri (Stanford, PRS multi-ancestria, la mas prometedora), Burcu Darst, David Conti, Chloe Sarnowski, Mohamad Saad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>SRC-0185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Karolinska Institutet - noticias de concesiones ERC</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>https://news.ki.se/five-ki-researchers-receive-erc-starting-grants-in-2026</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Notas institucionales de concesion de ERC con nombre, departamento, acronimo, titulo, importe y duracion. El PATRON (nota de prensa de la institucion, no el PDF del ERC) es la via practica para explotar el angulo de dinero nuevo.</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>WebSearch: ERC grant 2026 awarded genetics mental health polygenic scores professor press release university</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Anual, en las semanas siguientes a cada ronda ERC (StG ~septiembre, CoG ~diciembre, AdG ~junio)</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>NUEVA el 2026-09-21 y ha producido la mejor ficha de la pasada (L-0026, Shuyang Yao).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>SRC-0186</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ERC - PDF oficial de resultados por panel</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>https://erc.europa.eu/system/files/2026-09/erc-2026-stg-results-ls.pdf</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>La lista oficial de PIs premiados. Usar SIEMPRE la variante por dominio '-results-ls.pdf' (solo Life Sciences, ~10 paginas), nunca el 'all-domains'.</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>patron de nombre de fichero erc-AAAA-stg-results-ls.pdf</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Anual por convocatoria</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>LECCION CARA del 2026-09-21: el PDF 'all domains' de 2025 no es procesable (binario para WebFetch; extraido por zlib, el texto sale fragmentado por kerning y los codigos de panel quedan desalineados respecto a los nombres, o sea inservible para atribuir panel a PI). Busqueda por polygenic, GWAS, biobank, heritability, psychiatric y mental health sobre ese texto: CERO coincidencias. La variante LS de 2026 no se ha abierto todavia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>SRC-0187</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Feinstein Institutes / Richa Saxena lab - paginas de empleo de laboratorio</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>https://saxena.mgh.harvard.edu/our-lab/jobs-in-the-lab/</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Las plazas del laboratorio de sueno y genomica de Richa Saxena (MGH/Broad).</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>vigilar si desaparece el 'Coming Soon!'</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>AVISO: saxenalab.org NO es este laboratorio, es el de Shreya Saxena (Yale). El sitio correcto es saxena.mgh.harvard.edu.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J169"/>
+  <autoFilter ref="A1:J188"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10828,7 +11955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H331"/>
+  <dimension ref="A1:H391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -24591,8 +25718,2368 @@
         </is>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>E-0001</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>World Congress of Psychiatric Genetics (WCPG) 2026</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama eventos</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>https://ispg.net/wcpg-2026/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>E-0002</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>ASHG 2026 Annual Meeting</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama eventos</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>https://ashgmeeting.ashg.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>E-0003</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>ESHG Conference 2027 (European Human Genetics Conference)</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama eventos</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>https://2027.eshg.org/abstracts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>E-0004</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>Behavior Genetics Association (BGA) 2027 Annual Meeting</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama eventos</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>https://bga.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>E-0005</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>IGES 2026 Annual Meeting &amp; Education Workshop</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama eventos</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/2026-annual-meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>E-0006</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>SOBP 2027 Annual Meeting</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama eventos</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>https://sobp.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>E-0007</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>Sleep Europe 2026 (28th ESRS Congress)</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama eventos</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>https://congrex.com/events/sleep-europe-2026-the-28th-congress-of-the-european-sleep-research-society/</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>E-0008</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>SLEEP 2027 (APSS Annual Meeting)</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama eventos</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>https://aasm.org/event/sleep-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>E-0017</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>GAW 2027 - Genetic Analysis Workshop (convocatoria de ideas abierta)</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama eventos</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>E-0019</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>EPA 2027 - 35th European Congress of Psychiatry</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>alta de la rama eventos</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>https://epa-congress.org/abstract-submission/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>E-0020</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Probabilistic Modeling in Genomics 2027 (ProbGen 2027)</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>alta de la rama eventos</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>https://meetings.cshl.edu/meetings.aspx?meet=PRGEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>E-0021</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Epigenomics of Common Diseases 2026</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>alta de la rama eventos</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>https://coursesandconferences.wellcomeconnectingscience.org/event/epigenomics-of-common-diseases-20261104/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>T-0001</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>International Statistical Genetics Workshop (el 'Boulder Workshop')</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>https://www.colorado.edu/ibg/workshop-2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>T-0002</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Genetic Epidemiology (short course)</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>T-0003</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Mendelian Randomization (short course)</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>T-0004</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Genetic Analysis of Population-based Association Studies</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>https://coursesandconferences.wellcomeconnectingscience.org/event/genetic-analysis-of-population-based-association-studies-20240902/</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>T-0007</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Advanced Mendelian Randomization</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/advanced-mr/</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>T-0008</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>Machine Learning with Omics Data</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>T-0009</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Molecular Epidemiology</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/molecular-epidemiology/</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>T-0011</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Genetic and Epigenetic Epidemiology (curso especializado del EEPE)</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>https://www.eepe.org/registration-2-2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>T-0012</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>SMARTbiomed Summer School: Causal inference, statistical genetics and machine learning in common disease epidemiology and biology</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>revision semanal de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>https://smartbiomed.dk/news-and-events/summer-school</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>T-0014</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>SSGAC/CESR Social-Science Genetics Methods Workshop</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>alta de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>https://www.thessgac.org/events</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>T-0015</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Reproducible Health Data Science</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>alta de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>T-0016</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Causal Inference in Epidemiology: Concepts and Methods</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>alta de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>training</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>T-0017</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Federated analysis for polygenic risk score calculations</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>alta de la rama formacion</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>https://www.ebi.ac.uk/training/events/federated-analysis-polygenic-risk-score-calculations/</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>L-0011</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>Population Genetics of Human Communication (PGHC) - Departamento de Language &amp; Genetics, Max Planck</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>seguimiento semanal de la rama grupos</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>https://www.mpi.nl/career-education/vacancies/vacancy/3-year-postdoctoral-research-scientist-position-statistical-0</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>L-0005</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>MRC Centre for Neuropsychiatric Genetics &amp; Genomics</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>seguimiento semanal de la rama grupos</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>https://cardiffuniweb.eploy.net/vacancies/</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>L-0008</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>Saxena Lab (genomica del sueno y circadiana)</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>seguimiento semanal de la rama grupos</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>https://saxena.mgh.harvard.edu/our-lab/jobs-in-the-lab/</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>L-0012</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>Grupo de genetica estadistica psiquiatrica de Wouter Peyrot (proyecto ERC PersonalRiskProfile)</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>seguimiento semanal de la rama grupos</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>https://werkenbij.amsterdamumc.org/en/vacancies/all-vacancies</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>L-0013</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Grupo de Kelli Lehto, Instituto de Genomica (proyecto ERC AT-TENSION)</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>seguimiento semanal de la rama grupos</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>https://genomics.ut.ee/en/research-group-neuropsychiatric-genomics</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>L-0001</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Complex Trait Genetics (CTG) Lab</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>seguimiento semanal de la rama grupos</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>https://cncr.nl/ctg/jobs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>L-0024</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Department of Genetic Epidemiology in Psychiatry (grupo de Fabian Streit)</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>seguimiento semanal de la rama grupos</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>https://www.zi-mannheim.de/en/research/people/person/2092.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>L-0004</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Generation R - genetica del sueno infantil</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>seguimiento semanal de la rama grupos</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>https://hsph.harvard.edu/profile/henning-tiemeier/</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>L-0026</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>Yao Lab / proyecto CANARY, Department of Medical Epidemiology and Biostatistics</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>alta de la rama de descubrimiento de grupos</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>https://news.ki.se/five-ki-researchers-receive-erc-starting-grants-in-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>L-0027</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Huang Lab, Analytic and Translational Genetics Unit (ATGU)</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>alta de la rama de descubrimiento de grupos</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>https://huanglab.ac/home-page/</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>L-0028</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Psychiatric Genetics group / PGC Anxiety Disorders working group</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>alta de la rama de descubrimiento de grupos</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>https://www.ukw.de/aktuelle-meldungen/detail/news/angst-im-genom-neue-genetische-zusammenhaenge-mit-angstsymptomen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>L-0029</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Robinson Lab, Center for Genomic Medicine and Dept. of Psychiatry</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>alta de la rama de descubrimiento de grupos</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>https://www.robinsonlab.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>L-0030</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Mattheisen group, Dept. of Community Health and Epidemiology (y Faculty of Computer Science)</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>alta de la rama de descubrimiento de grupos</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>https://medicine.dal.ca/departments/department-sites/community-health/our-people/our-faculty/ManuelMattheisen.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>L-0031</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Laboratory of Neurogenomic Biomarkers, Institute of Behavioral Science</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>alta de la rama de descubrimiento de grupos</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>https://feinstein.northwell.edu/institutes-researchers/our-researchers/todd-lencz-phd</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>groups</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>L-0032</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Institute of Medical Biometry and Statistics, grupo de genetica estadistica</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>alta de la rama de descubrimiento de grupos</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/board-of-directors</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>SRC-0169</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr"/>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>SRC-0170</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>SRC-0171</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>SRC-0172</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>SRC-0173</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>SRC-0174</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>SRC-0175</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>SRC-0176</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>SRC-0177</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>SRC-0178</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr"/>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>SRC-0179</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>SRC-0180</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>SRC-0181</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>SRC-0182</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>SRC-0183</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>SRC-0184</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>SRC-0185</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>SRC-0186</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>SRC-0187</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>alta de superficie de monitorizacion</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>ecosystem</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>SUB-0019</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>candidata de suscripcion, Status TODO</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H331"/>
+  <autoFilter ref="A1:H391"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41227,7 +44714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:Z33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -41433,7 +44920,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Confirmado en cncr.nl/ctg/jobs/ el 2026-09-07: NO hay plaza postdoc ni de doctorado anunciada. La pagina solo ofrece practicas de grado/master (contacto Gerda Berkhout) y avisa de que no quedan plazas de practicas para primavera/verano 2026; remite a los listados VU-CNCR para lo demas. La financiacion Gravitation hasta 2030 sigue implicando contratacion recurrente, asi que el correo en frio sigue siendo la via.</t>
+          <t>Sin vacantes de postdoc ni doctorado en Complex Trait Genetics a 2026-09-21: la pagina del grupo solo ofrece practicas y remite con 'For other openings, see also the VU-CNCR listings'. El tablon del CNCR tiene UNA sola vacante, Postdoc project: In vitro models to study Neuron-glia interactions (Molecular and Cellular Neurobiology), fuera del area; la fila de CTG aparece vacia. La financiacion Gravitation hasta 2030 sigue implicando contratacion recurrente, asi que el correo en frio sigue siendo la via.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -41483,7 +44970,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -41493,7 +44980,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -41501,7 +44988,11 @@
           <t>UNCHANGED</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Suscribir la alerta de empleo del CNCR (cncr.nl/cncr/jobs/) para no depender del barrido semanal.</t>
+        </is>
+      </c>
       <c r="X2" t="inlineStr">
         <is>
           <t>NEW</t>
@@ -41509,12 +45000,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://cncr.nl/ctg/</t>
+          <t>https://cncr.nl/ctg/jobs/</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>cncr.nl/ctg/jobs/ reabierta el 2026-09-14: sigue sin plazas cientificas, solo practicas de grado y master. AVISO DE FIABILIDAD DE LA FUENTE: la pagina no se ha tocado y mantiene los plazos de 2025-2026, senal de que NO es un canal fiable de vigilancia semanal -- la ausencia de plaza aqui no prueba que el grupo no contrate.</t>
+          <t>Paginas propias de CTG y del CNCR abiertas el 2026-09-21. Cambio operativo: ctg.cncr.nl/jobs ahora es un 301 a cncr.nl/ctg/. Existe alerta de empleo suscribible en cncr.nl/cncr/jobs/.</t>
         </is>
       </c>
     </row>
@@ -41835,7 +45326,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Correo en frio a Henning Tiemeier como PI de Generation R, proponiendo genetica del sueno en primera infancia sobre Generation R / Generation R Next y ofreciendo el pipeline GWAS-PRS mas la mirada clinica. Su direccion institucional NO esta verificada: sacarla de la ficha de Erasmus MC o de Pure antes de escribir. Kocevska baja a contacto secundario opcional, solo para orientacion.</t>
+          <t>PENDIENTE: el email institucional de Tiemeier NO se ha obtenido y no se inventa. Ficha a abrir: hsph.harvard.edu/profile/henning-tiemeier/. Confirmado que el es el PI senior al que escribir, no Kocevska.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -41875,7 +45366,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -41885,7 +45376,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -41895,7 +45386,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Localizar la direccion institucional de Tiemeier en Erasmus MC o Pure y escribirle con una propuesta de una pagina sobre determinantes geneticos del sueno en los primeros anos dentro de Generation R. NO escribir a Kocevska como si fuera PI.</t>
+          <t>Primera tarea de la rama de grupos la semana que viene: abrir la ficha de Harvard Chan y la de Erasmus MC para extraer el email institucional. No escribir a nadie antes de tenerlo.</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -41910,7 +45401,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Tier 1 abierto el 2026-09-14: perfil oficial de Harvard Chan, que confirma su catedra de Epidemiologia Psiquiatrica en Erasmus MC y su liderazgo de Generation R. Salvedad honesta: ese perfil NO nombra el sueno entre sus temas; el vinculo con la linea de sueno de Generation R se deduce de su coautoria en Kocevska 2024, Koopman-Verhoeff 2020 y Mulder 2019 (JCPP), es decir del registro de publicaciones, no de una declaracion institucional -- por eso LIKELY. La URL apunta a Harvard porque no hay ficha suya viva verificada en erasmusmc.nl. Ademas: Kocevska NO figura entre los 28 miembros listados del grupo Sleep &amp; Cognition de Van Someren en el NIN (Tier 1), asi que su situacion actual esta sin confirmar en ningun sitio.</t>
+          <t>Rol confirmado el 2026-09-21 por dos fuentes Tier 2 concordantes (perfil de Harvard Chan y directorio del Population Center): Professor of Social and Behavioral Sciences y Sumner and Esther Feldberg Chair of Maternal and Child Health en la Harvard T.H. Chan School of Public Health, y a la vez Professor of Psychiatric Epidemiology en el Erasmus MC de Rotterdam, donde sigue dirigiendo la investigacion sobre desarrollo cognitivo, emocional y conductual en la cohorte Generation R; dirige desde 2018 el Maternal and Child Center of Excellence de Harvard Chan. Email SIN verificar.</t>
         </is>
       </c>
     </row>
@@ -41957,7 +45448,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Revisado el 2026-09-07 en el portal oficial de vacantes de Cardiff (cardiffuniweb.eploy.net, el ATS propio de la universidad): NINGUNA plaza de genetica, genomica, psiquiatria o bioinformatica en la primera pagina de resultados (28 vacantes, pagina 1 de 3; la paginacion no me dejo pasar de ahi). Lo unico proximo de lejos es 'Research Assistant/Associate (Statistics)', cierre 17-sep-2026, sin escuela identificada - merece una mirada antes de esa fecha. La pagina de vacantes del propio Centro bloquea el acceso automatico (HTTP 403).</t>
+          <t>Sin vacantes de genetica, genomica, bioinformatica ni estadistica abiertas a 2026-09-21. La plaza de Research Assistant/Associate (Statistics) que quedo pendiente la semana pasada CERRO el 17-sep-2026 y ya no figura en el portal. Unica adyacente: Research Assistant ref 447, Division of Psychological Medicine and Clinical Neurosciences (estudio CONNECT), Grade 5, 33.951-36.636 GBP, publicada el 11-sep y con cierre el 25-sep-2026: es la division que aloja el MRC Centre de Walters, pero es un grado 5 sin perfil de genetica estadistica y cierra en 4 dias. Tambien Technician ref 669, Cancer and Genetics, Wales Cancer Biobank, cierre 23-sep-2026, grado 3, no procede.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -42002,12 +45493,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -42017,7 +45508,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -42027,7 +45518,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Mirar la vacante 'Research Assistant/Associate (Statistics)' antes del 17-sep-2026 y averiguar de que escuela es; investigar el Brain and Genomics Hub y quien contrata en el. La pagina de vacantes del Centro hay que abrirla a mano (bloquea bots).</t>
+          <t>Revisar el portal eploy cada lunes filtrando por School of Medicine y por Division of Psychological Medicine and Clinical Neurosciences. Mientras tanto, Walters sigue siendo contacto en frio para 2027.</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -42037,12 +45528,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://www.cardiff.ac.uk/centre-neuropsychiatric-genetics-genomics</t>
+          <t>https://cardiffuniweb.eploy.net/vacancies/</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>El 2026-09-07 abri el portal oficial de vacantes de Cardiff (Tier 1) y confirme que no hay nada de genetica en la pagina 1 de 3. Las paginas del Centro (cardiff.ac.uk/centre-neuropsychiatric-genetics-genomics y su subpagina de vacantes) devuelven 403 a acceso automatico: intentado dos veces, no insisto. Por eso sigue en LIKELY y no sube a VERIFIED.</t>
+          <t>Portal eploy de Cardiff abierto el 2026-09-21: 21 vacantes vivas, 12 visibles en la primera pagina (el parametro de paginacion no cambia el listado). CORRECCION DE URL: cardiffuniweb.eploy.net/vacancies/vacancies.aspx da 404, hay que usar la raiz /vacancies/. cardiff.ac.uk/jobs/vacancies da 403, igual que la pagina de vacantes del propio Centre.</t>
         </is>
       </c>
     </row>
@@ -42353,7 +45844,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Revisada la pagina de oportunidades del propio laboratorio (saxena.mgh.harvard.edu/our-lab/jobs-in-the-lab/) el 2026-09-07: literalmente dice 'Coming Soon!' - NO hay ninguna plaza publicada. La homepage si invita a escribir ('We are looking for talented, enthusiastic researchers to join us'), asi que la via es el correo en frio, no esperar un anuncio. Merece vigilancia semanal porque la pagina esta preparada para publicar.</t>
+          <t>Sin cambios a 2026-09-21: la pagina de empleo del laboratorio sigue diciendo literalmente 'Coming Soon!'. La portada si dice 'We are looking for talented, enthusiastic researchers to join us', o sea que reclutan por contacto directo y no por anuncio.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -42363,7 +45854,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Correo en frio a Richa Saxena o Hassan Dashti (Saxena Lab, 185 Cambridge St, 5th Floor, Boston MA 02114) - gancho: su review en revision en Journal of Sleep Research mas interes en genetica del sueno; ofrecer habilidades de genetica estadistica (linea 1) aplicadas al sueno (linea 3). La propia web pide que la gente interesada escriba, asi que un correo en frio aqui esta explicitamente invitado.</t>
+          <t>Formulario de contacto del laboratorio en saxena.mgh.harvard.edu; no hay email nominal publicado, solo el formulario y la direccion postal (185 Cambridge St, 5th Floor, Boston, MA 02114). EE.UU. exigiria patrocinio de visado.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -42403,7 +45894,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -42413,7 +45904,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -42423,7 +45914,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Vigilar semanalmente la pagina de oportunidades del laboratorio; en paralelo mandar el correo en frio, que la web lo pide expresamente.</t>
+          <t>Carta en frio por el formulario en 2027 con el angulo de genetica del sueno infantil. Requiere patrocinio de visado.</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -42433,12 +45924,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>https://saxena.mgh.harvard.edu/</t>
+          <t>https://saxena.mgh.harvard.edu/our-lab/jobs-in-the-lab/</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>saxena.mgh.harvard.edu/our-lab/jobs-in-the-lab/ reabierta el 2026-09-14: literal 'Coming Soon!', sin plazas.</t>
+          <t>Pagina propia del laboratorio abierta el 2026-09-21. AVISO IMPORTANTE: saxenalab.org NO es este laboratorio, es el de Shreya Saxena (Yale). El sitio correcto de Richa Saxena es saxena.mgh.harvard.edu.</t>
         </is>
       </c>
     </row>
@@ -42749,17 +46240,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ABIERTA Y CONFIRMADA el 2026-09-14: '3-year Postdoctoral Research Scientist Position in Statistical Genomics/Genetic Epidemiology', revision rodante desde el 8-oct-2026 'until the position is filled', inicio propuesto 1-dic-2026 'although the start date is negotiable'. Requisito literal: 'hold, or expect to obtain shortly, a PhD'.</t>
+          <t>ABIERTA Y CONFIRMADA de nuevo el 2026-09-21, sin cambios: postdoc de 3 anos en Statistical Genomics/Genetic Epidemiology, revision continua desde el 8-oct-2026 hasta cubrir la plaza, inicio propuesto 1-dic-2026 negociable. Ni el plazo ni la fecha de inicio se han movido. Requisito literal: doctorado obtenido o 'expected shortly'. Sigue siendo la UNICA plaza viva de toda esta pestana.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Financiacion nuclear Max Planck; la plaza es un contrato de 3 anos ya presupuestado dentro del Departamento de Language and Genetics</t>
+          <t>Max Planck Society. Grupo Population Genetics of Human Communication, con colaboracion de Conor Dolan y Dorret Boomsma (VU Amsterdam) y la red Gene Amsterdam.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Consultas cientificas informales a Beate St Pourcain (beate.stpourcain [at] mpi.nl); consultas generales a la secretaria del Departamento de Language &amp; Genetics (secretariat.genetics [at] mpi.nl). Se puede escribir ANTES del 8-oct-2026 para sondear la fecha de inicio.</t>
+          <t>beate.stpourcain@mpi.nl (cientifico) y secretariat.genetics@mpi.nl (general).</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -42774,7 +46265,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>El encaje cientifico no cambia: genomica estadistica y epidemiologia genetica sobre comportamiento social desde la primera infancia, trayectorias de salud mental y el consorcio EAGLE de cohortes de nacimiento, es decir sus lineas 1 y 3 a la vez, en la UE y sin visado. Lo que cambia esta semana es la lectura del calendario, y conviene decirla sin adornos: el anuncio exige doctorado en mano o 'a punto de obtenerlo' y su defensa esta prevista para feb-2028, catorce meses despues del inicio propuesto. 'Negociable' en un anuncio Max Planck suele significar semanas o pocos meses, no mas de un ano, y el anuncio no cuantifica el margen. Analisis, no dato verificado: esta convocatoria concreta probablemente NO es alcanzable para ella. Su valor real es abrir la puerta a la SIGUIENTE plaza del grupo PGHC, asi que el correo antes del 8-oct sigue siendo la accion correcta pero con otro objetivo: presentarse como candidata de la ronda 2027-2028, no competir por esta.</t>
+          <t>Encaje tematico alto (genomica estadistica del desarrollo, consorcio EAGLE, datos de gemelos) pero DESENCAJE TEMPORAL SEVERO, y esto es lo que hay que leer de la fila: inicio 1-dic-2026 frente a disponibilidad mid-2027, con defensa ETA feb-2028, catorce meses despues del arranque propuesto. 'Negociable' en un anuncio Max Planck rara vez significa mas de un ano. Analisis, no dato verificado: esta convocatoria concreta probablemente no es alcanzable, asi que el correo antes del 8-oct debe posicionarla para rondas futuras, NO competir por esta plaza.</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -42799,7 +46290,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -42809,17 +46300,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Escribir a beate.stpourcain@mpi.nl antes del 8-oct-2026 con la pregunta en los dos sentidos: hasta donde llega el margen del inicio, y si el grupo preve nuevas plazas en 2027-2028. Presentarse como candidata de la siguiente ronda.</t>
+          <t>Escribir a beate.stpourcain@mpi.nl ANTES del 8-oct-2026 presentandose y preguntando explicitamente si el inicio negociable admite 2027-2028 o si habra nuevas rondas. No presentar candidatura formal a esta plaza sin esa respuesta.</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -42834,7 +46325,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Anuncio completo releido en mpi.nl el 2026-09-14 (Tier 1): sigue publicado y sin cambios respecto al 2026-09-07. La reserva de calendario es lectura propia del texto del anuncio, no una declaracion del grupo.</t>
+          <t>Pagina propia de vacantes del MPI Nijmegen abierta el 2026-09-21. Correccion de URL: mpi.nl/career/vacancies da 404; la viva es mpi.nl/career-education/vacancies.</t>
         </is>
       </c>
     </row>
@@ -42881,7 +46372,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Ninguna plaza concreta anunciada en la pagina institucional; el ERC Starting Grant de 1,5 M EUR implica contrataciones de doctorandos y postdocs en el arranque del proyecto. Sin verificar: consultar la bolsa de empleo de Amsterdam UMC.</t>
+          <t>Sin vacantes del area a 2026-09-21: el tablon en ingles de Amsterdam UMC solo publica dos plazas, ninguna del campo (Assistant professor in infectious diseases tenure track, y Postdoc in FAIR biomedical data interoperability). No hay postdoc ni doctorado en genetica psiquiatrica en el grupo de Peyrot pese al ERC Starting Grant de 1,5 M EUR. Salvedad de cobertura: Amsterdam UMC mantiene un tablon APARTE en neerlandes que no se ha abierto.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -42931,38 +46422,38 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Escribir correo en frio a Peyrot antes de fin de 2026 presentando disponibilidad desde mediados de 2027 y pidiendo una videollamada de 20 minutos; en paralelo, localizar su direccion institucional exacta en pure.amsterdamumc.nl y revisar la bolsa de empleo de Amsterdam UMC por si sale la plaza del ERC.</t>
+          <t>Revisar mensualmente tambien el tablon en neerlandes. Contacto en frio a Peyrot en 2027 apoyandose en el ERC recien concedido: los ERC contratan a lo largo de varios anos, no solo al arrancar.</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://www.amsterdamumc.org/en/research/institutes/amsterdam-public-health/news/wouter-peyrot-awarded-erc-starting-grant-for-personalized-genetic-risk-profiles-in-psychiatry-1</t>
+          <t>https://werkenbij.amsterdamumc.org/en/vacancies/all-vacancies</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Tier 1: nota oficial de Amsterdam UMC sobre el ERC Starting Grant, leida el 2026-09-07. Perfiles institucionales complementarios en amsterdamumc.org/en/research/researchers/wouter-peyrot.htm y research.vumc.nl. El encargo de la rama lo senalaba como pendiente de la pasada del 2026-08-24.</t>
+          <t>Tablon oficial en ingles de Amsterdam UMC abierto el 2026-09-21.</t>
         </is>
       </c>
     </row>
@@ -43009,17 +46500,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>No hay plaza publicada verificada. El ERC Starting Grant es de 2025 y arranca con equipo por formar: es el momento tipico de contratar doctorandos y postdocs.</t>
+          <t>Sin plazas anunciadas en la pagina del grupo a 2026-09-21. Hay una oferta de postdoc de su grupo circulando en el boletin de la Behavior Genetics Association con cierre el 2 de marzo, pero NO se ha podido confirmar el ano ni si sigue viva: se da por CADUCADA salvo prueba en contra.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ERC Starting Grant de 1,5 millones de euros, proyecto AT-TENSION, panel SH4, confirmado en la lista oficial de investigadores principales de las ERC Starting Grants 2025 (erc.europa.eu, erc-2025-stg-results-all-domains.pdf) que he descargado y leido el 2026-09-07, y en la nota de la Universidad de Tartu.</t>
+          <t>ERC Starting Grant (AT-TENSION). El grupo participa en TIMESPAN, COVIDMENT, PGC, CoMorMent, PsycheMERGE, EstWell y R2D2-MH, y ha recogido datos de bienestar y salud mental de mas de 86.000 participantes del Biobanco de Estonia.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Correo en frio a Kelli Lehto (profesora asociada del Institute of Genomics; direccion en la ficha de personal de ut.ee, no verificada). Gancho: AT-TENSION necesita gente que sepa unir fenotipo clinico y genetica estadistica sobre biobancos, y ella es medica que ya trabaja con pipelines GWAS/PRS. Mencionar explicitamente el multi-biobanco: la experiencia con datos del proyecto QIMR encaja con el trabajo entre cohortes.</t>
+          <t>genoomika@ut.ee (email de grupo; sin email nominal de Lehto verificado).</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -43054,43 +46545,43 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Correo en frio a Kelli Lehto con CV y las dos fechas de disponibilidad; preguntar si AT-TENSION prevee contratar en 2027 y ofrecer la vertiente de fenotipado clinico. Confirmar antes su direccion institucional en la ficha de personal de ut.ee.</t>
+          <t>Buscar el email nominal de Lehto en ut.ee/en/employee/kelli-lehto y escribirle en frio en 2027 con el angulo del ERC AT-TENSION (TDAH adulto, genomica y ciencia de datos).</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://ut.ee/en/news/erc-grant-helps-explore-innovative-approaches-improve-diagnosis-adhd-adults</t>
+          <t>https://genomics.ut.ee/en/research-group-neuropsychiatric-genomics</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Tier 1: lista oficial de PIs de las ERC Starting Grants 2025 (https://erc.europa.eu/system/files/2025-09/erc-2025-stg-results-all-domains.pdf) descargada y extraida localmente el 2026-09-07, entrada LEHTO Kelli, University of Tartu, EE, AT-TENSION, panel SH4; mas nota institucional de la Universidad de Tartu. Tier 2 de apoyo: ERR y EurekAlert.</t>
+          <t>Pagina propia del grupo abierta el 2026-09-21: confirma a Kelli Lehto como PI y profesora asociada. Bloqueos nuevos: ut.ee/en/vacancies da 404 y ut.ee/en/content/job-offers da 403, asi que el tablon central de Tartu no es accesible por esa via.</t>
         </is>
       </c>
     </row>
@@ -44392,7 +47883,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Central Institute of Mental Health (ZI Mannheim), Medical Faculty Mannheim, Heidelberg University</t>
+          <t>Hector Institute for Artificial Intelligence in Psychiatry (HITKIP), Zentralinstitut fuer Seelische Gesundheit (ZI Mannheim), Medical Faculty Mannheim, Heidelberg University</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -44417,7 +47908,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Desconocido: no se pudo abrir la pagina del departamento (dos URL de zi-mannheim.de dieron 404).</t>
+          <t>Desconocido: no se ha revisado el tablon de empleo del ZI. Lo que se resuelve esta semana es la adscripcion y el contacto, que estaban mal.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -44427,12 +47918,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Correo en frio a Fabian Streit citando su co-presidencia del MDD Working Group del PGC como referencia compartida. Gancho: capacidad independiente en PLINK/R para GWAS-PRS y disponibilidad para trabajo sobre NAKO o sobre los datos del consorcio de personalidad limite. Proponer explicitamente co-escribir una solicitud Humboldt o MSCA con el como host.</t>
+          <t>fabian.streit@zi-mannheim.de (PROBABLE, tomado de la direccion de correspondencia de sus articulos indexados, no verificado en la ficha). Telefono +49 621 1703-6054. Conviene confirmar el email escribiendo primero a la secretaria del HITKIP o por el formulario del ZI antes de la carta en frio.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Co-chair del MDD Working Group del PGC; trabajos recientes sobre vias geneticas directas e indirectas entre neuroticismo parental y problemas emocionales de la descendencia en siete cohortes europeas.</t>
+          <t>Schwaba et al. 2026, 'Robust inference and correlates from genetic associations with personality', Nature; O'Connell et al. 2025, 'Genomics yields biological and phenotypic insights into bipolar disorder', Nature. Ambos destacados en su propia ficha institucional.</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -44462,43 +47953,43 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Localizar a mano la pagina del Department of Genetic Epidemiology in Psychiatry del ZI Mannheim y su direccion de correo antes de escribir; la adscripcion es Tier 2 y esta sin confirmar.</t>
+          <t>Confirmar el email por la secretaria del HITKIP o el formulario del ZI, y solo entonces escribir en frio.</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>https://pgc.unc.edu/for-researchers/working-groups/mdd/</t>
+          <t>https://www.zi-mannheim.de/en/research/people/person/2092.html</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>Su co-presidencia del MDD WG SI esta verificada en la pagina Tier 1 del PGC (2026-09-14). La adscripcion al Department of Genetic Epidemiology in Psychiatry del ZI Mannheim procede de fuentes Tier 2 y dos intentos de URL en zi-mannheim.de devolvieron 404: por eso la fila es UNVERIFIED y la URL apunta al PGC, que es lo unico comprobado.</t>
+          <t>CORRECCION: esta fila lo situaba en el Departamento de Genetic Epidemiology in Psychiatry, y eso esta DESACTUALIZADO. Su ficha institucional viva, abierta el 2026-09-21 tras los dos 404 de la semana pasada, lo situa en el HITKIP con el Personality Disorders Genomics Group. El email no se renderiza en la ficha (ofuscado).</t>
         </is>
       </c>
     </row>
@@ -44630,8 +48121,932 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>L-0026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Yao Lab / proyecto CANARY, Department of Medical Epidemiology and Biostatistics</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Shuyang Yao</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Karolinska Institutet (MEB)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Suecia</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Genetica psiquiatrica de la esquizofrenia; riesgo asociado al consumo de cannabis en la adolescencia; integracion multi-omica de datos geneticos humanos con modelos animales; epidemiologia genetica sobre registros nacionales suecos.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>GWAS y datos geneticos y moleculares humanos, multi-omica, epidemiologia de registros. El brazo animal (THC en cerebro en desarrollo) no seria suyo.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>No verificado: no se ha abierto la pagina de vacantes de KI. Un ERC Starting Grant recien concedido de 1,5 M EUR a 5 anos implica contratacion a corto plazo, pero no hay oferta publicada localizada.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ERC Starting Grant 2026, 1,5 millones de euros (~16,6 millones SEK) a 5 anos, proyecto CANARY. Fuente: nota oficial de Karolinska Institutet 'Five KI researchers receive ERC Starting Grants in 2026', abierta y leida el 2026-09-21.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Email directo a Shuyang Yao (MEB, KI); buscar antes su direccion en ki.se. El correo debe PROPONER UNA FUNCION, no pedir una oportunidad: (a) felicitar por CANARY nombrando el proyecto, (b) dos frases diciendo que es medica terminando tesis en genetica estadistica con dos primeros-autores en revision (Journal of Sleep Research y Nature Mental Health), (c) ofrecerse concretamente para el brazo de genetica estadistica HUMANA del proyecto (GWAS/PRS, PLINK/R), que es justo lo que un proyecto mitad animal mitad humano necesita cubrir con alguien autonomo, (d) dar fechas: libre mid-2027 sin doctorado terminado, feb-2028 con el, (e) CV de una pagina. Ciudadania UE: cero friccion administrativa en Suecia.</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>ERC Starting Grant 2026 (CANARY). Lista de publicaciones no revisada.</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>El mejor encaje de la semana, por cuatro razones concretas. LINEA: esquizofrenia mas genetica de rasgos complejos son sus lineas 1 y 2 exactas. TECNICA: el proyecto necesita a alguien que corra GWAS/PRS sobre datos humanos de forma independiente, que es precisamente lo que ella hace sin supervision, y NO exige neuroimagen ni electrofisiologia, que son sus tecnicas solo-supervisadas. RUNWAY: dinero nuevo a 5 anos desde 2026 cubre con holgura una incorporacion en 2027-2028, y un PI que acaba de recibir su primer ERC esta montando equipo, no defendiendo plazas de veinte postdocs ya instalados. CULTURA: en el MEB de Karolinska, departamento de epidemiologia genetica, un perfil MD que programa es moneda de alto valor. El primer correo va descrito en Contact_Route.</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>KI atrae mucha solicitud, pero un ERC StG recien concedido en un tema de nicho (cannabis-esquizofrenia multiomica) todavia no ha generado cola, y el brazo humano compite con menos gente que un puesto generico de genetica psiquiatrica.</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Escribir a Shuyang Yao en octubre-noviembre 2026 felicitando por CANARY y ofreciendo el brazo de genetica estadistica humana. Buscar antes su email institucional en ki.se y comprobar la pagina de vacantes de KI.</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>https://news.ki.se/five-ki-researchers-receive-erc-starting-grants-in-2026</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Nota de prensa oficial de Karolinska Institutet, abierta el 2026-09-21: confirma nombre, departamento, acronimo CANARY, titulo completo, importe (1,5 M EUR) y duracion (5 anos). Angulo de descubrimiento: premios de financiacion frescos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>L-0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Huang Lab, Analytic and Translational Genetics Unit (ATGU)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Hailiang Huang</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Massachusetts General Hospital / Stanley Center for Psychiatric Research, Broad Institute / Harvard Medical School</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Boston (Cambridge, MA)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Genetica estadistica de trastornos complejos; arquitectura genetica de esquizofrenia y trastorno bipolar; genomica cross-ancestry; enfermedad inflamatoria intestinal.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Genetica estadistica y metodos computacionales, GWAS multi-ancestria, fine-mapping, recursos genomicos de poblaciones diversas.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>No verificado del todo: la portada del laboratorio no publica ofertas y la seccion 'Opportunities' del menu no se abrio por techo de llamadas. Contacto general publicado: admin@atgu.mgh.harvard.edu.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sin cifras verificadas: la web no lista grants. Si lista premios recientes, Theodore Reich Early Career Award de la ISPG (sep-2025) y Pamela Sklar Innovation Award (oct-2024). Este hueco de runway es la debilidad de la ficha.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Email a Hailiang Huang, via admin@atgu.mgh.harvard.edu o su direccion de HMS. El correo debe: (a) citar un paper concreto suyo de cross-ancestry en esquizofrenia, buscado antes y no improvisado, (b) presentarse como medica con residencia de Laboratorio y tesis en genetica estadistica, (c) decir que quiere trabajar en transferibilidad de PRS entre ancestrias y que ya maneja pipelines GWAS/PRS sin supervision, (d) preguntar explicitamente si habra plazas de postdoc en el ciclo 2027-2028, (e) mencionar en UNA linea al final que es ciudadana UE y necesitaria patrocinio de visado. Enviar en otono, no en verano.</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Theodore Reich Early Career Award (ISPG, 2025); Pamela Sklar Innovation Award (2024); Tesorero de la junta de la ISPG en el mandato actual.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Es el laboratorio que describe LITERALMENTE su linea 1 (genetica estadistica de rasgos complejos) aplicada a su linea 2 (psiquiatria). LINEA: esquizofrenia y bipolar con enfoque metodologico, sin neuroimagen ni electrofisiologia de por medio. TECNICA: todo es PLINK/R/Python sobre sumstats y genotipos, exactamente su zona autonoma, y la transferibilidad de PRS entre ancestrias es una habilidad escasa y muy vendible. CULTURA: ATGU y el Stanley Center forman medicos-analistas y tienen tradicion de acoger perfiles MD reconvertidos a genetica estadistica, asi que su combinacion se lee como continuidad y no como rareza; el premio de carrera temprana de la ISPG en 2025 apunta a laboratorio en expansion. Los dos frenos, dichos sin adornos: runway sin verificar y necesidad de patrocinio de visado.</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Broad y ATGU son uno de los destinos mas solicitados del mundo en genetica psiquiatrica y reciben candidaturas espontaneas de forma continua.</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Abrir la pagina 'Opportunities' de huanglab.ac y, si no hay convocatoria, enviar candidatura espontanea a admin@atgu.mgh.harvard.edu citando un paper cross-ancestry concreto.</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>https://huanglab.ac/home-page/</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Web propia del laboratorio (huanglab.ac) abierta el 2026-09-21: lineas, premios 2024-2025 y email de contacto. Su papel como Treasurer confirmado en ispg.net/about-us/board-of-directors/, tambien abierta. Angulo de descubrimiento: juntas de sociedades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>L-0028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Psychiatric Genetics group / PGC Anxiety Disorders working group</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Angelika Erhardt-Lehmann (co-liderazgo con Juergen Deckert, Heike Weber y Nora Strom)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Universitaetsklinikum Wuerzburg, Dept. of Psychiatry, Psychosomatics and Psychotherapy (con afiliacion al Max Planck Institute of Psychiatry, Munich)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Wuerzburg</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Genetica y epigenetica de los trastornos de ansiedad; GWAS de ansiedad mayor y de severidad de sintomas de ansiedad generalizada; fenotipos dimensionales de miedo.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>GWAS y meta-analisis a gran escala en consorcio (PGC), epigenetica, fenotipado clinico profundo.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>No verificado: no se han abierto las paginas de vacantes del UKW ni del MPI de Psiquiatria.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NO VERIFICADO para 2026-2028, y es un hueco real. La financiacion historica del eje de ansiedad de Wuerzburg fue el SFB/TRR 58 de la DFG ('Fear, Anxiety and Anxiety Disorders'), activo 2008-2020 y por tanto YA CERRADO. Hay que preguntar por el runway antes de invertir esfuerzo.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Email a Angelika Erhardt-Lehmann; localizar antes su direccion en ukw.de. El correo debe: (a) referirse al GWAS de Nature Genetics 2026 y al meta-analisis de sintomas cuantitativos de 2026 por su CONTENIDO, no por cortesia, (b) presentarse como medica que termina tesis en genetica estadistica y que ya ha trabajado en un proyecto de consorcio internacional (QIMR Berghofer, manuscrito en revision en Nature Mental Health), (c) proponerse para analisis de fenotipos dimensionales y PRS dentro del PGC Anxiety, (d) preguntar DIRECTAMENTE si hay financiacion proyectada para 2027-2028 y de que fuente, (e) ofrecer trabajar en ingles.</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>GWAS de trastornos de ansiedad mayores en 122.341 casos de ascendencia europea, 58 loci, senalando senalizacion GABAergica, Nature Genetics (feb-2026, colaboracion Texas A&amp;M / Dalhousie / KCL / Wuerzburg); meta-analisis genome-wide de sintomas de ansiedad generalizada medidos cuantitativamente, Nature Human Behaviour (jun-2026).</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>LINEA: GWAS de trastornos de salud mental es su linea 2 declarada, y aqui esta dentro del grupo que acaba de publicar el GWAS de referencia del campo. TECNICA: trabajo de consorcio puro sobre sumstats y cohortes, 100% en su zona autonoma (PLINK/R), sin nada de neuroimagen obligatoria. CULTURA: entorno clinico-universitario aleman donde un perfil MD con tesis en genetica estadistica se lee como candidata natural a Wissenschaftliche Mitarbeiterin; la doble sede (Wuerzburg y MPI Munich) duplica las puertas. MOVILIDAD: ciudadania UE, cero visado. El punto debil, y por eso 4 y no 5, es que el runway de financiacion esta sin verificar y el consorcio que sostenia esta linea cerro en 2020: eso se pregunta en el primer correo, no se asume.</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Grupo clinico aleman de tamano medio, menos expuesto a candidaturas internacionales masivas que Broad o KI, pero con visibilidad alta tras dos papers de primer nivel en 2026.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Localizar el email institucional de Erhardt-Lehmann en ukw.de y escribirle preguntando por financiacion 2027-2028 y por un rol analitico en el PGC Anxiety.</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>https://www.ukw.de/aktuelle-meldungen/detail/news/angst-im-genom-neue-genetische-zusammenhaenge-mit-angstsymptomen/</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Confirmado el 2026-09-21 por concordancia de varias fuentes Tier 2 (PMC del GWAS de ansiedad con 58 loci, PMC del meta-analisis de sintomas de ansiedad generalizada, notas de prensa del Universitaetsklinikum Wuerzburg). NO se abrio ninguna pagina institucional directamente: de ahi LIKELY y no VERIFIED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>L-0029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Robinson Lab, Center for Genomic Medicine and Dept. of Psychiatry</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Elise B. Robinson</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Massachusetts General Hospital / Broad Institute of MIT and Harvard (afiliada al Dept. of Epidemiology de la Harvard T.H. Chan School of Public Health y a ATGU)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Boston (Cambridge, MA)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Genetica estadistica de factores de riesgo comunes y raros en trastornos neuropsiquiatricos graves; variabilidad del neurodesarrollo; diferencias dentro y entre trastornos psiquiatricos; proyecto NeuroDev en poblaciones africanas.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Genetica estadistica, epidemiologia psiquiatrica, metodos cuantitativos para asociaciones conductuales y celulares.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>No verificado: no se abrio robinsonlab.org ni ninguna pagina de vacantes.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>No verificado. Es faculty del Broad y afiliada de SFARI y de la Simons Foundation segun resultados de busqueda, lo que sugiere financiacion estable, pero no se ha abierto ninguna fuente que lo confirme con cifras.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Email a Elise Robinson, via el CGM del MassGeneral o robinsonlab.org. El correo debe: (a) abrir con la conexion entre variabilidad del neurodesarrollo y fenotipos de sueno en los primeros 3 anos, citando su propia revision en revision en el Journal of Sleep Research, (b) presentarse como MD con pipeline GWAS/PRS autonoma, (c) proponer un tema CONCRETO, por ejemplo PRS psiquiatricos y sueno infantil como fenotipo dimensional temprano, (d) preguntar por plazas de postdoc en el ciclo 2027-2028, (e) senalar la necesidad de visado, al final y en una linea.</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Co-chair del PGC Autism Working Group; lidera la NeuroDevelopmental Variability Initiative del Broad y el proyecto NeuroDev. Publicaciones concretas de 2025-2026 sin verificar.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>LINEA: su combinacion de genetica estadistica y epidemiologia psiquiatrica es casi literalmente el perfil que Ana esta construyendo, y Robinson hizo ese mismo camino (ScD en epidemiologia psiquiatrica y luego postdoc en genetica estadistica en MGH/Broad): es un modelo de carrera, no solo un laboratorio. ANGULO PROPIO, y es el argumento fuerte: su linea 3 (genetica del sueno en lactantes y ninos pequenos) se vende muy bien como fenotipo de variabilidad del neurodesarrollo temprano, que es exactamente la NDV Initiative; ningun otro grupo de la tabla ofrece ese encaje. TECNICA: comun y raro sobre datos humanos con metodos cuantitativos, nada que exija neuroimagen o electrofisiologia autonoma. Frenos: visado y una competencia altisima.</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Broad, Harvard Chan y Simons/SFARI: uno de los ecosistemas con mas demanda de postdocs del mundo.</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Abrir robinsonlab.org, localizar la seccion de contacto o 'join', y buscar una publicacion de 2025-2026 concreta que citar antes de escribir.</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>https://www.robinsonlab.org/</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Perfiles concordantes de Broad Institute, MGH Center for Genomic Medicine y Harvard Chan recogidos en busqueda el 2026-09-21; ninguna pagina abierta directamente, por eso LIKELY. Angulo de descubrimiento: co-presidencias de working groups del PGC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>L-0030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Mattheisen group, Dept. of Community Health and Epidemiology (y Faculty of Computer Science)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Manuel Mattheisen</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Dalhousie University</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Halifax, Nueva Escocia</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Factores de riesgo geneticos de rasgos complejos en estudios a gran escala; predictores geneticos de inicio, curso y respuesta al tratamiento; implementacion clinica de hallazgos geneticos; desarrollo de metodos bioestadisticos y bioinformaticos.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Epidemiologia genetica, bioestadistica, GWAS de consorcio (analista principal de los GWAS de TOC y de trastornos de ansiedad del PGC), desarrollo de herramientas.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>No verificado: no se abrieron paginas de vacantes de Dalhousie.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>No verificado: no se encontro anuncio de financiacion 2026 concreto.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Email a Manuel Mattheisen (Dept. of Community Health and Epidemiology, Dalhousie). El correo debe: (a) decir en la PRIMERA linea que es medica que termina tesis en genetica estadistica y que su residencia es de Medicina de Laboratorio, o sea implementacion clinica, que es su lenguaje, (b) citar su papel como lead analyst del GWAS de ansiedad del PGC, (c) proponer un rol de analista en los GWAS de TOC y ansiedad diciendo que ya ha analizado dentro de un proyecto de consorcio (QIMR Berghofer), (d) preguntar por financiacion disponible y por la via administrativa (postdoc frente a research associate) para 2027-2028.</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Coautor del GWAS de trastornos de ansiedad mayores (Nature Genetics, feb-2026); co-chair del PGC TS/OCD working group; analista principal de los GWAS de TOC y ansiedad del PGC.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>LINEA: genetica estadistica de rasgos complejos mas GWAS psiquiatricos, sus lineas 1 y 2 sin desvio. TECNICA: grupo de metodos y analisis de consorcio, trabajo enteramente PLINK/R/Python sobre datos humanos, su zona autonoma; y como ademas desarrollan herramientas, hay margen para pasar de usuaria de pipelines a desarrolladora de metodos, que es justo lo que le falta para tener un perfil diferenciado. CULTURA, y es el argumento decisivo: el PI comparte su trayectoria exacta, medico reconvertido a bioestadistica genetica, asi que su MD mas tesis en genetica estadistica se lee como continuidad; y el enfoque explicito en implementacion clinica encaja con su residencia de Medicina de Laboratorio. MOVILIDAD: Canada exige permiso de trabajo pero es sensiblemente menos hostil que EE.UU.</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>No se hallaron convocatorias abiertas ni indicios de volumen de candidaturas. Dalhousie esta fuera de los circuitos de maxima demanda, lo que sugiere competencia mas baja que Boston o Estocolmo, pero no esta verificado.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Abrir el perfil de Mattheisen en medicine.dal.ca (Community Health and Epidemiology), sacar su email y escribirle proponiendose como analista del PGC con enfoque de implementacion clinica.</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>https://medicine.dal.ca/departments/department-sites/community-health/our-people/our-faculty/ManuelMattheisen.html</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Perfiles concordantes de Dalhousie (Community Health and Epidemiology, Psychiatry, Computer Science) y ResearchGate recogidos en busqueda el 2026-09-21; ninguna pagina abierta directamente. Angulo de descubrimiento: co-presidencias de working groups del PGC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L-0031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Laboratory of Neurogenomic Biomarkers, Institute of Behavioral Science</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Todd Lencz</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>The Feinstein Institutes for Medical Research, Northwell Health (Zucker School of Medicine at Hofstra/Northwell)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Manhasset, Nueva York</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Estados Unidos</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Genetica a gran escala de esquizofrenia y enfermedad mental grave; genomica cognitiva y neurodesarrollo; scores de riesgo poligenico biologicamente informados; propiedades estadisticas y aspectos eticos del cribado poligenico de embriones.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>GWAS, PRS incluidos los biologicamente informados, integracion con datos de neuroimagen, modelizacion estadistica de prediccion poligenica.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>No verificado: no se abrio la pagina de vacantes del Feinstein.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Subvencion del NIH de 3,1 millones de dolares a 5 anos para el eje de genomica cognitiva y PRS biologicamente informados, continuacion del proyecto 'Cognitive Genomics as a Window on Neurodevelopment and Psychopathology'; ademas un proyecto financiado por el NIH sobre cribado poligenico de embriones con el Harvard Center for Bioethics y la Universidad Hebrea de Jerusalen. Fuente: sala de prensa del Feinstein y BioSpace, coincidentes, no abiertas directamente.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Email a Todd Lencz. El correo debe: (a) mencionar el proyecto de PRS biologicamente informados y preguntar si el equipo analitico va a crecer, (b) decir que es medica con residencia de Laboratorio y tesis en genetica estadistica, y que le interesan tanto la construccion de PRS como sus propiedades estadisticas de cara al uso clinico, (c) ser explicita y honesta: autonoma en PLINK/R y pipelines GWAS/PRS, con experiencia SUPERVISADA en neuroimagen, sin fingir, (d) dar fechas 2027-2028 y mencionar el visado en una sola linea al final.</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Subvencion NIH de 3,1 M USD a 5 anos (genomica cognitiva y PRS); miembro de la junta de la ISPG como Chair of Ethics, Position, and Public Policy en el mandato actual, verificado en ispg.net.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>LINEA: PRS de trastornos psiquiatricos, su linea 2 exacta, con un componente metodologico (PRS biologicamente informados) que le daria una habilidad transferible y escasa. TECNICA: el nucleo es PRS y GWAS, que hace sola; el proyecto integra neuroimagen, tecnica solo-supervisada para ella, pero aqui entraria como CONSUMIDORA de fenotipos de imagen y no como quien los adquiere, asi que no es bloqueante, y conviene decirlo asi en el correo. RUNWAY: es la ficha con financiacion mejor documentada despues de Yao, 3,1 M USD a 5 anos mas un segundo proyecto NIH activo. Y hay un argumento que no se repite en ninguna otra ficha de la tabla: es el unico grupo donde su formacion MEDICA es por si sola un argumento de peso, porque las implicaciones clinicas y eticas del PRS son parte del objeto de estudio. Freno: visado estadounidense.</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Grupo fuerte pero fuera del triangulo Broad-KCL-KI; en EE.UU. la competencia por postdoc en genetica psiquiatrica es alta en general, pero el Feinstein recibe menos candidaturas espontaneas internacionales que Boston.</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Abrir el perfil de Todd Lencz en feinstein.northwell.edu, confirmar la subvencion del NIH en la nota de prensa oficial y escribirle preguntando por el crecimiento del equipo analitico para 2027-2028.</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>https://feinstein.northwell.edu/institutes-researchers/our-researchers/todd-lencz-phd</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Dos fuentes Tier 2 coincidentes (sala de prensa de los Feinstein Institutes y BioSpace) sobre la subvencion de 3,1 M USD, el 2026-09-21; su papel en la junta de la ISPG SI esta verificado en ispg.net/about-us/board-of-directors/, abierta directamente. Angulo de descubrimiento: juntas de sociedades mas premios de financiacion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>L-0032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Institute of Medical Biometry and Statistics, grupo de genetica estadistica</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Silke Szymczak</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>University of Luebeck</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Luebeck</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Alemania</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Genetica estadistica y bioinformatica; metodos de analisis de datos geneticos de alta dimension. NO verificadas sus lineas concretas en la web del instituto.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>No verificadas.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>No verificado: no se buscaron vacantes.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>No verificado.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Email a Silke Szymczak. Doble uso: como grupo europeo de metodos donde reforzar el lado estadistico de su perfil sin salir de la UE, o mas realista de momento, como PUERTA DE ENTRADA a la red de la IGES (recomendacion, contactos, visibilidad en el congreso anual).</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Miembro de la junta de la IGES, mandato 2025-2027 (verificado en la pagina oficial de la sociedad).</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Encaje parcial: es genetica estadistica (linea 1) pero no consta trabajo en psiquiatria ni en sueno (lineas 2 y 3), y sus temas concretos no estan verificados. Vale como opcion UE sin visado y como puerta a la red IGES, no como destino prioritario.</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sin datos.</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Abrir la web del Institut fuer Medizinische Biometrie und Statistik de la Universitaet zu Luebeck y verificar si su linea toca rasgos complejos psiquiatricos. Si no, archivar como contacto de red de la IGES y no como grupo objetivo.</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>https://www.geneticepi.org/board-of-directors</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Lo UNICO verificado el 2026-09-21 es su pertenencia a la junta de la IGES (pagina oficial abierta). Todo lo demas es inferencia sin verificar y queda marcado como tal; la URL es la de la junta porque no se ha abierto ninguna pagina institucional suya.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z26"/>
+  <autoFilter ref="A1:Z33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -44642,7 +49057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -44661,8 +49076,8 @@
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="52" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="17" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
@@ -44889,12 +49304,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>VERIFIED en fechas; UNVERIFIED en cuotas y modalidad virtual</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -44904,7 +49319,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -44914,7 +49329,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>La inscripcion sigue ABIERTA a 15 dias del congreso y sin fecha de cierre publicada: si va, inscribirse esta misma semana en https://ispg.societyconference.com/v2/ y escribir a info@ispg.net preguntando por la cuota Student/Post-Doc y por si existe opcion virtual, porque ninguna de las dos cosas esta publicada en ningun sitio accesible.</t>
+          <t>Empieza en 8 dias. Si quisiera asistir en remoto o de ultima hora, escribir esta semana a la secretaria de ISPG: no hay ninguna tarifa publicada que podamos citar. Vigilar ispg.net/past-congresses el 5-oct-2026, porque la sede de WCPG 2027 suele anunciarse en la asamblea del propio congreso.</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -44929,7 +49344,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Tier 1, ispg.net/wcpg-2026 el 2026-09-14: sigue diciendo 'Registration for WCPG 2026 is now OPEN!' sin fecha de cierre, sin tabla de cuotas y SIN mencion alguna a asistencia virtual. ECIP Travel Award confirmado CERRADO (14-may-2026); su elegibilidad incluia literalmente 'medical student, post-doctoral researcher, or less than five years out of a doctoral program'. Cuotas 2026 siguen UNVERIFIED tras un segundo intento por otra puerta: ispg.societyconference.com/conf solo devuelve botones 'Register Now' sin tabla de precios (carga por JavaScript) e ispg.net/registration SIGUE mostrando el WCPG 2022 de Florencia. ANCLA HISTORICA, NO es la tarifa de 2026: en Florencia 2022 la categoria Student/Post-Doc fue 396 EUR early, 462 regular, 506 on-site, y el Education Day suelto 198 EUR. No insistir mas por via automatica.</t>
+          <t>ispg.net/wcpg-2026 abierta el 2026-09-21: confirma 29-sep a 03-oct-2026 en Glasgow y dice solo 'Registration is now OPEN'. NO publica tarifas ni tarifa late/onsite ni opcion virtual; el portal de inscripcion carga por JavaScript y no es legible por herramienta (tercer intento fallido, no insistir). WCPG 2027 NO esta anunciado: ispg.net/past-congresses solo lista 2026 como proximo. La ficha de Clocate titulada 'WCPG 2027' esta vacia, sin fechas ni ciudad: es un marcador, no un anuncio.</t>
         </is>
       </c>
     </row>
@@ -44986,7 +49401,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>396</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -45026,7 +49441,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -45036,7 +49451,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -45046,7 +49461,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>RELOJ VIVO: la tarifa anticipada sigue abierta hasta manana 15-sep-2026 a las 17:00 ET. Si va, hacerse socia student/trainee de ASHG ANTES de inscribirse: la cuota cae de 775 USD (~713 EUR) a 435 USD (~400 EUR), un ahorro de ~313 EUR que supera de largo la cuota de socia. A partir del 16-sep solo queda late/onsite, y no hay tarifa de un dia ni opcion virtual.</t>
+          <t>Descartar 2026: entre 396 y 710 EUR de inscripcion mas vuelo transatlantico y hotel en Montreal, sin abstract aceptado, no sale pagandolo ella. Apuntar a ASHG 2027 en Nashville (E-0012) y solo con travel award.</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -45061,7 +49476,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Tier 1, ashgmeeting.ashg.org/attend/register el 2026-09-14: la ventana anticipada (13-ago a 15-sep, 17:00 ET) NO ha cerrado todavia. Tabla completa en USD, anticipada/late: socio ASHG o Early Career 785/920; socio student-trainee 435/460; no socio 1.250/1.400; no socio student-trainee 775/825; emerito 290/290; RLC renta baja 0/0; RLC renta media-baja 310/310. Cost_EUR 715 se mantiene sobre la base no-socio trainee anticipada (775 USD x 0,92); por la via de socia serian ~400 EUR. Literal: 'Registration is for the full meeting; there is no one-day or exhibits-only registration.' El plazo de resumenes late-breaking (26-ago-2026) ya paso: el unico reloj vivo es el de inscripcion, y por eso la columna Deadline lleva esa fecha y no una de resumenes.</t>
+          <t>ashg.org/registration-rates abierta el 2026-09-21. Tramo Late/Onsite vigente desde que cerro Advance el 15-sep-2026 y hasta el congreso (20-24 oct 2026): socia estudiante/trainee 460 USD = 396 EUR; NO socia estudiante 825 USD = 710 EUR; socia profesional 920 USD = 791 EUR; no socia profesional 1400 USD = 1204 EUR. Conversion a ~0.86 EUR/USD. Cubre solo la inscripcion. La pagina de tarifas NO lista ninguna inscripcion virtual con precio: la existencia de opcion virtual queda SIN CONFIRMAR.</t>
         </is>
       </c>
     </row>
@@ -45154,7 +49569,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -45164,7 +49579,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -45174,7 +49589,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Plazo de resumenes abierto de par en par y a casi cinco meses vista: es el envio europeo mas planificable que tiene. Preparar el resumen en enero-2027 (notificacion a principios de abril, congreso en junio, ya fuera de la residencia). Vigilar 2027.eshg.org para cuotas y bursaries de jovenes investigadores, aun sin anunciar.</t>
+          <t>Su congreso grande mas alcanzable: hibrido, en la UE, sin visado. Marcar en calendario la apertura de sumision en diciembre-2026 y enviar abstract antes del 2027-02-04 a las 23:59 CET.</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -45189,7 +49604,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>Tier 1, 2027.eshg.org/abstracts el 2026-09-14: plazo regular literal 'Thursday, February 04, 2027 at 23:59 hrs CET', notificacion 'beginning of April 2027', congreso 12-15 jun 2027 en Rotterdam. La pagina NO anuncia todavia ronda late-breaking, ni cuotas, ni becas para 2027 (las que aparecen son las de 2026). Tier 2 (erdera.org) indica que esta planificado como evento HIBRIDO, lo que abriria una via barata de asistencia remota: sin confirmar en la web oficial.</t>
+          <t>2027.eshg.org/abstracts abierta el 2026-09-21: 12-15 jun 2027 en Rotterdam, formato hibrido, plazo de abstracts 2027-02-04 23:59 CET CONFIRMADO. La sumision regular abre en diciembre-2026 y la notificacion llega a primeros de abril-2027. Presentar en el congreso es obligatorio para que el abstract se publique en el European Journal of Human Genetics. Todavia no hay cuotas ni premios de viaje publicados.</t>
         </is>
       </c>
     </row>
@@ -45269,12 +49684,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -45284,17 +49699,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Vigilar bga.org (BGA Current Meeting) a partir de enero-2027: plazo de resumenes, web del congreso y plazo de student travel awards siguen como TBA.</t>
+          <t>Revisar bga.org en enero-2027: el plazo de abstracts de la BGA suele caer entre febrero y abril. Dato util de red: la presidenta de programa es Sarah Medland (QIMR), donde ella ya hizo estancia, y el anfitrion local es Scott Vrieze (U. Minnesota).</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -45309,7 +49724,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>bga.org reabierta el 2026-09-14: 29-jun a 2-jul-2027 en Minneapolis, local host Scott Vrieze, program chair Sarah Medland (la misma PI de L-0002, conexion calida de su estancia en QIMR). Plazo de resumenes, web del congreso, cuotas y becas de estudiante siguen TBA.</t>
+          <t>Pagina 'Future Meetings' de bga.org, leida el 2026-09-21 via buscador (el sitio es un portal de club y no se abre directo): 29-jun a 02-jul-2027 en Minneapolis. El plazo de abstracts, el programa y la inscripcion figuran explicitamente como TBA. Cuotas sin publicar.</t>
         </is>
       </c>
     </row>
@@ -45361,12 +49776,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>664</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -45406,7 +49821,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -45416,7 +49831,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -45426,7 +49841,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>RELOJ VIVO a 5 dias: la tarifa early de IGES cierra el 19-sep-2026 y desde el 20-sep sube a late. Solo tiene sentido moverla si YA ha decidido ir a ASHG 2026 (misma region, dias consecutivos); el plazo de resumenes cerro el 30-may-2026, asi que iria como oyente. Si no va a ASHG, dejarla pasar y apuntarla como objetivo 2027.</t>
+          <t>Nada que hacer para 2026: sin abstract y con viaje a Quebec, no sale. Lo que si merece la pena es hacerse socia estudiante de la IGES: es su sociedad natural, da la lista de correo por la que se anunciara la siguiente fase del GAW 2027 y abarata la inscripcion de IGES 2027.</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -45441,7 +49856,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>Tier 1, geneticepi.org/2026-annual-meeting el 2026-09-14 (primera apertura DIRECTA; antes solo se habia leido via buscador). Cuotas en USD, early/late-onsite: socio academia 826/918; socio jubilado-estudiante-renta baja 662/772; no socio academia 1.033/1.125; no socio estudiante-renta baja 772/882; Education Workshop 85. Ventana: early hasta el 19-sep, late del 20-sep al 20-oct. Cost_EUR 710 = 772 USD (no socio estudiante, early) x 0,92. La columna Deadline lleva el cierre de la tarifa early porque el plazo de resumenes ya vencio. AVISO DE FIABILIDAD: esa misma pagina devolvio al extraerla una linea suelta 'June 1-2, 2026' que contradice todo lo demas; las fechas 18-20-oct-2026 en Esterel estan confirmadas por la ficha oficial via buscador y por la propia ventana de inscripcion (que cierra el 20-oct), asi que la linea de junio se descarta como error de la pagina, no se adopta en silencio.</t>
+          <t>iges.memberclicks.net/2026-annual-meeting abierta el 2026-09-21: la inscripcion SIGUE ABIERTA en tramo Late/Onsite del 20-sep al 20-oct-2026. Socia estudiante/jubilada/bajos ingresos 772 USD = 664 EUR; no socia estudiante 882 USD = 759 EUR; socia academica 918 USD = 790 EUR; no socia profesional 1125 USD = 968 EUR. Education Workshop aparte, 85 USD = 73 EUR, en McGill. Conversion ~0.86 EUR/USD. El plazo de abstracts ya no figura (cerrado). Sin opcion virtual ni premios de viaje mencionados.</t>
         </is>
       </c>
     </row>
@@ -45521,12 +49936,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>VERIFIED en fechas y ciudad; UNVERIFIED en plazos y cuotas</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -45536,7 +49951,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -45546,7 +49961,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Revisar sobp.org en noviembre-2026 buscando la convocatoria de resumenes de 2027; entrar por sobp.org/meetings, porque la ruta /meetings/future-meetings NO existe.</t>
+          <t>Revisar sobp.org en noviembre-2026 para el call for abstracts. Prioridad baja: el tema de 2027 se aleja de su trabajo.</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -45561,7 +49976,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>Intento de verificacion el 2026-09-14 fallido: sobp.org/meetings solo muestra un indice con enlaces a 'Future Meetings' y a la reunion de 2017, sin fechas ni plazos, y sobp.org/meetings/future-meetings devuelve 404. Las fechas 6-8 may 2027 en Chicago siguen apoyadas SOLO en fuentes secundarias. La convocatoria de resumenes de 2027 sigue sin publicarse (en ediciones previas abre hacia oct-nov del ano anterior).</t>
+          <t>sobp.org/sobp-annual-meeting abierta el 2026-09-21: 6-8 may 2027 en Chicago. El tema anunciado es 'The Metabolic Brain - Reconceptualizing Mental Illnesses as Systemic Disorders through Metabolism', que queda lejos de la genetica estadistica: el encaje es mas bajo de lo que sugiere el nombre del congreso. La sumision que figura cerrada en la web es la de 2026; historicamente SOBP abre abstracts en otono y cierra en enero. Cuotas sin publicar.</t>
         </is>
       </c>
     </row>
@@ -45645,12 +50060,12 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>VERIFIED en fechas y sede; UNVERIFIED en cuotas</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -45660,7 +50075,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -45670,7 +50085,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Ya no hay via para presentar en 2026: solo cabe ir de oyente (cuota sin verificar) o esperar al proximo Sleep Europe, que por bienalidad tocaria en 2028. Dejar de gastar intentos en la pagina de resumenes de esrs.eu.</t>
+          <t>Si le interesa, tiene que abrir ella misma esrs.eu/sleep-congress/registration desde un navegador normal: es un bloqueo antibot, no una pagina caida. Por via automatica no hay forma de obtener el precio.</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -45680,12 +50095,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://esrs.eu/sleep-congress/abstracts/</t>
+          <t>https://congrex.com/events/sleep-europe-2026-the-28th-congress-of-the-european-sleep-research-society/</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>El intento anterior devolvio HTTP 403 en la pagina oficial de resumenes; en esta pasada se recupero su contenido a traves del buscador (esrs.eu/sleep-congress/abstracts) sin abrirla directamente, de ahi LIKELY. Sede confirmada: Maastricht (MECC), Paises Bajos, 20-23 oct 2026 (no Amsterdam). Plazo ordinario de resumenes 1-abr-2026 CERRADO y ventana de late breaking abstracts 1-jun a 31-jul-2026 17:00 CEST tambien CERRADA. Cuotas de inscripcion no verificadas.</t>
+          <t>Confirmado por segunda puerta el 2026-09-21, el PCO oficial (Congrex Switzerland): congreso HIBRIDO, 20-23 oct 2026, MECC Maastricht (Forum 100, 6229 GV). La tarifa early cerro el 2026-07-28. Ni Congrex ni los buscadores publican importes; la unica pagina con la tabla de cuotas es esrs.eu/sleep-congress/registration, que devuelve 403 a acceso automatizado por tercera semana. El caracter hibrido implica modalidad online, sin precio verificable.</t>
         </is>
       </c>
     </row>
@@ -45765,12 +50180,12 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>LIKELY</t>
+          <t>LIKELY en fechas; UNVERIFIED en plazo de abstracts</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -45780,7 +50195,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -45790,7 +50205,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Conflicto de fechas resuelto, no hace falta volver sobre el. Queda un solo reloj: la convocatoria de resumenes de SLEEP 2027, aun sin abrir. Revisar sleepmeeting.org/call-for-abstracts en noviembre-2026 (en la edicion 2026 cerro el 8-dic-2025). La inscripcion abre en enero-2027.</t>
+          <t>Volver a comprobar en noviembre-2026 usando la ficha de aasm.org, no sleepmeeting.org: el call for abstracts de SLEEP suele abrir en otono y cerrar el primer dia habil de diciembre.</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -45800,12 +50215,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>https://www.sleepmeeting.org/</t>
+          <t>https://aasm.org/event/sleep-2027/</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>CONFLICTO RESUELTO el 2026-09-14, y las dos fechas eran ciertas: describian cosas distintas. Los cursos de posgrado con entrada aparte son sabado y domingo 5 y 6 de junio, y la sesion general va de domingo a miercoles, 6 a 9 de junio de 2027; el 5-jun que teniamos era el arranque de los CURSOS, no del congreso. Se adopta 6-9 jun 2027 como congreso. Sede: Colorado Convention Center, Denver; 41a reunion anual de la APSS. LIKELY y no VERIFIED porque sleepmeeting.org devolvio contenido vacio al abrirla directamente (segunda pasada consecutiva: dejar de abrirla directamente) y el texto se obtuvo via buscador, coincidiendo con la ficha aasm.org/event/sleep-2027.</t>
+          <t>sleepmeeting.org no se abrio (bloqueo conocido, devuelve contenido vacio por tercera semana); usada la ficha de AASM como puerta alternativa. Se mantienen 6-9 jun 2027 en Denver como fechas del congreso; una fuente Tier 2 (eMedEvents) da la 41a reunion anual de APSS como 5-9 jun 2027 en el Colorado Convention Center, y ese dia extra suele ser la jornada de cursos previa, asi que no es contradiccion. Plazo de abstracts AUN NO PUBLICADO: solo circulan los de 2026.</t>
         </is>
       </c>
     </row>
@@ -46755,7 +51170,11 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
@@ -46789,32 +51208,32 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Abrir la noticia 'Call for Ideas: Genetic Analysis Workshop (GAW) 2027' en geneticepi.org para ver el plazo exacto de la convocatoria de ideas y quien coordina; despues vigilar geneticepi.org/meetings para sede, fechas y plazo de resumenes.</t>
+          <t>La convocatoria de IDEAS ya vencio: no hay nada que enviar. Lo siguiente es la convocatoria de PARTICIPACION, en la que los grupos se apuntan a los datos elegidos, y se anunciara en geneticepi.org y en la lista de correo de la IGES: vigilar esa pagina cada mes. Merece la pena entrar cuando abra, porque el GAW es trabajo colaborativo con publicacion conjunta y es una via realista de coautoria para quien aun no tiene publicaciones destacadas.</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -46825,7 +51244,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>Detectado el 2026-09-14 como titular de 'latest news' en la portada de geneticepi.org mientras se verificaba el E-0005, y confirmado como entrada existente en el buscador. UNVERIFIED de forma deliberada: NO se abrio la noticia, asi que no se conocen plazo de la convocatoria, sede, fechas ni cuotas, y ninguno de esos datos se inventa aqui. Lo unico que se afirma es que la convocatoria de ideas para GAW 2027 existe y esta publicada por la IGES. La URL apunta a la portada y no al enlace largo de la noticia porque ese enlace lleva parametros de sesion.</t>
+          <t>geneticepi.org, seccion 'latest news', abierta el 2026-09-21. CERRADO lo que quedaba pendiente: la convocatoria de ideas del GAW 2027 cerro el 2026-09-04, hace 17 dias. Era una llamada de IDEAS de datos y preguntas de analisis, no de abstracts, por formulario de Google. Coordina Danny Panyard desde la IGES; su correo aparece ofuscado en la pagina y no se transcribe. El GAW vuelve en 2027 tras haberse interrumpido por falta de financiacion. Fechas y sede del GAW 2027 aun sin especificar.</t>
         </is>
       </c>
     </row>
@@ -46945,8 +51364,400 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>E-0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EPA 2027 - 35th European Congress of Psychiatry</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Congress</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>European Psychiatric Association</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Florence</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2027-04-03</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2027-04-06</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Si - travel grants para early career, se solicitan DENTRO de la propia sumision del abstract</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Psiquiatras, investigadores en salud mental, early career psychiatrists</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>ES EL UNICO EVENTO DE TODO EL MAPA CON EL PLAZO ABIERTO HOY, Y ES TAMBIEN EL UNICO CON DINERO ATADO AL PLAZO: los travel grants de early career se piden marcando una casilla DENTRO de la sumision del abstract, no despues, asi que enviar hoy es la unica via de que el viaje salga gratis. Lo que gana: Florencia es un vuelo corto y barato desde Malaga, sin visado; el congreso tiene 56 topicos entre ellos neurociencia y genetica, asi que un e-poster de GWAS/PRS de trastornos psiquiatricos entra sin forzar nada; y le pone su trabajo delante de psiquiatras europeos con grupo propio, que para una medica que busca postdoc clinico-genetico son mas utiles que un publico puramente metodologico. Material ya lo tiene: los dos manuscritos en revision. En contra: es un congreso clinico enorme y la visibilidad por poster es baja. El riesgo real es el calendario, NO el encaje: no hay late-breaking, asi que si no envia hoy pierde la edicion 2027 entera.</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>HOY 21-sep-2026: enviar el abstract por el sistema online (no se aceptan por correo) y marcar la casilla de travel grant en la misma sumision. Notificacion a mediados de diciembre-2026. OJO si la aceptan: el autor presentador debe confirmar e inscribirse antes del 2027-02-01 o cae del programa.</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>https://epa-congress.org/abstract-submission/</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>epa-congress.org/abstract-submission abierta el 2026-09-21: fechas, sede, plazo de hoy, ausencia de late-breaking, early bird 2027-01-27 y confirmacion del presentador 2027-02-01 leidos todos en la pagina oficial. Las cuotas de inscripcion no estan publicadas; la inscripcion abre el 2027-01-27, que es tambien el cierre de early bird, de ahi que Cost_EUR quede vacio en vez de inventado. El ano pasado la EPA extendio el plazo tres dias anunciandolo en su cuenta de X, asi que si se pasa de hoy conviene mirar si hay extension, pero la pagina oficial NO promete ninguna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>E-0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Probabilistic Modeling in Genomics 2027 (ProbGen 2027)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Methods conference</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Cold Spring Harbor Laboratory</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cold Spring Harbor NY</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2027-03-01</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2027-03-04</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2027-01-08</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Desconocido</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Desarrolladores de metodos en genetica estadistica y de poblaciones</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>El temario incluye explicitamente 'Quantitative Genetics and Association Mapping', que es su linea 1, y los organizadores (Nandita Garud, Adam Siepel, Yun Song) son nombres centrales de la genetica estadistica. El freno es que es una reunion de gente que DESARROLLA metodos y ella es usuaria de PLINK y R: 804-1088 EUR mas vuelo a Nueva York no se sostienen pagandolo ella. La jugada sensata es la inscripcion VIRTUAL de estudiante, 168 EUR, que da orales por Zoom, galeria de posters, el Slack del congreso y el archivo de video.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>XS virtual / M presencial</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Decidir antes del 2027-01-08 si envia abstract; si no, inscripcion virtual de estudiante (plazo estandar de inscripcion 2027-02-25, 17:00 ET).</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>https://meetings.cshl.edu/meetings.aspx?meet=PRGEN</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>meetings.cshl.edu abierta el 2026-09-21. Precios originales en USD a ~0.86 EUR/USD: paquete estudiante presencial sin alojamiento 935 USD = 804 EUR; con alojamiento 1265 USD = 1088 EUR; VIRTUAL para estudiante de posgrado 195 USD = 168 EUR, que es el importe cargado en Cost_EUR. La ficha aparece etiquetada como 'past event' por un artefacto de la plantilla web, pero fechas, plazos y paquetes de 2027 estan publicados y son coherentes. CSHL recomienda que quien presente asista en persona.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>E-0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Epigenomics of Common Diseases 2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Conference (hibrida)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Wellcome Connecting Science</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Hinxton (Cambridge)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-11-06</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Si, bursaries de hasta el 50% de la cuota, pero exigian abstract y cerraron el 2026-08-03</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Investigadores en epigenomica, enfermedad compleja, desarrollo y envejecimiento</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Tangencial a sus tres lineas y con los dos plazos que importaban ya vencidos: este ano solo podria ir de oyente.</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Si quiere escuchar, inscribirse en virtual antes del 2026-10-26 por 63 EUR. Lo importante de esta fila no es 2026: es poner en seguimiento el calendario de conferencias de Wellcome Connecting Science para cazar 'Genomics of Brain Disorders' 2027-2028 con tiempo de pedir bursary, que cierra unos 3 meses antes del evento.</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>https://coursesandconferences.wellcomeconnectingscience.org/event/epigenomics-of-common-diseases-20261104/</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Pagina oficial del evento abierta el 2026-09-21. Precios originales en GBP a ~1.15 EUR/GBP: virtual estudiante 55 GBP = 63 EUR (importe cargado); virtual academico 105 GBP = 121 EUR; presencial estudiante tarifa late 429 GBP = 493 EUR mas 240 GBP = 276 EUR por noche de alojamiento en campus. La presencial tardia cierra el 2026-10-05 y la virtual el 2026-10-26. Se ficha sobre todo porque descubre el patron util: las conferencias de esta serie son baratas para estudiantes, estan en Europa, tienen modalidad virtual y dan bursaries priorizando doctorandos. La edicion 2026 de 'Genomics of Brain Disorders', que si es su tema, fue el 16-18 sep 2026 y ya paso.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Z19"/>
+  <autoFilter ref="A1:Z22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -46957,7 +51768,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -46974,7 +51785,7 @@
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="51" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
@@ -47146,7 +51957,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Solo el ISCEP (Regeneron Genetics Center), restringido a nacionales Y residentes de paises de renta baja o media-baja: ella NO es elegible. Ninguna otra exencion publicada.</t>
+          <t>Programa ISCEP financiado por el Regeneron Genetics Center, mas apoyo de la subvencion NIMH MH19918; existe inscripcion anticipada para quien necesita visado. NO hay beca individual localizada para ella.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -47171,12 +51982,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>VERIFIED en fechas y formato; UNVERIFIED en coste</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -47186,7 +51997,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -47196,7 +52007,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>La inscripcion 2027 AUN NO ESTA ABIERTA. Revisar colorado.edu/ibg/workshop-2027 a partir de noviembre-2026 (en ediciones previas abrio unos 3 meses antes) y reservar presupuesto propio de ~600 USD de cuota academica.</t>
+          <t>La inscripcion NO ha abierto y no hay tarifa publicada. Revisar colorado.edu/ibg/workshop-2027 cada 3-4 semanas desde noviembre-2026, o escribir a IBGworkshop@colorado.edu pidiendo aviso de apertura. Recordar que este taller de marzo se imparte cada TRES anos: perder 2027 significa esperar a 2030.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -47211,7 +52022,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Pagina oficial del taller 2027 leida el 2026-09-14: confirma 'March 1 - March 5, 2027' en Boulder y advierte que 'the syllabus has yet to be decided upon'; NO publica cuota, plazo ni formulario. La pagina general (colorado.edu/ibg/workshop) confirma que la semana de marzo en Boulder es el Latent Genetics Course, que se imparte cada tres anos (2024, 2027, 2030) -- si se pierde 2027, la siguiente es 2030. Cost_EUR 550 sigue siendo ESTIMACION a partir de los 600 USD de cuota academica de 2024, no un dato de 2027.</t>
+          <t>Pagina oficial del taller 2027 abierta el 2026-09-21: 1-5 mar 2027, presencial en Boulder, eje 'latent genetic modeling', con PRS, randomizacion mendeliana, GenomicSEM, GREML y potencia estadistica en el temario. Sin enlace de inscripcion y sin tarifa: los 550 EUR de esta fila siguen siendo ESTIMACION. La tarifa academica de 2024 fue 600 USD, solo como referencia historica. Las URL colorado.edu/ibg/international-workshop y /isg-workshop dan 404; el patron vivo es workshop-AAAA.</t>
         </is>
       </c>
     </row>
@@ -47293,7 +52104,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -47303,7 +52114,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -47313,7 +52124,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ACCION INMINENTE Y CON DOS FECHAS: crear o reactivar la cuenta de reservas desde el mediodia del 2026-09-23 (dentro de 9 dias) y reservar plaza el 2026-10-07 a mediodia hora del RU, cuando abren las reservas de todo el programa 2026/27.</t>
+          <t>Crear YA la cuenta de reservas (disponible desde el 23-sep-2026) y reservar el 7-oct-2026 a las 12:00 hora del RU, que es cuando abren las reservas del programa 2026/27.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -47323,12 +52134,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/genetic-epidemiology/</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Catalogo oficial de cursos cortos de Bristol leido el 2026-09-14: confirma '27-29 January and 1-3 February 2027' (dos bloques). Confirmado tambien el dato clave de la rama, literal: 'From midday on Wednesday 23 September 2026 you will be able to register/re-register a short course booking account' y 'Bookings for the 2026/27 short course programme open midday Wednesday 7 October 2026'. La politica general es 'bookings close two weeks before the start of each course', coherente con el plazo 2027-01-13. AVISO DE RUTA: el catalogo ha cambiado de direccion; bristol.ac.uk/medical-school/study/short-courses/ redirige a /short-courses-and-cpd/short-courses/courses/.</t>
+          <t>Listado oficial 2026/27 de Bristol abierto el 2026-09-21: el curso son DOS bloques, 27-29 ene y 1-3 feb 2027. Deadline = dos semanas antes del inicio, regla general de Bristol. La tarifa individual solo se ve abriendo la pagina del curso, no comprobada esta semana. OJO: las URL con /study/short-courses/ redirigen 302 a /short-courses-and-cpd/short-courses/.</t>
         </is>
       </c>
     </row>
@@ -47410,7 +52221,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -47420,7 +52231,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -47430,7 +52241,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>ACCION INMINENTE: cuenta de reservas desde el 2026-09-23 a mediodia y reserva el 2026-10-07 a mediodia. Este va ANTES que T-0007, porque es su prerrequisito.</t>
+          <t>Crear la cuenta de reservas ya y reservar el 7-oct-2026 a las 12:00 RU.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -47440,12 +52251,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>http://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/mr/</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Catalogo oficial de Bristol leido el 2026-09-14: 'Mendelian Randomization, 15-19 March 2027'. Plazo derivado de la politica publicada 'bookings close two weeks before the start of each course'.</t>
+          <t>Listado oficial 2026/27 de Bristol abierto el 2026-09-21: 15-19 mar 2027. Deadline = dos semanas antes del inicio. Tarifa individual sin comprobar esta semana.</t>
         </is>
       </c>
     </row>
@@ -47510,12 +52321,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>VERIFIED (negativo)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -47525,17 +52336,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Volver a mirar en enero-2027; si para entonces no hay convocatoria 2027, bajar la cadencia de revision a trimestral y no redescubrirlo</t>
+          <t>Una sola revision en enero-2027 y, si sigue sin haber edicion, CERRAR la fila en vez de arrastrarla.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -47550,7 +52361,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Catalogo de Wellcome Connecting Science reabierto el 2026-09-14: solo lista dos cursos ('Accelerating Translation of Biodata to Impact', 22-24 sep 2026, y 'Scalable Genomics and Pangenomics', 11-16 oct 2026), ambos con plazos ya cerrados. NO hay edicion 2026 ni 2027 de 'Genetic Analysis of Population-based Association Studies'. Sigue como elemento de vigilancia; proxima comprobacion en enero-2027.</t>
+          <t>Catalogo de Wellcome Connecting Science revisado el 2026-09-21: solo muestra ediciones de este curso hasta septiembre-2025 y el listado de cursos proximos ofrece unicamente dos de 2026 (Accelerating Translation of Biodata to Impact, 22-24 sep 2026, y Scalable Genomics and Pangenomics, 11-16 oct 2026). NINGUN curso de 2027 anunciado: es un negativo verificado, no un fallo de busqueda.</t>
         </is>
       </c>
     </row>
@@ -47795,7 +52606,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Online en directo</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -47815,12 +52626,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>725</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sin beca ni exencion aplicable; coste integro a su cargo.</t>
+          <t>Ninguna localizada para ella: los cinco packs de vales de Bristol excluyen su caso</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -47850,7 +52661,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -47860,7 +52671,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -47870,7 +52681,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>NO reservable en la practica para 2026: exige haber hecho antes el curso introductorio de MR, que ella hara en marzo-2027. Objetivo real: la edicion de noviembre-2027. Aun asi, confirmar en octubre-2026 si aceptan 'equivalente' con experiencia propia en MR.</t>
+          <t>EL RELOJ MAS CERCANO DE ESTA PESTANA. Crear la cuenta de reservas desde el 23-sep-2026 y reservar el 7-oct-2026 a las 12:00 RU. No puede estar agotado todavia porque las reservas no han abierto.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -47881,7 +52692,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Ficha oficial leida el 2026-09-14: 25-27 nov 2026, cuota 630 GBP (= 737 EUR a 1,17), reservas abren el 2026-10-07 a mediodia y cierran dos semanas antes del inicio. Prerrequisito EXPLICITO: haber completado el curso introductorio de MR o equivalente y tener experiencia haciendo analisis de MR. Se trabaja en R, con Posit Cloud como alternativa.</t>
+          <t>Pagina oficial del curso abierta el 2026-09-21: 630 GBP = ~725 EUR a 1.15 (antes figuraban 737 EUR). Las reservas cierran dos semanas antes del inicio, de ahi el 2026-11-11. Formato online.</t>
         </is>
       </c>
     </row>
@@ -47959,7 +52770,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -47969,7 +52780,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -47990,7 +52801,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Fechas confirmadas en el catalogo oficial de Bristol el 2026-09-14 ('22-24 June 2027'). Plazo derivado de la politica publicada de cierre dos semanas antes. La ficha propia del curso todavia no existe: /machine-learning-with-omics-data/ y /machine-learning-omics/ devuelven 404. Referencia de precio: los otros cursos de 3 dias del programa estan en 630-750 GBP.</t>
+          <t>Listado oficial 2026/27 de Bristol abierto el 2026-09-21: 22-24 jun 2027. Deadline = dos semanas antes. Tarifa sin publicar en el listado.</t>
         </is>
       </c>
     </row>
@@ -48072,7 +52883,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -48082,7 +52893,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -48103,7 +52914,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Ficha oficial leida el 2026-09-14: 22-24 marzo 2027, 750 GBP (= 878 EUR a 1,17), online en directo, practicas en R via Posit Cloud, acceso a grabaciones 5 meses. Temario: diseno de estudios moleculares, interpretacion biologica de metilacion/metabolitos/expresion/proteinas, biomarcadores, inferencia causal y MR.</t>
+          <t>Listado oficial 2026/27 de Bristol abierto el 2026-09-21: 22-24 mar 2027. Deadline = dos semanas antes.</t>
         </is>
       </c>
     </row>
@@ -48243,11 +53054,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Toscana, Italia (presencial, residencial)</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+          <t>Florencia, Italia</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2027-07-05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2027-07-09</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
@@ -48256,7 +53075,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>No consta beca ni exencion en la pagina de inscripcion; la cuota incluye docencia, materiales, alojamiento compartido y comidas, y baja 250-345 EUR en modalidad no residencial.</t>
+          <t>Ninguna localizada: la pagina no menciona becas ni exenciones</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -48286,38 +53105,38 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Revisar eepe.org en enero-2027: la edicion 2027 se anunciara con el curso residencial (mediados de junio a principios de julio) y los especializados la semana siguiente. Compararla entonces con el MR de Bristol de marzo-2027, que cubre parte del mismo terreno mas barato.</t>
+          <t>La inscripcion abre en NOVIEMBRE-2026 y no hay fecha de cierre publicada: volver a mirar a primeros de noviembre e inscribirse en cuanto abra. Contacto: eepe@eepe.org.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>https://www.eepe.org/courses-2/</t>
+          <t>https://www.eepe.org/registration-2-2/</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>eepe.org/courses-2/ y eepe.org/registration-2-2/ leidas el 2026-09-14 (Tier 1). Edicion 2026: curso residencial de 3 semanas del 15-jun al 3-jul-2026 (3.965 EUR, fuera de alcance por duracion) y cursos especializados de 5 dias del 6 al 10 de julio de 2026, entre ellos este, a 1.575 EUR en regimen residencial compartido; habitacion individual +595 a +750 EUR. Cuotas en euros, sin conversion. La edicion 2027 NO esta anunciada: las fechas se dejan vacias a proposito en vez de extrapolar. La web no publica fechas limite ni becas; el contacto es eepe@eepe.org.</t>
+          <t>Pagina oficial del EEPE abierta el 2026-09-21: el modulo especializado Genetic and Epigenetic Epidemiology cae en la semana del 5-9 jul 2027, en Florencia, con docentes de Queensland y Bristol. Los 1575 EUR son la banda BAJA de un rango 1575-1715 EUR segun alojamiento, e incluyen matricula, materiales, alojamiento y comidas. Secretaria en ISGlobal Barcelona.</t>
         </is>
       </c>
     </row>
@@ -48344,7 +53163,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sonderborg, Dinamarca (presencial, residencial)</t>
+          <t>Sandbjerg Gods, Sonderborg, Dinamarca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -48352,12 +53171,12 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>632</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>No consta beca ni exencion.</t>
+          <t>Ninguna localizada</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -48382,32 +53201,32 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>Coste VERIFIED; fechas 2027 UNVERIFIED</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UPDATED</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>No hay convocatoria abierta. Escribir a smartbiomed_info@au.dk en enero-2027 preguntando si habra edicion y en que fechas; si la hay, es candidata de primera linea.</t>
+          <t>Revisar en enero-febrero 2027, cuando historicamente publican el plazo (2025 cerro el 19-abr y 2026 el 12-abr).</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -48418,7 +53237,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Pagina oficial leida el 2026-09-14 (ultima revision del sitio: 2026-08-04, sin anuncio posterior a 2025). Edicion 2025: 23-27 jun 2025 en Sandbjerg Gods, cuota 4.718,75 DKK con IVA (= 633 EUR a 7,46 DKK/EUR), plazo 19-abr-2025, cuatro modulos en paralelo (Introduction to Statistical Genetics, R Package Development, Introduction to Causal Inference, Applied Machine Learning with Python). Fechas de una edicion futura: NO anunciadas, no se extrapolan.</t>
+          <t>smartbiomed.dk/news-and-events/summer-school abierta el 2026-09-21: la pagina fue actualizada por ultima vez el 2026-08-04 y solo detalla la edicion 2025 (23-27 jun 2025, 4718.75 DKK con IVA = ~632 EUR, incluyendo todas las comidas y habitacion individual; tema 'Causal inference, statistical genetics, and machine learning'; docentes Florian Prive, Michael Sachs, Erin Gabriel, Andrey Kormilitzin). Las fechas 21-25 jun 2027 proceden de UN SOLO extracto de buscador atribuido a esa misma pagina y NO se ven en ella: no se cargan como dato.</t>
         </is>
       </c>
     </row>
@@ -48523,8 +53342,444 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T-0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SSGAC/CESR Social-Science Genetics Methods Workshop</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Social Science Genetic Association Consortium (SSGAC) con CESR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Taller online (serie)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>No aplica si se confirma que es gratuito; sin coste publicado</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Cierra de lleno dos huecos suyos, metodologia PRS moderna e inferencia causal, y lo hace en el unico formato que su calendario admite: online y por sesiones sueltas, sin pedir dias libres en plena residencia. Lo imparte el entorno de De Vlaming y Okbay, que es gente de referencia en prediccion poligenica. Coste sin confirmar, asi que no se puede decir si necesita financiacion, pero los talleres de esta serie suelen ser gratuitos: relacion esfuerzo-beneficio muy alta para una sesion de una tarde.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Entrar en thessgac.org/events y apuntarse a la sesion del 15-oct-2026; comprobar de paso si la serie continua en 2027.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>https://www.thessgac.org/events</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Pagina oficial de eventos del SSGAC consultada el 2026-09-21: figura como proximo evento. No hay coste ni plazo publicados, de ahi LIKELY. La summer school presencial del SSGAC no tiene edicion anunciada desde la de Amsterdam de julio-2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T-0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Reproducible Health Data Science</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>University of Bristol, Bristol Medical School</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Curso corto</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2027-01-21</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2027-01-26</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2027-01-07</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Ninguna localizada</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Cubre en parte su hueco de flujos de trabajo reproducibles y computacion a escala, pero el eje es R y no Python, y choca de calendario con Genetic Epidemiology (T-0002), que empieza el 27 de enero: encadenarlos son diez dias de clase seguidos en plena residencia.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>VERIFIED en fechas; UNVERIFIED en tarifa</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Abrir la pagina del curso despues del 7-oct-2026 para ver la tarifa y decidir junto con T-0002, no por separado.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Listado oficial 2026/27 de Bristol abierto el 2026-09-21: dos bloques, 21-22 y 25-26 ene 2027. Cierra dos semanas antes del inicio. Tarifa no visible en el listado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T-0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Causal Inference in Epidemiology: Concepts and Methods</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>University of Bristol, Bristol Medical School</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Curso corto</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2027-06-28</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2027-07-02</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2027-06-14</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Ninguna localizada</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Solapa conceptualmente con los dos cursos de randomizacion mendeliana (T-0003 y T-0007), asi que es alternativa y no complemento: solo tiene sentido si renuncia a esos dos.</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>VERIFIED en fechas; UNVERIFIED en tarifa</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Valorar solo si descarta los dos cursos de MR. Choca ademas con la semana del modulo del EEPE (T-0011, 5-9 jul 2027).</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/medical-school/short-courses-and-cpd/short-courses/courses/</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Listado oficial 2026/27 de Bristol abierto el 2026-09-21: 28-jun a 2-jul 2027. Cierra dos semanas antes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T-0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Federated analysis for polygenic risk score calculations</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMBL-EBI Training</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Curso</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sin confirmar (online o Hinxton)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sin confirmar; EMBL-EBI suele ser gratuito o de bajo coste</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Si se confirma, es metodologia PRS moderna, que es su hueco principal, en el proveedor mas barato del mapa (comparese con T-0013, que es gratuito). Se ficha UNVERIFIED y no se descarta precisamente para que no haya que redescubrirlo: el dato que falta es fecha y formato, no el encaje.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Que ella abra la URL en un navegador normal, o buscar la URL canonica del curso por otra puerta: ebi.ac.uk/training/events entra en bucle de redirecciones y no es accesible por herramienta.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>https://www.ebi.ac.uk/training/events/federated-analysis-polygenic-risk-score-calculations/</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Solo aparece en resultados de buscador el 2026-09-21; la pagina NO se ha podido abrir por el bucle de redirecciones conocido de ebi.ac.uk/training/events. Fila deliberadamente UNVERIFIED: existencia no confirmada.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W14"/>
+  <autoFilter ref="A1:W18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -49958,7 +55213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -50961,8 +56216,60 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SUB-0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CNCR / VU Amsterdam - alerta de empleo por email</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>https://cncr.nl/cncr/jobs/</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>GROUPS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aviso por correo de cada vacante nueva del CNCR, el centro donde esta el grupo Complex Trait Genetics de Danielle Posthuma (L-0001), por departamento.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>L-0001 es Fit 5 y su unica via es el correo en frio porque nunca anuncia nada en su propia pagina: la alerta sustituye el barrido semanal a ciegas y avisa el dia que CTG publique algo, que es el momento en que el correo en frio deja de ser en frio.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Pagina abierta y verificada el 2026-09-21 por la rama de grupos: la alerta suscribible existe en esa pagina. Alta que la dueña tiene que hacer ella; la rutina no se suscribe en su nombre.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J19"/>
+  <autoFilter ref="A1:J20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/research.xlsx
+++ b/docs/research.xlsx
@@ -23,17 +23,17 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'action_now'!$A$1:$L$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'postdocs'!$A$1:$AD$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'jobs'!$A$1:$AB$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'fellowships'!$A$1:$AB$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'groups'!$A$1:$Z$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'events'!$A$1:$Z$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'training'!$A$1:$W$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'watchlist_closed'!$A$1:$L$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'subscriptions'!$A$1:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'sources'!$A$1:$J$202</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'inbox_triage'!$A$1:$I$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$391</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'changelog'!$A$1:$H$442</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'readme'!$A$1:$B$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
@@ -2044,7 +2044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J188"/>
+  <dimension ref="A1:J202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -11823,8 +11823,736 @@
         </is>
       </c>
     </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>SRC-0188</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>JobTech Dev - API abierta de Platsbanken (Arbetsformedlingen, portal estatal sueco de empleo)</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>https://jobsearch.api.jobtechdev.se/search</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Todas las vacantes publicadas en Platsbanken, el portal publico nacional de Suecia, incluidas las de Karolinska Institutet, Uppsala, Goteborg, Estocolmo y SLU, con fecha de publicacion, fecha de cierre, municipio, empleador, URL del anuncio y, via /ad/&lt;id&gt;, el TEXTO COMPLETO del anuncio en JSON.</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>GET /search?q=&lt;terminos&gt;&amp;limit=15 ; detalle GET /ad/&lt;id&gt; ; usar terminos suecos ('postdoktor', 'genomik', 'epidemiologi', 'biostatistik') y nombres de empleador: la busqueda libre es difusa y 'GWAS' o 'polygenic' devuelven 0 resultados.</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>NUEVA 2026-09-28. Sin autenticacion, sin bloqueos, sin JavaScript: la fuente mas amable para un agente de todas las probadas en esta rama. Cobertura topica delgada (7 consultas -&gt; 2 filas utiles), porque los postdocs suecos de genetica psiquiatrica se anuncian con titulos genericos tipo 'Postdoktor'. Sirve tambien para la rama 4 (empleo clinico e industria en Suecia).</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>SRC-0189</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Jobnet.dk - portal publico de empleo de Dinamarca</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>https://job.jobnet.dk/CV/FindWork</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Vacantes publicas danesas; seria el rodeo natural al bloqueo 403 de international.au.dk (Aarhus: iPSYCH, NCRR, QGG).</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>SearchString=postdoc genetics (probado tambien /CV/FindWork/SearchAPI)</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>nunca</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>BLOQUEO DURO 2026-09-28: toda ruta de busqueda responde 301 y acaba en https://nemlog-in.mitid.dk/error, es decir exige identificacion MitID danesa. Inutilizable por un agente y probablemente tambien por la duena sin MitID. NO volver a gastar llamadas aqui; para Dinamarca hay que buscar otro rodeo (agregadores o paginas de departamento).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>SRC-0190</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Starfatorg - tablon estatal de empleo de Islandia (ahora en Island.is)</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>https://island.is/starfatorg</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Plazas del Estado islandes, incluida la Universidad de Islandia, donde esta el grupo de Unnur Valdimarsdottir (ERC StressGene, ya registrado como P-0004).</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>buscador de la pagina; probado ?s=postdoctoral y ?s=nydoktor</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>mensual</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>BLOQUEO PARCIAL 2026-09-28: starfatorg.is redirige (301) a island.is/starfatorg, una pagina Next.js de 1,2 MB cuyos listados se cargan por cliente y NO aparecen en __NEXT_DATA__, asi que un fetch plano no devuelve ni un titulo. Queda sin explorar la API GraphQL de island.is; si alguna pasada futura la encuentra, Islandia se abre. Mientras tanto, para Islandia sigue sirviendo EURAXESS (asi salio P-0004).</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>SRC-0191</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>AcademicTransfer - busqueda por palabra clave (patron de URL que si funciona)</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>https://www.academictransfer.com/en/jobs/?q=statistical%20genetics</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Vacantes de universidades, UMCs e institutos de los Paises Bajos (Erasmus MC, VU Amsterdam / Netherlands Twin Register, Amsterdam UMC, KNAW) con fecha de publicacion y de cierre en el propio listado.</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Parametro ?q= sobre /en/jobs/ con el termino entre comillas URL-encoded: ?q=statistical%20genetics, ?q=genetic%20epidemiology, ?q=postdoc%20genetics. Orden y facetas academico/no academico disponibles en la pagina. NO usar /en/search/ ni /en/jobs/search/: ambos devuelven 404, que es el 404 que arrastrabamos.</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Encargo de la semana pasada resuelto. Comprobado el 2026-09-28: /en/jobs/?q=... responde 200 y renderiza los resultados en HTML plano (no hace falta JS). El 2026-09-28 la busqueda 'statistical genetics' daba 5 resultados y ninguno relevante (plantas, leucodistrofias); 'psychiatric' daba 0. El buscador es laxo: filtra por texto libre, no por campo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>SRC-0192</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Nature Careers - busqueda por palabra clave (parametro correcto) y patron de URL de ficha</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/jobs?keywords=psychiatric%20genetics</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Listado filtrado de Nature Careers con facetas de disciplina, tipo de puesto, pais, banda salarial y titulacion (PhD/MD), util para barrer 'statistical genetics', 'psychiatric genetics', 'polygenic' y 'sleep genetics'.</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>?keywords=&lt;termino&gt; sobre /naturecareers/jobs. OJO: el parametro ?q= se ignora y devuelve el listado generico. Las fichas solo se abren con el patron /naturecareers/job/&lt;id-numerico&gt;/&lt;slug&gt;/; la forma /naturecareers/job/&lt;slug-largo&gt; devuelve HTTP 400 y los sourceId antiguos dan 404 en la API.</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Distinto de SRC-0003, que solo guarda el dominio sin query. Comprobado el 2026-09-28 con curl y user-agent de navegador: 200 y HTML plano. Consecuencia practica: las URL de fichas guardadas en filas antiguas (P-0003, P-0011) ya no son recuperables; hay que reconstruirlas desde la busqueda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>SRC-0193</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>University of Edinburgh - API Oracle de reclutamiento, patron de consulta que SI devuelve vacantes</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>https://elxw.fa.em3.oraclecloud.com/hcmRestApi/resources/latest/recruitingCEJobRequisitions</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Todas las vacantes vivas de la Universidad de Edimburgo con titulo, id, fecha de publicacion y campus; el detalle completo (descripcion, salario, grupo, PI) se saca luego de recruitingCEJobRequisitionDetails con finder=ById;Id="&lt;id&gt;",siteNumber=CX_1</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>?onlyData=true&amp;expand=requisitionList&amp;finder=findReqs;siteNumber=CX_1,keyword=&lt;palabra&gt;,limit=50,sortBy=POSTING_DATES_DESC -- LA CLAVE ES expand=requisitionList: sin ese parametro la API responde 200 y da TotalJobsCount correcto pero requisitionList vacio, que es exactamente por lo que el 14-09 parecia que solo habia mejora genetica de Easter Bush. Palabras probadas: genetics (8), genomics (4), psychiatr (0)</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Resuelve el encargo A3. Descarga con curl y parseo con python3, no con fetch de pagina: ed.ac.uk/jobs solo sirve el armazon. A 2026-09-28 Edimburgo NO tiene nada de genetica psiquiatrica ni estadistica: 'psychiatr' da 0 y los ocho hits de 'genetics' son epigenetica humeda (Sproul, Institute of Genetics and Cancer), cromosomas de germinal en mosca (Ross) y mejora genetica vegetal/animal de Easter Bush.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>SRC-0194</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>King's College London - buscador propio, juego de terminos utiles</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/search</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Vacantes de KCL con titulo, referencia, facultad/directorate y fecha de cierre; el listado por si solo ya sirve como Tier 1 para existencia y plazo</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>?term=IoPPN (11 plazas, 5 de ellas etiquetadas IoPPN); ?term=genetics (55); ?term=statistical%20genetics (4, el filtro mas rentable del perfil); ?term=sleep (1); ?term=polygenic (0, no usar)</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Completa el encargo A1. Ojo: term=IoPPN devuelve 11, no ~15, y solo 5 llevan la etiqueta IoPPN -- el resto son de otras facultades que mencionan el instituto. Se pagina de 10 en 10, asi que term=genetics (55) exige paginar; 'statistical genetics' es el atajo que evita esa paginacion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SRC-0195</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>QIMR Berghofer - listado completo de vacantes (portal TurboRecruit)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>https://qimrberghofer.turborecruit.com.au/</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Indice de todas las vacantes vivas del instituto con titulo, referencia y enlace a la ficha; a 2026-09-28 hay 6 en total</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>raiz del portal, sin filtro: el volumen es tan bajo que se lee entero de una vez</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Fuente de institucion directa con via de contacto real (estancia previa de la candidata). Sirve ademas para cerrar filas por ausencia: si una referencia ya no figura aqui, esta cerrada. qimrberghofer.edu.au redirige 301 a qimrb.edu.au, pero el portal turborecruit responde bien. Las fichas NO publican fecha de cierre en el indice, hay que abrirlas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>SRC-0196</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Hospital del Mar Research Institute (IMIM) - convocatorias temporales</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>http://www.imim.cat/ofertes/es_convocatories-temporals.html</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Convocatorias temporales del IMIM, centro de la red CIBERSAM con programa de neurociencias y genetica psiquiatrica</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>listado completo de convocatorias temporales</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>BLOQUEADA AL FETCH AUTOMATICO. imim.es redirige 302 a imim.cat y imim.cat devuelve 403. Solo utilizable a mano en navegador. No volver a gastar presupuesto en el fetch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SRC-0197</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron Institut de Recerca (VHIR) - ofertas de trabajo</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>https://vhir.vallhebron.com/en/talent/job-opportunities</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Convocatorias del VHIR, centro CIBERSAM; es la casa del grupo de genetica psiquiatrica de Marta Ribases (TDAH), el objetivo mas afin del perfil en Espana</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>listado completo de job opportunities</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>RESPONDE 200 PERO SE RENDERIZA CON JAVASCRIPT: el HTML servido es solo el armazon de la seccion y no contiene ninguna vacante. No cuenta como fuente que funcione via fetch. Alternativas a explorar la semana que viene sin volver a esta URL: el listado de VHIR en InfoJobs (vhir.ofertas-trabajo.infojobs.net) o su pagina de empresa en LinkedIn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SRC-0198</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Illumina - API publica de su portal de empleo Workday</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>https://illumina.wd1.myworkdayjobs.com/wday/cxs/illumina/illumina-careers/jobs</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Todas las vacantes de Illumina en JSON legible por un agente, con titulo, localizacion y antiguedad del anuncio. Resuelve el problema de que el portal de Illumina es una SPA que no sirve las ofertas en el HTML: este endpoint si las sirve, en una sola llamada POST</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>POST con cuerpo JSON {"appliedFacets":{},"limit":20,"offset":0,"searchText":"&lt;termino&gt;"}; probar searchText 'genetics', 'statistical', 'population genetics', 'bioinformatics'</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Comprobado el 2026-09-28: searchText 'genetics' devuelve 14 resultados, dominados por ventas; lo unico cientificamente cercano son Senior Bioinformatics Scientist y Bioinformatics Scientist/Engineer DRAGEN Array en Cambridge (Reino Unido) y Director Clinical Bioinformatics en San Diego. Ninguna vacante de genetica estadistica. El mismo patron de URL sirve para cualquier empleador que use Workday, sustituyendo el tenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>SRC-0199</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Servicio Aragones de Salud - bolsas de empleo temporal de personal sanitario</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>https://www.aragon.es/-/personal-sanitario-2</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Indice de las bolsas de empleo temporal abiertas y permanentes del Servicio Aragones de Salud por categoria, incluida la de Facultativo Especialista de Area en Analisis Clinicos y Bioquimica Clinica, con las resoluciones y los actos centralizados de adjudicacion</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Buscar las categorias 'Analisis Clinicos y Bioquimica Clinica' y 'Laboratorio Clinico'</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Aragon no estaba en la base hasta esta pasada; de aqui sale la fila nueva de bolsa permanente de FEA. Vigilar si la categoria se reconvierte a Laboratorio Clinico por el Real Decreto 101/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SRC-0200</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Astursalud - noticias y bolsas de empleo del SESPA</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>https://www.astursalud.es/noticias</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Resoluciones de creacion y gestion de las bolsas de empleo del Servicio de Salud del Principado de Asturias, incluida la nueva categoria de FEA de Laboratorio Clinico creada por resolucion de 02-12-2025</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Buscar 'bolsa de empleo' y 'Laboratorio Clinico'</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Anadida sin abrir la pagina en esta pasada: la pista llego por una nota del sindicato USIPA. Primera tarea al usarla, verificar el mecanismo y el plazo de inscripcion de la bolsa de FEA de Laboratorio Clinico</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SRC-0201</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SEMEDLAB (Sociedad Espanola de Medicina de Laboratorio) - ofertas laborales</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>https://semedlab.es/ofertas-laborales/</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Bolsa de empleo de la sociedad de SU especialidad: plazas de facultativo especialista en Analisis Clinicos / Bioquimica Clinica y de jefatura adjunta de laboratorio en hospitales y laboratorios privados de toda Espana. A 2026-09-28 hay 10 ofertas vivas (Granollers, Pamplona, Majadahonda, Coslada, Ciudad Real, Vigo, Burjassot, Valdebebas, Alcobendas, Manresa). Es el carril clinico privado, complementario a las bolsas y oposiciones de las CCAA que ya cubre la rama 4 y a AEGH-empleo (SRC-0156), que es de genetica.</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>listado completo de /ofertas-laborales/; abrir cada oferta para sacar fecha, contrato y contacto, porque el indice no los muestra</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>semanal</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Alta 2026-09-28 por la rama 5 (fuente nueva de la semana). ADVERTENCIA de uso: el indice NO publica fecha de alta ni plazo de ninguna oferta, asi que la novedad no es detectable desde el listado — hay que comparar la lista con la de la semana anterior o abrir cada ficha. La sociedad es el resultado de la fusion de las tres sociedades espanolas de medicina de laboratorio (antes SEQC-ML); el dominio antiguo seqc.es sigue publicando ofertas sueltas en su seccion de actualidad, que NO es este listado.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J188"/>
+  <autoFilter ref="A1:J202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11955,7 +12683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H391"/>
+  <dimension ref="A1:H442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -28078,8 +28806,2150 @@
       </c>
       <c r="H391" t="inlineStr"/>
     </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>P-0041</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Postdoctor in Bioinformatics and Cancer Genetics</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 1. Fit 2, Confidence LIKELY, Status OPEN, plazo: 2026-10-10</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>https://arbetsformedlingen.se/platsbanken/annonser/31459110</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>P-0042</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Postdoktor - modelos celulares de leucemia definidos geneticamente (TP53), Institutionen for immunologi, genetik och patologi</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 1. Fit 2, Confidence LIKELY, Status OPEN, plazo: 2026-10-07</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>https://arbetsformedlingen.se/platsbanken/annonser/31455640</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>P-0043</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Postdoc in Statistical Genetics - Casale Group</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 2. Fit 3, Confidence LIKELY, Status OPEN, plazo: 2026-11-04</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/12864992/postdoc-in-statistical-genetics-casale-group/</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>P-0044</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>GLAD-NI Research Fellow (estudio GLAD-MHG, NIHR BioResource)</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 2. Fit 2, Confidence LIKELY, Status OPEN, plazo: 2026-10-05</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSX751/glad-ni-research-fellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>P-0045</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Computational Senior Research Fellow (proyecto ERC-Synergy MUTAHOME)</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 2. Fit 1, Confidence LIKELY, Status OPEN, plazo: 2026-10-17</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DTB231/computational-senior-research-fellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>P-0046</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Post-doctoral Research Associate in Machine Learning for Mental Health (proyecto PROSPECT, UKRI)</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 3. Fit 3, Confidence VERIFIED, Status OPEN, plazo: 2026-10-18</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/159026-post-doctoral-research-associate-in-machine-learning-for-mental-health</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>P-0047</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Research Associate in MND Genetics</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 3. Fit 2, Confidence VERIFIED, Status OPEN, plazo: 2026-10-05</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/159106-research-associate-in-mnd-genetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>P-0048</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Clinical Research Fellow (IoPPN)</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 3. Fit 2, Confidence LIKELY, Status OPEN, plazo: 2026-10-07</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/158285-clinical-research-fellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>P-0049</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Research Officer/Senior Research Officer - Cardiovascular Disease Prevention Group (ref. BV000085)</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 3. Fit 2, Confidence VERIFIED, Status OPEN, plazo: 2026-10-09</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>https://qimrberghofer.turborecruit.com.au/job/job_details.cfm?id=582956</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>P-0050</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Postdoctoral Position in Genetic Epidemiology of Alzheimer Disease</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 5. Fit 4, Confidence LIKELY, Status OPEN, plazo: sin plazo: el anuncio dice 'the position will remain open until filled'</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>https://iges.memberclicks.net/assets/Postdoc%20position%20at%20Boston%20University-June2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>P-0051</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Scientist en genomica estadistica y psiquiatria (Center for Precision Psychiatry)</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 5. Fit 3, Confidence LIKELY, Status ROLLING, plazo: sin fecha de cierre: el anuncio no publica plazo alguno</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>https://iges.memberclicks.net/postdoc-may2026-columbiauniversity</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>P-0052</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Fellow en genomica y multi-omica de trastornos mentales graves</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 5. Fit 3, Confidence UNVERIFIED, Status OPEN, plazo: 2026-10-15</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466098370/</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>P-0053</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Research Associates in Statistical Genetics (2 plazas)</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 5. Fit 3, Confidence LIKELY, Status CLOSED, plazo: 2026-04-12</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>https://jobs.le.ac.uk/vacancies/13082/research-associate-2-posts-available.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>P-0054</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow in Integrative Molecular Epidemiology</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 5. Fit 2, Confidence UNVERIFIED, Status OPEN, plazo: no publicado en el tablon</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>https://iges.memberclicks.net/assets/Lunenfeld-Tanenbaum_Research_Institute-post_doc_job%20posting_2603.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>P-0055</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Bioinformatician / Computational Biology</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 5. Fit 2, Confidence UNVERIFIED, Status OPEN, plazo: no publicado en el tablon</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>https://iges.memberclicks.net/bioinformatician-switzerland-jan2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>P-0029</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Fellow/Research Fellow in Statistical Genomics (R-68861)</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Confidence, Deadline, Duration, Fit_1_5, Fit_Rationale, Last_Verified, Next_Action, Open_Date, Requirements_Key, Salary_EUR_Year, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>https://uq.wd3.myworkdayjobs.com/uqcareers/job/St-Lucia-Campus/Postdoctoral-Research-Fellow-Research-Fellow-in-Statistical-Genomics_R-68861-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>P-0019</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow in Neurogenetics</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, City, Confidence, Deadline, Last_Verified, Next_Action, Salary_EUR_Year, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>https://jobs.sciencecareers.org/job/679674/postdoctoral-fellow-in-neurogenetics/</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>P-0003</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow in Psychiatric Genomics</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Confidence, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/postdoctoral-fellow-in-psychiatric-genomics-icahn-school-of-medicine-at-mount-sinai-ismms-mshs-754125</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>P-0011</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Postdoctoral positions in human population genetics, complex disease and cancer</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Confidence, Next_Action, Source_Note, Status</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/postdoctoral-positions-in-human-population-genetics-complex-disease-and-cancer-in-new-york-city-usa-albert-einstein-college-of-medicine-einstein-757285</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>P-0008</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Computational Scientist I - McCarroll Lab</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Confidence, Last_Verified, Next_Action, Status, URL</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>https://broadinstitute.avature.net/careers</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>P-0017</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Research Officer - Experimental Biology and Surveillance Innovation</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Confidence, Last_Verified, Next_Action, Status</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>https://qimrberghofer.turborecruit.com.au/job/job_details.cfm?id=581998</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>P-0036</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Research Scientist - Maternal Sleep</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Confidence, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/158385-research-scientist-maternal-sleep</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>P-0022</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Clinical Research Associate (farmacogenomica clinica)</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Source_Note</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>https://iaejup.fa.ocs.oraclecloud.com/hcmUI/CandidateExperience/en/sites/UOA-Careers/job/3142/</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>postdocs</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>P-0002</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Scientist in Statistical Genomics / Genetic Epidemiology</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Confidence, Deadline, Duration, Last_Verified, Next_Action, Salary_EUR_Year, Source_Note, Start_Date, Status</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>https://recruitingapp-5569.de.umantis.com/Vacancies/496/Description/2?lang=eng</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>J-0016</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Bolsa de empleo temporal abierta y permanente del Servicio Aragones de Salud - Facultativo Especialista de Area en Analisis Clinicos y Bioquimica Clinica</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 4. Fit 4, Confidence LIKELY, Status ROLLING, plazo: Sin fecha de cierre: la inscripcion es permanente. Los cortes de valoracion y los actos centralizados de adjudicacion se celebran periodicamente; el ultimo acto centralizado publicado es del 26-05-2026 y las listas provisionales de admitidos/excluidos son de la resolucion de 17-12-2025</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>https://www.aragon.es/-/analisis-clinicos-y-bioquimica-clinica-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>J-0017</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Bolsa de empleo de Facultativo Especialista de Area de Laboratorio Clinico del SESPA (Asturias), creada por resolucion de 02-12-2025</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 4. Fit 4, Confidence UNVERIFIED, Status ROLLING, plazo: No consta en la fuente consultada si la inscripcion es permanente o por ventanas: ESE ES EL DATO QUE FALTA</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>https://usipa.es/creacion-bolsa-empleo-fea-de-laboratorio-clinico/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>J-0018</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Concurso-oposicion 2026 de Facultativo Especialista de Area en Laboratorio Clinico del Servicio Navarro de Salud-Osasunbidea (Resolucion 1515E/2026, 3 plazas nivel A)</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 4. Fit 3, Confidence LIKELY, Status CLOSED, plazo: La ficha marca el expediente como 'En resolucion' y no publica las fechas del plazo de solicitudes, lo que indica que el plazo ya se cerro; no se inventa fecha</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>https://www.navarra.es/es/tramites/on/-/line/facultativo-especialista-de-area-en-laboratorio-clinico-concurso-oposicion-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>J-0019</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Junior Medical Science Liaison - talent pipeline de Medical Affairs de IQVIA en Madrid (Job ID R1523392)</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 4. Fit 4, Confidence UNVERIFIED, Status ROLLING, plazo: No hay plazo: es un pipeline de talento abierto, no una convocatoria con cierre</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>https://www.biotecnika.com/medical-science-liaison-job-at-iqvia-spain/</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>J-0020</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Senior Statistical Geneticist (remoto en Estados Unidos)</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>Alta en la pasada positions 2026-09-28, rama 4. Fit 2, Confidence VERIFIED, Status OPEN, plazo: El anuncio no publica fecha de cierre; el formulario de Greenhouse sigue activo</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/bridgebio/jobs/5179747007</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>J-0003</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Via transitoria al titulo de especialista en Genetica Medica y en Genetica de Laboratorio (dos reales decretos separados, aun sin publicar)</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Confidence, Fit_Rationale, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>https://www.sanidad.gob.es/normativa/audiencia/home.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>J-0010</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Bolsa de Empleo Abierta y Permanente (BAPE) de Sacyl - categoria Licenciados Especialistas (incluye Analisis Clinicos y Bioquimica Clinica)</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Confidence, Fit_Rationale, Last_Verified, Next_Action</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>https://www.saludcastillayleon.es/profesionales/es/bolsa</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>J-0002</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Bolsa Unica de Empleo del SAS - inscripcion como Facultativo Especialista de Area (Laboratorio Clinico)</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Last_Verified, Source_Note</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>https://www.sspa.juntadeandalucia.es/servicioandaluzdesalud/profesionales/ofertas-de-empleo/bolsa-de-empleo</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>J-0007</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Convocatorias de empleo FIMABIS / IBIMA-Plataforma BIONAND (portal RFGI-SSPA)</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Last_Verified, Source_Note</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>https://www.rfgi.es/ConvocatoriasPropiasFIMABIS/es/Convocatorias/DesgloseEstadoTipoConvocatoria/FIMAB_EM</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>J-0008</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Seleccion temporal de FEA del SERGAS (listas de contratacion, Galicia)</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Last_Verified, Source_Note</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>https://www.sergas.gal/Recursos-Humanos/Emprego-publico-Seleccion-temporal?idioma=es</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>J-0011</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Borsa de treball de l'Institut Catala de la Salut - facultatiu/iva especialista</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>Columnas tocadas: Change_Flag, Last_Verified, Source_Note</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>https://ics.gencat.cat/ca/lics/treballeu-a-lics/treball-temporal/borsa-de-treball/</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>SRC-0188</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>JobTech Dev - API abierta de Platsbanken (Arbetsformedlingen, portal estatal sueco de empleo)</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Todas las vacantes publicadas en Platsbanken, el portal publico nacional de Suecia, incluidas las de Karolinska Institutet, Uppsala, Goteborg, Estocolmo y SLU,  | query: GET /search?q=&lt;terminos&gt;&amp;limit=15 ; detalle GET /ad/&lt;id&gt; ; usar terminos suecos ('postdoktor', 'genomik', 'epidemiologi'</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>https://jobsearch.api.jobtechdev.se/search</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>SRC-0189</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Jobnet.dk - portal publico de empleo de Dinamarca</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Vacantes publicas danesas; seria el rodeo natural al bloqueo 403 de international.au.dk (Aarhus: iPSYCH, NCRR, QGG). | query: SearchString=postdoc genetics (probado tambien /CV/FindWork/SearchAPI)</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>https://job.jobnet.dk/CV/FindWork</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>SRC-0190</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Starfatorg - tablon estatal de empleo de Islandia (ahora en Island.is)</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Plazas del Estado islandes, incluida la Universidad de Islandia, donde esta el grupo de Unnur Valdimarsdottir (ERC StressGene, ya registrado como P-0004). | query: buscador de la pagina; probado ?s=postdoctoral y ?s=nydoktor</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>https://island.is/starfatorg</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>SRC-0191</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>AcademicTransfer - busqueda por palabra clave (patron de URL que si funciona)</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Vacantes de universidades, UMCs e institutos de los Paises Bajos (Erasmus MC, VU Amsterdam / Netherlands Twin Register, Amsterdam UMC, KNAW) con fecha de public | query: Parametro ?q= sobre /en/jobs/ con el termino entre comillas URL-encoded: ?q=statistical%20genetics, ?q=genetic%20epidemi</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>https://www.academictransfer.com/en/jobs/?q=statistical%20genetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>SRC-0192</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Nature Careers - busqueda por palabra clave (parametro correcto) y patron de URL de ficha</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Listado filtrado de Nature Careers con facetas de disciplina, tipo de puesto, pais, banda salarial y titulacion (PhD/MD), util para barrer 'statistical genetics | query: ?keywords=&lt;termino&gt; sobre /naturecareers/jobs. OJO: el parametro ?q= se ignora y devuelve el listado generico. Las ficha</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/jobs?keywords=psychiatric%20genetics</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>SRC-0193</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>University of Edinburgh - API Oracle de reclutamiento, patron de consulta que SI devuelve vacantes</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Todas las vacantes vivas de la Universidad de Edimburgo con titulo, id, fecha de publicacion y campus; el detalle completo (descripcion, salario, grupo, PI) se  | query: ?onlyData=true&amp;expand=requisitionList&amp;finder=findReqs;siteNumber=CX_1,keyword=&lt;palabra&gt;,limit=50,sortBy=POSTING_DATES_DE</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>https://elxw.fa.em3.oraclecloud.com/hcmRestApi/resources/latest/recruitingCEJobRequisitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>SRC-0194</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>King's College London - buscador propio, juego de terminos utiles</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Vacantes de KCL con titulo, referencia, facultad/directorate y fecha de cierre; el listado por si solo ya sirve como Tier 1 para existencia y plazo | query: ?term=IoPPN (11 plazas, 5 de ellas etiquetadas IoPPN); ?term=genetics (55); ?term=statistical%20genetics (4, el filtro m</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/search</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>SRC-0195</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>QIMR Berghofer - listado completo de vacantes (portal TurboRecruit)</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Indice de todas las vacantes vivas del instituto con titulo, referencia y enlace a la ficha; a 2026-09-28 hay 6 en total | query: raiz del portal, sin filtro: el volumen es tan bajo que se lee entero de una vez</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>https://qimrberghofer.turborecruit.com.au/</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>SRC-0196</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Hospital del Mar Research Institute (IMIM) - convocatorias temporales</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Convocatorias temporales del IMIM, centro de la red CIBERSAM con programa de neurociencias y genetica psiquiatrica | query: listado completo de convocatorias temporales</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>http://www.imim.cat/ofertes/es_convocatories-temporals.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>SRC-0197</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Vall d'Hebron Institut de Recerca (VHIR) - ofertas de trabajo</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Convocatorias del VHIR, centro CIBERSAM; es la casa del grupo de genetica psiquiatrica de Marta Ribases (TDAH), el objetivo mas afin del perfil en Espana | query: listado completo de job opportunities</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>https://vhir.vallhebron.com/en/talent/job-opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>SRC-0198</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Illumina - API publica de su portal de empleo Workday</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuente nueva. Todas las vacantes de Illumina en JSON legible por un agente, con titulo, localizacion y antiguedad del anuncio. Resuelve el problema de que el portal de Illumi | query: POST con cuerpo JSON {"appliedFacets":{},"limit":20,"offset":0,"searchText":"&lt;termino&gt;"}; probar searchText 'genetics', </t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>https://illumina.wd1.myworkdayjobs.com/wday/cxs/illumina/illumina-careers/jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>SRC-0199</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Servicio Aragones de Salud - bolsas de empleo temporal de personal sanitario</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Indice de las bolsas de empleo temporal abiertas y permanentes del Servicio Aragones de Salud por categoria, incluida la de Facultativo Especialista de Area en  | query: Buscar las categorias 'Analisis Clinicos y Bioquimica Clinica' y 'Laboratorio Clinico'</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>https://www.aragon.es/-/personal-sanitario-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>SRC-0200</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Astursalud - noticias y bolsas de empleo del SESPA</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Resoluciones de creacion y gestion de las bolsas de empleo del Servicio de Salud del Principado de Asturias, incluida la nueva categoria de FEA de Laboratorio C | query: Buscar 'bolsa de empleo' y 'Laboratorio Clinico'</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>https://www.astursalud.es/noticias</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>sources</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>SRC-0201</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>SEMEDLAB (Sociedad Espanola de Medicina de Laboratorio) - ofertas laborales</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>Fuente nueva. Bolsa de empleo de la sociedad de SU especialidad: plazas de facultativo especialista en Analisis Clinicos / Bioquimica Clinica y de jefatura adjunta de laborat | query: listado completo de /ofertas-laborales/; abrir cada oferta para sacar fecha, contrato y contacto, porque el indice no lo</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>https://semedlab.es/ofertas-laborales/</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>SUB-0020</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Platsbanken (Arbetsformedlingen) - aviso por correo de busqueda guardada</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Propuesta, Status TODO. Correo con las vacantes nuevas de todo el sector publico sueco que casen con una busqueda guardada ('postdoktor', 'genomik', 'epidemiologi', 'biostatistik', 'Ka</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>https://arbetsformedlingen.se/platsbanken</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>positions</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>subscriptions</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>SUB-0021</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Genomics England - avisos por correo de nuevas vacantes</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Propuesta, Status TODO. Aviso por correo cada vez que Genomics England abre una vacante, con seleccion de departamentos en el propio formulario (interesan Bioinformatics Research Servi</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>https://www.genomicsengland.co.uk/careers/open-positions</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H391"/>
+  <autoFilter ref="A1:H442"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -28485,7 +31355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD41"/>
+  <dimension ref="A1:AD56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28846,17 +31716,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3 anos</t>
+          <t>3 anos (fixed-term)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>73999-91055 bruto (incl. 8% de paga de vacaciones), segun experiencia</t>
+          <t>73999,91-91055,27 EUR/ano segun experiencia, incluido el 8% de subsidio de vacaciones</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-12-01 (negociable)</t>
+          <t>2026-12-01 (inicio propuesto en el anuncio)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -28871,7 +31741,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>sin fecha de cierre publicada; la pagina institucional marca 'DEADLINE HAS PASSED' en las demas vacantes y esta NO lo lleva, luego sigue abierta sin plazo</t>
+          <t>sin fecha de cierre en la ficha institucional, pero el tablon de la ISPG (Tier 2) precisa ahora que la revision de candidaturas empieza el 2026-10-08: hay ventana efectiva, no plazo formal</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -28911,7 +31781,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -28921,7 +31791,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -28931,7 +31801,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Sigue viva tras un mes. Es la unica ROLLING de su linea exacta: escribir a Language and Genetics (MPI Nijmegen) presentandose como MD con pipeline GWAS/PRS propio y preguntar si aceptan incorporacion en 2028 (defensa ETA feb-2028); si contestan que no esperan tanto, pedir que la avisen de la siguiente convocatoria.</t>
+          <t>URGENTE respecto a semanas anteriores: el tablon de la ISPG (Tier 2) dice que la revision de candidaturas arranca el 08-10-2026, asi que el "sin plazo" de esta fila tiene fecha efectiva a diez dias. Escribir YA a Beate St Pourcain (beate.stpourcain@mpi.nl), sin candidatura formal, con dos preguntas: si el inicio propuesto (01-12-2026) admite diferirse a mediados de 2027 o a 2028, y si confirma la fecha del 08-10. El gancho es el solapamiento exacto con sus lineas 1-3 (genetica estadistica de rasgos complejos, GWAS/PRS y genetica del sueno infantil) mas el combo MD+PhD. CHOQUE DE CALENDARIO SERIO: el anuncio propone empezar el 01-12-2026 y ella no esta libre hasta el 22-05-2027, ni con el doctorado defendido hasta febrero de 2028 (ETA).</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -28946,7 +31816,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>Reverificada 2026-09-21 en Tier 1: www.mpi.nl/career-education/vacancies la sigue listando como unica vacante sin 'DEADLINE HAS PASSED'. Ficha: https://www.mpi.nl/career-education/vacancies/vacancy/3-year-postdoctoral-research-scientist-position-statistical-0 ; la solicitud se envia por el formulario umantis de la columna URL.</t>
+          <t>Reverificada 2026-09-21 en Tier 1 (www.mpi.nl/career-education/vacancies la listaba como unica vacante sin 'DEADLINE HAS PASSED'). 2026-09-28, rama 5: el tablon de empleo de la ISPG (SRC-0030) reproduce la plaza con salario 73.999,91-91.055,27 EUR (coincide con la fila) y anade un dato NUEVO que no estaba en la ficha institucional: 'rolling review beginning October 8, 2026'. Ese dato es Tier 2 y no se ha confirmado en el dominio del MPI, por lo que Last_Verified y Confidence no se tocan. | 2026-09-28, rama 3: abierta ademas la ficha del portal umantis (Tier 1), que confirma la plaza viva, sin fecha de cierre, en linea desde el 12-08-2026, 3 anos, 73.999,91-91.055,27 EUR/ano e inicio propuesto el 01-12-2026. De ahi que Last_Verified y VERIFIED si suban: lo que queda sin confirmar en el dominio del MPI es unicamente la fecha del 08-10-2026.</t>
         </is>
       </c>
     </row>
@@ -29048,7 +31918,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -29058,7 +31928,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>Sigue sin verificar. El buscador de Nature Careers ignora el parametro q= (devuelve el listado generico de anuncios recientes, sin ningun resultado de genetica estadistica), asi que no se puede comprobar si el anuncio continua activo. Probar la pagina de carreras de Mount Sinai directamente (mejor via rama 3) o la landing por disciplina de Nature Careers.</t>
+          <t>El anuncio de Nature Careers ya NO se puede recuperar: la URL guardada devuelve HTTP 400 y la API de Nature responde 404 'job not found (jobId: 754125)', lo que apunta a que la oferta se ha retirado del tablon. En paralelo, la pagina del Mullins Lab sigue declarando plazas abiertas de postdoc y staff scientist con contacto niamh.mullins@mssm.edu (no se pudo abrir: labs.icahn.mssm.edu devuelve 403). Conflicto declarado, no resuelto. Accion para la duena: escribir directamente a niamh.mullins@mssm.edu preguntando por plazas de 2027-2028, con el gancho MD+PhD y GWAS/PRS psiquiatricos; visado J-1/H-1B a negociar.</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -29073,7 +31943,7 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Rama 2 (tablones academicos), via Nature Careers (SRC-0003). El fetch directo devolvio HTTP 400 y labs.icahn.mssm.edu 403: los datos proceden solo de resumenes de resultados de busqueda, de ahi UNVERIFIED.</t>
+          <t>Re-verificacion intentada el 2026-09-28 por tres vias: URL guardada de Nature Careers (HTTP 400), API de Nature por sourceId 754125 (404) y pagina del laboratorio (403 Akamai). Last_Verified NO se sube: no se abrio ninguna pagina Tier 1.</t>
         </is>
       </c>
     </row>
@@ -29272,7 +32142,7 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>-460</v>
+        <v>-466</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -29418,7 +32288,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -29560,7 +32430,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-143</v>
+        <v>-149</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -29725,12 +32595,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -29740,7 +32610,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -29750,7 +32620,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>Abrir a mano el buscador de broadinstitute.avature.net y filtrar por McCarroll para confirmar si la plaza sigue viva; el listado no es navegable por agente dentro de presupuesto.</t>
+          <t>RECUPERADA: la sospecha de la semana pasada era un artefacto de la paginacion. Recorriendo el portal Avature con jobOffset (0, 6, 12, 18, 24, 30) la plaza aparece viva en el tramo jobOffset=24 con la referencia 22042. Deja de estar UNVERIFIED y vuelve a OPEN con URL directa. Sin fecha de cierre publicada, asi que no hay urgencia de plazo: leer la ficha y decidir si se escribe al McCarroll Lab.</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -29760,7 +32630,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>https://broadinstitute.avature.net/careers</t>
+          <t>https://broadinstitute.avature.net/en_US/careers/JobDetail/Computational-Scientist-I-McCarroll-Lab/22042</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -29825,7 +32695,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-214</v>
+        <v>-220</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -30120,7 +32990,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -30130,7 +33000,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>Sigue sin verificar por la misma razon que P-0003: la busqueda por palabra clave de Nature Careers no filtra. Intentar la pagina de empleo de Albert Einstein College of Medicine (rama 3).</t>
+          <t>Mismo patron que P-0003: la URL de Nature Careers devuelve HTTP 400 y la API responde 404 'job not found (jobId: 757285)', probable retirada del anuncio. No hay confirmacion independiente de que la plaza siga abierta. Pendiente para la rama 3: abrir el portal de empleo propio del Albert Einstein College of Medicine y cerrar o confirmar la fila.</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -30145,7 +33015,7 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>Rama 2, Nature Careers (SRC-0003); fetch bloqueado (HTTP 400), contenido solo desde el resumen de busqueda.</t>
+          <t>Re-verificacion intentada el 2026-09-28 (Nature Careers, URL y API). Last_Verified sin cambio: no se abrio pagina Tier 1.</t>
         </is>
       </c>
     </row>
@@ -30217,7 +33087,7 @@
         </is>
       </c>
       <c r="O13" t="n">
-        <v>-18</v>
+        <v>-24</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -30355,7 +33225,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-15</v>
+        <v>-21</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -30489,7 +33359,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>-4</v>
+        <v>-10</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -30619,7 +33489,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-25</v>
+        <v>-31</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -30749,7 +33619,7 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -30869,7 +33739,7 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
@@ -30911,27 +33781,27 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>Sin accion. La jugada real en QIMR es la via de contacto personal, no el portal.</t>
+          <t>Ya no figura en el listado completo de vacantes de QIMR Berghofer (a 2026-09-28 solo hay 6 y esta no esta). Cerrada, sin coste: salio del mismo listado que se abrio para el resto de la rama.</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -31006,7 +33876,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -31118,7 +33988,11 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>no publicada: 'Salary Commensurate With Experience'</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
@@ -31126,7 +34000,14 @@
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>14</v>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Doctorado (o MD) y experiencia en genetica/genomica; anuncio dice salario acorde a experiencia</t>
@@ -31159,39 +34040,39 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>LIKELY</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
+          <t>UPDATED</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>Sigue abierta con plazo publicado 2026-10-11, incompatible con su disponibilidad (residencia hasta 05-2027, doctorado ETA 02-2028). Interesa como precedente: el NIA reabre plazas intramurales de neurogenetica con regularidad; revisar en 2027.</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>Abrir a mano en navegador el anuncio 679674 de Science Careers antes de 2026-10-31 para capturar laboratorio, PI y correo de contacto, y guardarlos como gancho para escribir en Q3 2027</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
           <t>https://jobs.sciencecareers.org/job/679674/postdoctoral-fellow-in-neurogenetics/</t>
@@ -31199,7 +34080,7 @@
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>Rama 2. Aparece en el buscador de Science Careers (query 'statistical genetics', 2026-09-07); la pagina de detalle devuelve HTTP 403 al fetch, un solo intento, no verificado.</t>
+          <t>jobs.sciencecareers.org (SRC-0004), Tier 2: anuncio abierto y leido el 2026-09-28, 'Closing date Oct 11, 2026'. La fecha no se pudo cruzar con la pagina del NIH porque www.training.nih.gov devuelve 403 (SRC-0149), por eso Confidence LIKELY y no VERIFIED.</t>
         </is>
       </c>
     </row>
@@ -31615,12 +34496,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -31640,7 +34521,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>Rama 5 (buzon y novedad), tablon de empleo de la ISPG (SRC-0030) el 2026-09-07. Los datos proceden del anuncio reproducido en el tablon de la ISPG; no se abrio el portal Oracle de la universidad, por eso UNVERIFIED.</t>
+          <t>Rama 5 (buzon y novedad), tablon de empleo de la ISPG (SRC-0030) el 2026-09-07 y reconfirmada alli el 2026-09-28: sigue publicada con el mismo salario (CAD 76.135-85.660) y sin plazo. Los datos proceden del anuncio reproducido en el tablon de la ISPG; el portal Oracle de la Universidad de Alberta sigue sin abrirse (renderizado por JavaScript), asi que Last_Verified y Confidence no se suben.</t>
         </is>
       </c>
     </row>
@@ -31712,7 +34593,7 @@
         </is>
       </c>
       <c r="O24" t="n">
-        <v>-112</v>
+        <v>-118</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -32255,7 +35136,7 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -32379,7 +35260,7 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -32393,7 +35274,7 @@
         </is>
       </c>
       <c r="O29" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -32442,12 +35323,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -32463,7 +35344,7 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Re-verificado el 2026-09-21 por DOS ramas y con una discrepancia de confianza que se deja escrita en vez de resolverse en silencio. Rama 2 abrio la ficha DSU830 de jobs.ac.uk (Tier 2): sigue abierta, cierre 2026-09-23, publicada el 2026-09-03 por Medical &amp; Molecular Genetics de KCL, salario GBP 46.189-51.174 con London Weighting, y aparece ademas bajo la palabra clave 'polygenic'. Rama 3 vio en el buscador propio de KCL (Tier 1) un Bioinformatician (oferta 157045, Faculty of Life Sciences &amp; Medicine, Guy's Hospital) con la MISMA fecha de cierre, casi con seguridad la misma plaza, pero no abrio la ficha individual. Se fija Confidence = LIKELY (dos fuentes independientes coinciden) y no VERIFIED, porque nadie llego a leer la ficha Tier 1 completa.</t>
+          <t>Re-verificado el 2026-09-21 por DOS ramas y con una discrepancia de confianza que se deja escrita en vez de resolverse en silencio. Rama 2 abrio la ficha DSU830 de jobs.ac.uk (Tier 2): sigue abierta, cierre 2026-09-23, publicada el 2026-09-03 por Medical &amp; Molecular Genetics de KCL, salario GBP 46.189-51.174 con London Weighting, y aparece ademas bajo la palabra clave 'polygenic'. Rama 3 vio en el buscador propio de KCL (Tier 1) un Bioinformatician (oferta 157045, Faculty of Life Sciences &amp; Medicine, Guy's Hospital) con la MISMA fecha de cierre, casi con seguridad la misma plaza, pero no abrio la ficha individual. Se fija Confidence = LIKELY (dos fuentes independientes coinciden) y no VERIFIED, porque nadie llego a leer la ficha Tier 1 completa. | Cerrada el 2026-09-28 por vencimiento del plazo publicado (2026-09-23), ya contrastado en una pasada anterior; no se ha vuelto a abrir la ficha, asi que Last_Verified no se toca.</t>
         </is>
       </c>
     </row>
@@ -32510,12 +35391,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>hasta 2,5 anos, jornada completa</t>
+          <t>hasta 2,5 anos, contrato temporal a tiempo completo</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>61700-82100 aprox (AUD 106294-113660 nivel A / AUD 119463-141545 nivel B, mas 17% de superannuacion)</t>
+          <t>A$106.293,57-113.659,72 (Nivel Academico A) o A$119.462,94-141.545,09 (Nivel B) + 17% de superannuation; cifras en dolares australianos, sin conversion a euros</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -32531,15 +35412,15 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Doctorado (se admiten tanto recien doctorados como postdocs con recorrido); desarrollo de metodos estadisticos para datos genomicos y omicos de celula unica a gran escala, identificacion de variacion causal, prediccion de fenotipos y priorizacion de genes en poblaciones geneticamente diversas; se espera transitar hacia laboratorio propio en 5 anos y, en nivel B, liderar solicitudes de financiacion; supervision de estudiantes</t>
+          <t>Doctorado en genetica estadistica, genetica cuantitativa, biologia computacional, estadistica, ciencia de datos o disciplina muy proxima. Plaza ofertada a Nivel A o B segun trayectoria; pensada para quien quiera montar programa propio y dirigir laboratorio en cinco anos. Institute for Molecular Bioscience, campus St Lucia</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -32549,7 +35430,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Es genetica estadistica de rasgos complejos pura -su linea 1- en el grupo de Loic Yengo en el IMB, uno de los sitios de referencia mundiales, y ella ya tiene vinculo australiano vivo (estancia en QIMR Berghofer) y stack propio (PLINK, R, pipelines GWAS-PRS a nivel independiente). Lo que la deja en 3 y no en 5 es el reloj, no el tema: la plaza se cierra el 12-13 de octubre de 2026 y arranca de inmediato, mientras ella no defiende hasta febrero de 2028 (ETA) y no esta libre hasta el fin de la residencia el 22-05-2027; ademas el anuncio esta escrito para 'recien doctorados o postdocs' con recorrido publicable, y ella solo tiene dos primeros autores en revision. Condiciones publicadas: 2,5 anos, AUD 106.294-113.660 (nivel A) o 119.463-141.545 (nivel B) mas 17% de superannuacion, campus de St Lucia; el anuncio no menciona patrocinio de visado, que ella necesitaria por no ser ciudadana australiana. Accion util: escribir a Yengo presentandose para la siguiente ronda (2027-2028) con el gancho del manuscrito de QIMR en revision en Nature Mental Health y el perfil MD+PhD.</t>
+          <t>Es el mejor encaje tematico del lote academico: grupo de Loic Yengo (PCTG, IMB), genetica estadistica de rasgos complejos, su linea 1, y ella ya tiene conexion con Australia por la estancia en QIMR Berghofer, lo que da contexto y referencias locales. Lo que lo baja a 3 es el reloj y el nivel: exige doctorado terminado y cierra el 12-10-2026, con su defensa en ETA febrero 2028 y la residencia hasta 22-05-2027, asi que no puede optar a esta edicion; ademas el anuncio busca a alguien que transite hacia liderar laboratorio propio en cinco anos, un escalon por encima de un primer postdoc. Salario publicado y alto (A$106.294-141.545 + 17% super) y contrato de hasta 2,5 anos. Visado: necesitaria patrocinio australiano, que UQ suele gestionar para postdocs. A quien escribir: Prof. Loic Yengo, con el gancho de la estancia en QIMR Berghofer y el manuscrito en Nature Mental Health en revision, para preguntar por plazas en 2027-2028 en lugar de por esta.</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -32574,7 +35455,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -32584,7 +35465,7 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
@@ -32594,7 +35475,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>No presentarse a R-68861 (el reloj no cuadra). Escribir a Loic Yengo en otono de 2027 y vigilar cnsgenomics.com/content/recruitment y la API Workday de UQ para la siguiente convocatoria</t>
+          <t>CONFLICTO DE PLAZO RESUELTO: el cierre real es lunes 12-10-2026 a las 23:00 AEST (texto del anuncio, 'Applications close Monday 12 October 2026 at 11.00pm AEST'); el endDate 2026-10-13 de Workday es la fecha en que se retira la oferta del portal, un dia despues. Deadline corregido a 2026-10-12. No es candidatura viable ahora: escribir a Loic Yengo por plazas de 2027-2028.</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -32605,7 +35486,7 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>Re-verificado el 2026-09-21 por la API publica Workday de UQ (SRC-0127), porque la ficha HTML es una SPA vacia para el fetch: canApply=true, postedOn 'Posted 9 Days Ago', startDate 2026-09-11, endDate 2026-10-13. CONFLICTO de plazo declarado: el cuerpo del anuncio dice 'Applications close Monday 12 October 2026 at 11.00pm AEST' mientras el campo endDate de Workday marca 2026-10-13; se mantiene 2026-10-13 en la columna pero el limite real para la dueña es el 12 de octubre AEST.</t>
+          <t>API publica de Workday de UQ (SRC-0127), Tier 1: leido el JSON de la ficha R-68861 el 2026-09-28 (startDate 2026-09-11, endDate 2026-10-13, canApply true, descripcion completa). La ficha web sigue siendo una SPA vacia.</t>
         </is>
       </c>
     </row>
@@ -32655,7 +35536,7 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -32665,7 +35546,7 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -32710,12 +35591,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -32731,7 +35612,7 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Re-verificado el 2026-09-21 en cardiffuniweb.eploy.net (vacante ID 447, Division of Psychological Medicine and Clinical Neurosciences): sigue abierta, cierra el 2026-09-25, salario Grade 5 GBP 33.951-36.636.</t>
+          <t>Re-verificado el 2026-09-21 en cardiffuniweb.eploy.net (vacante ID 447, Division of Psychological Medicine and Clinical Neurosciences): sigue abierta, cierra el 2026-09-25, salario Grade 5 GBP 33.951-36.636. | Cerrada el 2026-09-28 por vencimiento del plazo publicado (2026-09-25), ya contrastado en una pasada anterior; no se ha vuelto a abrir la ficha, asi que Last_Verified no se toca.</t>
         </is>
       </c>
     </row>
@@ -32789,7 +35670,7 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -32799,7 +35680,7 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -32844,12 +35725,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -32865,7 +35746,7 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>Re-verificado el 2026-09-21 en la ficha Tier 1 de KCL (157565): sigue abierta, publicada el 2026-09-07, cierre 2026-09-21, salario GBP 45.031-48.607 incl. London Weighting</t>
+          <t>Re-verificado el 2026-09-21 en la ficha Tier 1 de KCL (157565): sigue abierta, publicada el 2026-09-07, cierre 2026-09-21, salario GBP 45.031-48.607 incl. London Weighting | Cerrada el 2026-09-28 por vencimiento del plazo publicado (2026-09-21), ya contrastado en una pasada anterior; no se ha vuelto a abrir la ficha, asi que Last_Verified no se toca.</t>
         </is>
       </c>
     </row>
@@ -32933,7 +35814,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>-5</v>
+        <v>-11</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -33053,7 +35934,7 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M34" t="inlineStr"/>
@@ -33063,7 +35944,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -33108,12 +35989,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>UPDATED</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -33129,7 +36010,7 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>Re-verificado el 2026-09-21 en werkenbijerasmusmc.nl (Tier 1): sigue publicada. En todo el portal de Erasmus MC solo hay dos postdocs ahora mismo (este y uno de artrosis de rodilla); nada de epidemiologia genetica ni de genetica del sueno.</t>
+          <t>Re-verificado el 2026-09-21 en werkenbijerasmusmc.nl (Tier 1): sigue publicada. En todo el portal de Erasmus MC solo hay dos postdocs ahora mismo (este y uno de artrosis de rodilla); nada de epidemiologia genetica ni de genetica del sueno. | Cerrada el 2026-09-28 por vencimiento del plazo publicado (2026-09-25), ya contrastado en una pasada anterior; no se ha vuelto a abrir la ficha, asi que Last_Verified no se toca.</t>
         </is>
       </c>
     </row>
@@ -33459,7 +36340,7 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
@@ -33498,27 +36379,27 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>No presentarse; sirve para no redescubrirla y como senal de que el grupo de Josip Car (AI &amp; Personalised Health) contrata en sueno: guardar el contacto por si sale algo de genetica del sueno en 2027</t>
+          <t>Confirmada viva en el buscador propio de KCL: ref. 158385, Faculty of Life Sciences &amp; Medicine, campus Guy's, cierre 19-10-2026 sin cambios. Sigue siendo Fit 2, no requiere accion.</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr"/>
@@ -33730,7 +36611,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -33744,7 +36625,7 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -33793,12 +36674,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -33814,7 +36695,7 @@
       </c>
       <c r="AD39" t="inlineStr">
         <is>
-          <t>Tier 1, pagina propia del CNIO (https://www.cnio.es/acerca-del-cnio/ofertas-de-empleo/), abierta sin bloqueo el 2026-09-21. Es el unico postdoc del listado del CNIO en esta pasada; el resto son predoctorales, tecnicos y administracion.</t>
+          <t>Tier 1, pagina propia del CNIO (https://www.cnio.es/acerca-del-cnio/ofertas-de-empleo/), abierta sin bloqueo el 2026-09-21. Es el unico postdoc del listado del CNIO en esta pasada; el resto son predoctorales, tecnicos y administracion. | Cerrada el 2026-09-28 por vencimiento del plazo publicado (2026-09-26), ya contrastado en una pasada anterior; no se ha vuelto a abrir la ficha, asi que Last_Verified no se toca.</t>
         </is>
       </c>
     </row>
@@ -33876,7 +36757,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -33890,7 +36771,7 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -33939,12 +36820,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -33960,7 +36841,7 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Tier 1, listado propio del IiSGM leido el 2026-09-21 (tres convocatorias abiertas: 94_2026, 96_2026 y 98_2026). Fuente NUEVA para esta rama.</t>
+          <t>Tier 1, listado propio del IiSGM leido el 2026-09-21 (tres convocatorias abiertas: 94_2026, 96_2026 y 98_2026). Fuente NUEVA para esta rama. | Cerrada el 2026-09-28 por vencimiento del plazo publicado (2026-09-26), ya contrastado en una pasada anterior; no se ha vuelto a abrir la ficha, asi que Last_Verified no se toca.</t>
         </is>
       </c>
     </row>
@@ -34107,8 +36988,2218 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P-0041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Postdoctor in Bioinformatics and Cancer Genetics</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Goteborgs universitet (University of Gothenburg)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>no publicado en el registro del portal nacional</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>no publicado en el registro del portal nacional</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Goteborg</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Postdoktor (contrato postdoctoral sueco)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>no publicado en el registro del portal nacional</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>13</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>doctorado; bioinformatica y genetica del cancer</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Bioinformatica de genetica del cancer: comparte el utillaje computacional pero ninguna de sus tres lineas (rasgos complejos, GWAS/PRS psiquiatricos, sueno) y el plazo del 10-10-2026 es incompatible con su reloj, que no la libera hasta mediados de 2027.</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Postdoc de bioinformatica en universidad sueca grande, anunciado en el portal publico nacional: visibilidad alta, nicho tecnico estrecho.</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Ninguna: se registra para no volver a descubrirla en la API sueca.</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>https://arbetsformedlingen.se/platsbanken/annonser/31459110</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>API publica JobTech Dev de Platsbanken (Arbetsformedlingen, portal estatal sueco de empleo), registro estructurado del anuncio del empleador con fechas de publicacion y cierre. Ficha institucional (Varbi) no abierta, asi que no es Tier 1 leido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P-0042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Postdoktor - modelos celulares de leucemia definidos geneticamente (TP53), Institutionen for immunologi, genetik och patologi</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Uppsala universitet</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Institutionen for immunologi, genetik och patologi (programa leucemia/TP53)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>no nombrado en el anuncio (se cita 'PI(erna) for leukemi/TP53-programmet')</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Postdoktor (contrato postdoctoral sueco)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>no publicado en el anuncio</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>10</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>doctorado; edicion genomica CRISPR/Cas, biologia funcional del cancer, perfilado de respuesta a farmacos, imagen de alto contenido (Cell Painting) y analisis cuantitativo; 70-80% trabajo experimental de laboratorio</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>El anuncio pide 70-80% de trabajo humedo autonomo (CRISPR, lineas isogenicas, Cell Painting) y solo 20-30% de analisis: su nivel independiente es genetica estadistica, no mesa de laboratorio, y el cierre del 07-10-2026 choca de frente con su disponibilidad (mediados de 2027).</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Perfil hibrido humedo+computacional poco frecuente, pero anunciado en el portal estatal y en Varbi con dos semanas de ventana.</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>Ninguna: se registra para no volver a descubrirla en la API sueca.</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>https://arbetsformedlingen.se/platsbanken/annonser/31455640</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>API publica JobTech Dev (endpoint /ad/31455640): texto completo del anuncio leido desde el portal estatal sueco. Enlace de solicitud institucional https://uu.varbi.com/se/what:job/jobID:962054 no abierto, asi que no cuenta como Tier 1 verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P-0043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Postdoc in Statistical Genetics - Casale Group</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Human Technopole</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Casale Group, Health Data Science Centre</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>no nombrado con nombre de pila en el anuncio: figura solo como 'Casale Group' (jefe de grupo del Health Data Science Centre)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Contrato temporal (fixed term), jornada completa</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>no publicada en el anuncio</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>hasta 43000 segun la experiencia del candidato (cifra publicada en el anuncio)</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>no publicada</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>no publicada; el anuncio aparece entre los mas recientes de Nature Careers el 2026-09-28</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-11-04</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>38</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Doctorado (PhD). Desarrollo de metodos computacionales que conecten variacion genetica humana con funcion biologica; genetica de poblaciones a escala con datos single-cell, espaciales y multimodales; interseccion de genetica estadistica, machine learning y biologia mecanistica</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Encaja con su linea 1 (genetica estadistica de rasgos complejos) y trabaja con genetica humana a escala poblacional, que es exactamente donde ella tiene nivel independiente (PLINK, R, pipelines GWAS-PRS). Pero el puesto esta escrito para alguien que DESARROLLA metodos en la interseccion de genetica estadistica y machine learning, integrando single-cell, datos espaciales y multimodales: ella no ha desarrollado metodos ni maneja single-cell/ML a nivel independiente (su Python es asistido por IA), asi que la candidatura exigiria reencuadrar su perfil como analista aplicada con MD, no como metodologa. Choque de calendario decisivo: el anuncio cierra el 2026-11-04 y exige doctorado, y su defensa es ETA febrero 2028, con la residencia de Medicina de Laboratorio hasta 22-05-2027; no puede optar a esta edicion, y el interes real es el grupo y la convocatoria recurrente, no esta plaza. Visado: ninguno, Italia es UE y su movilidad es libre. Salario publicado, hasta 43.000 EUR/ano, sin suelo definido por ella, razonable para postdoc en Milan. Trabajo de candidatura: carta, research statement y referencias, mas justificar el salto a metodos; realista M. A quien escribir: no hay correo en el anuncio; el gancho seria el paper de Nature Mental Health en revision (proyecto QIMR) y su combinacion MD+PhD para anclar genetica a fenotipo clinico, dirigido al Health Data Science Centre de Human Technopole.</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Instituto de nueva creacion muy financiado, plaza de metodos en genetica estadistica + IA con red ELLIS y Helmholtz Munich; el anuncio no publica numero de solicitantes, la estimacion es cualitativa</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>No es candidatura de esta edicion (cierra 2026-11-04, ella no esta disponible). Vigilar la pagina de empleo propia de Human Technopole en 2027 y, si la linea interesa, escribir al grupo Casale antes de la siguiente convocatoria.</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>https://www.nature.com/naturecareers/job/12864992/postdoc-in-statistical-genetics-casale-group/</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>Nature Careers (SRC-0003), Tier 2: leido el anuncio completo el 2026-09-28 con el patron de URL valido /naturecareers/job/&lt;id&gt;/&lt;slug&gt;/. No se abrio la pagina Tier 1 de Human Technopole, de ahi Confidence LIKELY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P-0044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>GLAD-NI Research Fellow (estudio GLAD-MHG, NIHR BioResource)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Queen's University Belfast</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>School of Psychology, laboratorio STARC (Stress, Trauma and Related Conditions)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Prof. Cherie Armour</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Belfast</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Fixed-Term/Contract, jornada completa</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2,5 anos</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>42972-51270 GBP/ano (cifra publicada en libras, sin conversion)</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>no publicada</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>8</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Doctorado (obtenido o a punto de obtener) en Psicologia, Epidemiologia, Estadistica o afin; licenciatura en Psicologia o afin; gestion de proyecto; enlace de datos y confidencialidad. Ref 26/113629</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Cohorte de psiquiatria de precision con secuenciacion completa de genoma (GLAD/NIHR BioResource), pero el puesto es de reclutamiento de participantes, gestion de encuestas psicosociales y enlace de datos, no de analisis genetico, y cierra el 2026-10-05, cuando ella sigue en residencia hasta mayo de 2027.</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Plaza de perfil psicologico-epidemiologico en Belfast; sin datos de solicitantes publicados</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>Ninguna: plazo incompatible con su disponibilidad. Queda registrada para no redescubrirla y porque el consorcio GLAD-MHG es un objetivo a seguir (rama 3).</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DSX751/glad-ni-research-fellow</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>jobs.ac.uk (SRC-0002), Tier 2: anuncio completo leido el 2026-09-28 en la busqueda keywords='statistical genetics' ordenada por mas reciente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P-0045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Computational Senior Research Fellow (proyecto ERC-Synergy MUTAHOME)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Queen Mary University of London</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Barts Cancer Institute (con Francis Crick Institute)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>no nombrado en el anuncio</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Fixed-Term/Contract, jornada completa</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>no publicada</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>54617-60901 GBP/ano (cifra publicada en libras, sin conversion)</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>no publicada</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>20</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Cientifico senior con base solida en genetica humana y estadistica, analisis de datos genomicos y transcriptomicos, mutaciones somaticas y expansion clonal. Ref 11499</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Es genomica somatica del cancer a nivel senior (metodos de expansion clonal, multi-omica de tejidos), ni su tema ni su antiguedad, y cierra el 2026-10-17.</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Plaza senior en un centro ERC-Synergy con el Crick; sin datos publicados</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>Ninguna. Registrada solo para no redescubrirla en la busqueda 'statistical genetics' de jobs.ac.uk.</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>https://www.jobs.ac.uk/job/DTB231/computational-senior-research-fellow</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>jobs.ac.uk (SRC-0002), Tier 2, leido el 2026-09-28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P-0046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Post-doctoral Research Associate in Machine Learning for Mental Health (proyecto PROSPECT, UKRI)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Research Department of Biomedical Computing, Faculty of Life Sciences &amp; Medicine (St Thomas' Hospital)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Dr Sarah Morgan (Sarah.e.morgan@kcl.ac.uk)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Fixed-term, jornada completa</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2 anos, con posible extension a 4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>45031-52514 GBP/ano incluida London Weighting (cifra publicada en libras; no convertida a euros)</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>no publicado; entrevistas previstas noviembre 2026, por lo que el arranque sera probablemente principios de 2027</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>no publicado en la pagina de la vacante</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>21</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Doctorado (o a punto de terminar) en informatica, ingenieria, fisica, matematicas, psiquiatria, psicologia o neurociencia; experiencia practica con datos de RM cerebral; machine learning solido en Python (scikit-learn, PyTorch, TensorFlow); publicaciones. Deseable: analisis de redes/teoria de grafos y experiencia en salud mental. Se pide CV y carta de idoneidad.</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Encaja con su linea 2 (psiquiatria/salud mental: el proyecto PROSPECT predice la evolucion longitudinal de sintomas en psicosis) y el empleador valora explicitamente el perfil clinico -- una MD que entiende la psicopatologia y ademas programa es exactamente el hueco que suele faltar en un equipo de biomedical computing. Pero no es un 4 porque los dos requisitos ESENCIALES son precisamente sus dos puntos debiles declarados: RM cerebral 'hands-on' y machine learning fuerte en PyTorch/TensorFlow. Su neuroimagen es de nivel supervisado (formacion y estancia, no despliegue autonomo) y su Python es asistido por IA; aqui no hay genetica estadistica ni GWAS/PRS que compensen. Es un 3 con condicion que resolver: tendria que poder demostrar analisis de RM propio, no de curso. Trabajo de candidatura bajo (CV + supporting statement, sin charla ni cartas), asi que S: 1-2 dias bien invertidos, y el plazo del 18-10-2026 es holgado. Salario 45.031-52.514 GBP con London Weighting, muy por encima de un sueldo de residente y sin suelo salarial que incumplir. Visado: Reino Unido ya no es UE, necesita Skilled Worker; KCL patrocina de forma rutinaria en grado Research Associate, asi que es friccion administrativa, no bloqueo. CHOQUE DE CALENDARIO, y es el problema real: con entrevistas en noviembre de 2026 el puesto arranca a principios de 2027, y ella no esta libre hasta el 22-05-2027 (fin de residencia) y hasta febrero de 2028 (ETA) para plazas que exijan doctorado ya defendido -- y esta lo exige o casi. Solo tiene sentido presentarse si Sarah Morgan acepta un inicio muy diferido; ese es el primer correo, breve, preguntando por la flexibilidad de la fecha de inicio antes de escribir la carta.</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Postdoc de ML en salud mental en KCL, financiado por UKRI, en Londres y con salario publicado: atrae a la cantera muy numerosa de doctores en ML/neuroimagen del Reino Unido, que cumplen los esenciales de fabrica.</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>Antes de escribir nada, un correo corto a Sarah.e.morgan@kcl.ac.uk preguntando si el inicio admite diferirse mas alla de mayo de 2027; si la respuesta es no, archivar sin gastar la candidatura.</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/159026-post-doctoral-research-associate-in-machine-learning-for-mental-health</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>Tier 1: buscador propio de KCL (https://www.kcl.ac.uk/jobs/search?term=...) y despues la pagina oficial de la vacante, abiertas las dos en esta pasada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P-0047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Research Associate in MND Genetics</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>UK MND Research Institute, Department of Basic and Clinical Neuroscience, IoPPN (Denmark Hill)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Prof. Ammar Al-Chalabi (ammar.al-chalabi@kcl.ac.uk)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Fixed-term, jornada completa (35 h/semana)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>hasta el 31 de marzo de 2028</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>45031-52514 GBP/ano incluida London Weighting (cifra publicada en libras; no convertida a euros)</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>no publicado en la pagina de la vacante</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>8</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Doctorado en bioinformatica o genetica; conocimiento actualizado de pipelines NGS y analisis de datos de secuenciacion de ADN a gran escala; Unix/Linux y programacion (Python, Java, Bash, Perl o R); identificacion de marcadores genomicos de enfermedad; publicaciones. Deseable: genetica estadistica y machine learning.</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Es genetica en el IoPPN, pero los esenciales son pipelines NGS y secuenciacion a gran escala -- que ella no maneja -- y la genetica estadistica que si domina figura solo como deseable; ademas el contrato termina el 31-03-2028, un mes despues de su defensa prevista, asi que el calendario lo hace materialmente imposible.</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Plaza de bioinformatica de secuenciacion en un instituto de referencia en ELA con salario publicado en Londres.</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>No presentarse. Queda registrada para no volver a descubrirla y como prueba de que el grupo de Al-Chalabi contrata en genetica: si reabre una plaza de genetica estadistica con plazo en 2027-2028, ese si es su perfil.</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/159106-research-associate-in-mnd-genetics</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Tier 1: buscador propio de KCL filtrado por IoPPN y por 'statistical genetics', y despues la pagina oficial de la vacante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P-0048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Clinical Research Fellow (IoPPN)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>King's College London</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Institute of Psychiatry, Psychology &amp; Neuroscience (IoPPN)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>no identificado: solo se leyo la ficha del listado, no la pagina completa de la vacante</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>no leido (Clinical Research Fellow, categoria clinica)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>no leido</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>no leido</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>no leido</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>no publicado en el listado</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>10</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>no leidos: la ficha del buscador da titulo, referencia 158285, facultad IoPPN y fecha de cierre, pero no se abrio la pagina completa por presupuesto</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Plaza clinica del IoPPN (ref. 158285) distinta de las ya registradas P-0016 y P-0018; cierra el 07-10-2026, imposible con la residencia hasta el 22-05-2027, y no se pudo leer el contenido para saber si toca genetica psiquiatrica.</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>No se abrio la vacante completa.</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>Registrada para no redescubrirla. Si interesa el detalle, abrir la pagina a mano; el plazo la descarta de todos modos.</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>https://www.kcl.ac.uk/jobs/158285-clinical-research-fellow</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Tier 1 parcial: vista en el buscador propio de KCL filtrado por IoPPN (titulo, referencia, facultad y fecha de cierre). No se abrio la pagina de la vacante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P-0049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Research Officer/Senior Research Officer - Cardiovascular Disease Prevention Group (ref. BV000085)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>QIMR Berghofer Medical Research Institute</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Cardiovascular Disease Prevention Group</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Dr Ellie Paige, Team Head (ellie.paige@qimrb.edu.au)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Brisbane</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Fixed-term, jornada completa (se considera parcial)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>hasta el 30 de junio de 2028</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>98983-132583 AUD/ano mas superannuation y salary packaging (cifra publicada en dolares australianos; no convertida a euros)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>no publicado en la pagina de la vacante</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>12</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Doctorado en epidemiologia, salud publica, medicina, bioestadistica o ciencia de datos; MINIMO 3 anos de experiencia postdoctoral analizando datos sanitarios enlazados a gran escala; Stata, R o SAS. Exige ciudadania australiana, residencia permanente o permiso de trabajo valido: NO se ofrece patrocinio.</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Es epidemiologia de prevencion cardiovascular con datos enlazados, no genetica, pide un minimo de 3 anos postdoctorales que ella no tendra y ademas exige permiso de trabajo previo sin patrocinio, lo que la excluye formalmente como no residente.</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Rango salarial alto y plaza de dos anos y medio, pero restringida de hecho al mercado australiano por el requisito de permiso de trabajo.</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>No presentarse. Registrada sobre todo por el dato reutilizable: QIMR Berghofer publica 'work eligibility' sin patrocinio, asi que toda plaza suya hay que leerla asumiendo que el visado corre por su cuenta.</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>https://qimrberghofer.turborecruit.com.au/job/job_details.cfm?id=582956</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Tier 1: listado completo de vacantes de qimrberghofer.turborecruit.com.au y despues la ficha oficial de la vacante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P-0050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Postdoctoral Position in Genetic Epidemiology of Alzheimer Disease</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Boston University School of Medicine</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Biomedical Genetics division, Department of Medicine</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Lindsay Farrer (farrer@bu.edu, tel. 617-638-5393)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Boston (MA)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Postdoc de investigacion</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>no publicado en el anuncio</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>inmediato posible, pero el anuncio dice literalmente que hay fechas de inicio posteriores disponibles ('later start dates are available')</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>sin plazo: el anuncio dice 'the position will remain open until filled'</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>PhD (o estar en proceso de completarlo — el anuncio admite explicitamente 'in the process of completing a PhD or equivalent'); campos preferentes epidemiologia genetica, bioestadistica/estadistica, bioinformatica, genetica humana, matematica aplicada; analisis de datos de alto rendimiento (GWAS, exome chip arrays, genome/exome/RNA sequencing, resecuenciacion dirigida de genes) para el Alzheimer Disease Genetics Consortium y el Alzheimer Disease Sequencing Project; programacion en R u otro software estadistico y experiencia con grandes conjuntos de datos, a indicar en la carta; ciudadania o residencia permanente en EE. UU. 'preferable but not required'; candidatura = carta + CV + TRES cartas de recomendacion por email</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Es el mejor hallazgo de la rama esta semana y lo es por una razon de calendario, no solo de tema. Contenido: GWAS y secuenciacion de exoma/genoma sobre cohortes grandes (ADGC, ADSP) es su linea 1 (genetica estadistica de rasgos complejos) ejecutada con su pipeline real — PLINK/R sobre datos de biobanco — y el entorno declarado (varios epidemiologos geneticos a nivel de facultad, programas de formacion en genetica estadistica y bioinformatica, un Statistical Genetics Working Group de toda la universidad, cluster MGHPCC) es formacion metodologica, que es lo que le falta para dar el salto de tesis a independencia. El combo MD+PhD juega a favor: es una division de Biomedical Genetics dentro de una facultad de medicina trabajando una enfermedad con fenotipado clinico, donde una medica que sabe leer una historia clinica y correr un GWAS vale mas que un bioinformatico puro. CALENDARIO, el punto decisivo: dos de los tres candados habituales caen. El anuncio acepta doctorandos en proceso de terminar ('in the process of completing a PhD'), asi que su defensa prevista en febrero de 2028 (ETA, no fijada) no la descalifica de entrada; y dice expresamente que admite fechas de inicio posteriores y que la plaza queda abierta hasta cubrirse, lo que es compatible con su disponibilidad real a partir del 22-05-2027 (fin de residencia). No puntua 5 por dos motivos honestos: la plaza se publico el 17-06-2026 y 'abierta hasta cubrirse' a mas de tres meses puede significar que ya este cubierta sin que el tablon lo retire, y el desfase entre 'puede empezar ya' y 'yo estoy libre en 18-20 meses' es largo incluso para un PI flexible. Trabajo de candidatura: carta + CV + TRES cartas de recomendacion. Las cartas son el cuello de botella real (hay que pedirlas con semanas de margen a la direccion de tesis en Murcia, a QIMR Berghofer y al grupo de Japon), pero no hay plazo que presione, asi que se puede preparar con calma. Retribucion: no publicada; los postdocs de BU siguen escala NIH, sin suelo declarado por ella, asi que no es un filtro. Visado: EE. UU. exige patrocinio (J-1 o H-1B); el anuncio dice que la ciudadania o residencia estadounidense es 'preferible pero no requerida', lo que es lo mas cerca de una invitacion explicita a extranjeras que se ve en un anuncio americano — no es un bloqueo, es una linea a mencionar en la carta. A QUIEN ESCRIBIR Y CON QUE GANCHO: Dr. Lindsay Farrer (farrer@bu.edu), que es quien recibe las candidaturas directamente, sin portal intermedio. Gancho: MD (Complutense 2019) + tesis en genetica estadistica de rasgos complejos con GWAS/PRS propios en PLINK y R, dos manuscritos como primera autora en revision (uno en Nature Mental Health, del proyecto QIMR Berghofer), y disponibilidad a partir de mediados de 2027 — preguntar de frente si la plaza admite un inicio en 2027 o si conviene volver a escribir en otono de 2026, que convierte un 'demasiado pronto' en un contacto vivo en lugar de una candidatura perdida.</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Razonado, no medido: grupo de referencia mundial en genetica del Alzheimer, PI con peso en ADGC y ADSP, plaza sin plazo y abierta hasta cubrirse (premia al que llega antes y con cartas listas), y candidatura por email directo, lo que atrae mucho volumen espontaneo.</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>Escribir a farrer@bu.edu preguntando (a) si la plaza sigue viva a septiembre de 2026 y (b) si una fecha de inicio en el segundo semestre de 2027, con defensa prevista en febrero de 2028, entra en lo que consideran. Pedir ya las tres cartas de recomendacion en paralelo, porque son el unico elemento que no se puede improvisar.</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>https://iges.memberclicks.net/assets/Postdoc%20position%20at%20Boston%20University-June2026.pdf</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Rama 5 (novedad), encargo IGES Position Openings (SRC-0155) del 2026-09-28. El anuncio es un PDF con membrete de Biomedical Genetics, Department of Medicine, Boston University School of Medicine (72 East Concord Street) alojado por la IGES: documento de la institucion, leido integro por mi. NO se abrio ninguna pagina en bumc.bu.edu, asi que la vigencia a fecha de hoy no esta confirmada en un dominio de BU: de ahi Confidence LIKELY y no VERIFIED. Fecha de publicacion 2026-06-17 tomada del sello del tablon de la IGES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P-0051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Scientist en genomica estadistica y psiquiatria (Center for Precision Psychiatry)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Columbia University</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Department of Biostatistics y Stavros Niarchos Foundation Center for Precision Psychiatry</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Iuliana Ionita-Laza</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nueva York (NY)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Postdoc de investigacion</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>no publicado; el anuncio solo dice 'competitive'</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>sin fecha de cierre: el anuncio no publica plazo alguno</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>PhD en estadistica, bioestadistica o ciencias de la computacion; fuertes habilidades de programacion; formacion en genetica descrita como deseable pero opcional; investigacion metodologica y aplicada en la interseccion de la genomica estadistica y la psiquiatria, con metodos estadisticos y de aprendizaje automatico integrativos sobre datos omicos e historias clinicas electronicas aplicados a rasgos psiquiatricos; candidatura por email con carta, CV y dos referencias</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Tema: es exactamente el cruce de sus lineas 1 y 2 (metodos de genomica estadistica aplicados a rasgos psiquiatricos), y el uso de historias clinicas electronicas como fenotipo es donde su titulo de medicina deja de ser un adorno y se convierte en ventaja tecnica: sabe que significa un codigo diagnostico y donde miente. Es rolling y sin plazo, lo que en principio encaja con una disponibilidad lejana. Por que 3 y no 4: el requisito esta escrito para una candidata de metodos pura — 'PhD in statistics, biostatistics, or computer science', con la genetica marcada como deseable-opcional, que es el reparto inverso al suyo. Su doctorado esta en un programa de Psicologia (Universidad de Murcia) y su fuerza es la genetica estadistica aplicada con PLINK y R, con Python asistido por IA; en un departamento de Bioestadistica de Columbia compite contra gente que desarrolla el metodo y lo implementa en C++. Necesita reencuadre: presentarse como la persona que aporta el fenotipo clinico y la genetica, no el estimador nuevo. Ademas el reloj no se ha resuelto, solo se ha diferido: PhD requerido (febrero de 2028, ETA) y no esta libre hasta el 22-05-2027, sobre una plaza publicada en abril de 2026 y sin plazo, que es la clase de puesto que se cubre cuando aparece el candidato adecuado, no cuando ella este lista. Trabajo de candidatura: bajo — carta, CV y dos nombres de referencia por email, sin portal. Retribucion 'competitive' sin cifra; sin suelo fijado por ella no es un filtro. Visado: EE. UU. exige patrocinio (J-1/H-1B) y el anuncio no dice nada al respecto. A quien escribir: Dra. Iuliana Ionita-Laza, que recibe las candidaturas directamente. El email figura en el anuncio pero venia ofuscado en la copia recuperada, asi que hay que tomarlo de la ficha del Department of Biostatistics de Columbia y no inventarlo. Gancho util: MD + genetica estadistica de trastornos psiquiatricos y un manuscrito en revision en Nature Mental Health, ofreciendose para la parte de fenotipado con historias clinicas; y preguntar si mantienen la busqueda abierta de cara a 2027-2028.</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Razonado, no medido: Columbia, centro financiado por la Stavros Niarchos Foundation, requisito de perfil metodologico puro y candidatura por email sin plazo — el flujo espontaneo de doctores en bioestadistica hacia este tipo de plaza es alto.</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Escribir a la PI (email en la ficha del Department of Biostatistics de Columbia; NO usar una direccion adivinada) preguntando si la busqueda sigue viva y si aceptarian candidaturas con defensa prevista en 2028. Si responde, reencuadrar la carta hacia fenotipado clinico + genetica, no hacia desarrollo de metodos.</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>https://iges.memberclicks.net/postdoc-may2026-columbiauniversity</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Rama 5 (novedad), encargo IGES Position Openings (SRC-0155) del 2026-09-28. Ficha reproducida integra en el tablon de la IGES (texto suministrado por la institucion, Tier 2 en cuanto a alojamiento); no se abrio ninguna pagina de columbia.edu, luego sin Last_Verified. Fecha de publicacion 2026-04-25 segun el sello del tablon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P-0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Postdoctoral Research Fellow en genomica y multi-omica de trastornos mentales graves</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>grupo participante en el Psychiatric Genomics Consortium (no nombrado en la ficha del tablon)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>no nombrado; contacto administrativo publicado: Grace Lutter (graced@email.unc.edu), coordinacion del PGC</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Bonn</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3 anos</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>no publicado en la ficha del tablon</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>no publicado: el tablon PGC Careers no sella la fecha de alta de sus entradas</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>18</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>PhD en un campo computacional o con experiencia demostrada en genetica; analisis de datos genomicos, transcriptomicos y lipidomicos a gran escala en trastornos mentales graves; Python y R; contrato de tres anos con margen para desarrollar linea propia junto a la colaborativa</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Contenido: linea 2 del perfil casi literal — genomica de trastornos mentales graves en un grupo del PGC, que es la red donde vive el GWAS psiquiatrico mundial, y con Python y R como herramientas declaradas (R es su lengua materna analitica; Python lo usa asistido). Alemania es UE: cero friccion de visado o permiso de trabajo para ella, y una entrada en un grupo del PGC es capital de red que se cobra durante una decada. La capa lipidomica es lo unico realmente ajeno a su formacion. Por que NO puede puntuar mas alto: el reloj. Exige PhD ya defendido y su defensa esta prevista en febrero de 2028 (ETA, no fijada), asi que a 15-10-2026 es formalmente INELEGIBLE; y ni siquiera esta disponible antes del 22-05-2027 por la residencia de Medicina de Laboratorio en Malaga. Un contrato de tres anos que se convoca con cierre en octubre de 2026 arranca en 2027 como muy tarde: no hay forma honesta de encajarla en esta edicion. La fila existe por el grupo, no por la plaza. Trabajo de candidatura: irrelevante esta vez, porque no se va a presentar. Lo que si merece trabajo es identificar en la ficha completa de LinkedIn de que grupo de Bonn se trata (el Institute of Human Genetics de Bonn es el nodo PGC habitual) y anotar al PI real para escribirle en 2027. A quien escribir: de momento el unico contacto publicado es administrativo (coordinacion del PGC en UNC), que no es la puerta util. Hay que abrir la ficha de LinkedIn para sacar el nombre del grupo antes de gastar un correo.</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Razonado, no medido: plaza de tres anos en un grupo del PGC anunciada a traves del tablon de la propia red y de LinkedIn, con plazo corto — concentra candidaturas de toda la red en cuatro semanas.</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>NO presentarse: inelegible (PhD sin defender) e indisponible (residencia hasta el 22-05-2027). Abrir la ficha de LinkedIn una sola vez para identificar el grupo y el PI de Bonn, anotarlo como via de contacto para 2027-2028, y dejar la fila como registro para no redescubrirla.</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4466098370/</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Rama 5 (novedad), PGC Careers (SRC-0157) el 2026-09-28: unica entrada viva de la tabla. Datos tomados de la tabla del PGC, que es Tier 2 y no sella fechas de alta; la ficha original (LinkedIn) no se abrio, de ahi Confidence UNVERIFIED y ningun Last_Verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P-0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Research Associates in Statistical Genetics (2 plazas)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>University of Leicester</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Genetic Epidemiology Group</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Martin Tobin (martin.tobin@leicester.ac.uk), Catherine John (catherine.john@leicester.ac.uk), Richard Packer (richard.packer@leicester.ac.uk)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Leicester</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Research Associate, temporal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2 anos iniciales</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>no publicado en el anuncio recuperado</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>-168</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>PhD (o a punto de completarlo) en genetica estadistica, epidemiologia genetica o campo afin, declarado ESENCIAL; experiencia con conjuntos de datos genomicos a gran escala; solidas habilidades computacionales y de programacion; trayectoria de productividad investigadora; se valora experiencia con plataformas de biobanco o historias clinicas electronicas</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>La plaza esta CERRADA (plazo 12-04-2026, cinco meses antes de esta pasada) y se registra por lo que queda vivo de ella, no por la vacante. Contenido: 'Research Associate in Statistical Genetics' en el Genetic Epidemiology Group de Leicester es el titulo exacto de su linea 1, con el detalle relevante de que el anuncio aceptaba PhD 'or near completion' y valoraba expresamente biobancos e historias clinicas electronicas — las dos cosas que su combinacion MD + tesis en genetica estadistica aporta juntas. Reino Unido exige ahora patrocinio de visado Skilled Worker incluso para ciudadanas UE, coste y tramite que hay que anotar pero que una universidad britanica tramita de rutina. Lo que hace que esta fila valga su sitio son TRES nombres con correo institucional publicado en el anuncio, en un grupo cuya rotacion de plazas es regular: Martin Tobin, Catherine John y Richard Packer. Es la via de contacto en frio mejor documentada que ha salido en toda la pasada. Trabajo: escribir un correo, no preparar una candidatura. Gancho: preguntar si el grupo preve nuevas plazas de Research Associate en 2027, presentandose como MD con pipeline GWAS/PRS propio (PLINK, R) y disponibilidad a partir de mediados de 2027, y pedir que la tengan en cuenta cuando se reabra. Un 'avisame cuando salga' de un grupo asi vale mas que tres candidaturas ciegas a plazas ya publicadas.</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>No se publico numero de candidaturas y la plaza ya esta resuelta; sin base para estimar.</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>Correo en frio a Catherine John y Richard Packer (con copia a Martin Tobin) preguntando por futuras plazas de Research Associate en genetica estadistica en 2027 y ofreciendo CV. No hay nada que solicitar: el plazo cerro el 12-04-2026.</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>https://jobs.le.ac.uk/vacancies/13082/research-associate-2-posts-available.html</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Rama 5 (novedad), encargo IGES Position Openings (SRC-0155) del 2026-09-28: el tablon la sigue listando en la seccion de plazas actuales aunque el plazo cerro el 12-04-2026, dato a tener en cuenta sobre la frescura de esa seccion. Texto del anuncio leido en la ficha alojada por la IGES; no se abrio jobs.le.ac.uk, luego sin Last_Verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Postdoctoral Fellow in Integrative Molecular Epidemiology</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Lunenfeld-Tanenbaum Research Institute (Sinai Health)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>no nombrado en la ficha</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>no nombrado en la ficha del tablon</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Postdoc</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>no publicado en el tablon</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>epidemiologia molecular integrativa; detalle no extraido (no se abrio el PDF del anuncio)</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Epidemiologia molecular integrativa en Canada, adyacente pero no sobre sus lineas (no es genetica estadistica ni GWAS/PRS), publicada en marzo de 2026 y sin plazo ni PI publicados, con visado canadiense y una indisponibilidad suya hasta mediados de 2027: se registra fechada para no volver a descubrirla.</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Sin datos publicados.</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>Ninguna. Fila de registro: solo abrir el PDF si en 2027 sigue listada y las lineas de genetica estadistica no dan nada.</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>https://iges.memberclicks.net/assets/Lunenfeld-Tanenbaum_Research_Institute-post_doc_job%20posting_2603.pdf</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Rama 5 (novedad), IGES Position Openings (SRC-0155) el 2026-09-28. Fecha de publicacion 2026-03-13 tomada del sello del tablon; el PDF del anuncio no se abrio (presupuesto), de ahi UNVERIFIED.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Bioinformatician / Computational Biology</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Medizincampus Davos</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>no nombrado en la ficha</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>no nombrado en la ficha del tablon</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Davos</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Puesto de personal cientifico (bioinformatica)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>no publicado</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>no publicado en el tablon</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>bioinformatica / biologia computacional; detalle no extraido (no se abrio la ficha)</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Puesto de bioinformatica en Suiza publicado en enero de 2026 (el mas antiguo de la seccion 'actuales' del tablon IGES, con riesgo alto de estar ya cubierto), sin PI ni plazo publicados y con un perfil de bioinformatica de servicio que no es su linea ni aprovecha el MD: se registra fechado para cerrar el encargo y no redescubrirlo.</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Sin datos publicados.</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>Ninguna. Fila de registro.</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>https://iges.memberclicks.net/bioinformatician-switzerland-jan2026</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>Rama 5 (novedad), IGES Position Openings (SRC-0155) el 2026-09-28. Fecha de publicacion 2026-01-07 tomada del sello del tablon; ficha no abierta, de ahi UNVERIFIED.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AD41"/>
+  <autoFilter ref="A1:AD56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34119,7 +39210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AB21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -34132,7 +39223,7 @@
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="52" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
     <col width="52" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="52" customWidth="1" min="14" max="14"/>
@@ -34509,34 +39600,34 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Nada que presentar antes de mayo de 2027. Hasta entonces: mantener archivada la documentacion de meritos (contratos, cursos, posteres, publicaciones) y, a principios de 2027, preguntar a la unidad de personal de Malaga a que categoria de bolsa se mapea el nuevo titulo de Laboratorio Clinico. Inscribirse en la Bolsa Unica inmediatamente despues del 22-05-2027.</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Nada que presentar antes de mayo de 2027. Hasta entonces: mantener archivada la documentacion de meritos (contratos, cursos, posteres, publicaciones) y, a principios de 2027, preguntar a la unidad de personal de Malaga a que categoria de bolsa se mapea el nuevo titulo de Laboratorio Clinico. Inscribirse en la Bolsa Unica inmediatamente despues del 22-05-2027.</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>https://www.sspa.juntadeandalucia.es/servicioandaluzdesalud/profesionales/ofertas-de-empleo/bolsa-de-empleo</t>
@@ -34544,7 +39635,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Rama 4. Pagina de bolsa del SAS abierta (Tier 1): expone las subbolsas de seleccion y provision (PIT) y el proceso de baremo y alegaciones. La pagina no enumera por si misma el listado de categorias FEA, de ahi la advertencia y no una afirmacion.</t>
+          <t>Tier 1: portal de Bolsa de empleo del Servicio Andaluz de Salud, abierto y respondiendo 200 el 2026-09-28; sin cambio material respecto a la verificacion anterior</t>
         </is>
       </c>
     </row>
@@ -34609,7 +39700,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sigue sin haber movimiento y la espera ya es el dato. Listado de audiencia e informacion publica del Ministerio abierto hoy: solo dos proyectos vivos, DG/79/26 (orden de actualizacion de la cartera comun de servicios y de la prestacion ortoprotesica, del 15-09 al 06-10-2026) y DG/73/26 (real decreto de promocion y publicidad de formulas infantiles, del 08 al 29-09-2026); ha cerrado el DG/72/26 que figuraba la pasada anterior. Ninguno es de Genetica: los dos reales decretos no han entrado en audiencia publica. Lo nuevo de esta pasada es que la cronologia queda fechada hasta el ultimo escalon conocido. Las resoluciones de la Direccion General de Ordenacion Profesional que acordaron iniciar el procedimiento de elaboracion de ambos reales decretos son de junio de 2025; la consulta publica previa del titulo de Genetica de Laboratorio es de 01-07-2025; y el 23-12-2025 la propia Direccion General declaro que los borradores y las memorias de analisis de impacto normativo estaban practicamente ultimados y que los textos saldrian en breve a informacion y audiencia publica. Desde ese en breve han pasado NUEVE MESES sin que aparezcan en el listado, quince desde la consulta publica previa y veintiuno desde el acuerdo de la Comision de Recursos Humanos del SNS de diciembre de 2024. Esa declaracion de diciembre de 2025 es prensa sectorial, Tier 2, no una fuente oficial, y como tal se registra. La misma prensa sostiene que Sanidad apunta a ofertar las primeras plazas de Genetica en la convocatoria MIR de 2027, lo que exigiria publicar los reales decretos con bastante antelacion; no lo confirma ningun documento oficial y no se da por bueno, pero es el unico indicio de calendario que existe y conviene vigilarlo porque, de cumplirse, el borrador tendria que salir a audiencia en los proximos meses. Para ELLA nada cambia en lo esencial y ese es el riesgo: lo que sigue sin existir en ningun texto oficial es la disposicion transitoria de acceso excepcional al titulo. Ni la nota de prensa de 13-06-2025, ni el documento de consulta publica previa, ni las declaraciones de diciembre la mencionan. La hipotesis de que exigira acreditar anos de ejercicio en el area al modo de Pediatria y Urgencias sigue siendo hipotesis, y si se confirma ella no cumplira al terminar la residencia de Laboratorio Clinico en mayo de 2027. Cada mes de retraso empeora su posicion por partida doble: retrasa la via y aumenta la probabilidad de que el periodo de ejercicio exigible se cuente hacia atras desde una fecha en la que ella todavia no ejercia</t>
+          <t>EL RIESGO GRANDE DEL PERFIL, y a 2026-09-28 sigue sin resolverse. Cronologia fechada, ampliada esta semana: resoluciones de inicio de tramitacion en junio de 2025; consulta publica previa el 01-07-2025; el 23-12-2025 la Direccion General de Ordenacion Profesional declara los borradores 'practicamente ultimados'; el 15-04-2026 la ministra de Sanidad dice que el proceso 'esta en sus ultimas revisiones para iniciar el tramite de audiencia de forma inminente' y la propia Direccion General de Ordenacion Profesional admite que 'es dificil que todo este engranaje este listo para el examen de 2027', desplazando el estreno MIR a 2028; el 21-09-2026 el listado de audiencia publica de Sanidad seguia sin ningun proyecto de Genetica; y el 27-09-2026, comprobado de nuevo por esta rutina, ese listado tiene exactamente tres proyectos abiertos -Fondo de cohesion sanitaria (DG/87/26), cartera de servicios comunes de salud publica (DG/79/26) y preparados para lactantes (DG/73/26)- y NINGUNO es de Genetica. Quince meses desde el inicio de la tramitacion y el proyecto no ha llegado siquiera a audiencia publica: LA ESPERA ES EL DATO. Y hay un dato nuevo que la empeora, porque encadena plazos: segun la informacion de 15-04-2026, tras la publicacion en el BOE hacen falta tres meses mas para constituir las comisiones nacionales y otros seis para elaborar los programas formativos. Si el real decreto se publicase hoy, el engranaje no estaria montado antes de mediados de 2027. Por que le importa tanto a ella: es MD con residencia de Analisis Clinicos (fin 22-05-2027) y tesis en genetica estadistica, es decir el perfil exacto al que apunta la disposicion transitoria de acceso extraordinario al titulo -que si figura en los borradores y que, segun las declaraciones recogidas, se basara en anos de experiencia y competencias demostrables-. El acceso a Genetica Medica queda reservado a licenciados en Medicina, lo que juega a su favor. Pero mientras el real decreto no se publique no hay requisitos, no hay plazo y no hay nada que solicitar: no es un tramite que se pueda preparar, es un reloj que hay que vigilar. Que puede hacer entretanto, y es trabajo real: acumular y documentar experiencia atribuible a genetica (rotaciones, informes, publicaciones, tesis) porque sera lo que baremen si la via transitoria se articula por meritos acreditados.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -34634,7 +39725,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -34644,7 +39735,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -34654,7 +39745,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Seguir revisando cada semana el listado de audiencia publica de Sanidad y tambien el escalon previo de consulta publica; en el BOE buscar por titulo cada mes. Novedad a vigilar con prioridad: si la prensa sectorial acierta y Sanidad quiere plazas de Genetica en el MIR 2027, el borrador tiene que salir a audiencia en los proximos meses, asi que un vistazo semanal al listado es ahora mas rentable que nunca. Cuando aparezca el borrador, alegar por el buzon proyectosnormativos-dgorden@sanidad.gob.es sobre el computo de la residencia de Laboratorio Clinico. Si en 2027 sigue sin haber borrador, escribir a la AEGH preguntando por la disposicion transitoria</t>
+          <t>Vigilancia semanal de dos paginas y nada mas: el listado de audiencia publica de Sanidad (SRC-0055) y el BOE (SRC-0028). Cuando el proyecto aparezca en audiencia publica, leer la disposicion transitoria el mismo dia y extraer los requisitos de acceso extraordinario y el plazo. Suscribirse a la lista 'Participacion Publica en Proyectos Normativos' del Ministerio de Sanidad, que avisa por correo de cada nuevo tramite de audiencia, eliminaria el riesgo de perder la ventana</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -35142,34 +40233,34 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>En marzo de 2027 revisar semanalmente el portal RFGI (tipo FIMAB_EM) y, antes, en Q4 2026, escribir a la ECAI de Bioinformatica de IBIMA (Juan Antonio Garcia Ranea) presentandose como MD residente de Laboratorio Clinico con pipelines GWAS/PRS propios y disponibilidad a partir de junio de 2027</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>En marzo de 2027 revisar semanalmente el portal RFGI (tipo FIMAB_EM) y, antes, en Q4 2026, escribir a la ECAI de Bioinformatica de IBIMA (Juan Antonio Garcia Ranea) presentandose como MD residente de Laboratorio Clinico con pipelines GWAS/PRS propios y disponibilidad a partir de junio de 2027</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>https://www.rfgi.es/ConvocatoriasPropiasFIMABIS/es/Convocatorias/DesgloseEstadoTipoConvocatoria/FIMAB_EM</t>
@@ -35177,7 +40268,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>Rama 3 (instituciones). Ruta descubierta abriendo https://ibima.eu/es/trabaja-con-nosotros/, que enlaza este portal como su unica via de ofertas publicas; portal abierto y confirmado vivo el 2026-09-07. Las convocatorias individuales no se listan sin navegar por el portal (contenido cargado tras la pagina indice), asi que no se ha verificado ninguna convocatoria concreta. La pagina de transparencia de la Junta de Andalucia para FIMABIS devuelve HTTP 403 al fetch automatico.</t>
+          <t>Tier 1: portal RFGI-SSPA de convocatorias propias de FIMABIS, abierto el 2026-09-28; responde 200 y mantiene las pestanas de Convocatorias Abiertas / Cerradas / Proximas, pero el listado se carga dentro de un marco y no se rindio en texto, de modo que se confirma que el portal sigue vivo, no que haya convocatoria abierta hoy</t>
         </is>
       </c>
     </row>
@@ -35271,34 +40362,34 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
+          <t>UNCHANGED</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>En marzo de 2027 abrir sergas.gal/Recursos-Humanos/Emprego-publico-Seleccion-temporal y confirmar en la propia resolucion el plazo anual de inscripcion en listas; preparar la documentacion en abril de 2027 e inscribirse en el plazo de marzo-abril de 2028, ya con el titulo</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>NEW</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>En marzo de 2027 abrir sergas.gal/Recursos-Humanos/Emprego-publico-Seleccion-temporal y confirmar en la propia resolucion el plazo anual de inscripcion en listas; preparar la documentacion en abril de 2027 e inscribirse en el plazo de marzo-abril de 2028, ya con el titulo</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>https://www.sergas.gal/Recursos-Humanos/Emprego-publico-Seleccion-temporal?idioma=es</t>
@@ -35306,7 +40397,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>Rama 4 (mas alla de la academia), carril 2 sistema publico. Pagina Tier 1 abierta y leida el 2026-09-07 tras redireccion 301 de sergas.es a sergas.gal. La ventana anual 1-marzo/30-abril procede de la pagina general de contratacion temporal de la Xunta (Tier 2) y queda marcada como LIKELY dentro de la fila.</t>
+          <t>Tier 1: pagina de seleccion temporal de FEA del SERGAS, abierta el 2026-09-28. Sigue activa y con movimiento (la convocatoria mas reciente listada se publico en el DOG el 31-08-2026, de Embriologo/a en Reproduccion Humana Asistida, 6 plazas). La unica convocatoria de FEA Bioquimica Clinica/Analisis Clinicos que figura sigue siendo la de la Unidad de Metabolopatias del Area Sanitaria de Santiago de Compostela y Barbanza, publicada el 01-07-2025: ninguna nueva de su categoria desde entonces</t>
         </is>
       </c>
     </row>
@@ -35372,7 +40463,7 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-56</v>
+        <v>-62</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -35511,7 +40602,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Es una via PERMANENTE, del tipo que sobrevive a su calendario: ella no puede presentarse a nada que se cierre antes del 22-05-2027, y esta bolsa admite altas en cualquier momento con cortes anuales de baremacion. La categoria existe y esta viva: la pagina de convocatorias abiertas de Sacyl nombra literalmente Licenciado Especialista en Analisis Clinicos y en Bioquimica Clinica, los titulos que el RD 101/2025 sustituye por Laboratorio Clinico, que es el que ella obtendra. La solicitud es ligera (alta telematica y autobaremo, la documentacion se aporta despues), de ahi el esfuerzo XS-S, pero el autobaremo decide el orden en la lista, asi que el expediente de meritos tiene que estar ordenado antes. EL ENCARGO PENDIENTE QUEDA RESUELTO Y LA REGLA ERA REAL: abierto hoy el PDF de procedimiento de inscripcion FIN MIR/EIR de Sacyl, confirma que el plazo son DOS DIAS HABILES contados desde el dia siguiente a la finalizacion oficial de la residencia, por el articulo 15 de la ORDEN SAN/713/2016. Esto convierte la fila en una tarea con reloj de precision y no en una gestion tranquila: si se pasa esos dos dias, pierde la via especifica de alta como fin de residencia. Un matiz critico que el PDF obliga a anotar: la fecha que cuenta no es la de su contrato sino la fecha oficial de finalizacion del programa que publica el Ministerio en la guia del residente, y las fechas de 2025 que el propio PDF tabula lo demuestran, porque los R4 terminaron el 19-07-2025 y los R2/EIR el 22-05-2025, es decir el dia de fin varia por promocion y no coincide necesariamente con el aniversario del contrato. Si su fecha oficial fuera el 22-05-2027, que cae en sabado, los dos dias habiles serian el lunes 24 y el martes 25 de mayo de 2027, y su limite real de inscripcion seria el 25-05-2027. Si el Ministerio fija julio, como a los R4 de 2025, todo el calculo se desplaza. Sin sueldo publicado en la pagina: seria el de FEA estatutario temporal de Castilla y Leon. Sin visado ni homologacion, ciudadana UE con titulo espanol. A quien escribir: Servicio de Seleccion de la Direccion General de Personal y Desarrollo Profesional, Paseo de Zorrilla n 1, Valladolid, con dos preguntas, a que categoria de bolsa se mapea el nuevo titulo de Laboratorio Clinico y cual es su fecha oficial de fin de formacion</t>
+          <t>La bolsa abierta y permanente (BAPE) de Sacyl sigue viva y comprobada el 2026-09-28, y esta semana la pagina publica DOS cosas nuevas que la afectan directamente. Primera, y es la importante: la Gerencia Regional de Salud avisa de la 'reciente creacion de la categoria de Licenciado Especialista en Laboratorio Clinico, que unifica las especialidades de Bioquimica Clinica y Analisis Clinicos'. Las bolsas de ambas categorias siguen existiendo por separado por ahora, pero se han actualizado las zonas solicitables y los especialistas de las dos categorias pueden ya pedir todas las gerencias; a los inscritos en Bioquimica Clinica se les dio hasta el 09-09-2026 para modificar zonificacion con efecto 10-09-2026 y a los de Analisis Clinicos se les recuerda revisar la suya (campos Gerencia, Centro y Departamento). Es la ejecucion en Castilla y Leon del Real Decreto 101/2025, y confirma que cuando ella termine la residencia el 22-05-2027 el titulo que presentara se encuadrara en la categoria unificada. Segunda: la pagina publica un documento especifico de 'Procedimiento inscripcion FIN MIR_EIR 2026. BOLSA EMPLEO', es decir Sacyl documenta expresamente como se inscriben los residentes que acaban. Ese es el documento que hay que leer en su version 2027. El mecanismo fijado la semana pasada sigue siendo el nucleo y no se reabre: el articulo 15 de la ORDEN SAN/713/2016 da DOS DIAS HABILES contados desde el dia siguiente a la finalizacion oficial de la residencia, y la fecha que vale es la del Ministerio en la guia del residente, no la del contrato. Con fin de residencia el 22-05-2027, la ventana es de dos dias habiles: es el plazo mas corto y menos perdonable de toda la base, y por eso esta fila merece un recordatorio con fecha y no una revision semanal. Encaje: via clinica del perfil, no la investigadora; el PhD cuenta como merito de baremo. Sin visado, mudanza desde Malaga a Castilla y Leon, que el perfil acepta. Sin interlocutor con nombre: el canal es el portal de bolsa de Sacyl.</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -35536,7 +40627,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -35546,7 +40637,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -35556,7 +40647,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>Confirmado el plazo de dos dias habiles, quedan dos cosas y ninguna es opcional. Primero, en enero de 2027 comprobar en la guia del residente del Ministerio la fecha OFICIAL de finalizacion de su promocion, porque de ella y no de su contrato cuelga el computo; si coincide con el 22-05-2027 el limite de inscripcion es el 25-05-2027. Segundo, en abril de 2027 tener el autobaremo y la documentacion de meritos ya montados para poder registrarse el mismo dia habil siguiente al fin de la residencia. Si por cualquier causa terminase despues de la fecha oficial, comunicarlo al Servicio de Seleccion en Valladolid, que reabre los mismos dos dias habiles</t>
+          <t>Poner un recordatorio duro para el 22-05-2027 con la ventana de dos dias habiles del art. 15 de la ORDEN SAN/713/2016, usando la fecha de fin de residencia del Ministerio y no la del contrato. Antes, en primavera de 2027, descargar la version actualizada del 'Procedimiento inscripcion FIN MIR_EIR' y comprobar si la bolsa a la que hay que inscribirse ya es la de Licenciado Especialista en Laboratorio Clinico en lugar de la de Analisis Clinicos</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr"/>
@@ -35657,22 +40748,22 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -35688,7 +40779,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>Rama 4, carril 2. Abierta la pagina Tier 1 de funcionament de la borsa del ICS: confirma inscripcion telematica, exigencia de titulacion habilitante cargada, homologacion de titulos extranjeros y las reglas de baremacion del desempeno, pero NO publica calendario de plazos, de ahi LIKELY y no VERIFIED. El requisito de nacionalidad UE procede de la pagina de tramits de la Generalitat.</t>
+          <t>Tier 1: pagina de la borsa de treball del Institut Catala de la Salut, abierta el 2026-09-28. Sigue publicando el acceso a Inscripcio a la borsa de treball, el Pacte de seleccio temporal y los criterios de valoracion de merits: bolsa viva, sin cambio material</t>
         </is>
       </c>
     </row>
@@ -36180,8 +41271,685 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>J-0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bolsa de empleo temporal abierta y permanente del Servicio Aragones de Salud - Facultativo Especialista de Area en Analisis Clinicos y Bioquimica Clinica</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Servicio Aragones de Salud (SALUD), Gobierno de Aragon</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sistema publico de salud (CCAA Aragon)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Zaragoza, Huesca y Teruel (todos los sectores sanitarios de Aragon)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Nombramientos estatutarios temporales (sustituciones, interinidades y eventuales) adjudicados en actos centralizados periodicos</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>No se publica en la pagina de la bolsa; retribuciones por tablas del Servicio Aragones de Salud para FEA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>La pagina la describe como convocatoria abierta y permanente y no publica fecha de apertura</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Sin fecha de cierre: la inscripcion es permanente. Los cortes de valoracion y los actos centralizados de adjudicacion se celebran periodicamente; el ultimo acto centralizado publicado es del 26-05-2026 y las listas provisionales de admitidos/excluidos son de la resolucion de 17-12-2025</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Titulo de especialista en Analisis Clinicos o en Bioquimica Clinica (categoria de FEA). Inscripcion y autobaremacion en el Portal de Recursos Humanos del Servicio Aragones de Salud</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Es la misma via que J-0002/J-0008/J-0010/J-0011 pero en una CCAA que hasta hoy no estaba en la base: una bolsa abierta y permanente permite inscribirse sin esperar a una OPE, y al ser permanente no choca con sus relojes - puede registrarse en cuanto obtenga el titulo de especialista de Laboratorio Medicina el 22-05-2027 y empezar a acumular puntuacion sin renunciar a la via investigadora. Le encaja por la mitad clinica del combo MD+PhD (residencia de Analisis Clinicos en el Hospital Regional Universitario de Malaga, 22-05-2023 a 22-05-2027), no por la de genetica estadistica: aqui su PhD solo puntua como merito de formacion e investigacion en el baremo. Lo que exige la candidatura es administrativo, no cientifico: inscripcion en el Portal de Recursos Humanos de SALUD, autobaremacion y aportacion documental de titulos, servicios prestados, publicaciones y formacion; eso es trabajo de horas (Effort XS-S), no de semanas, y no hay presion de plazo porque no hay plazo. El salario no se publica en la pagina: son las tablas estatutarias de FEA de Aragon, del orden de lo que cobra un FEA en cualquier CCAA, y el nombramiento es temporal por definicion, asi que esto es una via de entrada y de arraigo, no una plaza fija. Sin implicacion de visado: es EU/Espana; si implica mudanza desde Malaga a Aragon, que el perfil admite sin restricciones. No hay PI ni responsable con nombre a quien escribir: el canal es el propio portal y, para dudas, el Servicio de Provision de Personal Estatutario de la Direccion de Recursos Humanos de SALUD. Aviso honesto: la pagina no explicita si la ventana de inscripcion esta abierta en este momento ni el efecto de la nueva categoria unificada de Laboratorio Clinico creada por el Real Decreto 101/2025, que en Castilla y Leon ya ha obligado a reordenar las bolsas de Analisis Clinicos y Bioquimica Clinica (ver J-0010). Eso es lo primero que hay que confirmar.</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Bolsa permanente de una especialidad con pocos efectivos en una CCAA pequena: la competencia real depende de la antiguedad acumulada por los ya inscritos, no del numero de solicitantes; sin datos publicados de tamano de la bolsa</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Confirmar en el Portal de Recursos Humanos del Servicio Aragones de Salud si la inscripcion esta abierta ahora y si la bolsa se ha reconvertido a la categoria unica de Laboratorio Clinico; anotar que documentacion admite para autobaremar la tesis y las publicaciones antes de mayo de 2027</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>https://www.aragon.es/-/analisis-clinicos-y-bioquimica-clinica-1</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>Tier 1: pagina oficial de aragon.es abierta en esta pasada (2026-09-28). Descubierta a partir de una busqueda web de bolsas permanentes de FEA de laboratorio en las CCAA que faltaban en la base</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>J-0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bolsa de empleo de Facultativo Especialista de Area de Laboratorio Clinico del SESPA (Asturias), creada por resolucion de 02-12-2025</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Servicio de Salud del Principado de Asturias (SESPA)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sistema publico de salud (CCAA Asturias)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Oviedo, Gijon, Aviles y resto de areas sanitarias de Asturias</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Nombramientos estatutarios temporales a traves de bolsa de empleo</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>No publicado en la fuente consultada</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>No consta en la fuente consultada si la inscripcion es permanente o por ventanas: ESE ES EL DATO QUE FALTA</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Titulo de FEA de Laboratorio Clinico (categoria nueva del Real Decreto 101/2025). La resolucion integra de oficio a los ya inscritos en las bolsas de FEA de Analisis Clinicos y de Bioquimica Clinica con su puntuacion</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Segunda CCAA nueva de la pasada y la mas interesante conceptualmente: Asturias ya ha ejecutado la unificacion que el Real Decreto 101/2025 impone, creando la categoria de FEA de Laboratorio Clinico y volcando en ella a los inscritos en Analisis Clinicos y Bioquimica Clinica con su puntuacion. Para ella eso significa que el titulo que obtendra el 22-05-2027 sera directamente el de la categoria vigente, sin transito administrativo intermedio, y que la bolsa ya esta constituida cuando llegue. Encaja por la via clinica del perfil (residencia de Analisis Clinicos en Malaga), no por la genetica estadistica; el PhD entra como merito de baremo. Lo que exige la candidatura es documental: inscripcion en la bolsa del SESPA y acreditacion de titulo, servicios prestados y meritos. El trabajo real es de horas y no hay presion de plazo conocida, pero justamente el plazo es lo que no esta verificado. Sin visado (Espana/UE); implica mudanza desde Malaga, que el perfil acepta. No hay interlocutor con nombre: el canal es el area de personal del SESPA y el propio portal Astursalud. AVISO DE HONESTIDAD, no lo pases por alto: esta fila se ha construido sobre una nota sindical (USIPA) que cita la resolucion de 02-12-2025 con referencia BOPA 2026-00059; ni el texto de la resolucion ni la pagina oficial de Astursalud se han abierto en esta pasada, de modo que el mecanismo y el calendario de inscripcion, los requisitos exactos y si la bolsa esta abierta hoy siguen SIN verificar. Confidence UNVERIFIED y Last_Verified vacio a proposito.</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Especialidad de laboratorio con pocos efectivos y bolsa recien constituida; la ventaja real la tienen los volcados de oficio desde las bolsas antiguas, que llegan con puntuacion acumulada</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Abrir la resolucion en el BOPA (referencia 2026-00059) y la pagina de bolsas de Astursalud para fijar: si la inscripcion es abierta y permanente o por ventanas, el plazo vigente y los requisitos de titulacion. Hasta entonces no tratar el Status ROLLING como verificado</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>https://usipa.es/creacion-bolsa-empleo-fea-de-laboratorio-clinico/</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>LEAD de Tier 2: nota del sindicato USIPA abierta en esta pasada, que cita la resolucion de la Direccion Gerencia del SESPA de 02-12-2025 y la referencia BOPA 2026-00059. El texto oficial no se ha leido</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>J-0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Concurso-oposicion 2026 de Facultativo Especialista de Area en Laboratorio Clinico del Servicio Navarro de Salud-Osasunbidea (Resolucion 1515E/2026, 3 plazas nivel A)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Servicio Navarro de Salud-Osasunbidea, Gobierno de Navarra</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sistema publico de salud (CCAA Navarra)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pamplona</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Onsite</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Plaza estatutaria fija (nivel A); la convocatoria genera ademas listas de contratacion temporal y de promocion interna</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>No publicado en la ficha del tramite; nivel A de las tablas del Gobierno de Navarra</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>No consta en la ficha del tramite; la convocatoria es la Resolucion 1515E/2026, publicada en el Boletin Oficial de Navarra</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>La ficha marca el expediente como 'En resolucion' y no publica las fechas del plazo de solicitudes, lo que indica que el plazo ya se cerro; no se inventa fecha</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Exige estar en posesion del titulo de especialista en Analisis Clinicos y/o Bioquimica Clinica, o estar en condiciones de obtenerlo, EN LA FECHA DE FIN DEL PLAZO DE PRESENTACION DE SOLICITUDES</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Navarra es la tercera CCAA nueva de esta pasada, y esta fila existe sobre todo para fijar el mecanismo, no para que se presente: el requisito literal es tener el titulo de especialista, o estar en condiciones de obtenerlo, a la fecha de fin del plazo de solicitudes, y ella no termina la residencia hasta el 22-05-2027. Con el expediente ya 'En resolucion' en septiembre de 2026, ESTA edicion le queda fuera por calendario, y hay que decirlo asi. Lo que si le sirve: una convocatoria de estas genera listas de contratacion temporal y de promocion interna, y son esas listas -no las 3 plazas fijas (1 libre, 1 promocion, 1 reserva de discapacidad)- la puerta realista para 2027. Y fija el patron navarro: Navarra ya convoca la categoria con el nombre nuevo, Laboratorio Clinico, aunque el requisito de titulacion siga redactado como Analisis Clinicos y/o Bioquimica Clinica. Esfuerzo, cuando llegue la edicion que si le sirva: un concurso-oposicion es examen mas baremo de meritos, semanas de preparacion (Effort M-L), muy por encima de una simple inscripcion en bolsa. Sin visado, mudanza a Pamplona. Sin interlocutor con nombre: el canal es el Servicio de Recursos Humanos del SNS-O y el propio tramite en navarra.es.</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Concurso-oposicion de 3 plazas de las que solo 1 es de turno libre: por definicion muy competido frente a una bolsa permanente</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>LIKELY</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Localizar en el Boletin Oficial de Navarra la Resolucion 1515E/2026 para leer las bases, confirmar que el plazo se cerro y, sobre todo, ver como y cuando se constituyen las listas de contratacion temporal que derivan de ella; poner una alerta para la siguiente convocatoria de la categoria</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>https://www.navarra.es/es/tramites/on/-/line/facultativo-especialista-de-area-en-laboratorio-clinico-concurso-oposicion-2026</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>Tier 1: ficha oficial del tramite en navarra.es abierta en esta pasada (2026-09-28). Las fechas del plazo no figuran en la ficha y no se han inventado</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>J-0019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Junior Medical Science Liaison - talent pipeline de Medical Affairs de IQVIA en Madrid (Job ID R1523392)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>IQVIA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CRO / Medical Affairs (comunicacion cientifica)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Madrid</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Field-based en la Comunidad de Madrid, con desplazamientos; no es un puesto remoto</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>No publicado en la fuente consultada; se describe como talent pipeline, es decir manifestacion de interes para futuras incorporaciones, no una vacante con plazo</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>ROLLING</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>No publicado en la fuente consultada</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>No hay plazo: es un pipeline de talento abierto, no una convocatoria con cierre</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Titulacion superior PhD, PharmD o MD en ciencias de la vida; espanol e ingles fluidos; carne de conducir en vigor; capacidad de interpretar datos clinicos complejos y de mantener intercambio cientifico no promocional con KOL e investigadores</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Es el mejor encaje de carril 3 que ha aparecido, y lo es por una razon concreta: el requisito de entrada es MD, PhD o PharmD, y ella tiene el MD (Complutense, 2019) ya en mano y el PhD en curso, asi que cumple el filtro titulacion el primer dia, sin depender del ETA de febrero de 2028. Espanol nativo mas ingles C2 cubren el requisito de idiomas literal. Y el trabajo -sintetizar datos clinicos, responder consultas medicas y sostener conversacion cientifica de igual a igual con clinicos- es exactamente la habilidad que ya ejercita entre la residencia y la tesis. Que exige la candidatura: al ser un pipeline y no una vacante, lo que se manda es CV y perfil, no cartas ni research statement ni charla; el esfuerzo es de horas (XS) y no hay presion de plazo, lo que lo hace compatible con su situacion actual mucho mejor que cualquier vacante con cierre. El precio de eso es que tampoco hay garantia de proceso: un pipeline puede no activarse nunca. Relojes: no exige doctorado defendido, asi que su ventana es mediados de 2027 (fin de residencia el 22-05-2027) y encaja sin choque siempre que el proceso se active entonces; si IQVIA activase la contratacion en 2026 habria conflicto con la residencia y habria que decirlo en la entrevista. Salario y contrato no publicados: un MSL junior en Espana es contrato indefinido de empresa, no estatutario, y supone salir de la via clinica y de la investigadora - decision de carrera, no solo de empleo. Sin visado (Espana). Dos condiciones materiales que hay que resolver antes: es un puesto field-based en Madrid, es decir mudanza desde Malaga y viaje continuo, y exige carne de conducir en vigor, dato que el perfil no recoge. Sin interlocutor con nombre; el canal es el portal de empleo de IQVIA.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Los puestos de MSL junior en Espana atraen a medicos, farmaceuticos y doctores en ciencias de la vida en volumen; un pipeline abierto sin plazo acumula candidaturas indefinidamente</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>XS</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Buscar el Job ID R1523392 en jobs.iqvia.com para confirmar que el pipeline sigue activo, leer la ficha oficial y comprobar area terapeutica y tipo de contrato; verificar el requisito de carne de conducir y decidir si registrarse ya o esperar a principios de 2027</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>https://www.biotecnika.com/medical-science-liaison-job-at-iqvia-spain/</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>LEAD de Tier 2: agregador biotecnika, abierto en esta pasada, que cita el Job ID R1523392 del portal jobs.iqvia.com. La ficha oficial de IQVIA no se ha abierto, por eso Confidence UNVERIFIED y Last_Verified vacio</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>J-0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Senior Statistical Geneticist (remoto en Estados Unidos)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BridgeBio Pharma</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>I+D farmaceutica (genetica humana)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Remoto en Estados Unidos, con viajes trimestrales a San Francisco</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Remote-US</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Empleo indefinido de empresa</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Publicado en dolares: 185.000-230.000 USD anuales (rango de California)</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No publicado en el anuncio</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>El anuncio no publica fecha de cierre; el formulario de Greenhouse sigue activo</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>PhD en statistical genetics, human genetics o biologia computacional MAS 5+ anos de experiencia EN LA INDUSTRIA; experiencia acreditada con UK Biobank y All of Us; dominio de Python; analisis de WES/WGS y genotipado en array; pruebas de asociacion de variante unica y gene-based</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Es su tema exacto -genetica estadistica de rasgos complejos sobre biobancos- pero el anuncio pide 5+ anos de experiencia previa en industria y dominio de Python como lenguaje principal, y ella llega con cero anos de industria y Python asistido, ademas de necesitar patrocinio de visado para Estados Unidos y no estar libre hasta febrero de 2028 si se exige el PhD defendido: se registra para que no se vuelva a descubrir y como prueba de que BridgeBio es un empleador de su especialidad al que merece la pena volver cuando publique un puesto de entrada.</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Puesto senior de genetica estadistica remoto en Estados Unidos con salario publicado alto: atrae al grueso del mercado americano del area</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>VERIFIED</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>No presentarse. Revisar una vez al trimestre el tablon de Greenhouse de BridgeBio buscando un puesto de Statistical Geneticist sin el requisito de 5 anos de industria</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/bridgebio/jobs/5179747007</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>Tier 1: anuncio oficial en el tablon de Greenhouse de BridgeBio, abierto en esta pasada (2026-09-28)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AB16"/>
+  <autoFilter ref="A1:AB21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36797,7 +42565,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -36937,7 +42705,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -37331,7 +43099,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -38745,7 +44513,7 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -39268,7 +45036,7 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -39408,7 +45176,7 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -40052,7 +45820,7 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -41067,7 +46835,7 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -44360,7 +50128,7 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>-171</v>
+        <v>-177</v>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
@@ -44488,7 +50256,7 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -55213,7 +60981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -56268,8 +62036,112 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SUB-0020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Platsbanken (Arbetsformedlingen) - aviso por correo de busqueda guardada</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>https://arbetsformedlingen.se/platsbanken</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>POSTDOCS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Correo con las vacantes nuevas de todo el sector publico sueco que casen con una busqueda guardada ('postdoktor', 'genomik', 'epidemiologi', 'biostatistik', 'Karolinska'), incluidos los postdocs de Karolinska, Uppsala, Goteborg y Estocolmo.</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Es el unico portal nacional del EEE que en esta pasada ha respondido sin bloqueo alguno (API abierta, sin login), justo lo contrario de Dinamarca (exige MitID), Noruega (buscador roto) y EURAXESS (facetas rotas). La alerta por correo resuelve el punto flaco de la fuente: los titulos suecos son genericos y la busqueda libre es difusa, asi que conviene que el portal empuje y no tener que tirar de consultas.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Comprobado el 2026-09-28: ninguna URL de arbetsformedlingen.se ni de jobtechdev.se estaba en subscriptions.tsv. La alerta requiere cuenta en arbetsformedlingen.se; interfaz en sueco (la version en ingles del portal es parcial). No suscrita en su nombre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SUB-0021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Genomics England - avisos por correo de nuevas vacantes</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>https://www.genomicsengland.co.uk/careers/open-positions</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>JOBS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aviso por correo cada vez que Genomics England abre una vacante, con seleccion de departamentos en el propio formulario (interesan Bioinformatics Research Services, Bioinformatics Engineering, Clinical, Data y Applied Machine Learning)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Genomics England es el empleador que el perfil senala en carril 1 y el mas afin a su combo MD mas genetica estadistica en un sistema publico de salud, pero su tablon esta casi siempre vacio: comprobado el 2026-09-28, tiene UNA sola vacante abierta, de Performance &amp; MI en Londres, irrelevante para ella, igual que el 14-09-2026. Mirarlo cada semana es gastar presupuesto para leer un cero; el aviso por correo convierte esa vigilancia en coste cero y elimina el riesgo de perder una vacante de las que duran poco</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TODO</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>El formulario esta al final de la pagina de Open positions, bajo 'Get notified of new positions'; pide correo y departamentos de interes. Comprobado que la URL no figura en subscriptions.tsv en ningun Status. No suscribirse en su nombre: lo hace ella</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J20"/>
+  <autoFilter ref="A1:J22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>